--- a/results/plots/agent_rewards_cumulative.xlsx
+++ b/results/plots/agent_rewards_cumulative.xlsx
@@ -479,7 +479,7 @@
         <v>-3.159722222222224</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>8.600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -545,7 +545,7 @@
         <v>-3.159722222222224</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>8.600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -676,17 +676,17 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>

--- a/results/plots/agent_rewards_cumulative.xlsx
+++ b/results/plots/agent_rewards_cumulative.xlsx
@@ -476,7 +476,7 @@
         <v>-20.88028902850273</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.3</v>
+        <v>-3</v>
       </c>
       <c r="F2" t="n">
         <v>-0.5</v>
@@ -496,7 +496,7 @@
         <v>-15.08041566639237</v>
       </c>
       <c r="E3" t="n">
-        <v>-10.1</v>
+        <v>-13</v>
       </c>
       <c r="F3" t="n">
         <v>-18.5</v>
@@ -516,7 +516,7 @@
         <v>-16.24192719111304</v>
       </c>
       <c r="E4" t="n">
-        <v>-13.2</v>
+        <v>-3</v>
       </c>
       <c r="F4" t="n">
         <v>-18.5</v>
@@ -536,7 +536,7 @@
         <v>-18.76282389482354</v>
       </c>
       <c r="E5" t="n">
-        <v>4.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
         <v>-3.5</v>
@@ -556,7 +556,7 @@
         <v>-9.011605956684511</v>
       </c>
       <c r="E6" t="n">
-        <v>-10.1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>-12.5</v>
@@ -576,7 +576,7 @@
         <v>-16.88493498782972</v>
       </c>
       <c r="E7" t="n">
-        <v>-5</v>
+        <v>-9</v>
       </c>
       <c r="F7" t="n">
         <v>-12.5</v>
@@ -596,7 +596,7 @@
         <v>-22.1585517447926</v>
       </c>
       <c r="E8" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="F8" t="n">
         <v>-8</v>
@@ -616,7 +616,7 @@
         <v>-14.86028872807583</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.199999999999999</v>
+        <v>-11</v>
       </c>
       <c r="F9" t="n">
         <v>-11</v>
@@ -636,7 +636,7 @@
         <v>-16.66542535497044</v>
       </c>
       <c r="E10" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
         <v>-2</v>
@@ -656,7 +656,7 @@
         <v>-16.50768248317392</v>
       </c>
       <c r="E11" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
         <v>-11</v>
@@ -676,7 +676,7 @@
         <v>-22.1585747570583</v>
       </c>
       <c r="E12" t="n">
-        <v>13.9</v>
+        <v>-11</v>
       </c>
       <c r="F12" t="n">
         <v>-12.5</v>
@@ -696,7 +696,7 @@
         <v>-16.07701479937518</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1</v>
+        <v>-9</v>
       </c>
       <c r="F13" t="n">
         <v>-3.5</v>
@@ -716,7 +716,7 @@
         <v>-25.44342248327767</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
         <v>-5</v>
@@ -736,7 +736,7 @@
         <v>-14.49481384471911</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.300000000000001</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>-18.5</v>
@@ -756,7 +756,7 @@
         <v>-19.39923887184475</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.299999999999999</v>
+        <v>-13</v>
       </c>
       <c r="F16" t="n">
         <v>-12.5</v>
@@ -776,7 +776,7 @@
         <v>-15.21056902635355</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7999999999999999</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
         <v>-12.5</v>
@@ -796,7 +796,7 @@
         <v>-18.66489425226396</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3000000000000002</v>
+        <v>-11</v>
       </c>
       <c r="F18" t="n">
         <v>-11</v>
@@ -816,7 +816,7 @@
         <v>-9.011666353277461</v>
       </c>
       <c r="E19" t="n">
-        <v>13.9</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
         <v>-12.5</v>
@@ -836,7 +836,7 @@
         <v>-12.42194598309683</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
         <v>-8</v>
@@ -856,7 +856,7 @@
         <v>-8.344026407773633</v>
       </c>
       <c r="E21" t="n">
-        <v>-8.5</v>
+        <v>-3</v>
       </c>
       <c r="F21" t="n">
         <v>-17</v>
@@ -876,7 +876,7 @@
         <v>-10.61191573078219</v>
       </c>
       <c r="E22" t="n">
-        <v>-12.1</v>
+        <v>-11</v>
       </c>
       <c r="F22" t="n">
         <v>-5</v>
@@ -896,7 +896,7 @@
         <v>-13.76809791504057</v>
       </c>
       <c r="E23" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="F23" t="n">
         <v>-21.5</v>
@@ -916,7 +916,7 @@
         <v>-13.61382958064067</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1</v>
+        <v>9</v>
       </c>
       <c r="F24" t="n">
         <v>-9.5</v>
@@ -936,7 +936,7 @@
         <v>-17.04709742089801</v>
       </c>
       <c r="E25" t="n">
-        <v>4.8</v>
+        <v>-5</v>
       </c>
       <c r="F25" t="n">
         <v>-5</v>
@@ -956,7 +956,7 @@
         <v>-11.45515617083332</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
         <v>-9.5</v>
@@ -976,7 +976,7 @@
         <v>-22.65071637595969</v>
       </c>
       <c r="E27" t="n">
-        <v>2.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
         <v>-12.5</v>
@@ -996,7 +996,7 @@
         <v>-18.723853564575</v>
       </c>
       <c r="E28" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
         <v>-6.5</v>
@@ -1016,7 +1016,7 @@
         <v>-19.58043031028957</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.1</v>
+        <v>5</v>
       </c>
       <c r="F29" t="n">
         <v>-11</v>
@@ -1036,7 +1036,7 @@
         <v>-21.81599222693938</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7999999999999998</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
         <v>-5</v>
@@ -1056,7 +1056,7 @@
         <v>-12.33207495069766</v>
       </c>
       <c r="E31" t="n">
-        <v>12.8</v>
+        <v>-3</v>
       </c>
       <c r="F31" t="n">
         <v>-9.5</v>
@@ -1076,7 +1076,7 @@
         <v>-12.07550353950178</v>
       </c>
       <c r="E32" t="n">
-        <v>3.9</v>
+        <v>9</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
@@ -1096,7 +1096,7 @@
         <v>-13.9055061383892</v>
       </c>
       <c r="E33" t="n">
-        <v>1.7</v>
+        <v>-7</v>
       </c>
       <c r="F33" t="n">
         <v>-5</v>
@@ -1116,7 +1116,7 @@
         <v>-20.68298851778319</v>
       </c>
       <c r="E34" t="n">
-        <v>3.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="F34" t="n">
         <v>-0.5</v>
@@ -1136,7 +1136,7 @@
         <v>-13.67390778367567</v>
       </c>
       <c r="E35" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="F35" t="n">
         <v>-9.5</v>
@@ -1156,7 +1156,7 @@
         <v>-9.665718240118361</v>
       </c>
       <c r="E36" t="n">
-        <v>4.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="F36" t="n">
         <v>-20</v>
@@ -1176,7 +1176,7 @@
         <v>-15.36778170122901</v>
       </c>
       <c r="E37" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F37" t="n">
         <v>-12.5</v>
@@ -1196,7 +1196,7 @@
         <v>-12.35413898216171</v>
       </c>
       <c r="E38" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
         <v>-21.5</v>
@@ -1216,7 +1216,7 @@
         <v>-16.22217341588913</v>
       </c>
       <c r="E39" t="n">
-        <v>6.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="F39" t="n">
         <v>2.5</v>
@@ -1236,7 +1236,7 @@
         <v>-10.00948967549725</v>
       </c>
       <c r="E40" t="n">
-        <v>18.8</v>
+        <v>5</v>
       </c>
       <c r="F40" t="n">
         <v>-17</v>
@@ -1256,7 +1256,7 @@
         <v>-15.10350776269546</v>
       </c>
       <c r="E41" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="F41" t="n">
         <v>-17</v>
@@ -1276,7 +1276,7 @@
         <v>-13.62641184742081</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.199999999999999</v>
+        <v>-11</v>
       </c>
       <c r="F42" t="n">
         <v>-12.5</v>
@@ -1296,7 +1296,7 @@
         <v>-14.71610395027719</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.3000000000000002</v>
+        <v>3</v>
       </c>
       <c r="F43" t="n">
         <v>-11</v>
@@ -1316,7 +1316,7 @@
         <v>-17.32238709223246</v>
       </c>
       <c r="E44" t="n">
-        <v>4.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="F44" t="n">
         <v>-6.5</v>
@@ -1336,7 +1336,7 @@
         <v>-18.3985178425561</v>
       </c>
       <c r="E45" t="n">
-        <v>3.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
         <v>2.5</v>
@@ -1356,7 +1356,7 @@
         <v>-13.92117656900311</v>
       </c>
       <c r="E46" t="n">
-        <v>3.9</v>
+        <v>-7</v>
       </c>
       <c r="F46" t="n">
         <v>-11</v>
@@ -1376,7 +1376,7 @@
         <v>-11.07952799310252</v>
       </c>
       <c r="E47" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F47" t="n">
         <v>-8</v>
@@ -1396,7 +1396,7 @@
         <v>-17.00931480520146</v>
       </c>
       <c r="E48" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="F48" t="n">
         <v>-18.5</v>
@@ -1416,7 +1416,7 @@
         <v>-12.51496523440635</v>
       </c>
       <c r="E49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
@@ -1436,7 +1436,7 @@
         <v>-12.56933176486039</v>
       </c>
       <c r="E50" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F50" t="n">
         <v>-2</v>
@@ -1456,7 +1456,7 @@
         <v>-18.61042700136766</v>
       </c>
       <c r="E51" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="F51" t="n">
         <v>-9.5</v>
@@ -1476,7 +1476,7 @@
         <v>-19.98298420591642</v>
       </c>
       <c r="E52" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="F52" t="n">
         <v>-18.5</v>
@@ -1496,7 +1496,7 @@
         <v>-6.672983718717866</v>
       </c>
       <c r="E53" t="n">
-        <v>-2.3</v>
+        <v>11</v>
       </c>
       <c r="F53" t="n">
         <v>-8</v>
@@ -1516,7 +1516,7 @@
         <v>-15.35638027898899</v>
       </c>
       <c r="E54" t="n">
-        <v>-4.1</v>
+        <v>7</v>
       </c>
       <c r="F54" t="n">
         <v>-11</v>
@@ -1536,7 +1536,7 @@
         <v>-15.19729180569158</v>
       </c>
       <c r="E55" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="F55" t="n">
         <v>-5</v>
@@ -1556,7 +1556,7 @@
         <v>-14.51951403443939</v>
       </c>
       <c r="E56" t="n">
-        <v>1.9</v>
+        <v>-1</v>
       </c>
       <c r="F56" t="n">
         <v>-14</v>
@@ -1596,7 +1596,7 @@
         <v>-16.72760094092684</v>
       </c>
       <c r="E58" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="F58" t="n">
         <v>-9.5</v>
@@ -1616,7 +1616,7 @@
         <v>-11.78050191422369</v>
       </c>
       <c r="E59" t="n">
-        <v>17.9</v>
+        <v>3</v>
       </c>
       <c r="F59" t="n">
         <v>-9.5</v>
@@ -1636,7 +1636,7 @@
         <v>-13.16902826441466</v>
       </c>
       <c r="E60" t="n">
-        <v>13.7</v>
+        <v>-9</v>
       </c>
       <c r="F60" t="n">
         <v>-0.5</v>
@@ -1656,7 +1656,7 @@
         <v>-18.54419594854977</v>
       </c>
       <c r="E61" t="n">
-        <v>0.7999999999999998</v>
+        <v>3</v>
       </c>
       <c r="F61" t="n">
         <v>-11</v>
@@ -1676,7 +1676,7 @@
         <v>-8.807644726031004</v>
       </c>
       <c r="E62" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="F62" t="n">
         <v>-11</v>
@@ -1716,7 +1716,7 @@
         <v>-15.86301331944633</v>
       </c>
       <c r="E64" t="n">
-        <v>11.9</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>-9.5</v>
@@ -1736,7 +1736,7 @@
         <v>-16.55071283344781</v>
       </c>
       <c r="E65" t="n">
-        <v>9.9</v>
+        <v>-3</v>
       </c>
       <c r="F65" t="n">
         <v>-0.5</v>
@@ -1756,7 +1756,7 @@
         <v>-17.9336097374753</v>
       </c>
       <c r="E66" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="F66" t="n">
         <v>-17</v>
@@ -1776,7 +1776,7 @@
         <v>-11.96824934592622</v>
       </c>
       <c r="E67" t="n">
-        <v>9.9</v>
+        <v>-5</v>
       </c>
       <c r="F67" t="n">
         <v>-3.5</v>
@@ -1796,7 +1796,7 @@
         <v>-11.58305819485098</v>
       </c>
       <c r="E68" t="n">
-        <v>3.9</v>
+        <v>9</v>
       </c>
       <c r="F68" t="n">
         <v>-6.5</v>
@@ -1816,7 +1816,7 @@
         <v>-16.96770942927208</v>
       </c>
       <c r="E69" t="n">
-        <v>2.8</v>
+        <v>-11</v>
       </c>
       <c r="F69" t="n">
         <v>-5</v>
@@ -1836,7 +1836,7 @@
         <v>-13.70594101887073</v>
       </c>
       <c r="E70" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="F70" t="n">
         <v>-11</v>
@@ -1856,7 +1856,7 @@
         <v>-13.35983540697217</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F71" t="n">
         <v>-11</v>
@@ -1876,7 +1876,7 @@
         <v>-13.73945420010882</v>
       </c>
       <c r="E72" t="n">
-        <v>6.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="F72" t="n">
         <v>-9.5</v>
@@ -1896,7 +1896,7 @@
         <v>-21.43215273472283</v>
       </c>
       <c r="E73" t="n">
-        <v>9.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>-14</v>
@@ -1916,7 +1916,7 @@
         <v>-19.93026650520377</v>
       </c>
       <c r="E74" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F74" t="n">
         <v>-6.5</v>
@@ -1936,7 +1936,7 @@
         <v>-13.63373489971633</v>
       </c>
       <c r="E75" t="n">
-        <v>3.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="F75" t="n">
         <v>-9.5</v>
@@ -1956,7 +1956,7 @@
         <v>-14.70893704404678</v>
       </c>
       <c r="E76" t="n">
-        <v>3.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="F76" t="n">
         <v>2.5</v>
@@ -1976,7 +1976,7 @@
         <v>-20.41126671783133</v>
       </c>
       <c r="E77" t="n">
-        <v>-6.1</v>
+        <v>-5</v>
       </c>
       <c r="F77" t="n">
         <v>-2</v>
@@ -1996,7 +1996,7 @@
         <v>-8.298668334372483</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.5</v>
+        <v>15</v>
       </c>
       <c r="F78" t="n">
         <v>-9.5</v>
@@ -2016,7 +2016,7 @@
         <v>-11.09414578630654</v>
       </c>
       <c r="E79" t="n">
-        <v>7.699999999999999</v>
+        <v>3</v>
       </c>
       <c r="F79" t="n">
         <v>-3.5</v>
@@ -2036,7 +2036,7 @@
         <v>-14.76956546226694</v>
       </c>
       <c r="E80" t="n">
-        <v>-5</v>
+        <v>17</v>
       </c>
       <c r="F80" t="n">
         <v>-5</v>
@@ -2056,7 +2056,7 @@
         <v>-14.11114333061668</v>
       </c>
       <c r="E81" t="n">
-        <v>6.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="F81" t="n">
         <v>-11</v>
@@ -2076,7 +2076,7 @@
         <v>-17.36533220259155</v>
       </c>
       <c r="E82" t="n">
-        <v>7.9</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>-9.5</v>
@@ -2096,7 +2096,7 @@
         <v>-14.29537266647307</v>
       </c>
       <c r="E83" t="n">
-        <v>9.500000000000002</v>
+        <v>7</v>
       </c>
       <c r="F83" t="n">
         <v>-11</v>
@@ -2116,7 +2116,7 @@
         <v>-15.52673225528131</v>
       </c>
       <c r="E84" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="F84" t="n">
         <v>-2</v>
@@ -2136,7 +2136,7 @@
         <v>-10.61618120478381</v>
       </c>
       <c r="E85" t="n">
-        <v>3.9</v>
+        <v>9</v>
       </c>
       <c r="F85" t="n">
         <v>-6.5</v>
@@ -2156,7 +2156,7 @@
         <v>-9.558453099269794</v>
       </c>
       <c r="E86" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F86" t="n">
         <v>-3.5</v>
@@ -2176,7 +2176,7 @@
         <v>-11.95578259847385</v>
       </c>
       <c r="E87" t="n">
-        <v>-6.3</v>
+        <v>7</v>
       </c>
       <c r="F87" t="n">
         <v>-2</v>
@@ -2196,7 +2196,7 @@
         <v>-14.53892114818133</v>
       </c>
       <c r="E88" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F88" t="n">
         <v>-0.5</v>
@@ -2236,7 +2236,7 @@
         <v>-8.626986066168405</v>
       </c>
       <c r="E90" t="n">
-        <v>17.7</v>
+        <v>9</v>
       </c>
       <c r="F90" t="n">
         <v>-9.5</v>
@@ -2256,7 +2256,7 @@
         <v>-14.42115485021459</v>
       </c>
       <c r="E91" t="n">
-        <v>-4.1</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
         <v>-2</v>
@@ -2276,7 +2276,7 @@
         <v>-14.81963907250334</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="F92" t="n">
         <v>-8</v>
@@ -2296,7 +2296,7 @@
         <v>-18.27445887317804</v>
       </c>
       <c r="E93" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="F93" t="n">
         <v>-0.5</v>
@@ -2316,7 +2316,7 @@
         <v>-14.01149006572236</v>
       </c>
       <c r="E94" t="n">
-        <v>3.299999999999999</v>
+        <v>7</v>
       </c>
       <c r="F94" t="n">
         <v>-2</v>
@@ -2336,7 +2336,7 @@
         <v>-11.76638385536769</v>
       </c>
       <c r="E95" t="n">
-        <v>15.9</v>
+        <v>11</v>
       </c>
       <c r="F95" t="n">
         <v>-5</v>
@@ -2356,7 +2356,7 @@
         <v>-9.413356115683376</v>
       </c>
       <c r="E96" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="F96" t="n">
         <v>-5</v>
@@ -2396,7 +2396,7 @@
         <v>-11.85349409751063</v>
       </c>
       <c r="E98" t="n">
-        <v>6.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="F98" t="n">
         <v>-3.5</v>
@@ -2416,7 +2416,7 @@
         <v>-15.24029031651793</v>
       </c>
       <c r="E99" t="n">
-        <v>3.9</v>
+        <v>15</v>
       </c>
       <c r="F99" t="n">
         <v>-5</v>
@@ -2436,7 +2436,7 @@
         <v>-16.01872556029471</v>
       </c>
       <c r="E100" t="n">
-        <v>11.9</v>
+        <v>7</v>
       </c>
       <c r="F100" t="n">
         <v>-2</v>
@@ -2456,7 +2456,7 @@
         <v>-11.30979160160691</v>
       </c>
       <c r="E101" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
@@ -2476,7 +2476,7 @@
         <v>-15.21465658295874</v>
       </c>
       <c r="E102" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F102" t="n">
         <v>-9.5</v>
@@ -2496,7 +2496,7 @@
         <v>-11.91209159844877</v>
       </c>
       <c r="E103" t="n">
-        <v>15.7</v>
+        <v>13</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -2516,7 +2516,7 @@
         <v>-18.47233524338426</v>
       </c>
       <c r="E104" t="n">
-        <v>13.7</v>
+        <v>15</v>
       </c>
       <c r="F104" t="n">
         <v>-11</v>
@@ -2536,7 +2536,7 @@
         <v>-15.99683898329127</v>
       </c>
       <c r="E105" t="n">
-        <v>23.7</v>
+        <v>21</v>
       </c>
       <c r="F105" t="n">
         <v>4</v>
@@ -2556,7 +2556,7 @@
         <v>-11.78397827839792</v>
       </c>
       <c r="E106" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="F106" t="n">
         <v>-12.5</v>
@@ -2576,7 +2576,7 @@
         <v>-14.09994806721748</v>
       </c>
       <c r="E107" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="F107" t="n">
         <v>-14</v>
@@ -2596,7 +2596,7 @@
         <v>-13.11527797743044</v>
       </c>
       <c r="E108" t="n">
-        <v>-13.2</v>
+        <v>21</v>
       </c>
       <c r="F108" t="n">
         <v>-9.5</v>
@@ -2616,7 +2616,7 @@
         <v>-10.20573754684604</v>
       </c>
       <c r="E109" t="n">
-        <v>0.6000000000000005</v>
+        <v>13</v>
       </c>
       <c r="F109" t="n">
         <v>-11</v>
@@ -2636,7 +2636,7 @@
         <v>-12.319581041081</v>
       </c>
       <c r="E110" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="F110" t="n">
         <v>-5</v>
@@ -2656,7 +2656,7 @@
         <v>-6.059953702883841</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.2999999999999998</v>
+        <v>11</v>
       </c>
       <c r="F111" t="n">
         <v>-0.5</v>
@@ -2676,7 +2676,7 @@
         <v>-13.07604183385386</v>
       </c>
       <c r="E112" t="n">
-        <v>7.9</v>
+        <v>11</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
@@ -2696,7 +2696,7 @@
         <v>-12.00565567818595</v>
       </c>
       <c r="E113" t="n">
-        <v>11.9</v>
+        <v>13</v>
       </c>
       <c r="F113" t="n">
         <v>-6.5</v>
@@ -2716,7 +2716,7 @@
         <v>-18.23586872181258</v>
       </c>
       <c r="E114" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="F114" t="n">
         <v>-2</v>
@@ -2736,7 +2736,7 @@
         <v>-16.23673636012176</v>
       </c>
       <c r="E115" t="n">
-        <v>-4.1</v>
+        <v>13</v>
       </c>
       <c r="F115" t="n">
         <v>-0.5</v>
@@ -2756,7 +2756,7 @@
         <v>-9.138045441859136</v>
       </c>
       <c r="E116" t="n">
-        <v>4.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="F116" t="n">
         <v>-6.5</v>
@@ -2776,7 +2776,7 @@
         <v>-8.735620769461221</v>
       </c>
       <c r="E117" t="n">
-        <v>1.9</v>
+        <v>9</v>
       </c>
       <c r="F117" t="n">
         <v>1</v>
@@ -2796,7 +2796,7 @@
         <v>-3.275988466822424</v>
       </c>
       <c r="E118" t="n">
-        <v>7.9</v>
+        <v>11</v>
       </c>
       <c r="F118" t="n">
         <v>-2</v>
@@ -2816,7 +2816,7 @@
         <v>-21.46730196390546</v>
       </c>
       <c r="E119" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F119" t="n">
         <v>-8</v>
@@ -2836,7 +2836,7 @@
         <v>-9.30602509382889</v>
       </c>
       <c r="E120" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="F120" t="n">
         <v>-2</v>
@@ -2856,7 +2856,7 @@
         <v>-15.45651431364378</v>
       </c>
       <c r="E121" t="n">
-        <v>9.9</v>
+        <v>19</v>
       </c>
       <c r="F121" t="n">
         <v>-2</v>
@@ -2876,7 +2876,7 @@
         <v>-6.65815148548338</v>
       </c>
       <c r="E122" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F122" t="n">
         <v>-8</v>
@@ -2896,7 +2896,7 @@
         <v>-6.936543698335337</v>
       </c>
       <c r="E123" t="n">
-        <v>17.9</v>
+        <v>-1</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
@@ -2916,7 +2916,7 @@
         <v>-11.38242419822538</v>
       </c>
       <c r="E124" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F124" t="n">
         <v>-6.5</v>
@@ -2936,7 +2936,7 @@
         <v>-15.10018684775595</v>
       </c>
       <c r="E125" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F125" t="n">
         <v>-3.5</v>
@@ -2956,7 +2956,7 @@
         <v>-14.27988774904433</v>
       </c>
       <c r="E126" t="n">
-        <v>21.7</v>
+        <v>9</v>
       </c>
       <c r="F126" t="n">
         <v>-5</v>
@@ -2976,7 +2976,7 @@
         <v>-6.334648954400722</v>
       </c>
       <c r="E127" t="n">
-        <v>2.6</v>
+        <v>15</v>
       </c>
       <c r="F127" t="n">
         <v>-12.5</v>
@@ -2996,7 +2996,7 @@
         <v>-13.5475756767352</v>
       </c>
       <c r="E128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F128" t="n">
         <v>-6.5</v>
@@ -3016,7 +3016,7 @@
         <v>-11.66477267457763</v>
       </c>
       <c r="E129" t="n">
-        <v>11.9</v>
+        <v>-1</v>
       </c>
       <c r="F129" t="n">
         <v>-3.5</v>
@@ -3036,7 +3036,7 @@
         <v>-14.70454073338186</v>
       </c>
       <c r="E130" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
@@ -3056,7 +3056,7 @@
         <v>-11.29764528453063</v>
       </c>
       <c r="E131" t="n">
-        <v>25.9</v>
+        <v>25</v>
       </c>
       <c r="F131" t="n">
         <v>-5</v>
@@ -3076,7 +3076,7 @@
         <v>-9.092734146744514</v>
       </c>
       <c r="E132" t="n">
-        <v>1.9</v>
+        <v>23</v>
       </c>
       <c r="F132" t="n">
         <v>1</v>
@@ -3096,7 +3096,7 @@
         <v>-7.953307220522068</v>
       </c>
       <c r="E133" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="F133" t="n">
         <v>-5</v>
@@ -3116,7 +3116,7 @@
         <v>-8.629619074258962</v>
       </c>
       <c r="E134" t="n">
-        <v>3.9</v>
+        <v>9</v>
       </c>
       <c r="F134" t="n">
         <v>-6.5</v>
@@ -3136,7 +3136,7 @@
         <v>-12.45493151160171</v>
       </c>
       <c r="E135" t="n">
-        <v>-0.1</v>
+        <v>1</v>
       </c>
       <c r="F135" t="n">
         <v>5.5</v>
@@ -3156,7 +3156,7 @@
         <v>-15.35178539224634</v>
       </c>
       <c r="E136" t="n">
-        <v>17.9</v>
+        <v>19</v>
       </c>
       <c r="F136" t="n">
         <v>-3.5</v>
@@ -3176,7 +3176,7 @@
         <v>-14.42757650544786</v>
       </c>
       <c r="E137" t="n">
-        <v>18.6</v>
+        <v>23</v>
       </c>
       <c r="F137" t="n">
         <v>-11</v>
@@ -3196,7 +3196,7 @@
         <v>-13.78355315746162</v>
       </c>
       <c r="E138" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F138" t="n">
         <v>-5</v>
@@ -3216,7 +3216,7 @@
         <v>-11.16316554267884</v>
       </c>
       <c r="E139" t="n">
-        <v>14.8</v>
+        <v>5</v>
       </c>
       <c r="F139" t="n">
         <v>-0.5</v>
@@ -3236,7 +3236,7 @@
         <v>-15.7222577936834</v>
       </c>
       <c r="E140" t="n">
-        <v>20.8</v>
+        <v>9</v>
       </c>
       <c r="F140" t="n">
         <v>1</v>
@@ -3256,7 +3256,7 @@
         <v>-18.80056717765801</v>
       </c>
       <c r="E141" t="n">
-        <v>6.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="F141" t="n">
         <v>5.5</v>
@@ -3276,7 +3276,7 @@
         <v>-12.75547358832381</v>
       </c>
       <c r="E142" t="n">
-        <v>-0.1</v>
+        <v>23</v>
       </c>
       <c r="F142" t="n">
         <v>-2</v>
@@ -3296,7 +3296,7 @@
         <v>-13.05017477055378</v>
       </c>
       <c r="E143" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="F143" t="n">
         <v>2.5</v>
@@ -3316,7 +3316,7 @@
         <v>-9.492785338822856</v>
       </c>
       <c r="E144" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F144" t="n">
         <v>5.5</v>
@@ -3336,7 +3336,7 @@
         <v>-12.82451007415136</v>
       </c>
       <c r="E145" t="n">
-        <v>4.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="F145" t="n">
         <v>-2</v>
@@ -3356,7 +3356,7 @@
         <v>-15.2583426766281</v>
       </c>
       <c r="E146" t="n">
-        <v>13.5</v>
+        <v>-1</v>
       </c>
       <c r="F146" t="n">
         <v>-5</v>
@@ -3376,7 +3376,7 @@
         <v>-8.936160793676258</v>
       </c>
       <c r="E147" t="n">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="F147" t="n">
         <v>-5</v>
@@ -3396,7 +3396,7 @@
         <v>-12.01544842174979</v>
       </c>
       <c r="E148" t="n">
-        <v>12.8</v>
+        <v>15</v>
       </c>
       <c r="F148" t="n">
         <v>-3.5</v>
@@ -3416,7 +3416,7 @@
         <v>-9.976100682743448</v>
       </c>
       <c r="E149" t="n">
-        <v>13.9</v>
+        <v>15</v>
       </c>
       <c r="F149" t="n">
         <v>2.5</v>
@@ -3436,7 +3436,7 @@
         <v>-9.072845539237004</v>
       </c>
       <c r="E150" t="n">
-        <v>18.8</v>
+        <v>11</v>
       </c>
       <c r="F150" t="n">
         <v>-0.5</v>
@@ -3456,7 +3456,7 @@
         <v>-9.050443784764134</v>
       </c>
       <c r="E151" t="n">
-        <v>20.6</v>
+        <v>29</v>
       </c>
       <c r="F151" t="n">
         <v>2.5</v>
@@ -3476,7 +3476,7 @@
         <v>-9.19299135802768</v>
       </c>
       <c r="E152" t="n">
-        <v>6.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="F152" t="n">
         <v>-6.5</v>
@@ -3496,7 +3496,7 @@
         <v>-11.48622657143188</v>
       </c>
       <c r="E153" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F153" t="n">
         <v>-5</v>
@@ -3516,7 +3516,7 @@
         <v>-12.33292625264692</v>
       </c>
       <c r="E154" t="n">
-        <v>10.8</v>
+        <v>9</v>
       </c>
       <c r="F154" t="n">
         <v>-5</v>
@@ -3536,7 +3536,7 @@
         <v>-8.749082119178086</v>
       </c>
       <c r="E155" t="n">
-        <v>9.9</v>
+        <v>15</v>
       </c>
       <c r="F155" t="n">
         <v>-6.5</v>
@@ -3556,7 +3556,7 @@
         <v>-8.914449436079753</v>
       </c>
       <c r="E156" t="n">
-        <v>15.9</v>
+        <v>25</v>
       </c>
       <c r="F156" t="n">
         <v>-3.5</v>
@@ -3576,7 +3576,7 @@
         <v>-3.178563438316917</v>
       </c>
       <c r="E157" t="n">
-        <v>9.699999999999999</v>
+        <v>29</v>
       </c>
       <c r="F157" t="n">
         <v>2.5</v>
@@ -3596,7 +3596,7 @@
         <v>-11.29514140666748</v>
       </c>
       <c r="E158" t="n">
-        <v>12.8</v>
+        <v>21</v>
       </c>
       <c r="F158" t="n">
         <v>4</v>
@@ -3616,7 +3616,7 @@
         <v>-16.68234331642212</v>
       </c>
       <c r="E159" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="F159" t="n">
         <v>5.5</v>
@@ -3636,7 +3636,7 @@
         <v>-17.327950736185</v>
       </c>
       <c r="E160" t="n">
-        <v>17.9</v>
+        <v>19</v>
       </c>
       <c r="F160" t="n">
         <v>2.5</v>
@@ -3656,7 +3656,7 @@
         <v>-11.49020960393287</v>
       </c>
       <c r="E161" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="F161" t="n">
         <v>4</v>
@@ -3676,7 +3676,7 @@
         <v>-1.895934786610538</v>
       </c>
       <c r="E162" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="F162" t="n">
         <v>-5</v>
@@ -3696,7 +3696,7 @@
         <v>-11.60328510091501</v>
       </c>
       <c r="E163" t="n">
-        <v>5.9</v>
+        <v>13</v>
       </c>
       <c r="F163" t="n">
         <v>-9.5</v>
@@ -3716,7 +3716,7 @@
         <v>-4.872661986196267</v>
       </c>
       <c r="E164" t="n">
-        <v>13.7</v>
+        <v>23</v>
       </c>
       <c r="F164" t="n">
         <v>-6.5</v>
@@ -3736,7 +3736,7 @@
         <v>-16.53562999078624</v>
       </c>
       <c r="E165" t="n">
-        <v>23.9</v>
+        <v>25</v>
       </c>
       <c r="F165" t="n">
         <v>-0.5</v>
@@ -3756,7 +3756,7 @@
         <v>-10.779735566366</v>
       </c>
       <c r="E166" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="F166" t="n">
         <v>1</v>
@@ -3776,7 +3776,7 @@
         <v>-7.441839040123449</v>
       </c>
       <c r="E167" t="n">
-        <v>11.9</v>
+        <v>27</v>
       </c>
       <c r="F167" t="n">
         <v>2.5</v>
@@ -3796,7 +3796,7 @@
         <v>-8.540216823457699</v>
       </c>
       <c r="E168" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F168" t="n">
         <v>1</v>
@@ -3816,7 +3816,7 @@
         <v>-13.36124095935507</v>
       </c>
       <c r="E169" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F169" t="n">
         <v>-6.5</v>
@@ -3836,7 +3836,7 @@
         <v>-7.941572000257956</v>
       </c>
       <c r="E170" t="n">
-        <v>13.9</v>
+        <v>17</v>
       </c>
       <c r="F170" t="n">
         <v>7</v>
@@ -3856,7 +3856,7 @@
         <v>-12.24259454888164</v>
       </c>
       <c r="E171" t="n">
-        <v>20.8</v>
+        <v>7</v>
       </c>
       <c r="F171" t="n">
         <v>2.5</v>
@@ -3876,7 +3876,7 @@
         <v>-9.577734981138333</v>
       </c>
       <c r="E172" t="n">
-        <v>13.7</v>
+        <v>21</v>
       </c>
       <c r="F172" t="n">
         <v>2.5</v>
@@ -3896,7 +3896,7 @@
         <v>-16.95493489049333</v>
       </c>
       <c r="E173" t="n">
-        <v>16.8</v>
+        <v>15</v>
       </c>
       <c r="F173" t="n">
         <v>-6.5</v>
@@ -3916,7 +3916,7 @@
         <v>-7.956608854497154</v>
       </c>
       <c r="E174" t="n">
-        <v>21.5</v>
+        <v>17</v>
       </c>
       <c r="F174" t="n">
         <v>-3.5</v>
@@ -3956,7 +3956,7 @@
         <v>-8.448732765702129</v>
       </c>
       <c r="E176" t="n">
-        <v>25.9</v>
+        <v>13</v>
       </c>
       <c r="F176" t="n">
         <v>7</v>
@@ -3976,7 +3976,7 @@
         <v>-11.73009639391955</v>
       </c>
       <c r="E177" t="n">
-        <v>15.9</v>
+        <v>31</v>
       </c>
       <c r="F177" t="n">
         <v>4</v>
@@ -3996,7 +3996,7 @@
         <v>-16.77275246571654</v>
       </c>
       <c r="E178" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="F178" t="n">
         <v>7</v>
@@ -4016,7 +4016,7 @@
         <v>-7.272125353914878</v>
       </c>
       <c r="E179" t="n">
-        <v>15.9</v>
+        <v>11</v>
       </c>
       <c r="F179" t="n">
         <v>-0.5</v>
@@ -4036,7 +4036,7 @@
         <v>-16.31510018076369</v>
       </c>
       <c r="E180" t="n">
-        <v>11.9</v>
+        <v>13</v>
       </c>
       <c r="F180" t="n">
         <v>-2</v>
@@ -4056,7 +4056,7 @@
         <v>-12.74747409402433</v>
       </c>
       <c r="E181" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F181" t="n">
         <v>5.5</v>
@@ -4076,7 +4076,7 @@
         <v>-13.55980417347203</v>
       </c>
       <c r="E182" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F182" t="n">
         <v>8.5</v>
@@ -4096,7 +4096,7 @@
         <v>-13.27490502800834</v>
       </c>
       <c r="E183" t="n">
-        <v>21.9</v>
+        <v>23</v>
       </c>
       <c r="F183" t="n">
         <v>7</v>
@@ -4116,7 +4116,7 @@
         <v>-12.74484715468625</v>
       </c>
       <c r="E184" t="n">
-        <v>13.7</v>
+        <v>17</v>
       </c>
       <c r="F184" t="n">
         <v>7</v>
@@ -4136,7 +4136,7 @@
         <v>-12.34849872044505</v>
       </c>
       <c r="E185" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F185" t="n">
         <v>-0.5</v>
@@ -4156,7 +4156,7 @@
         <v>-8.532723933054008</v>
       </c>
       <c r="E186" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F186" t="n">
         <v>-0.5</v>
@@ -4176,7 +4176,7 @@
         <v>-7.575287710323443</v>
       </c>
       <c r="E187" t="n">
-        <v>12.2</v>
+        <v>21</v>
       </c>
       <c r="F187" t="n">
         <v>-8</v>
@@ -4196,7 +4196,7 @@
         <v>-11.86378417977766</v>
       </c>
       <c r="E188" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F188" t="n">
         <v>5.5</v>
@@ -4216,7 +4216,7 @@
         <v>-12.69125732972837</v>
       </c>
       <c r="E189" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="F189" t="n">
         <v>4</v>
@@ -4236,7 +4236,7 @@
         <v>-7.146291150027026</v>
       </c>
       <c r="E190" t="n">
-        <v>18.8</v>
+        <v>17</v>
       </c>
       <c r="F190" t="n">
         <v>4</v>
@@ -4256,7 +4256,7 @@
         <v>-10.73034245970168</v>
       </c>
       <c r="E191" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F191" t="n">
         <v>-8</v>
@@ -4276,7 +4276,7 @@
         <v>-18.78829949929933</v>
       </c>
       <c r="E192" t="n">
-        <v>16.6</v>
+        <v>19</v>
       </c>
       <c r="F192" t="n">
         <v>4</v>
@@ -4296,7 +4296,7 @@
         <v>-19.06989102055279</v>
       </c>
       <c r="E193" t="n">
-        <v>19.9</v>
+        <v>19</v>
       </c>
       <c r="F193" t="n">
         <v>8.5</v>
@@ -4316,7 +4316,7 @@
         <v>-5.042595232131265</v>
       </c>
       <c r="E194" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="F194" t="n">
         <v>-0.5</v>
@@ -4336,7 +4336,7 @@
         <v>-7.306725776447404</v>
       </c>
       <c r="E195" t="n">
-        <v>7.700000000000001</v>
+        <v>7</v>
       </c>
       <c r="F195" t="n">
         <v>-2</v>
@@ -4356,7 +4356,7 @@
         <v>-11.2969328754405</v>
       </c>
       <c r="E196" t="n">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="F196" t="n">
         <v>-0.5</v>
@@ -4376,7 +4376,7 @@
         <v>-10.80408612837662</v>
       </c>
       <c r="E197" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="F197" t="n">
         <v>-5</v>
@@ -4396,7 +4396,7 @@
         <v>-10.88759817733926</v>
       </c>
       <c r="E198" t="n">
-        <v>17.9</v>
+        <v>23</v>
       </c>
       <c r="F198" t="n">
         <v>-0.5</v>
@@ -4416,7 +4416,7 @@
         <v>-13.59431403174799</v>
       </c>
       <c r="E199" t="n">
-        <v>18.8</v>
+        <v>21</v>
       </c>
       <c r="F199" t="n">
         <v>8.5</v>
@@ -4436,7 +4436,7 @@
         <v>-16.73414753036879</v>
       </c>
       <c r="E200" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F200" t="n">
         <v>2.5</v>
@@ -4456,7 +4456,7 @@
         <v>-12.17065885528252</v>
       </c>
       <c r="E201" t="n">
-        <v>13.9</v>
+        <v>7</v>
       </c>
       <c r="F201" t="n">
         <v>-0.5</v>
@@ -4476,7 +4476,7 @@
         <v>-9.682425408507925</v>
       </c>
       <c r="E202" t="n">
-        <v>18.8</v>
+        <v>15</v>
       </c>
       <c r="F202" t="n">
         <v>7</v>
@@ -4496,7 +4496,7 @@
         <v>-14.42541224847953</v>
       </c>
       <c r="E203" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="F203" t="n">
         <v>7</v>
@@ -4536,7 +4536,7 @@
         <v>-11.76448565489094</v>
       </c>
       <c r="E205" t="n">
-        <v>17.7</v>
+        <v>25</v>
       </c>
       <c r="F205" t="n">
         <v>4</v>
@@ -4556,7 +4556,7 @@
         <v>-8.468822193825609</v>
       </c>
       <c r="E206" t="n">
-        <v>12.8</v>
+        <v>17</v>
       </c>
       <c r="F206" t="n">
         <v>1</v>
@@ -4576,7 +4576,7 @@
         <v>-8.670738161587693</v>
       </c>
       <c r="E207" t="n">
-        <v>13.9</v>
+        <v>17</v>
       </c>
       <c r="F207" t="n">
         <v>1</v>
@@ -4596,7 +4596,7 @@
         <v>-7.822106310077424</v>
       </c>
       <c r="E208" t="n">
-        <v>13.9</v>
+        <v>9</v>
       </c>
       <c r="F208" t="n">
         <v>-14</v>
@@ -4616,7 +4616,7 @@
         <v>-12.1449725681243</v>
       </c>
       <c r="E209" t="n">
-        <v>8.800000000000001</v>
+        <v>19</v>
       </c>
       <c r="F209" t="n">
         <v>-6.5</v>
@@ -4636,7 +4636,7 @@
         <v>-7.434250898971669</v>
       </c>
       <c r="E210" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F210" t="n">
         <v>4</v>
@@ -4656,7 +4656,7 @@
         <v>-10.3552216026977</v>
       </c>
       <c r="E211" t="n">
-        <v>6.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="F211" t="n">
         <v>2.5</v>
@@ -4676,7 +4676,7 @@
         <v>-12.97258588476429</v>
       </c>
       <c r="E212" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F212" t="n">
         <v>5.5</v>
@@ -4696,7 +4696,7 @@
         <v>-7.268733793080432</v>
       </c>
       <c r="E213" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F213" t="n">
         <v>8.5</v>
@@ -4716,7 +4716,7 @@
         <v>-14.64730992827486</v>
       </c>
       <c r="E214" t="n">
-        <v>29.9</v>
+        <v>21</v>
       </c>
       <c r="F214" t="n">
         <v>11.5</v>
@@ -4736,7 +4736,7 @@
         <v>-6.230069394523568</v>
       </c>
       <c r="E215" t="n">
-        <v>15.9</v>
+        <v>17</v>
       </c>
       <c r="F215" t="n">
         <v>-6.5</v>
@@ -4756,7 +4756,7 @@
         <v>-5.029168024832028</v>
       </c>
       <c r="E216" t="n">
-        <v>21.9</v>
+        <v>21</v>
       </c>
       <c r="F216" t="n">
         <v>4</v>
@@ -4776,7 +4776,7 @@
         <v>-17.20137440692926</v>
       </c>
       <c r="E217" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F217" t="n">
         <v>-2</v>
@@ -4796,7 +4796,7 @@
         <v>-11.79624044528628</v>
       </c>
       <c r="E218" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="F218" t="n">
         <v>7</v>
@@ -4816,7 +4816,7 @@
         <v>-16.74489113681049</v>
       </c>
       <c r="E219" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F219" t="n">
         <v>2.5</v>
@@ -4836,7 +4836,7 @@
         <v>-11.34683513007241</v>
       </c>
       <c r="E220" t="n">
-        <v>19.7</v>
+        <v>21</v>
       </c>
       <c r="F220" t="n">
         <v>5.5</v>
@@ -4856,7 +4856,7 @@
         <v>-4.672589326071132</v>
       </c>
       <c r="E221" t="n">
-        <v>18.8</v>
+        <v>17</v>
       </c>
       <c r="F221" t="n">
         <v>4</v>
@@ -4876,7 +4876,7 @@
         <v>-5.574994098887871</v>
       </c>
       <c r="E222" t="n">
-        <v>17.9</v>
+        <v>17</v>
       </c>
       <c r="F222" t="n">
         <v>-0.5</v>
@@ -4896,7 +4896,7 @@
         <v>-7.561973782123608</v>
       </c>
       <c r="E223" t="n">
-        <v>12.8</v>
+        <v>17</v>
       </c>
       <c r="F223" t="n">
         <v>8.5</v>
@@ -4916,7 +4916,7 @@
         <v>-5.122821742112643</v>
       </c>
       <c r="E224" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F224" t="n">
         <v>2.5</v>
@@ -4936,7 +4936,7 @@
         <v>-8.540376647193753</v>
       </c>
       <c r="E225" t="n">
-        <v>29.9</v>
+        <v>27</v>
       </c>
       <c r="F225" t="n">
         <v>2.5</v>
@@ -4956,7 +4956,7 @@
         <v>-14.38422203108571</v>
       </c>
       <c r="E226" t="n">
-        <v>21.9</v>
+        <v>21</v>
       </c>
       <c r="F226" t="n">
         <v>5.5</v>
@@ -4996,7 +4996,7 @@
         <v>-8.624119528586101</v>
       </c>
       <c r="E228" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F228" t="n">
         <v>1</v>
@@ -5016,7 +5016,7 @@
         <v>-7.642849585159722</v>
       </c>
       <c r="E229" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F229" t="n">
         <v>-6.5</v>
@@ -5036,7 +5036,7 @@
         <v>-19.21652899798537</v>
       </c>
       <c r="E230" t="n">
-        <v>24.8</v>
+        <v>21</v>
       </c>
       <c r="F230" t="n">
         <v>2.5</v>
@@ -5056,7 +5056,7 @@
         <v>-7.446396844456115</v>
       </c>
       <c r="E231" t="n">
-        <v>23.9</v>
+        <v>25</v>
       </c>
       <c r="F231" t="n">
         <v>11.5</v>
@@ -5076,7 +5076,7 @@
         <v>-6.816178332842622</v>
       </c>
       <c r="E232" t="n">
-        <v>19.9</v>
+        <v>27</v>
       </c>
       <c r="F232" t="n">
         <v>-3.5</v>
@@ -5096,7 +5096,7 @@
         <v>-4.111224791603618</v>
       </c>
       <c r="E233" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="F233" t="n">
         <v>2.5</v>
@@ -5116,7 +5116,7 @@
         <v>-7.431045844935011</v>
       </c>
       <c r="E234" t="n">
-        <v>19.9</v>
+        <v>19</v>
       </c>
       <c r="F234" t="n">
         <v>7</v>
@@ -5136,7 +5136,7 @@
         <v>-3.793921272312653</v>
       </c>
       <c r="E235" t="n">
-        <v>23.7</v>
+        <v>21</v>
       </c>
       <c r="F235" t="n">
         <v>10</v>
@@ -5156,7 +5156,7 @@
         <v>-9.390426779972652</v>
       </c>
       <c r="E236" t="n">
-        <v>14.6</v>
+        <v>11</v>
       </c>
       <c r="F236" t="n">
         <v>5.5</v>
@@ -5176,7 +5176,7 @@
         <v>-6.645359241779041</v>
       </c>
       <c r="E237" t="n">
-        <v>34.8</v>
+        <v>23</v>
       </c>
       <c r="F237" t="n">
         <v>2.5</v>
@@ -5196,7 +5196,7 @@
         <v>-6.659235330907647</v>
       </c>
       <c r="E238" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F238" t="n">
         <v>10</v>
@@ -5216,7 +5216,7 @@
         <v>-7.389250931299761</v>
       </c>
       <c r="E239" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F239" t="n">
         <v>5.5</v>
@@ -5236,7 +5236,7 @@
         <v>-6.601754772706715</v>
       </c>
       <c r="E240" t="n">
-        <v>21.9</v>
+        <v>27</v>
       </c>
       <c r="F240" t="n">
         <v>10</v>
@@ -5256,7 +5256,7 @@
         <v>-10.54182006098494</v>
       </c>
       <c r="E241" t="n">
-        <v>23.9</v>
+        <v>19</v>
       </c>
       <c r="F241" t="n">
         <v>5.5</v>
@@ -5276,7 +5276,7 @@
         <v>-15.04528412633056</v>
       </c>
       <c r="E242" t="n">
-        <v>23.9</v>
+        <v>25</v>
       </c>
       <c r="F242" t="n">
         <v>10</v>
@@ -5296,7 +5296,7 @@
         <v>-4.485149225985528</v>
       </c>
       <c r="E243" t="n">
-        <v>14.8</v>
+        <v>21</v>
       </c>
       <c r="F243" t="n">
         <v>7</v>
@@ -5316,7 +5316,7 @@
         <v>-12.90464160657133</v>
       </c>
       <c r="E244" t="n">
-        <v>15.7</v>
+        <v>21</v>
       </c>
       <c r="F244" t="n">
         <v>5.5</v>
@@ -5336,7 +5336,7 @@
         <v>-10.64541686645118</v>
       </c>
       <c r="E245" t="n">
-        <v>23.9</v>
+        <v>15</v>
       </c>
       <c r="F245" t="n">
         <v>2.5</v>
@@ -5356,7 +5356,7 @@
         <v>-10.34030639977348</v>
       </c>
       <c r="E246" t="n">
-        <v>12.8</v>
+        <v>21</v>
       </c>
       <c r="F246" t="n">
         <v>4</v>
@@ -5376,7 +5376,7 @@
         <v>-10.19854567178833</v>
       </c>
       <c r="E247" t="n">
-        <v>30.8</v>
+        <v>33</v>
       </c>
       <c r="F247" t="n">
         <v>8.5</v>
@@ -5396,7 +5396,7 @@
         <v>-5.854820405046824</v>
       </c>
       <c r="E248" t="n">
-        <v>18.8</v>
+        <v>33</v>
       </c>
       <c r="F248" t="n">
         <v>11.5</v>
@@ -5416,7 +5416,7 @@
         <v>-8.740162907611163</v>
       </c>
       <c r="E249" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F249" t="n">
         <v>5.5</v>
@@ -5436,7 +5436,7 @@
         <v>-8.67301888488873</v>
       </c>
       <c r="E250" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F250" t="n">
         <v>4</v>
@@ -5456,7 +5456,7 @@
         <v>-15.23558737691752</v>
       </c>
       <c r="E251" t="n">
-        <v>24.8</v>
+        <v>29</v>
       </c>
       <c r="F251" t="n">
         <v>4</v>
@@ -5476,7 +5476,7 @@
         <v>-9.342347585650238</v>
       </c>
       <c r="E252" t="n">
-        <v>25.7</v>
+        <v>25</v>
       </c>
       <c r="F252" t="n">
         <v>7</v>
@@ -5496,7 +5496,7 @@
         <v>-4.00963828005715</v>
       </c>
       <c r="E253" t="n">
-        <v>18.6</v>
+        <v>35</v>
       </c>
       <c r="F253" t="n">
         <v>11.5</v>
@@ -5516,7 +5516,7 @@
         <v>-7.006825558338786</v>
       </c>
       <c r="E254" t="n">
-        <v>21.9</v>
+        <v>29</v>
       </c>
       <c r="F254" t="n">
         <v>4</v>
@@ -5536,7 +5536,7 @@
         <v>-9.100522115540389</v>
       </c>
       <c r="E255" t="n">
-        <v>21.7</v>
+        <v>25</v>
       </c>
       <c r="F255" t="n">
         <v>7</v>
@@ -5556,7 +5556,7 @@
         <v>-6.682488486241348</v>
       </c>
       <c r="E256" t="n">
-        <v>20.8</v>
+        <v>19</v>
       </c>
       <c r="F256" t="n">
         <v>8.5</v>
@@ -5576,7 +5576,7 @@
         <v>-7.919839588373449</v>
       </c>
       <c r="E257" t="n">
-        <v>22.8</v>
+        <v>19</v>
       </c>
       <c r="F257" t="n">
         <v>7</v>
@@ -5616,7 +5616,7 @@
         <v>-4.38164053542964</v>
       </c>
       <c r="E259" t="n">
-        <v>16.8</v>
+        <v>27</v>
       </c>
       <c r="F259" t="n">
         <v>5.5</v>
@@ -5636,7 +5636,7 @@
         <v>-9.879498904697028</v>
       </c>
       <c r="E260" t="n">
-        <v>5.9</v>
+        <v>33</v>
       </c>
       <c r="F260" t="n">
         <v>7</v>
@@ -5656,7 +5656,7 @@
         <v>-4.631422886825721</v>
       </c>
       <c r="E261" t="n">
-        <v>14.6</v>
+        <v>21</v>
       </c>
       <c r="F261" t="n">
         <v>5.5</v>
@@ -5676,7 +5676,7 @@
         <v>-12.30271398733114</v>
       </c>
       <c r="E262" t="n">
-        <v>21.7</v>
+        <v>25</v>
       </c>
       <c r="F262" t="n">
         <v>11.5</v>
@@ -5696,7 +5696,7 @@
         <v>-7.837332993512454</v>
       </c>
       <c r="E263" t="n">
-        <v>24.6</v>
+        <v>21</v>
       </c>
       <c r="F263" t="n">
         <v>10</v>
@@ -5716,7 +5716,7 @@
         <v>-11.30272089467063</v>
       </c>
       <c r="E264" t="n">
-        <v>19.9</v>
+        <v>25</v>
       </c>
       <c r="F264" t="n">
         <v>-2</v>
@@ -5736,7 +5736,7 @@
         <v>-2.232287562273741</v>
       </c>
       <c r="E265" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F265" t="n">
         <v>-0.5</v>
@@ -5756,7 +5756,7 @@
         <v>-8.845822814643235</v>
       </c>
       <c r="E266" t="n">
-        <v>15.9</v>
+        <v>7</v>
       </c>
       <c r="F266" t="n">
         <v>10</v>
@@ -5776,7 +5776,7 @@
         <v>-17.40506405164033</v>
       </c>
       <c r="E267" t="n">
-        <v>17.9</v>
+        <v>17</v>
       </c>
       <c r="F267" t="n">
         <v>5.5</v>
@@ -5796,7 +5796,7 @@
         <v>-7.497009722041158</v>
       </c>
       <c r="E268" t="n">
-        <v>26.8</v>
+        <v>27</v>
       </c>
       <c r="F268" t="n">
         <v>-8</v>
@@ -5816,7 +5816,7 @@
         <v>-6.347089668468085</v>
       </c>
       <c r="E269" t="n">
-        <v>31.7</v>
+        <v>27</v>
       </c>
       <c r="F269" t="n">
         <v>5.5</v>
@@ -5836,7 +5836,7 @@
         <v>-6.612981808812417</v>
       </c>
       <c r="E270" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F270" t="n">
         <v>4</v>
@@ -5856,7 +5856,7 @@
         <v>-11.06939687601137</v>
       </c>
       <c r="E271" t="n">
-        <v>13.9</v>
+        <v>23</v>
       </c>
       <c r="F271" t="n">
         <v>-5</v>
@@ -5876,7 +5876,7 @@
         <v>-3.758817514648497</v>
       </c>
       <c r="E272" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F272" t="n">
         <v>5.5</v>
@@ -5896,7 +5896,7 @@
         <v>-4.051877556375617</v>
       </c>
       <c r="E273" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F273" t="n">
         <v>7</v>
@@ -5916,7 +5916,7 @@
         <v>-10.52242670855952</v>
       </c>
       <c r="E274" t="n">
-        <v>33.7</v>
+        <v>35</v>
       </c>
       <c r="F274" t="n">
         <v>8.5</v>
@@ -5936,7 +5936,7 @@
         <v>-15.126689506234</v>
       </c>
       <c r="E275" t="n">
-        <v>19.7</v>
+        <v>23</v>
       </c>
       <c r="F275" t="n">
         <v>14.5</v>
@@ -5956,7 +5956,7 @@
         <v>-9.283689005874132</v>
       </c>
       <c r="E276" t="n">
-        <v>16.6</v>
+        <v>13</v>
       </c>
       <c r="F276" t="n">
         <v>8.5</v>
@@ -5976,7 +5976,7 @@
         <v>-7.94424447213977</v>
       </c>
       <c r="E277" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F277" t="n">
         <v>8.5</v>
@@ -5996,7 +5996,7 @@
         <v>-6.180337229755344</v>
       </c>
       <c r="E278" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F278" t="n">
         <v>5.5</v>
@@ -6016,7 +6016,7 @@
         <v>-8.982461384875723</v>
       </c>
       <c r="E279" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F279" t="n">
         <v>5.5</v>
@@ -6036,7 +6036,7 @@
         <v>-11.02713454495316</v>
       </c>
       <c r="E280" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F280" t="n">
         <v>13</v>
@@ -6056,7 +6056,7 @@
         <v>-14.250355621725</v>
       </c>
       <c r="E281" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F281" t="n">
         <v>4</v>
@@ -6096,7 +6096,7 @@
         <v>-1.583944458459632</v>
       </c>
       <c r="E283" t="n">
-        <v>30.8</v>
+        <v>29</v>
       </c>
       <c r="F283" t="n">
         <v>8.5</v>
@@ -6136,7 +6136,7 @@
         <v>-1.993944866098498</v>
       </c>
       <c r="E285" t="n">
-        <v>27.7</v>
+        <v>25</v>
       </c>
       <c r="F285" t="n">
         <v>10</v>
@@ -6156,7 +6156,7 @@
         <v>-7.962965242945846</v>
       </c>
       <c r="E286" t="n">
-        <v>28.8</v>
+        <v>33</v>
       </c>
       <c r="F286" t="n">
         <v>10</v>
@@ -6196,7 +6196,7 @@
         <v>-7.873822197284354</v>
       </c>
       <c r="E288" t="n">
-        <v>21.7</v>
+        <v>27</v>
       </c>
       <c r="F288" t="n">
         <v>4</v>
@@ -6216,7 +6216,7 @@
         <v>-5.515009419003278</v>
       </c>
       <c r="E289" t="n">
-        <v>33.9</v>
+        <v>29</v>
       </c>
       <c r="F289" t="n">
         <v>10</v>
@@ -6236,7 +6236,7 @@
         <v>-10.62394376937941</v>
       </c>
       <c r="E290" t="n">
-        <v>30.8</v>
+        <v>33</v>
       </c>
       <c r="F290" t="n">
         <v>7</v>
@@ -6256,7 +6256,7 @@
         <v>-4.861284849882093</v>
       </c>
       <c r="E291" t="n">
-        <v>29.9</v>
+        <v>21</v>
       </c>
       <c r="F291" t="n">
         <v>14.5</v>
@@ -6276,7 +6276,7 @@
         <v>-5.133218124018798</v>
       </c>
       <c r="E292" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F292" t="n">
         <v>7</v>
@@ -6296,7 +6296,7 @@
         <v>-8.421038212394912</v>
       </c>
       <c r="E293" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F293" t="n">
         <v>5.5</v>
@@ -6316,7 +6316,7 @@
         <v>-7.958357982669677</v>
       </c>
       <c r="E294" t="n">
-        <v>31.9</v>
+        <v>31</v>
       </c>
       <c r="F294" t="n">
         <v>11.5</v>
@@ -6336,7 +6336,7 @@
         <v>-7.403946284003434</v>
       </c>
       <c r="E295" t="n">
-        <v>23.9</v>
+        <v>29</v>
       </c>
       <c r="F295" t="n">
         <v>5.5</v>
@@ -6356,7 +6356,7 @@
         <v>-1.924384022657788</v>
       </c>
       <c r="E296" t="n">
-        <v>16.8</v>
+        <v>21</v>
       </c>
       <c r="F296" t="n">
         <v>5.5</v>
@@ -6376,7 +6376,7 @@
         <v>-9.63065438938828</v>
       </c>
       <c r="E297" t="n">
-        <v>28.59999999999999</v>
+        <v>29</v>
       </c>
       <c r="F297" t="n">
         <v>7</v>
@@ -6396,7 +6396,7 @@
         <v>-3.802405797042502</v>
       </c>
       <c r="E298" t="n">
-        <v>25.9</v>
+        <v>27</v>
       </c>
       <c r="F298" t="n">
         <v>10</v>
@@ -6416,7 +6416,7 @@
         <v>-2.270559716689897</v>
       </c>
       <c r="E299" t="n">
-        <v>20.8</v>
+        <v>29</v>
       </c>
       <c r="F299" t="n">
         <v>10</v>
@@ -6436,7 +6436,7 @@
         <v>-5.067145124015414</v>
       </c>
       <c r="E300" t="n">
-        <v>31.9</v>
+        <v>29</v>
       </c>
       <c r="F300" t="n">
         <v>13</v>
@@ -6456,7 +6456,7 @@
         <v>-3.739643154692641</v>
       </c>
       <c r="E301" t="n">
-        <v>31.9</v>
+        <v>27</v>
       </c>
       <c r="F301" t="n">
         <v>5.5</v>
@@ -6476,7 +6476,7 @@
         <v>-3.418293055915066</v>
       </c>
       <c r="E302" t="n">
-        <v>30.8</v>
+        <v>33</v>
       </c>
       <c r="F302" t="n">
         <v>13</v>
@@ -6496,7 +6496,7 @@
         <v>-4.344905760267247</v>
       </c>
       <c r="E303" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="F303" t="n">
         <v>7</v>
@@ -6516,7 +6516,7 @@
         <v>-15.2933712096641</v>
       </c>
       <c r="E304" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F304" t="n">
         <v>11.5</v>
@@ -6536,7 +6536,7 @@
         <v>-2.833311277806506</v>
       </c>
       <c r="E305" t="n">
-        <v>21.9</v>
+        <v>33</v>
       </c>
       <c r="F305" t="n">
         <v>11.5</v>
@@ -6556,7 +6556,7 @@
         <v>-6.487566266327902</v>
       </c>
       <c r="E306" t="n">
-        <v>35.5</v>
+        <v>37</v>
       </c>
       <c r="F306" t="n">
         <v>11.5</v>
@@ -6576,7 +6576,7 @@
         <v>-0.597558805795496</v>
       </c>
       <c r="E307" t="n">
-        <v>27.9</v>
+        <v>25</v>
       </c>
       <c r="F307" t="n">
         <v>16</v>
@@ -6596,7 +6596,7 @@
         <v>-7.007631493657506</v>
       </c>
       <c r="E308" t="n">
-        <v>30.6</v>
+        <v>29</v>
       </c>
       <c r="F308" t="n">
         <v>4</v>
@@ -6616,7 +6616,7 @@
         <v>-6.356009385510418</v>
       </c>
       <c r="E309" t="n">
-        <v>15.9</v>
+        <v>17</v>
       </c>
       <c r="F309" t="n">
         <v>14.5</v>
@@ -6636,7 +6636,7 @@
         <v>-12.60793338696019</v>
       </c>
       <c r="E310" t="n">
-        <v>32.8</v>
+        <v>33</v>
       </c>
       <c r="F310" t="n">
         <v>11.5</v>
@@ -6656,7 +6656,7 @@
         <v>-10.55619850873314</v>
       </c>
       <c r="E311" t="n">
-        <v>20.6</v>
+        <v>19</v>
       </c>
       <c r="F311" t="n">
         <v>8.5</v>
@@ -6676,7 +6676,7 @@
         <v>-8.036085399538264</v>
       </c>
       <c r="E312" t="n">
-        <v>32.8</v>
+        <v>35</v>
       </c>
       <c r="F312" t="n">
         <v>11.5</v>
@@ -6696,7 +6696,7 @@
         <v>-7.133811441293342</v>
       </c>
       <c r="E313" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F313" t="n">
         <v>5.5</v>
@@ -6716,7 +6716,7 @@
         <v>-1.537075693521595</v>
       </c>
       <c r="E314" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F314" t="n">
         <v>11.5</v>
@@ -6736,7 +6736,7 @@
         <v>-4.000693130585137</v>
       </c>
       <c r="E315" t="n">
-        <v>23.9</v>
+        <v>37</v>
       </c>
       <c r="F315" t="n">
         <v>17.5</v>
@@ -6756,7 +6756,7 @@
         <v>-7.442802803480682</v>
       </c>
       <c r="E316" t="n">
-        <v>30.6</v>
+        <v>31</v>
       </c>
       <c r="F316" t="n">
         <v>-2</v>
@@ -6776,7 +6776,7 @@
         <v>0.321256182415646</v>
       </c>
       <c r="E317" t="n">
-        <v>33.5</v>
+        <v>25</v>
       </c>
       <c r="F317" t="n">
         <v>13</v>
@@ -6796,7 +6796,7 @@
         <v>-6.598016050430667</v>
       </c>
       <c r="E318" t="n">
-        <v>16.8</v>
+        <v>33</v>
       </c>
       <c r="F318" t="n">
         <v>10</v>
@@ -6816,7 +6816,7 @@
         <v>-6.205783364635726</v>
       </c>
       <c r="E319" t="n">
-        <v>25.7</v>
+        <v>21</v>
       </c>
       <c r="F319" t="n">
         <v>8.5</v>
@@ -6836,7 +6836,7 @@
         <v>-4.879434422761875</v>
       </c>
       <c r="E320" t="n">
-        <v>25.7</v>
+        <v>37</v>
       </c>
       <c r="F320" t="n">
         <v>14.5</v>
@@ -6856,7 +6856,7 @@
         <v>-8.815660834151867</v>
       </c>
       <c r="E321" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F321" t="n">
         <v>5.5</v>
@@ -6876,7 +6876,7 @@
         <v>-4.880041842271443</v>
       </c>
       <c r="E322" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F322" t="n">
         <v>16</v>
@@ -6896,7 +6896,7 @@
         <v>1.3390683303161</v>
       </c>
       <c r="E323" t="n">
-        <v>33.7</v>
+        <v>25</v>
       </c>
       <c r="F323" t="n">
         <v>16</v>
@@ -6916,7 +6916,7 @@
         <v>-7.534882036620827</v>
       </c>
       <c r="E324" t="n">
-        <v>29.9</v>
+        <v>37</v>
       </c>
       <c r="F324" t="n">
         <v>13</v>
@@ -6936,7 +6936,7 @@
         <v>-1.437938527968541</v>
       </c>
       <c r="E325" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F325" t="n">
         <v>8.5</v>
@@ -6956,7 +6956,7 @@
         <v>-3.084487384043165</v>
       </c>
       <c r="E326" t="n">
-        <v>31.9</v>
+        <v>25</v>
       </c>
       <c r="F326" t="n">
         <v>11.5</v>
@@ -6976,7 +6976,7 @@
         <v>-4.984577567865049</v>
       </c>
       <c r="E327" t="n">
-        <v>33.9</v>
+        <v>33</v>
       </c>
       <c r="F327" t="n">
         <v>14.5</v>
@@ -6996,7 +6996,7 @@
         <v>-12.47954626896995</v>
       </c>
       <c r="E328" t="n">
-        <v>30.8</v>
+        <v>31</v>
       </c>
       <c r="F328" t="n">
         <v>14.5</v>
@@ -7016,7 +7016,7 @@
         <v>-10.71310955210427</v>
       </c>
       <c r="E329" t="n">
-        <v>28.8</v>
+        <v>31</v>
       </c>
       <c r="F329" t="n">
         <v>16</v>
@@ -7036,7 +7036,7 @@
         <v>-4.214159442252412</v>
       </c>
       <c r="E330" t="n">
-        <v>33.9</v>
+        <v>27</v>
       </c>
       <c r="F330" t="n">
         <v>10</v>
@@ -7056,7 +7056,7 @@
         <v>-10.32175432625408</v>
       </c>
       <c r="E331" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F331" t="n">
         <v>8.5</v>
@@ -7076,7 +7076,7 @@
         <v>-3.847451207287437</v>
       </c>
       <c r="E332" t="n">
-        <v>27.9</v>
+        <v>29</v>
       </c>
       <c r="F332" t="n">
         <v>11.5</v>
@@ -7096,7 +7096,7 @@
         <v>-7.577111428170915</v>
       </c>
       <c r="E333" t="n">
-        <v>30.8</v>
+        <v>31</v>
       </c>
       <c r="F333" t="n">
         <v>4</v>
@@ -7116,7 +7116,7 @@
         <v>-12.39685699336666</v>
       </c>
       <c r="E334" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F334" t="n">
         <v>14.5</v>
@@ -7136,7 +7136,7 @@
         <v>-4.536191961028859</v>
       </c>
       <c r="E335" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F335" t="n">
         <v>13</v>
@@ -7156,7 +7156,7 @@
         <v>-3.793876976120675</v>
       </c>
       <c r="E336" t="n">
-        <v>20.8</v>
+        <v>31</v>
       </c>
       <c r="F336" t="n">
         <v>7</v>
@@ -7176,7 +7176,7 @@
         <v>1.892030835894608</v>
       </c>
       <c r="E337" t="n">
-        <v>26.8</v>
+        <v>31</v>
       </c>
       <c r="F337" t="n">
         <v>7</v>
@@ -7216,7 +7216,7 @@
         <v>-1.615861001382153</v>
       </c>
       <c r="E339" t="n">
-        <v>34.8</v>
+        <v>37</v>
       </c>
       <c r="F339" t="n">
         <v>11.5</v>
@@ -7236,7 +7236,7 @@
         <v>-5.341940188564537</v>
       </c>
       <c r="E340" t="n">
-        <v>20.8</v>
+        <v>27</v>
       </c>
       <c r="F340" t="n">
         <v>10</v>
@@ -7256,7 +7256,7 @@
         <v>-5.309355549382947</v>
       </c>
       <c r="E341" t="n">
-        <v>32.59999999999999</v>
+        <v>37</v>
       </c>
       <c r="F341" t="n">
         <v>16</v>
@@ -7276,7 +7276,7 @@
         <v>-5.062973998838486</v>
       </c>
       <c r="E342" t="n">
-        <v>29.9</v>
+        <v>33</v>
       </c>
       <c r="F342" t="n">
         <v>13</v>
@@ -7296,7 +7296,7 @@
         <v>-3.868067795346402</v>
       </c>
       <c r="E343" t="n">
-        <v>25.9</v>
+        <v>31</v>
       </c>
       <c r="F343" t="n">
         <v>13</v>
@@ -7316,7 +7316,7 @@
         <v>-1.295206924452152</v>
       </c>
       <c r="E344" t="n">
-        <v>25.7</v>
+        <v>31</v>
       </c>
       <c r="F344" t="n">
         <v>11.5</v>
@@ -7336,7 +7336,7 @@
         <v>-4.563509516184059</v>
       </c>
       <c r="E345" t="n">
-        <v>31.9</v>
+        <v>35</v>
       </c>
       <c r="F345" t="n">
         <v>11.5</v>
@@ -7356,7 +7356,7 @@
         <v>-4.52968578496577</v>
       </c>
       <c r="E346" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F346" t="n">
         <v>14.5</v>
@@ -7376,7 +7376,7 @@
         <v>0.5616403015032345</v>
       </c>
       <c r="E347" t="n">
-        <v>32.8</v>
+        <v>31</v>
       </c>
       <c r="F347" t="n">
         <v>8.5</v>
@@ -7396,7 +7396,7 @@
         <v>-1.932480718018562</v>
       </c>
       <c r="E348" t="n">
-        <v>33.9</v>
+        <v>33</v>
       </c>
       <c r="F348" t="n">
         <v>16</v>
@@ -7416,7 +7416,7 @@
         <v>-2.492076983508796</v>
       </c>
       <c r="E349" t="n">
-        <v>19.9</v>
+        <v>27</v>
       </c>
       <c r="F349" t="n">
         <v>13</v>
@@ -7436,7 +7436,7 @@
         <v>-6.866377835308298</v>
       </c>
       <c r="E350" t="n">
-        <v>41.7</v>
+        <v>43</v>
       </c>
       <c r="F350" t="n">
         <v>5.5</v>
@@ -7456,7 +7456,7 @@
         <v>-8.46601744993502</v>
       </c>
       <c r="E351" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F351" t="n">
         <v>5.5</v>
@@ -7476,7 +7476,7 @@
         <v>-8.503358770040659</v>
       </c>
       <c r="E352" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F352" t="n">
         <v>8.5</v>
@@ -7496,7 +7496,7 @@
         <v>-3.401522239735685</v>
       </c>
       <c r="E353" t="n">
-        <v>29.7</v>
+        <v>31</v>
       </c>
       <c r="F353" t="n">
         <v>5.5</v>
@@ -7516,7 +7516,7 @@
         <v>-4.889302168656975</v>
       </c>
       <c r="E354" t="n">
-        <v>39.9</v>
+        <v>39</v>
       </c>
       <c r="F354" t="n">
         <v>5.5</v>
@@ -7536,7 +7536,7 @@
         <v>-5.45993309037005</v>
       </c>
       <c r="E355" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F355" t="n">
         <v>14.5</v>
@@ -7556,7 +7556,7 @@
         <v>-2.72317301315674</v>
       </c>
       <c r="E356" t="n">
-        <v>31.7</v>
+        <v>31</v>
       </c>
       <c r="F356" t="n">
         <v>14.5</v>
@@ -7576,7 +7576,7 @@
         <v>-7.169360862597371</v>
       </c>
       <c r="E357" t="n">
-        <v>26.6</v>
+        <v>27</v>
       </c>
       <c r="F357" t="n">
         <v>13</v>
@@ -7596,7 +7596,7 @@
         <v>-10.81470985813222</v>
       </c>
       <c r="E358" t="n">
-        <v>39.7</v>
+        <v>43</v>
       </c>
       <c r="F358" t="n">
         <v>14.5</v>
@@ -7616,7 +7616,7 @@
         <v>-8.107163803570021</v>
       </c>
       <c r="E359" t="n">
-        <v>29.9</v>
+        <v>27</v>
       </c>
       <c r="F359" t="n">
         <v>11.5</v>
@@ -7636,7 +7636,7 @@
         <v>-6.220465292608457</v>
       </c>
       <c r="E360" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F360" t="n">
         <v>19</v>
@@ -7656,7 +7656,7 @@
         <v>-5.504144096772184</v>
       </c>
       <c r="E361" t="n">
-        <v>32.4</v>
+        <v>39</v>
       </c>
       <c r="F361" t="n">
         <v>8.5</v>
@@ -7676,7 +7676,7 @@
         <v>-2.475755123102916</v>
       </c>
       <c r="E362" t="n">
-        <v>24.8</v>
+        <v>31</v>
       </c>
       <c r="F362" t="n">
         <v>17.5</v>
@@ -7696,7 +7696,7 @@
         <v>-7.444069608672705</v>
       </c>
       <c r="E363" t="n">
-        <v>37.7</v>
+        <v>41</v>
       </c>
       <c r="F363" t="n">
         <v>14.5</v>
@@ -7716,7 +7716,7 @@
         <v>-2.021784772990322</v>
       </c>
       <c r="E364" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F364" t="n">
         <v>14.5</v>
@@ -7736,7 +7736,7 @@
         <v>-2.354104958383093</v>
       </c>
       <c r="E365" t="n">
-        <v>32.59999999999999</v>
+        <v>37</v>
       </c>
       <c r="F365" t="n">
         <v>19</v>
@@ -7756,7 +7756,7 @@
         <v>-6.192040211684938</v>
       </c>
       <c r="E366" t="n">
-        <v>39.9</v>
+        <v>31</v>
       </c>
       <c r="F366" t="n">
         <v>20.5</v>
@@ -7776,7 +7776,7 @@
         <v>-5.675692005440896</v>
       </c>
       <c r="E367" t="n">
-        <v>42.8</v>
+        <v>39</v>
       </c>
       <c r="F367" t="n">
         <v>16</v>
@@ -7796,7 +7796,7 @@
         <v>-6.218050842224281</v>
       </c>
       <c r="E368" t="n">
-        <v>39.9</v>
+        <v>35</v>
       </c>
       <c r="F368" t="n">
         <v>19</v>
@@ -7816,7 +7816,7 @@
         <v>-3.07883011643317</v>
       </c>
       <c r="E369" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F369" t="n">
         <v>16</v>
@@ -7836,7 +7836,7 @@
         <v>0.4454353742164699</v>
       </c>
       <c r="E370" t="n">
-        <v>15.7</v>
+        <v>35</v>
       </c>
       <c r="F370" t="n">
         <v>19</v>
@@ -7856,7 +7856,7 @@
         <v>-5.299662112462816</v>
       </c>
       <c r="E371" t="n">
-        <v>31.7</v>
+        <v>33</v>
       </c>
       <c r="F371" t="n">
         <v>20.5</v>
@@ -7876,7 +7876,7 @@
         <v>-4.275349160139813</v>
       </c>
       <c r="E372" t="n">
-        <v>37.9</v>
+        <v>41</v>
       </c>
       <c r="F372" t="n">
         <v>20.5</v>
@@ -7896,7 +7896,7 @@
         <v>2.760114520882845</v>
       </c>
       <c r="E373" t="n">
-        <v>38.8</v>
+        <v>35</v>
       </c>
       <c r="F373" t="n">
         <v>11.5</v>
@@ -7916,7 +7916,7 @@
         <v>-2.233175560934974</v>
       </c>
       <c r="E374" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F374" t="n">
         <v>11.5</v>
@@ -7936,7 +7936,7 @@
         <v>-3.849263004804139</v>
       </c>
       <c r="E375" t="n">
-        <v>33.9</v>
+        <v>39</v>
       </c>
       <c r="F375" t="n">
         <v>13</v>
@@ -7956,7 +7956,7 @@
         <v>-7.439318426871877</v>
       </c>
       <c r="E376" t="n">
-        <v>35.9</v>
+        <v>37</v>
       </c>
       <c r="F376" t="n">
         <v>16</v>
@@ -7976,7 +7976,7 @@
         <v>0.3988126622416603</v>
       </c>
       <c r="E377" t="n">
-        <v>33.9</v>
+        <v>35</v>
       </c>
       <c r="F377" t="n">
         <v>17.5</v>
@@ -7996,7 +7996,7 @@
         <v>-5.219605923776177</v>
       </c>
       <c r="E378" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F378" t="n">
         <v>10</v>
@@ -8016,7 +8016,7 @@
         <v>1.436115308975747</v>
       </c>
       <c r="E379" t="n">
-        <v>28.8</v>
+        <v>33</v>
       </c>
       <c r="F379" t="n">
         <v>20.5</v>
@@ -8036,7 +8036,7 @@
         <v>-2.555545674890773</v>
       </c>
       <c r="E380" t="n">
-        <v>35.9</v>
+        <v>43</v>
       </c>
       <c r="F380" t="n">
         <v>16</v>
@@ -8056,7 +8056,7 @@
         <v>-5.898584918723315</v>
       </c>
       <c r="E381" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F381" t="n">
         <v>14.5</v>
@@ -8076,7 +8076,7 @@
         <v>-7.073209898845452</v>
       </c>
       <c r="E382" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F382" t="n">
         <v>7</v>
@@ -8096,7 +8096,7 @@
         <v>-3.622977285184998</v>
       </c>
       <c r="E383" t="n">
-        <v>40.8</v>
+        <v>41</v>
       </c>
       <c r="F383" t="n">
         <v>19</v>
@@ -8116,7 +8116,7 @@
         <v>-9.917287036815871</v>
       </c>
       <c r="E384" t="n">
-        <v>30.8</v>
+        <v>31</v>
       </c>
       <c r="F384" t="n">
         <v>13</v>
@@ -8136,7 +8136,7 @@
         <v>0.5373091015979023</v>
       </c>
       <c r="E385" t="n">
-        <v>25.5</v>
+        <v>41</v>
       </c>
       <c r="F385" t="n">
         <v>17.5</v>
@@ -8156,7 +8156,7 @@
         <v>-0.9602138229564684</v>
       </c>
       <c r="E386" t="n">
-        <v>29.7</v>
+        <v>37</v>
       </c>
       <c r="F386" t="n">
         <v>14.5</v>
@@ -8176,7 +8176,7 @@
         <v>-2.535567183211558</v>
       </c>
       <c r="E387" t="n">
-        <v>39.7</v>
+        <v>41</v>
       </c>
       <c r="F387" t="n">
         <v>10</v>
@@ -8196,7 +8196,7 @@
         <v>2.200141246463018</v>
       </c>
       <c r="E388" t="n">
-        <v>33.5</v>
+        <v>31</v>
       </c>
       <c r="F388" t="n">
         <v>11.5</v>
@@ -8216,7 +8216,7 @@
         <v>1.811103417675227</v>
       </c>
       <c r="E389" t="n">
-        <v>34.8</v>
+        <v>37</v>
       </c>
       <c r="F389" t="n">
         <v>17.5</v>
@@ -8236,7 +8236,7 @@
         <v>-9.225704108485532</v>
       </c>
       <c r="E390" t="n">
-        <v>38.8</v>
+        <v>41</v>
       </c>
       <c r="F390" t="n">
         <v>14.5</v>
@@ -8276,7 +8276,7 @@
         <v>-1.257155408909161</v>
       </c>
       <c r="E392" t="n">
-        <v>33.7</v>
+        <v>33</v>
       </c>
       <c r="F392" t="n">
         <v>16</v>
@@ -8296,7 +8296,7 @@
         <v>-4.429092056794652</v>
       </c>
       <c r="E393" t="n">
-        <v>38.6</v>
+        <v>43</v>
       </c>
       <c r="F393" t="n">
         <v>14.5</v>
@@ -8316,7 +8316,7 @@
         <v>-2.148827803887845</v>
       </c>
       <c r="E394" t="n">
-        <v>33.9</v>
+        <v>33</v>
       </c>
       <c r="F394" t="n">
         <v>14.5</v>
@@ -8336,7 +8336,7 @@
         <v>-6.628430276399285</v>
       </c>
       <c r="E395" t="n">
-        <v>37.9</v>
+        <v>39</v>
       </c>
       <c r="F395" t="n">
         <v>17.5</v>
@@ -8356,7 +8356,7 @@
         <v>-2.811622576116388</v>
       </c>
       <c r="E396" t="n">
-        <v>34.8</v>
+        <v>37</v>
       </c>
       <c r="F396" t="n">
         <v>11.5</v>
@@ -8376,7 +8376,7 @@
         <v>1.516348024524294</v>
       </c>
       <c r="E397" t="n">
-        <v>43.9</v>
+        <v>31</v>
       </c>
       <c r="F397" t="n">
         <v>19</v>
@@ -8396,7 +8396,7 @@
         <v>0.7759562547179837</v>
       </c>
       <c r="E398" t="n">
-        <v>34.8</v>
+        <v>39</v>
       </c>
       <c r="F398" t="n">
         <v>20.5</v>
@@ -8436,7 +8436,7 @@
         <v>5.906920073781943</v>
       </c>
       <c r="E400" t="n">
-        <v>28.8</v>
+        <v>37</v>
       </c>
       <c r="F400" t="n">
         <v>14.5</v>
@@ -8456,7 +8456,7 @@
         <v>-1.152800133799763</v>
       </c>
       <c r="E401" t="n">
-        <v>33.9</v>
+        <v>39</v>
       </c>
       <c r="F401" t="n">
         <v>17.5</v>
@@ -8476,7 +8476,7 @@
         <v>1.92235435186735</v>
       </c>
       <c r="E402" t="n">
-        <v>34.59999999999999</v>
+        <v>41</v>
       </c>
       <c r="F402" t="n">
         <v>13</v>
@@ -8496,7 +8496,7 @@
         <v>-1.324647806147128</v>
       </c>
       <c r="E403" t="n">
-        <v>28.8</v>
+        <v>41</v>
       </c>
       <c r="F403" t="n">
         <v>13</v>
@@ -8516,7 +8516,7 @@
         <v>-1.675220191202326</v>
       </c>
       <c r="E404" t="n">
-        <v>33.9</v>
+        <v>31</v>
       </c>
       <c r="F404" t="n">
         <v>17.5</v>
@@ -8536,7 +8536,7 @@
         <v>3.285523000699553</v>
       </c>
       <c r="E405" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="F405" t="n">
         <v>11.5</v>
@@ -8556,7 +8556,7 @@
         <v>1.498901900880138</v>
       </c>
       <c r="E406" t="n">
-        <v>30.8</v>
+        <v>29</v>
       </c>
       <c r="F406" t="n">
         <v>16</v>
@@ -8576,7 +8576,7 @@
         <v>0.3891414475957226</v>
       </c>
       <c r="E407" t="n">
-        <v>35.7</v>
+        <v>37</v>
       </c>
       <c r="F407" t="n">
         <v>20.5</v>
@@ -8596,7 +8596,7 @@
         <v>-5.627019008818197</v>
       </c>
       <c r="E408" t="n">
-        <v>36.8</v>
+        <v>41</v>
       </c>
       <c r="F408" t="n">
         <v>14.5</v>
@@ -8636,7 +8636,7 @@
         <v>0.125617946470375</v>
       </c>
       <c r="E410" t="n">
-        <v>34.59999999999999</v>
+        <v>35</v>
       </c>
       <c r="F410" t="n">
         <v>20.5</v>
@@ -8656,7 +8656,7 @@
         <v>-5.092614484938498</v>
       </c>
       <c r="E411" t="n">
-        <v>38.8</v>
+        <v>43</v>
       </c>
       <c r="F411" t="n">
         <v>10</v>
@@ -8676,7 +8676,7 @@
         <v>-4.108693146142889</v>
       </c>
       <c r="E412" t="n">
-        <v>35.7</v>
+        <v>37</v>
       </c>
       <c r="F412" t="n">
         <v>13</v>
@@ -8696,7 +8696,7 @@
         <v>-7.463804828800212</v>
       </c>
       <c r="E413" t="n">
-        <v>31.9</v>
+        <v>35</v>
       </c>
       <c r="F413" t="n">
         <v>17.5</v>
@@ -8716,7 +8716,7 @@
         <v>-1.055122844270363</v>
       </c>
       <c r="E414" t="n">
-        <v>31.5</v>
+        <v>37</v>
       </c>
       <c r="F414" t="n">
         <v>16</v>
@@ -8736,7 +8736,7 @@
         <v>-1.215686709645218</v>
       </c>
       <c r="E415" t="n">
-        <v>33.9</v>
+        <v>35</v>
       </c>
       <c r="F415" t="n">
         <v>17.5</v>
@@ -8756,7 +8756,7 @@
         <v>-4.396800403551372</v>
       </c>
       <c r="E416" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="F416" t="n">
         <v>22</v>
@@ -8776,7 +8776,7 @@
         <v>-2.291263596076391</v>
       </c>
       <c r="E417" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F417" t="n">
         <v>22</v>
@@ -8796,7 +8796,7 @@
         <v>-1.338984177475091</v>
       </c>
       <c r="E418" t="n">
-        <v>39.9</v>
+        <v>35</v>
       </c>
       <c r="F418" t="n">
         <v>19</v>
@@ -8816,7 +8816,7 @@
         <v>-2.378608825728114</v>
       </c>
       <c r="E419" t="n">
-        <v>37.9</v>
+        <v>37</v>
       </c>
       <c r="F419" t="n">
         <v>20.5</v>
@@ -8836,7 +8836,7 @@
         <v>-4.478171664319876</v>
       </c>
       <c r="E420" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="F420" t="n">
         <v>19</v>
@@ -8856,7 +8856,7 @@
         <v>3.493919627918584</v>
       </c>
       <c r="E421" t="n">
-        <v>34.59999999999999</v>
+        <v>33</v>
       </c>
       <c r="F421" t="n">
         <v>20.5</v>
@@ -8876,7 +8876,7 @@
         <v>-0.4493073074287441</v>
       </c>
       <c r="E422" t="n">
-        <v>37.9</v>
+        <v>39</v>
       </c>
       <c r="F422" t="n">
         <v>19</v>
@@ -8896,7 +8896,7 @@
         <v>-3.529479282034087</v>
       </c>
       <c r="E423" t="n">
-        <v>32.8</v>
+        <v>43</v>
       </c>
       <c r="F423" t="n">
         <v>20.5</v>
@@ -8916,7 +8916,7 @@
         <v>5.505363169646428</v>
       </c>
       <c r="E424" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="F424" t="n">
         <v>16</v>
@@ -8936,7 +8936,7 @@
         <v>-1.289749166080068</v>
       </c>
       <c r="E425" t="n">
-        <v>35.9</v>
+        <v>37</v>
       </c>
       <c r="F425" t="n">
         <v>17.5</v>
@@ -8956,7 +8956,7 @@
         <v>-6.328346785914285</v>
       </c>
       <c r="E426" t="n">
-        <v>41.9</v>
+        <v>45</v>
       </c>
       <c r="F426" t="n">
         <v>19</v>
@@ -8976,7 +8976,7 @@
         <v>-2.245770890171666</v>
       </c>
       <c r="E427" t="n">
-        <v>39.7</v>
+        <v>43</v>
       </c>
       <c r="F427" t="n">
         <v>20.5</v>
@@ -8996,7 +8996,7 @@
         <v>0.8586256083960975</v>
       </c>
       <c r="E428" t="n">
-        <v>39.9</v>
+        <v>35</v>
       </c>
       <c r="F428" t="n">
         <v>20.5</v>
@@ -9016,7 +9016,7 @@
         <v>-1.440130905972663</v>
       </c>
       <c r="E429" t="n">
-        <v>33.9</v>
+        <v>41</v>
       </c>
       <c r="F429" t="n">
         <v>17.5</v>
@@ -9036,7 +9036,7 @@
         <v>-6.031533531499719</v>
       </c>
       <c r="E430" t="n">
-        <v>38.6</v>
+        <v>43</v>
       </c>
       <c r="F430" t="n">
         <v>17.5</v>
@@ -9056,7 +9056,7 @@
         <v>-6.483394036182426</v>
       </c>
       <c r="E431" t="n">
-        <v>39.7</v>
+        <v>43</v>
       </c>
       <c r="F431" t="n">
         <v>22</v>
@@ -9076,7 +9076,7 @@
         <v>-4.129181923723293</v>
       </c>
       <c r="E432" t="n">
-        <v>36.8</v>
+        <v>39</v>
       </c>
       <c r="F432" t="n">
         <v>14.5</v>
@@ -9096,7 +9096,7 @@
         <v>-0.5394951999804173</v>
       </c>
       <c r="E433" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="F433" t="n">
         <v>19</v>
@@ -9116,7 +9116,7 @@
         <v>-4.91737737000209</v>
       </c>
       <c r="E434" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F434" t="n">
         <v>22</v>
@@ -9136,7 +9136,7 @@
         <v>-1.629499795376638</v>
       </c>
       <c r="E435" t="n">
-        <v>33.9</v>
+        <v>41</v>
       </c>
       <c r="F435" t="n">
         <v>19</v>
@@ -9156,7 +9156,7 @@
         <v>-2.000851078070042</v>
       </c>
       <c r="E436" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F436" t="n">
         <v>23.5</v>
@@ -9176,7 +9176,7 @@
         <v>-0.6395139177057325</v>
       </c>
       <c r="E437" t="n">
-        <v>33.7</v>
+        <v>45</v>
       </c>
       <c r="F437" t="n">
         <v>16</v>
@@ -9196,7 +9196,7 @@
         <v>-3.783377107596139</v>
       </c>
       <c r="E438" t="n">
-        <v>39.7</v>
+        <v>39</v>
       </c>
       <c r="F438" t="n">
         <v>19</v>
@@ -9216,7 +9216,7 @@
         <v>-0.1908777370631427</v>
       </c>
       <c r="E439" t="n">
-        <v>39.9</v>
+        <v>43</v>
       </c>
       <c r="F439" t="n">
         <v>17.5</v>
@@ -9236,7 +9236,7 @@
         <v>4.759227350410999</v>
       </c>
       <c r="E440" t="n">
-        <v>33.09999999999999</v>
+        <v>39</v>
       </c>
       <c r="F440" t="n">
         <v>17.5</v>
@@ -9256,7 +9256,7 @@
         <v>0.677884067585573</v>
       </c>
       <c r="E441" t="n">
-        <v>36.8</v>
+        <v>41</v>
       </c>
       <c r="F441" t="n">
         <v>17.5</v>
@@ -9276,7 +9276,7 @@
         <v>-0.0717583649901857</v>
       </c>
       <c r="E442" t="n">
-        <v>41.9</v>
+        <v>43</v>
       </c>
       <c r="F442" t="n">
         <v>19</v>
@@ -9296,7 +9296,7 @@
         <v>-1.541966372324565</v>
       </c>
       <c r="E443" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F443" t="n">
         <v>19</v>
@@ -9316,7 +9316,7 @@
         <v>-1.084744409189314</v>
       </c>
       <c r="E444" t="n">
-        <v>43.9</v>
+        <v>43</v>
       </c>
       <c r="F444" t="n">
         <v>22</v>
@@ -9336,7 +9336,7 @@
         <v>2.477458202909179</v>
       </c>
       <c r="E445" t="n">
-        <v>33.7</v>
+        <v>41</v>
       </c>
       <c r="F445" t="n">
         <v>16</v>
@@ -9356,7 +9356,7 @@
         <v>-0.888641577089203</v>
       </c>
       <c r="E446" t="n">
-        <v>35.9</v>
+        <v>41</v>
       </c>
       <c r="F446" t="n">
         <v>17.5</v>
@@ -9376,7 +9376,7 @@
         <v>-4.142588259792474</v>
       </c>
       <c r="E447" t="n">
-        <v>40.8</v>
+        <v>43</v>
       </c>
       <c r="F447" t="n">
         <v>19</v>
@@ -9396,7 +9396,7 @@
         <v>-7.494413186848452</v>
       </c>
       <c r="E448" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F448" t="n">
         <v>23.5</v>
@@ -9416,7 +9416,7 @@
         <v>-0.5810422459860057</v>
       </c>
       <c r="E449" t="n">
-        <v>37.9</v>
+        <v>35</v>
       </c>
       <c r="F449" t="n">
         <v>19</v>
@@ -9436,7 +9436,7 @@
         <v>-0.4650566229847108</v>
       </c>
       <c r="E450" t="n">
-        <v>34.8</v>
+        <v>39</v>
       </c>
       <c r="F450" t="n">
         <v>22</v>
@@ -9456,7 +9456,7 @@
         <v>-0.1039621030240891</v>
       </c>
       <c r="E451" t="n">
-        <v>43.9</v>
+        <v>35</v>
       </c>
       <c r="F451" t="n">
         <v>19</v>
@@ -9476,7 +9476,7 @@
         <v>0.5667753408456071</v>
       </c>
       <c r="E452" t="n">
-        <v>41.7</v>
+        <v>39</v>
       </c>
       <c r="F452" t="n">
         <v>19</v>
@@ -9496,7 +9496,7 @@
         <v>0.8474447506843528</v>
       </c>
       <c r="E453" t="n">
-        <v>45.9</v>
+        <v>37</v>
       </c>
       <c r="F453" t="n">
         <v>17.5</v>
@@ -9516,7 +9516,7 @@
         <v>1.226056193573341</v>
       </c>
       <c r="E454" t="n">
-        <v>34.6</v>
+        <v>39</v>
       </c>
       <c r="F454" t="n">
         <v>16</v>
@@ -9536,7 +9536,7 @@
         <v>-1.449163043556349</v>
       </c>
       <c r="E455" t="n">
-        <v>36.8</v>
+        <v>39</v>
       </c>
       <c r="F455" t="n">
         <v>19</v>
@@ -9576,7 +9576,7 @@
         <v>-3.258944684774359</v>
       </c>
       <c r="E457" t="n">
-        <v>39.9</v>
+        <v>45</v>
       </c>
       <c r="F457" t="n">
         <v>19</v>
@@ -9596,7 +9596,7 @@
         <v>0.3038155417847883</v>
       </c>
       <c r="E458" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F458" t="n">
         <v>20.5</v>
@@ -9616,7 +9616,7 @@
         <v>2.925567382898333</v>
       </c>
       <c r="E459" t="n">
-        <v>37.7</v>
+        <v>45</v>
       </c>
       <c r="F459" t="n">
         <v>20.5</v>
@@ -9636,7 +9636,7 @@
         <v>1.227335378612259</v>
       </c>
       <c r="E460" t="n">
-        <v>37.7</v>
+        <v>35</v>
       </c>
       <c r="F460" t="n">
         <v>22</v>
@@ -9656,7 +9656,7 @@
         <v>0.3567135355337989</v>
       </c>
       <c r="E461" t="n">
-        <v>37.7</v>
+        <v>47</v>
       </c>
       <c r="F461" t="n">
         <v>20.5</v>
@@ -9676,7 +9676,7 @@
         <v>-5.230389973549588</v>
       </c>
       <c r="E462" t="n">
-        <v>41.9</v>
+        <v>39</v>
       </c>
       <c r="F462" t="n">
         <v>16</v>
@@ -9696,7 +9696,7 @@
         <v>-4.468962519235912</v>
       </c>
       <c r="E463" t="n">
-        <v>36.6</v>
+        <v>41</v>
       </c>
       <c r="F463" t="n">
         <v>22</v>
@@ -9716,7 +9716,7 @@
         <v>3.142223358714665</v>
       </c>
       <c r="E464" t="n">
-        <v>42.8</v>
+        <v>47</v>
       </c>
       <c r="F464" t="n">
         <v>20.5</v>
@@ -9736,7 +9736,7 @@
         <v>1.02510534400717</v>
       </c>
       <c r="E465" t="n">
-        <v>43.9</v>
+        <v>43</v>
       </c>
       <c r="F465" t="n">
         <v>22</v>
@@ -9756,7 +9756,7 @@
         <v>-0.6141674555601673</v>
       </c>
       <c r="E466" t="n">
-        <v>41.9</v>
+        <v>47</v>
       </c>
       <c r="F466" t="n">
         <v>20.5</v>
@@ -9776,7 +9776,7 @@
         <v>-0.8160733879181367</v>
       </c>
       <c r="E467" t="n">
-        <v>42.8</v>
+        <v>41</v>
       </c>
       <c r="F467" t="n">
         <v>20.5</v>
@@ -9796,7 +9796,7 @@
         <v>1.137338576071934</v>
       </c>
       <c r="E468" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F468" t="n">
         <v>23.5</v>
@@ -9816,7 +9816,7 @@
         <v>0.6915120900000564</v>
       </c>
       <c r="E469" t="n">
-        <v>44.8</v>
+        <v>47</v>
       </c>
       <c r="F469" t="n">
         <v>22</v>
@@ -9836,7 +9836,7 @@
         <v>2.250366219827656</v>
       </c>
       <c r="E470" t="n">
-        <v>34.8</v>
+        <v>41</v>
       </c>
       <c r="F470" t="n">
         <v>20.5</v>
@@ -9856,7 +9856,7 @@
         <v>0.0206075063874691</v>
       </c>
       <c r="E471" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F471" t="n">
         <v>20.5</v>
@@ -9896,7 +9896,7 @@
         <v>-1.707842522936838</v>
       </c>
       <c r="E473" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F473" t="n">
         <v>23.5</v>
@@ -9916,7 +9916,7 @@
         <v>5.089236637678793</v>
       </c>
       <c r="E474" t="n">
-        <v>44.8</v>
+        <v>43</v>
       </c>
       <c r="F474" t="n">
         <v>19</v>
@@ -9936,7 +9936,7 @@
         <v>1.09868289235606</v>
       </c>
       <c r="E475" t="n">
-        <v>35.9</v>
+        <v>45</v>
       </c>
       <c r="F475" t="n">
         <v>23.5</v>
@@ -9956,7 +9956,7 @@
         <v>2.123629903505583</v>
       </c>
       <c r="E476" t="n">
-        <v>42.8</v>
+        <v>45</v>
       </c>
       <c r="F476" t="n">
         <v>23.5</v>
@@ -9976,7 +9976,7 @@
         <v>2.587962081711049</v>
       </c>
       <c r="E477" t="n">
-        <v>40.6</v>
+        <v>45</v>
       </c>
       <c r="F477" t="n">
         <v>22</v>
@@ -9996,7 +9996,7 @@
         <v>1.46521177615566</v>
       </c>
       <c r="E478" t="n">
-        <v>43.7</v>
+        <v>45</v>
       </c>
       <c r="F478" t="n">
         <v>20.5</v>
@@ -10016,7 +10016,7 @@
         <v>2.227730912077593</v>
       </c>
       <c r="E479" t="n">
-        <v>42.8</v>
+        <v>47</v>
       </c>
       <c r="F479" t="n">
         <v>23.5</v>
@@ -10036,7 +10036,7 @@
         <v>-2.852511499325471</v>
       </c>
       <c r="E480" t="n">
-        <v>38.8</v>
+        <v>41</v>
       </c>
       <c r="F480" t="n">
         <v>20.5</v>
@@ -10056,7 +10056,7 @@
         <v>1.656101105496402</v>
       </c>
       <c r="E481" t="n">
-        <v>43.9</v>
+        <v>47</v>
       </c>
       <c r="F481" t="n">
         <v>23.5</v>
@@ -10076,7 +10076,7 @@
         <v>-2.181595041450903</v>
       </c>
       <c r="E482" t="n">
-        <v>41.9</v>
+        <v>43</v>
       </c>
       <c r="F482" t="n">
         <v>22</v>
@@ -10096,7 +10096,7 @@
         <v>2.309738472745105</v>
       </c>
       <c r="E483" t="n">
-        <v>37.5</v>
+        <v>43</v>
       </c>
       <c r="F483" t="n">
         <v>22</v>
@@ -10116,7 +10116,7 @@
         <v>2.92055749528471</v>
       </c>
       <c r="E484" t="n">
-        <v>43.7</v>
+        <v>45</v>
       </c>
       <c r="F484" t="n">
         <v>23.5</v>
@@ -10156,7 +10156,7 @@
         <v>1.558160184887974</v>
       </c>
       <c r="E486" t="n">
-        <v>45.9</v>
+        <v>45</v>
       </c>
       <c r="F486" t="n">
         <v>22</v>
@@ -10196,7 +10196,7 @@
         <v>-6.425254374315139</v>
       </c>
       <c r="E488" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F488" t="n">
         <v>22</v>
@@ -10216,7 +10216,7 @@
         <v>-0.2984252876331439</v>
       </c>
       <c r="E489" t="n">
-        <v>45.9</v>
+        <v>47</v>
       </c>
       <c r="F489" t="n">
         <v>22</v>
@@ -10236,7 +10236,7 @@
         <v>1.906705737190377</v>
       </c>
       <c r="E490" t="n">
-        <v>41.9</v>
+        <v>47</v>
       </c>
       <c r="F490" t="n">
         <v>20.5</v>
@@ -10256,7 +10256,7 @@
         <v>-1.825583128419374</v>
       </c>
       <c r="E491" t="n">
-        <v>43.7</v>
+        <v>47</v>
       </c>
       <c r="F491" t="n">
         <v>22</v>
@@ -10276,7 +10276,7 @@
         <v>-0.5532374137363099</v>
       </c>
       <c r="E492" t="n">
-        <v>40.6</v>
+        <v>45</v>
       </c>
       <c r="F492" t="n">
         <v>20.5</v>
@@ -10316,7 +10316,7 @@
         <v>2.792917539201678</v>
       </c>
       <c r="E494" t="n">
-        <v>43.9</v>
+        <v>47</v>
       </c>
       <c r="F494" t="n">
         <v>23.5</v>
@@ -10356,7 +10356,7 @@
         <v>-2.12066542748762</v>
       </c>
       <c r="E496" t="n">
-        <v>42.6</v>
+        <v>47</v>
       </c>
       <c r="F496" t="n">
         <v>23.5</v>
@@ -10376,7 +10376,7 @@
         <v>1.224652498852347</v>
       </c>
       <c r="E497" t="n">
-        <v>42.8</v>
+        <v>47</v>
       </c>
       <c r="F497" t="n">
         <v>23.5</v>
@@ -10396,7 +10396,7 @@
         <v>2.687541208121736</v>
       </c>
       <c r="E498" t="n">
-        <v>40.8</v>
+        <v>43</v>
       </c>
       <c r="F498" t="n">
         <v>20.5</v>
@@ -10416,7 +10416,7 @@
         <v>0.8240832438619535</v>
       </c>
       <c r="E499" t="n">
-        <v>43.9</v>
+        <v>43</v>
       </c>
       <c r="F499" t="n">
         <v>23.5</v>
@@ -10436,7 +10436,7 @@
         <v>2.630254364117565</v>
       </c>
       <c r="E500" t="n">
-        <v>44.8</v>
+        <v>47</v>
       </c>
       <c r="F500" t="n">
         <v>23.5</v>
@@ -10456,7 +10456,7 @@
         <v>4.989565238231685</v>
       </c>
       <c r="E501" t="n">
-        <v>44.8</v>
+        <v>47</v>
       </c>
       <c r="F501" t="n">
         <v>23.5</v>
@@ -10522,7 +10522,7 @@
         <v>-20.88028902850273</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.3</v>
+        <v>-3</v>
       </c>
       <c r="F2" t="n">
         <v>-0.5</v>
@@ -10542,7 +10542,7 @@
         <v>-35.9607046948951</v>
       </c>
       <c r="E3" t="n">
-        <v>-14.4</v>
+        <v>-16</v>
       </c>
       <c r="F3" t="n">
         <v>-19</v>
@@ -10562,7 +10562,7 @@
         <v>-52.20263188600813</v>
       </c>
       <c r="E4" t="n">
-        <v>-27.6</v>
+        <v>-19</v>
       </c>
       <c r="F4" t="n">
         <v>-37.5</v>
@@ -10582,7 +10582,7 @@
         <v>-70.96545578083168</v>
       </c>
       <c r="E5" t="n">
-        <v>-22.8</v>
+        <v>-14</v>
       </c>
       <c r="F5" t="n">
         <v>-41</v>
@@ -10602,7 +10602,7 @@
         <v>-79.97706173751618</v>
       </c>
       <c r="E6" t="n">
-        <v>-32.9</v>
+        <v>-11</v>
       </c>
       <c r="F6" t="n">
         <v>-53.5</v>
@@ -10622,7 +10622,7 @@
         <v>-96.8619967253459</v>
       </c>
       <c r="E7" t="n">
-        <v>-37.9</v>
+        <v>-20</v>
       </c>
       <c r="F7" t="n">
         <v>-66</v>
@@ -10642,7 +10642,7 @@
         <v>-119.0205484701385</v>
       </c>
       <c r="E8" t="n">
-        <v>-42.9</v>
+        <v>-27</v>
       </c>
       <c r="F8" t="n">
         <v>-74</v>
@@ -10662,7 +10662,7 @@
         <v>-133.8808371982143</v>
       </c>
       <c r="E9" t="n">
-        <v>-50.09999999999999</v>
+        <v>-38</v>
       </c>
       <c r="F9" t="n">
         <v>-85</v>
@@ -10682,7 +10682,7 @@
         <v>-150.5462625531848</v>
       </c>
       <c r="E10" t="n">
-        <v>-44.39999999999999</v>
+        <v>-31</v>
       </c>
       <c r="F10" t="n">
         <v>-87</v>
@@ -10702,7 +10702,7 @@
         <v>-167.0539450363587</v>
       </c>
       <c r="E11" t="n">
-        <v>-39.59999999999999</v>
+        <v>-28</v>
       </c>
       <c r="F11" t="n">
         <v>-98</v>
@@ -10722,7 +10722,7 @@
         <v>-189.212519793417</v>
       </c>
       <c r="E12" t="n">
-        <v>-25.7</v>
+        <v>-39</v>
       </c>
       <c r="F12" t="n">
         <v>-110.5</v>
@@ -10742,7 +10742,7 @@
         <v>-205.2895345927922</v>
       </c>
       <c r="E13" t="n">
-        <v>-27.8</v>
+        <v>-48</v>
       </c>
       <c r="F13" t="n">
         <v>-114</v>
@@ -10762,7 +10762,7 @@
         <v>-230.7329570760698</v>
       </c>
       <c r="E14" t="n">
-        <v>-25.9</v>
+        <v>-43</v>
       </c>
       <c r="F14" t="n">
         <v>-119</v>
@@ -10782,7 +10782,7 @@
         <v>-245.2277709207889</v>
       </c>
       <c r="E15" t="n">
-        <v>-28.2</v>
+        <v>-42</v>
       </c>
       <c r="F15" t="n">
         <v>-137.5</v>
@@ -10802,7 +10802,7 @@
         <v>-264.6270097926337</v>
       </c>
       <c r="E16" t="n">
-        <v>-32.5</v>
+        <v>-55</v>
       </c>
       <c r="F16" t="n">
         <v>-150</v>
@@ -10822,7 +10822,7 @@
         <v>-279.8375788189873</v>
       </c>
       <c r="E17" t="n">
-        <v>-31.7</v>
+        <v>-48</v>
       </c>
       <c r="F17" t="n">
         <v>-162.5</v>
@@ -10842,7 +10842,7 @@
         <v>-298.5024730712512</v>
       </c>
       <c r="E18" t="n">
-        <v>-32</v>
+        <v>-59</v>
       </c>
       <c r="F18" t="n">
         <v>-173.5</v>
@@ -10862,7 +10862,7 @@
         <v>-307.5141394245287</v>
       </c>
       <c r="E19" t="n">
-        <v>-18.1</v>
+        <v>-52</v>
       </c>
       <c r="F19" t="n">
         <v>-186</v>
@@ -10882,7 +10882,7 @@
         <v>-319.9360854076255</v>
       </c>
       <c r="E20" t="n">
-        <v>-16.4</v>
+        <v>-49</v>
       </c>
       <c r="F20" t="n">
         <v>-194</v>
@@ -10902,7 +10902,7 @@
         <v>-328.2801118153991</v>
       </c>
       <c r="E21" t="n">
-        <v>-24.9</v>
+        <v>-52</v>
       </c>
       <c r="F21" t="n">
         <v>-211</v>
@@ -10922,7 +10922,7 @@
         <v>-338.8920275461813</v>
       </c>
       <c r="E22" t="n">
-        <v>-37</v>
+        <v>-63</v>
       </c>
       <c r="F22" t="n">
         <v>-216</v>
@@ -10942,7 +10942,7 @@
         <v>-352.6601254612219</v>
       </c>
       <c r="E23" t="n">
-        <v>-24.2</v>
+        <v>-50</v>
       </c>
       <c r="F23" t="n">
         <v>-237.5</v>
@@ -10962,7 +10962,7 @@
         <v>-366.2739550418626</v>
       </c>
       <c r="E24" t="n">
-        <v>-24.3</v>
+        <v>-41</v>
       </c>
       <c r="F24" t="n">
         <v>-247</v>
@@ -10982,7 +10982,7 @@
         <v>-383.3210524627606</v>
       </c>
       <c r="E25" t="n">
-        <v>-19.5</v>
+        <v>-46</v>
       </c>
       <c r="F25" t="n">
         <v>-252</v>
@@ -11002,7 +11002,7 @@
         <v>-394.7762086335939</v>
       </c>
       <c r="E26" t="n">
-        <v>-19.6</v>
+        <v>-43</v>
       </c>
       <c r="F26" t="n">
         <v>-261.5</v>
@@ -11022,7 +11022,7 @@
         <v>-417.4269250095536</v>
       </c>
       <c r="E27" t="n">
-        <v>-16.8</v>
+        <v>-42</v>
       </c>
       <c r="F27" t="n">
         <v>-274</v>
@@ -11042,7 +11042,7 @@
         <v>-436.1507785741286</v>
       </c>
       <c r="E28" t="n">
-        <v>-14.9</v>
+        <v>-37</v>
       </c>
       <c r="F28" t="n">
         <v>-280.5</v>
@@ -11062,7 +11062,7 @@
         <v>-455.7312088844182</v>
       </c>
       <c r="E29" t="n">
-        <v>-17</v>
+        <v>-32</v>
       </c>
       <c r="F29" t="n">
         <v>-291.5</v>
@@ -11082,7 +11082,7 @@
         <v>-477.5472011113575</v>
       </c>
       <c r="E30" t="n">
-        <v>-16.2</v>
+        <v>-27</v>
       </c>
       <c r="F30" t="n">
         <v>-296.5</v>
@@ -11102,7 +11102,7 @@
         <v>-489.8792760620552</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.399999999999999</v>
+        <v>-30</v>
       </c>
       <c r="F31" t="n">
         <v>-306</v>
@@ -11122,7 +11122,7 @@
         <v>-501.9547796015569</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5000000000000013</v>
+        <v>-21</v>
       </c>
       <c r="F32" t="n">
         <v>-305</v>
@@ -11142,7 +11142,7 @@
         <v>-515.8602857399461</v>
       </c>
       <c r="E33" t="n">
-        <v>2.200000000000001</v>
+        <v>-28</v>
       </c>
       <c r="F33" t="n">
         <v>-310</v>
@@ -11162,7 +11162,7 @@
         <v>-536.5432742577293</v>
       </c>
       <c r="E34" t="n">
-        <v>5.9</v>
+        <v>-23</v>
       </c>
       <c r="F34" t="n">
         <v>-310.5</v>
@@ -11182,7 +11182,7 @@
         <v>-550.217182041405</v>
       </c>
       <c r="E35" t="n">
-        <v>10.9</v>
+        <v>-24</v>
       </c>
       <c r="F35" t="n">
         <v>-320</v>
@@ -11202,7 +11202,7 @@
         <v>-559.8829002815233</v>
       </c>
       <c r="E36" t="n">
-        <v>15.7</v>
+        <v>-15</v>
       </c>
       <c r="F36" t="n">
         <v>-340</v>
@@ -11222,7 +11222,7 @@
         <v>-575.2506819827523</v>
       </c>
       <c r="E37" t="n">
-        <v>22.7</v>
+        <v>-2</v>
       </c>
       <c r="F37" t="n">
         <v>-352.5</v>
@@ -11242,7 +11242,7 @@
         <v>-587.6048209649141</v>
       </c>
       <c r="E38" t="n">
-        <v>24.6</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
         <v>-374</v>
@@ -11262,7 +11262,7 @@
         <v>-603.8269943808032</v>
       </c>
       <c r="E39" t="n">
-        <v>31.4</v>
+        <v>6</v>
       </c>
       <c r="F39" t="n">
         <v>-371.5</v>
@@ -11282,7 +11282,7 @@
         <v>-613.8364840563004</v>
       </c>
       <c r="E40" t="n">
-        <v>50.2</v>
+        <v>11</v>
       </c>
       <c r="F40" t="n">
         <v>-388.5</v>
@@ -11302,7 +11302,7 @@
         <v>-628.9399918189958</v>
       </c>
       <c r="E41" t="n">
-        <v>49.2</v>
+        <v>8</v>
       </c>
       <c r="F41" t="n">
         <v>-405.5</v>
@@ -11322,7 +11322,7 @@
         <v>-642.5664036664167</v>
       </c>
       <c r="E42" t="n">
-        <v>48</v>
+        <v>-3</v>
       </c>
       <c r="F42" t="n">
         <v>-418</v>
@@ -11342,7 +11342,7 @@
         <v>-657.2825076166939</v>
       </c>
       <c r="E43" t="n">
-        <v>47.7</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>-429</v>
@@ -11362,7 +11362,7 @@
         <v>-674.6048947089264</v>
       </c>
       <c r="E44" t="n">
-        <v>52.5</v>
+        <v>5</v>
       </c>
       <c r="F44" t="n">
         <v>-435.5</v>
@@ -11382,7 +11382,7 @@
         <v>-693.0034125514825</v>
       </c>
       <c r="E45" t="n">
-        <v>56.2</v>
+        <v>6</v>
       </c>
       <c r="F45" t="n">
         <v>-433</v>
@@ -11402,7 +11402,7 @@
         <v>-706.9245891204856</v>
       </c>
       <c r="E46" t="n">
-        <v>60.1</v>
+        <v>-1</v>
       </c>
       <c r="F46" t="n">
         <v>-444</v>
@@ -11422,7 +11422,7 @@
         <v>-718.0041171135881</v>
       </c>
       <c r="E47" t="n">
-        <v>75.09999999999999</v>
+        <v>2</v>
       </c>
       <c r="F47" t="n">
         <v>-452</v>
@@ -11442,7 +11442,7 @@
         <v>-735.0134319187896</v>
       </c>
       <c r="E48" t="n">
-        <v>79.69999999999999</v>
+        <v>9</v>
       </c>
       <c r="F48" t="n">
         <v>-470.5</v>
@@ -11462,7 +11462,7 @@
         <v>-747.5283971531959</v>
       </c>
       <c r="E49" t="n">
-        <v>82.69999999999999</v>
+        <v>10</v>
       </c>
       <c r="F49" t="n">
         <v>-469.5</v>
@@ -11482,7 +11482,7 @@
         <v>-760.0977289180563</v>
       </c>
       <c r="E50" t="n">
-        <v>91.69999999999999</v>
+        <v>13</v>
       </c>
       <c r="F50" t="n">
         <v>-471.5</v>
@@ -11502,7 +11502,7 @@
         <v>-778.7081559194239</v>
       </c>
       <c r="E51" t="n">
-        <v>97.59999999999999</v>
+        <v>20</v>
       </c>
       <c r="F51" t="n">
         <v>-481</v>
@@ -11522,7 +11522,7 @@
         <v>-798.6911401253403</v>
       </c>
       <c r="E52" t="n">
-        <v>104.4</v>
+        <v>31</v>
       </c>
       <c r="F52" t="n">
         <v>-499.5</v>
@@ -11542,7 +11542,7 @@
         <v>-805.3641238440582</v>
       </c>
       <c r="E53" t="n">
-        <v>102.1</v>
+        <v>42</v>
       </c>
       <c r="F53" t="n">
         <v>-507.5</v>
@@ -11562,7 +11562,7 @@
         <v>-820.7205041230472</v>
       </c>
       <c r="E54" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="F54" t="n">
         <v>-518.5</v>
@@ -11582,7 +11582,7 @@
         <v>-835.9177959287388</v>
       </c>
       <c r="E55" t="n">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="F55" t="n">
         <v>-523.5</v>
@@ -11602,7 +11602,7 @@
         <v>-850.4373099631781</v>
       </c>
       <c r="E56" t="n">
-        <v>98.90000000000001</v>
+        <v>61</v>
       </c>
       <c r="F56" t="n">
         <v>-537.5</v>
@@ -11622,7 +11622,7 @@
         <v>-866.8288195547257</v>
       </c>
       <c r="E57" t="n">
-        <v>103.9</v>
+        <v>66</v>
       </c>
       <c r="F57" t="n">
         <v>-547</v>
@@ -11642,7 +11642,7 @@
         <v>-883.5564204956526</v>
       </c>
       <c r="E58" t="n">
-        <v>96.90000000000001</v>
+        <v>57</v>
       </c>
       <c r="F58" t="n">
         <v>-556.5</v>
@@ -11662,7 +11662,7 @@
         <v>-895.3369224098763</v>
       </c>
       <c r="E59" t="n">
-        <v>114.8</v>
+        <v>60</v>
       </c>
       <c r="F59" t="n">
         <v>-566</v>
@@ -11682,7 +11682,7 @@
         <v>-908.5059506742909</v>
       </c>
       <c r="E60" t="n">
-        <v>128.5</v>
+        <v>51</v>
       </c>
       <c r="F60" t="n">
         <v>-566.5</v>
@@ -11702,7 +11702,7 @@
         <v>-927.0501466228407</v>
       </c>
       <c r="E61" t="n">
-        <v>129.3</v>
+        <v>54</v>
       </c>
       <c r="F61" t="n">
         <v>-577.5</v>
@@ -11722,7 +11722,7 @@
         <v>-935.8577913488716</v>
       </c>
       <c r="E62" t="n">
-        <v>132.1</v>
+        <v>59</v>
       </c>
       <c r="F62" t="n">
         <v>-588.5</v>
@@ -11742,7 +11742,7 @@
         <v>-950.1468829227587</v>
       </c>
       <c r="E63" t="n">
-        <v>133.1</v>
+        <v>60</v>
       </c>
       <c r="F63" t="n">
         <v>-596.5</v>
@@ -11762,7 +11762,7 @@
         <v>-966.0098962422049</v>
       </c>
       <c r="E64" t="n">
-        <v>145</v>
+        <v>73</v>
       </c>
       <c r="F64" t="n">
         <v>-606</v>
@@ -11782,7 +11782,7 @@
         <v>-982.5606090756528</v>
       </c>
       <c r="E65" t="n">
-        <v>154.9</v>
+        <v>70</v>
       </c>
       <c r="F65" t="n">
         <v>-606.5</v>
@@ -11802,7 +11802,7 @@
         <v>-1000.494218813128</v>
       </c>
       <c r="E66" t="n">
-        <v>160.8</v>
+        <v>73</v>
       </c>
       <c r="F66" t="n">
         <v>-623.5</v>
@@ -11822,7 +11822,7 @@
         <v>-1012.462468159054</v>
       </c>
       <c r="E67" t="n">
-        <v>170.7</v>
+        <v>68</v>
       </c>
       <c r="F67" t="n">
         <v>-627</v>
@@ -11842,7 +11842,7 @@
         <v>-1024.045526353905</v>
       </c>
       <c r="E68" t="n">
-        <v>174.6000000000001</v>
+        <v>77</v>
       </c>
       <c r="F68" t="n">
         <v>-633.5</v>
@@ -11862,7 +11862,7 @@
         <v>-1041.013235783177</v>
       </c>
       <c r="E69" t="n">
-        <v>177.4000000000001</v>
+        <v>66</v>
       </c>
       <c r="F69" t="n">
         <v>-638.5</v>
@@ -11882,7 +11882,7 @@
         <v>-1054.719176802048</v>
       </c>
       <c r="E70" t="n">
-        <v>181.3000000000001</v>
+        <v>69</v>
       </c>
       <c r="F70" t="n">
         <v>-649.5</v>
@@ -11902,7 +11902,7 @@
         <v>-1068.07901220902</v>
       </c>
       <c r="E71" t="n">
-        <v>182.3000000000001</v>
+        <v>68</v>
       </c>
       <c r="F71" t="n">
         <v>-660.5</v>
@@ -11922,7 +11922,7 @@
         <v>-1081.818466409129</v>
       </c>
       <c r="E72" t="n">
-        <v>189.1000000000001</v>
+        <v>77</v>
       </c>
       <c r="F72" t="n">
         <v>-670</v>
@@ -11942,7 +11942,7 @@
         <v>-1103.250619143852</v>
       </c>
       <c r="E73" t="n">
-        <v>198.8000000000001</v>
+        <v>88</v>
       </c>
       <c r="F73" t="n">
         <v>-684</v>
@@ -11962,7 +11962,7 @@
         <v>-1123.180885649056</v>
       </c>
       <c r="E74" t="n">
-        <v>205.8000000000001</v>
+        <v>93</v>
       </c>
       <c r="F74" t="n">
         <v>-690.5</v>
@@ -11982,7 +11982,7 @@
         <v>-1136.814620548772</v>
       </c>
       <c r="E75" t="n">
-        <v>209.5000000000001</v>
+        <v>98</v>
       </c>
       <c r="F75" t="n">
         <v>-700</v>
@@ -12002,7 +12002,7 @@
         <v>-1151.523557592819</v>
       </c>
       <c r="E76" t="n">
-        <v>213.2</v>
+        <v>103</v>
       </c>
       <c r="F76" t="n">
         <v>-697.5</v>
@@ -12022,7 +12022,7 @@
         <v>-1171.93482431065</v>
       </c>
       <c r="E77" t="n">
-        <v>207.1000000000001</v>
+        <v>98</v>
       </c>
       <c r="F77" t="n">
         <v>-699.5</v>
@@ -12042,7 +12042,7 @@
         <v>-1180.233492645022</v>
       </c>
       <c r="E78" t="n">
-        <v>204.6000000000001</v>
+        <v>113</v>
       </c>
       <c r="F78" t="n">
         <v>-709</v>
@@ -12062,7 +12062,7 @@
         <v>-1191.327638431329</v>
       </c>
       <c r="E79" t="n">
-        <v>212.3</v>
+        <v>116</v>
       </c>
       <c r="F79" t="n">
         <v>-712.5</v>
@@ -12082,7 +12082,7 @@
         <v>-1206.097203893596</v>
       </c>
       <c r="E80" t="n">
-        <v>207.3</v>
+        <v>133</v>
       </c>
       <c r="F80" t="n">
         <v>-717.5</v>
@@ -12102,7 +12102,7 @@
         <v>-1220.208347224213</v>
       </c>
       <c r="E81" t="n">
-        <v>214.1000000000001</v>
+        <v>148</v>
       </c>
       <c r="F81" t="n">
         <v>-728.5</v>
@@ -12122,7 +12122,7 @@
         <v>-1237.573679426804</v>
       </c>
       <c r="E82" t="n">
-        <v>222.0000000000001</v>
+        <v>151</v>
       </c>
       <c r="F82" t="n">
         <v>-738</v>
@@ -12142,7 +12142,7 @@
         <v>-1251.869052093277</v>
       </c>
       <c r="E83" t="n">
-        <v>231.5000000000001</v>
+        <v>158</v>
       </c>
       <c r="F83" t="n">
         <v>-749</v>
@@ -12162,7 +12162,7 @@
         <v>-1267.395784348558</v>
       </c>
       <c r="E84" t="n">
-        <v>237.4000000000001</v>
+        <v>161</v>
       </c>
       <c r="F84" t="n">
         <v>-751</v>
@@ -12182,7 +12182,7 @@
         <v>-1278.011965553342</v>
       </c>
       <c r="E85" t="n">
-        <v>241.3000000000001</v>
+        <v>170</v>
       </c>
       <c r="F85" t="n">
         <v>-757.5</v>
@@ -12202,7 +12202,7 @@
         <v>-1287.570418652612</v>
       </c>
       <c r="E86" t="n">
-        <v>248.3000000000001</v>
+        <v>185</v>
       </c>
       <c r="F86" t="n">
         <v>-761</v>
@@ -12222,7 +12222,7 @@
         <v>-1299.526201251086</v>
       </c>
       <c r="E87" t="n">
-        <v>242.0000000000001</v>
+        <v>192</v>
       </c>
       <c r="F87" t="n">
         <v>-763</v>
@@ -12242,7 +12242,7 @@
         <v>-1314.065122399267</v>
       </c>
       <c r="E88" t="n">
-        <v>259.0000000000001</v>
+        <v>203</v>
       </c>
       <c r="F88" t="n">
         <v>-763.5</v>
@@ -12262,7 +12262,7 @@
         <v>-1329.050799518251</v>
       </c>
       <c r="E89" t="n">
-        <v>268.0000000000001</v>
+        <v>212</v>
       </c>
       <c r="F89" t="n">
         <v>-765.5</v>
@@ -12282,7 +12282,7 @@
         <v>-1337.677785584419</v>
       </c>
       <c r="E90" t="n">
-        <v>285.7</v>
+        <v>221</v>
       </c>
       <c r="F90" t="n">
         <v>-775</v>
@@ -12302,7 +12302,7 @@
         <v>-1352.098940434634</v>
       </c>
       <c r="E91" t="n">
-        <v>281.6</v>
+        <v>224</v>
       </c>
       <c r="F91" t="n">
         <v>-777</v>
@@ -12322,7 +12322,7 @@
         <v>-1366.918579507137</v>
       </c>
       <c r="E92" t="n">
-        <v>281.5</v>
+        <v>223</v>
       </c>
       <c r="F92" t="n">
         <v>-785</v>
@@ -12342,7 +12342,7 @@
         <v>-1385.193038380315</v>
       </c>
       <c r="E93" t="n">
-        <v>292.3</v>
+        <v>234</v>
       </c>
       <c r="F93" t="n">
         <v>-785.5</v>
@@ -12362,7 +12362,7 @@
         <v>-1399.204528446038</v>
       </c>
       <c r="E94" t="n">
-        <v>295.6</v>
+        <v>241</v>
       </c>
       <c r="F94" t="n">
         <v>-787.5</v>
@@ -12382,7 +12382,7 @@
         <v>-1410.970912301405</v>
       </c>
       <c r="E95" t="n">
-        <v>311.5</v>
+        <v>252</v>
       </c>
       <c r="F95" t="n">
         <v>-792.5</v>
@@ -12402,7 +12402,7 @@
         <v>-1420.384268417089</v>
       </c>
       <c r="E96" t="n">
-        <v>326.3</v>
+        <v>267</v>
       </c>
       <c r="F96" t="n">
         <v>-797.5</v>
@@ -12422,7 +12422,7 @@
         <v>-1434.670124181723</v>
       </c>
       <c r="E97" t="n">
-        <v>329.3</v>
+        <v>270</v>
       </c>
       <c r="F97" t="n">
         <v>-795</v>
@@ -12442,7 +12442,7 @@
         <v>-1446.523618279234</v>
       </c>
       <c r="E98" t="n">
-        <v>336.1</v>
+        <v>277</v>
       </c>
       <c r="F98" t="n">
         <v>-798.5</v>
@@ -12462,7 +12462,7 @@
         <v>-1461.763908595752</v>
       </c>
       <c r="E99" t="n">
-        <v>340</v>
+        <v>292</v>
       </c>
       <c r="F99" t="n">
         <v>-803.5</v>
@@ -12482,7 +12482,7 @@
         <v>-1477.782634156046</v>
       </c>
       <c r="E100" t="n">
-        <v>351.9</v>
+        <v>299</v>
       </c>
       <c r="F100" t="n">
         <v>-805.5</v>
@@ -12502,7 +12502,7 @@
         <v>-1489.092425757653</v>
       </c>
       <c r="E101" t="n">
-        <v>370.9</v>
+        <v>316</v>
       </c>
       <c r="F101" t="n">
         <v>-804.5</v>
@@ -12522,7 +12522,7 @@
         <v>-1504.307082340612</v>
       </c>
       <c r="E102" t="n">
-        <v>375.9</v>
+        <v>325</v>
       </c>
       <c r="F102" t="n">
         <v>-814</v>
@@ -12542,7 +12542,7 @@
         <v>-1516.219173939061</v>
       </c>
       <c r="E103" t="n">
-        <v>391.6</v>
+        <v>338</v>
       </c>
       <c r="F103" t="n">
         <v>-813</v>
@@ -12562,7 +12562,7 @@
         <v>-1534.691509182445</v>
       </c>
       <c r="E104" t="n">
-        <v>405.3</v>
+        <v>353</v>
       </c>
       <c r="F104" t="n">
         <v>-824</v>
@@ -12582,7 +12582,7 @@
         <v>-1550.688348165737</v>
       </c>
       <c r="E105" t="n">
-        <v>428.9999999999999</v>
+        <v>374</v>
       </c>
       <c r="F105" t="n">
         <v>-820</v>
@@ -12602,7 +12602,7 @@
         <v>-1562.472326444135</v>
       </c>
       <c r="E106" t="n">
-        <v>437.8</v>
+        <v>379</v>
       </c>
       <c r="F106" t="n">
         <v>-832.5</v>
@@ -12622,7 +12622,7 @@
         <v>-1576.572274511352</v>
       </c>
       <c r="E107" t="n">
-        <v>436.8</v>
+        <v>382</v>
       </c>
       <c r="F107" t="n">
         <v>-846.5</v>
@@ -12642,7 +12642,7 @@
         <v>-1589.687552488782</v>
       </c>
       <c r="E108" t="n">
-        <v>423.6</v>
+        <v>403</v>
       </c>
       <c r="F108" t="n">
         <v>-856</v>
@@ -12662,7 +12662,7 @@
         <v>-1599.893290035628</v>
       </c>
       <c r="E109" t="n">
-        <v>424.2</v>
+        <v>416</v>
       </c>
       <c r="F109" t="n">
         <v>-867</v>
@@ -12682,7 +12682,7 @@
         <v>-1612.212871076709</v>
       </c>
       <c r="E110" t="n">
-        <v>429.2</v>
+        <v>437</v>
       </c>
       <c r="F110" t="n">
         <v>-872</v>
@@ -12702,7 +12702,7 @@
         <v>-1618.272824779593</v>
       </c>
       <c r="E111" t="n">
-        <v>428.9</v>
+        <v>448</v>
       </c>
       <c r="F111" t="n">
         <v>-872.5</v>
@@ -12722,7 +12722,7 @@
         <v>-1631.348866613447</v>
       </c>
       <c r="E112" t="n">
-        <v>436.8</v>
+        <v>459</v>
       </c>
       <c r="F112" t="n">
         <v>-871.5</v>
@@ -12742,7 +12742,7 @@
         <v>-1643.354522291633</v>
       </c>
       <c r="E113" t="n">
-        <v>448.6999999999999</v>
+        <v>472</v>
       </c>
       <c r="F113" t="n">
         <v>-878</v>
@@ -12762,7 +12762,7 @@
         <v>-1661.590391013445</v>
       </c>
       <c r="E114" t="n">
-        <v>456.5999999999999</v>
+        <v>481</v>
       </c>
       <c r="F114" t="n">
         <v>-880</v>
@@ -12782,7 +12782,7 @@
         <v>-1677.827127373567</v>
       </c>
       <c r="E115" t="n">
-        <v>452.4999999999999</v>
+        <v>494</v>
       </c>
       <c r="F115" t="n">
         <v>-880.5</v>
@@ -12802,7 +12802,7 @@
         <v>-1686.965172815426</v>
       </c>
       <c r="E116" t="n">
-        <v>457.2999999999999</v>
+        <v>499</v>
       </c>
       <c r="F116" t="n">
         <v>-887</v>
@@ -12822,7 +12822,7 @@
         <v>-1695.700793584888</v>
       </c>
       <c r="E117" t="n">
-        <v>459.1999999999999</v>
+        <v>508</v>
       </c>
       <c r="F117" t="n">
         <v>-886</v>
@@ -12842,7 +12842,7 @@
         <v>-1698.97678205171</v>
       </c>
       <c r="E118" t="n">
-        <v>467.0999999999999</v>
+        <v>519</v>
       </c>
       <c r="F118" t="n">
         <v>-888</v>
@@ -12862,7 +12862,7 @@
         <v>-1720.444084015615</v>
       </c>
       <c r="E119" t="n">
-        <v>476.0999999999999</v>
+        <v>526</v>
       </c>
       <c r="F119" t="n">
         <v>-896</v>
@@ -12882,7 +12882,7 @@
         <v>-1729.750109109444</v>
       </c>
       <c r="E120" t="n">
-        <v>484.8999999999999</v>
+        <v>537</v>
       </c>
       <c r="F120" t="n">
         <v>-898</v>
@@ -12902,7 +12902,7 @@
         <v>-1745.206623423088</v>
       </c>
       <c r="E121" t="n">
-        <v>494.7999999999998</v>
+        <v>556</v>
       </c>
       <c r="F121" t="n">
         <v>-900</v>
@@ -12922,7 +12922,7 @@
         <v>-1751.864774908571</v>
       </c>
       <c r="E122" t="n">
-        <v>509.7999999999998</v>
+        <v>565</v>
       </c>
       <c r="F122" t="n">
         <v>-908</v>
@@ -12942,7 +12942,7 @@
         <v>-1758.801318606907</v>
       </c>
       <c r="E123" t="n">
-        <v>527.6999999999998</v>
+        <v>564</v>
       </c>
       <c r="F123" t="n">
         <v>-907</v>
@@ -12962,7 +12962,7 @@
         <v>-1770.183742805132</v>
       </c>
       <c r="E124" t="n">
-        <v>548.6999999999998</v>
+        <v>573</v>
       </c>
       <c r="F124" t="n">
         <v>-913.5</v>
@@ -12982,7 +12982,7 @@
         <v>-1785.283929652888</v>
       </c>
       <c r="E125" t="n">
-        <v>569.6999999999998</v>
+        <v>580</v>
       </c>
       <c r="F125" t="n">
         <v>-917</v>
@@ -13002,7 +13002,7 @@
         <v>-1799.563817401932</v>
       </c>
       <c r="E126" t="n">
-        <v>591.3999999999999</v>
+        <v>589</v>
       </c>
       <c r="F126" t="n">
         <v>-922</v>
@@ -13022,7 +13022,7 @@
         <v>-1805.898466356333</v>
       </c>
       <c r="E127" t="n">
-        <v>593.9999999999999</v>
+        <v>604</v>
       </c>
       <c r="F127" t="n">
         <v>-934.5</v>
@@ -13042,7 +13042,7 @@
         <v>-1819.446042033068</v>
       </c>
       <c r="E128" t="n">
-        <v>594.9999999999999</v>
+        <v>607</v>
       </c>
       <c r="F128" t="n">
         <v>-941</v>
@@ -13062,7 +13062,7 @@
         <v>-1831.110814707646</v>
       </c>
       <c r="E129" t="n">
-        <v>606.8999999999999</v>
+        <v>606</v>
       </c>
       <c r="F129" t="n">
         <v>-944.5</v>
@@ -13082,7 +13082,7 @@
         <v>-1845.815355441028</v>
       </c>
       <c r="E130" t="n">
-        <v>629.8999999999999</v>
+        <v>631</v>
       </c>
       <c r="F130" t="n">
         <v>-943.5</v>
@@ -13102,7 +13102,7 @@
         <v>-1857.113000725558</v>
       </c>
       <c r="E131" t="n">
-        <v>655.7999999999998</v>
+        <v>656</v>
       </c>
       <c r="F131" t="n">
         <v>-948.5</v>
@@ -13122,7 +13122,7 @@
         <v>-1866.205734872303</v>
       </c>
       <c r="E132" t="n">
-        <v>657.6999999999998</v>
+        <v>679</v>
       </c>
       <c r="F132" t="n">
         <v>-947.5</v>
@@ -13142,7 +13142,7 @@
         <v>-1874.159042092825</v>
       </c>
       <c r="E133" t="n">
-        <v>673.1999999999998</v>
+        <v>694</v>
       </c>
       <c r="F133" t="n">
         <v>-952.5</v>
@@ -13162,7 +13162,7 @@
         <v>-1882.788661167084</v>
       </c>
       <c r="E134" t="n">
-        <v>677.0999999999998</v>
+        <v>703</v>
       </c>
       <c r="F134" t="n">
         <v>-959</v>
@@ -13182,7 +13182,7 @@
         <v>-1895.243592678685</v>
       </c>
       <c r="E135" t="n">
-        <v>676.9999999999998</v>
+        <v>704</v>
       </c>
       <c r="F135" t="n">
         <v>-953.5</v>
@@ -13202,7 +13202,7 @@
         <v>-1910.595378070932</v>
       </c>
       <c r="E136" t="n">
-        <v>694.8999999999997</v>
+        <v>723</v>
       </c>
       <c r="F136" t="n">
         <v>-957</v>
@@ -13222,7 +13222,7 @@
         <v>-1925.02295457638</v>
       </c>
       <c r="E137" t="n">
-        <v>713.4999999999998</v>
+        <v>746</v>
       </c>
       <c r="F137" t="n">
         <v>-968</v>
@@ -13242,7 +13242,7 @@
         <v>-1938.806507733841</v>
       </c>
       <c r="E138" t="n">
-        <v>718.4999999999998</v>
+        <v>757</v>
       </c>
       <c r="F138" t="n">
         <v>-973</v>
@@ -13262,7 +13262,7 @@
         <v>-1949.96967327652</v>
       </c>
       <c r="E139" t="n">
-        <v>733.2999999999997</v>
+        <v>762</v>
       </c>
       <c r="F139" t="n">
         <v>-973.5</v>
@@ -13282,7 +13282,7 @@
         <v>-1965.691931070204</v>
       </c>
       <c r="E140" t="n">
-        <v>754.0999999999997</v>
+        <v>771</v>
       </c>
       <c r="F140" t="n">
         <v>-972.5</v>
@@ -13302,7 +13302,7 @@
         <v>-1984.492498247861</v>
       </c>
       <c r="E141" t="n">
-        <v>760.8999999999996</v>
+        <v>782</v>
       </c>
       <c r="F141" t="n">
         <v>-967</v>
@@ -13322,7 +13322,7 @@
         <v>-1997.247971836185</v>
       </c>
       <c r="E142" t="n">
-        <v>760.7999999999996</v>
+        <v>805</v>
       </c>
       <c r="F142" t="n">
         <v>-969</v>
@@ -13342,7 +13342,7 @@
         <v>-2010.298146606739</v>
       </c>
       <c r="E143" t="n">
-        <v>763.5999999999996</v>
+        <v>810</v>
       </c>
       <c r="F143" t="n">
         <v>-966.5</v>
@@ -13362,7 +13362,7 @@
         <v>-2019.790931945562</v>
       </c>
       <c r="E144" t="n">
-        <v>780.5999999999996</v>
+        <v>817</v>
       </c>
       <c r="F144" t="n">
         <v>-961</v>
@@ -13382,7 +13382,7 @@
         <v>-2032.615442019713</v>
       </c>
       <c r="E145" t="n">
-        <v>785.3999999999995</v>
+        <v>824</v>
       </c>
       <c r="F145" t="n">
         <v>-963</v>
@@ -13402,7 +13402,7 @@
         <v>-2047.873784696341</v>
       </c>
       <c r="E146" t="n">
-        <v>798.8999999999995</v>
+        <v>823</v>
       </c>
       <c r="F146" t="n">
         <v>-968</v>
@@ -13422,7 +13422,7 @@
         <v>-2056.809945490018</v>
       </c>
       <c r="E147" t="n">
-        <v>803.2999999999995</v>
+        <v>836</v>
       </c>
       <c r="F147" t="n">
         <v>-973</v>
@@ -13442,7 +13442,7 @@
         <v>-2068.825393911767</v>
       </c>
       <c r="E148" t="n">
-        <v>816.0999999999995</v>
+        <v>851</v>
       </c>
       <c r="F148" t="n">
         <v>-976.5</v>
@@ -13462,7 +13462,7 @@
         <v>-2078.801494594511</v>
       </c>
       <c r="E149" t="n">
-        <v>829.9999999999994</v>
+        <v>866</v>
       </c>
       <c r="F149" t="n">
         <v>-974</v>
@@ -13482,7 +13482,7 @@
         <v>-2087.874340133747</v>
       </c>
       <c r="E150" t="n">
-        <v>848.7999999999994</v>
+        <v>877</v>
       </c>
       <c r="F150" t="n">
         <v>-974.5</v>
@@ -13502,7 +13502,7 @@
         <v>-2096.924783918511</v>
       </c>
       <c r="E151" t="n">
-        <v>869.3999999999994</v>
+        <v>906</v>
       </c>
       <c r="F151" t="n">
         <v>-972</v>
@@ -13522,7 +13522,7 @@
         <v>-2106.117775276539</v>
       </c>
       <c r="E152" t="n">
-        <v>876.1999999999994</v>
+        <v>915</v>
       </c>
       <c r="F152" t="n">
         <v>-978.5</v>
@@ -13542,7 +13542,7 @@
         <v>-2117.604001847971</v>
       </c>
       <c r="E153" t="n">
-        <v>881.1999999999994</v>
+        <v>924</v>
       </c>
       <c r="F153" t="n">
         <v>-983.5</v>
@@ -13562,7 +13562,7 @@
         <v>-2129.936928100617</v>
       </c>
       <c r="E154" t="n">
-        <v>891.9999999999993</v>
+        <v>933</v>
       </c>
       <c r="F154" t="n">
         <v>-988.5</v>
@@ -13582,7 +13582,7 @@
         <v>-2138.686010219796</v>
       </c>
       <c r="E155" t="n">
-        <v>901.8999999999993</v>
+        <v>948</v>
       </c>
       <c r="F155" t="n">
         <v>-995</v>
@@ -13602,7 +13602,7 @@
         <v>-2147.600459655876</v>
       </c>
       <c r="E156" t="n">
-        <v>917.7999999999993</v>
+        <v>973</v>
       </c>
       <c r="F156" t="n">
         <v>-998.5</v>
@@ -13622,7 +13622,7 @@
         <v>-2150.779023094192</v>
       </c>
       <c r="E157" t="n">
-        <v>927.4999999999993</v>
+        <v>1002</v>
       </c>
       <c r="F157" t="n">
         <v>-996</v>
@@ -13642,7 +13642,7 @@
         <v>-2162.07416450086</v>
       </c>
       <c r="E158" t="n">
-        <v>940.2999999999993</v>
+        <v>1023</v>
       </c>
       <c r="F158" t="n">
         <v>-992</v>
@@ -13662,7 +13662,7 @@
         <v>-2178.756507817282</v>
       </c>
       <c r="E159" t="n">
-        <v>944.1999999999992</v>
+        <v>1024</v>
       </c>
       <c r="F159" t="n">
         <v>-986.5</v>
@@ -13682,7 +13682,7 @@
         <v>-2196.084458553467</v>
       </c>
       <c r="E160" t="n">
-        <v>962.0999999999992</v>
+        <v>1043</v>
       </c>
       <c r="F160" t="n">
         <v>-984</v>
@@ -13702,7 +13702,7 @@
         <v>-2207.5746681574</v>
       </c>
       <c r="E161" t="n">
-        <v>966.8999999999992</v>
+        <v>1052</v>
       </c>
       <c r="F161" t="n">
         <v>-980</v>
@@ -13722,7 +13722,7 @@
         <v>-2209.47060294401</v>
       </c>
       <c r="E162" t="n">
-        <v>972.5999999999992</v>
+        <v>1059</v>
       </c>
       <c r="F162" t="n">
         <v>-985</v>
@@ -13742,7 +13742,7 @@
         <v>-2221.073888044925</v>
       </c>
       <c r="E163" t="n">
-        <v>978.4999999999992</v>
+        <v>1072</v>
       </c>
       <c r="F163" t="n">
         <v>-994.5</v>
@@ -13762,7 +13762,7 @@
         <v>-2225.946550031122</v>
       </c>
       <c r="E164" t="n">
-        <v>992.1999999999992</v>
+        <v>1095</v>
       </c>
       <c r="F164" t="n">
         <v>-1001</v>
@@ -13782,7 +13782,7 @@
         <v>-2242.482180021908</v>
       </c>
       <c r="E165" t="n">
-        <v>1016.099999999999</v>
+        <v>1120</v>
       </c>
       <c r="F165" t="n">
         <v>-1001.5</v>
@@ -13802,7 +13802,7 @@
         <v>-2253.261915588274</v>
       </c>
       <c r="E166" t="n">
-        <v>1024.899999999999</v>
+        <v>1129</v>
       </c>
       <c r="F166" t="n">
         <v>-1000.5</v>
@@ -13822,7 +13822,7 @@
         <v>-2260.703754628397</v>
       </c>
       <c r="E167" t="n">
-        <v>1036.799999999999</v>
+        <v>1156</v>
       </c>
       <c r="F167" t="n">
         <v>-998</v>
@@ -13842,7 +13842,7 @@
         <v>-2269.243971451855</v>
       </c>
       <c r="E168" t="n">
-        <v>1051.799999999999</v>
+        <v>1169</v>
       </c>
       <c r="F168" t="n">
         <v>-997</v>
@@ -13862,7 +13862,7 @@
         <v>-2282.60521241121</v>
       </c>
       <c r="E169" t="n">
-        <v>1064.799999999999</v>
+        <v>1180</v>
       </c>
       <c r="F169" t="n">
         <v>-1003.5</v>
@@ -13882,7 +13882,7 @@
         <v>-2290.546784411468</v>
       </c>
       <c r="E170" t="n">
-        <v>1078.699999999999</v>
+        <v>1197</v>
       </c>
       <c r="F170" t="n">
         <v>-996.5</v>
@@ -13902,7 +13902,7 @@
         <v>-2302.78937896035</v>
       </c>
       <c r="E171" t="n">
-        <v>1099.499999999999</v>
+        <v>1204</v>
       </c>
       <c r="F171" t="n">
         <v>-994</v>
@@ -13922,7 +13922,7 @@
         <v>-2312.367113941488</v>
       </c>
       <c r="E172" t="n">
-        <v>1113.199999999999</v>
+        <v>1225</v>
       </c>
       <c r="F172" t="n">
         <v>-991.5</v>
@@ -13942,7 +13942,7 @@
         <v>-2329.322048831982</v>
       </c>
       <c r="E173" t="n">
-        <v>1129.999999999999</v>
+        <v>1240</v>
       </c>
       <c r="F173" t="n">
         <v>-998</v>
@@ -13962,7 +13962,7 @@
         <v>-2337.278657686479</v>
       </c>
       <c r="E174" t="n">
-        <v>1151.499999999999</v>
+        <v>1257</v>
       </c>
       <c r="F174" t="n">
         <v>-1001.5</v>
@@ -13982,7 +13982,7 @@
         <v>-2344.219427234649</v>
       </c>
       <c r="E175" t="n">
-        <v>1164.499999999999</v>
+        <v>1270</v>
       </c>
       <c r="F175" t="n">
         <v>-997.5</v>
@@ -14002,7 +14002,7 @@
         <v>-2352.668160000351</v>
       </c>
       <c r="E176" t="n">
-        <v>1190.399999999999</v>
+        <v>1283</v>
       </c>
       <c r="F176" t="n">
         <v>-990.5</v>
@@ -14022,7 +14022,7 @@
         <v>-2364.398256394271</v>
       </c>
       <c r="E177" t="n">
-        <v>1206.299999999999</v>
+        <v>1314</v>
       </c>
       <c r="F177" t="n">
         <v>-986.5</v>
@@ -14042,7 +14042,7 @@
         <v>-2381.171008859988</v>
       </c>
       <c r="E178" t="n">
-        <v>1216.2</v>
+        <v>1325</v>
       </c>
       <c r="F178" t="n">
         <v>-979.5</v>
@@ -14062,7 +14062,7 @@
         <v>-2388.443134213902</v>
       </c>
       <c r="E179" t="n">
-        <v>1232.1</v>
+        <v>1336</v>
       </c>
       <c r="F179" t="n">
         <v>-980</v>
@@ -14082,7 +14082,7 @@
         <v>-2404.758234394666</v>
       </c>
       <c r="E180" t="n">
-        <v>1244</v>
+        <v>1349</v>
       </c>
       <c r="F180" t="n">
         <v>-982</v>
@@ -14102,7 +14102,7 @@
         <v>-2417.50570848869</v>
       </c>
       <c r="E181" t="n">
-        <v>1265</v>
+        <v>1372</v>
       </c>
       <c r="F181" t="n">
         <v>-976.5</v>
@@ -14122,7 +14122,7 @@
         <v>-2431.065512662162</v>
       </c>
       <c r="E182" t="n">
-        <v>1286</v>
+        <v>1401</v>
       </c>
       <c r="F182" t="n">
         <v>-968</v>
@@ -14142,7 +14142,7 @@
         <v>-2444.340417690171</v>
       </c>
       <c r="E183" t="n">
-        <v>1307.9</v>
+        <v>1424</v>
       </c>
       <c r="F183" t="n">
         <v>-961</v>
@@ -14162,7 +14162,7 @@
         <v>-2457.085264844857</v>
       </c>
       <c r="E184" t="n">
-        <v>1321.6</v>
+        <v>1441</v>
       </c>
       <c r="F184" t="n">
         <v>-954</v>
@@ -14182,7 +14182,7 @@
         <v>-2469.433763565302</v>
       </c>
       <c r="E185" t="n">
-        <v>1344.6</v>
+        <v>1458</v>
       </c>
       <c r="F185" t="n">
         <v>-954.5</v>
@@ -14202,7 +14202,7 @@
         <v>-2477.966487498356</v>
       </c>
       <c r="E186" t="n">
-        <v>1365.6</v>
+        <v>1475</v>
       </c>
       <c r="F186" t="n">
         <v>-955</v>
@@ -14222,7 +14222,7 @@
         <v>-2485.54177520868</v>
       </c>
       <c r="E187" t="n">
-        <v>1377.8</v>
+        <v>1496</v>
       </c>
       <c r="F187" t="n">
         <v>-963</v>
@@ -14242,7 +14242,7 @@
         <v>-2497.405559388458</v>
       </c>
       <c r="E188" t="n">
-        <v>1394.8</v>
+        <v>1511</v>
       </c>
       <c r="F188" t="n">
         <v>-957.5</v>
@@ -14262,7 +14262,7 @@
         <v>-2510.096816718186</v>
       </c>
       <c r="E189" t="n">
-        <v>1397.8</v>
+        <v>1534</v>
       </c>
       <c r="F189" t="n">
         <v>-953.5</v>
@@ -14282,7 +14282,7 @@
         <v>-2517.243107868213</v>
       </c>
       <c r="E190" t="n">
-        <v>1416.6</v>
+        <v>1551</v>
       </c>
       <c r="F190" t="n">
         <v>-949.5</v>
@@ -14302,7 +14302,7 @@
         <v>-2527.973450327915</v>
       </c>
       <c r="E191" t="n">
-        <v>1439.6</v>
+        <v>1564</v>
       </c>
       <c r="F191" t="n">
         <v>-957.5</v>
@@ -14322,7 +14322,7 @@
         <v>-2546.761749827214</v>
       </c>
       <c r="E192" t="n">
-        <v>1456.2</v>
+        <v>1583</v>
       </c>
       <c r="F192" t="n">
         <v>-953.5</v>
@@ -14342,7 +14342,7 @@
         <v>-2565.831640847767</v>
       </c>
       <c r="E193" t="n">
-        <v>1476.1</v>
+        <v>1602</v>
       </c>
       <c r="F193" t="n">
         <v>-945</v>
@@ -14362,7 +14362,7 @@
         <v>-2570.874236079898</v>
       </c>
       <c r="E194" t="n">
-        <v>1486.9</v>
+        <v>1613</v>
       </c>
       <c r="F194" t="n">
         <v>-945.5</v>
@@ -14382,7 +14382,7 @@
         <v>-2578.180961856345</v>
       </c>
       <c r="E195" t="n">
-        <v>1494.6</v>
+        <v>1620</v>
       </c>
       <c r="F195" t="n">
         <v>-947.5</v>
@@ -14402,7 +14402,7 @@
         <v>-2589.477894731786</v>
       </c>
       <c r="E196" t="n">
-        <v>1491.6</v>
+        <v>1627</v>
       </c>
       <c r="F196" t="n">
         <v>-948</v>
@@ -14422,7 +14422,7 @@
         <v>-2600.281980860163</v>
       </c>
       <c r="E197" t="n">
-        <v>1509.1</v>
+        <v>1642</v>
       </c>
       <c r="F197" t="n">
         <v>-953</v>
@@ -14442,7 +14442,7 @@
         <v>-2611.169579037502</v>
       </c>
       <c r="E198" t="n">
-        <v>1527</v>
+        <v>1665</v>
       </c>
       <c r="F198" t="n">
         <v>-953.5</v>
@@ -14462,7 +14462,7 @@
         <v>-2624.76389306925</v>
       </c>
       <c r="E199" t="n">
-        <v>1545.8</v>
+        <v>1686</v>
       </c>
       <c r="F199" t="n">
         <v>-945</v>
@@ -14482,7 +14482,7 @@
         <v>-2641.498040599619</v>
       </c>
       <c r="E200" t="n">
-        <v>1570.8</v>
+        <v>1701</v>
       </c>
       <c r="F200" t="n">
         <v>-942.5</v>
@@ -14502,7 +14502,7 @@
         <v>-2653.668699454901</v>
       </c>
       <c r="E201" t="n">
-        <v>1584.7</v>
+        <v>1708</v>
       </c>
       <c r="F201" t="n">
         <v>-943</v>
@@ -14522,7 +14522,7 @@
         <v>-2663.351124863409</v>
       </c>
       <c r="E202" t="n">
-        <v>1603.5</v>
+        <v>1723</v>
       </c>
       <c r="F202" t="n">
         <v>-936</v>
@@ -14542,7 +14542,7 @@
         <v>-2677.776537111889</v>
       </c>
       <c r="E203" t="n">
-        <v>1616.1</v>
+        <v>1732</v>
       </c>
       <c r="F203" t="n">
         <v>-929</v>
@@ -14562,7 +14562,7 @@
         <v>-2689.336365651319</v>
       </c>
       <c r="E204" t="n">
-        <v>1633.1</v>
+        <v>1749</v>
       </c>
       <c r="F204" t="n">
         <v>-926.5</v>
@@ -14582,7 +14582,7 @@
         <v>-2701.10085130621</v>
       </c>
       <c r="E205" t="n">
-        <v>1650.8</v>
+        <v>1774</v>
       </c>
       <c r="F205" t="n">
         <v>-922.5</v>
@@ -14602,7 +14602,7 @@
         <v>-2709.569673500035</v>
       </c>
       <c r="E206" t="n">
-        <v>1663.6</v>
+        <v>1791</v>
       </c>
       <c r="F206" t="n">
         <v>-921.5</v>
@@ -14622,7 +14622,7 @@
         <v>-2718.240411661623</v>
       </c>
       <c r="E207" t="n">
-        <v>1677.5</v>
+        <v>1808</v>
       </c>
       <c r="F207" t="n">
         <v>-920.5</v>
@@ -14642,7 +14642,7 @@
         <v>-2726.0625179717</v>
       </c>
       <c r="E208" t="n">
-        <v>1691.4</v>
+        <v>1817</v>
       </c>
       <c r="F208" t="n">
         <v>-934.5</v>
@@ -14662,7 +14662,7 @@
         <v>-2738.207490539824</v>
       </c>
       <c r="E209" t="n">
-        <v>1700.2</v>
+        <v>1836</v>
       </c>
       <c r="F209" t="n">
         <v>-941</v>
@@ -14682,7 +14682,7 @@
         <v>-2745.641741438796</v>
       </c>
       <c r="E210" t="n">
-        <v>1725.2</v>
+        <v>1857</v>
       </c>
       <c r="F210" t="n">
         <v>-937</v>
@@ -14702,7 +14702,7 @@
         <v>-2755.996963041494</v>
       </c>
       <c r="E211" t="n">
-        <v>1732</v>
+        <v>1868</v>
       </c>
       <c r="F211" t="n">
         <v>-934.5</v>
@@ -14722,7 +14722,7 @@
         <v>-2768.969548926258</v>
       </c>
       <c r="E212" t="n">
-        <v>1751</v>
+        <v>1901</v>
       </c>
       <c r="F212" t="n">
         <v>-929</v>
@@ -14742,7 +14742,7 @@
         <v>-2776.238282719339</v>
       </c>
       <c r="E213" t="n">
-        <v>1774</v>
+        <v>1918</v>
       </c>
       <c r="F213" t="n">
         <v>-920.5</v>
@@ -14762,7 +14762,7 @@
         <v>-2790.885592647614</v>
       </c>
       <c r="E214" t="n">
-        <v>1803.9</v>
+        <v>1939</v>
       </c>
       <c r="F214" t="n">
         <v>-909</v>
@@ -14782,7 +14782,7 @@
         <v>-2797.115662042137</v>
       </c>
       <c r="E215" t="n">
-        <v>1819.8</v>
+        <v>1956</v>
       </c>
       <c r="F215" t="n">
         <v>-915.5</v>
@@ -14802,7 +14802,7 @@
         <v>-2802.144830066969</v>
       </c>
       <c r="E216" t="n">
-        <v>1841.7</v>
+        <v>1977</v>
       </c>
       <c r="F216" t="n">
         <v>-911.5</v>
@@ -14822,7 +14822,7 @@
         <v>-2819.346204473898</v>
       </c>
       <c r="E217" t="n">
-        <v>1852.7</v>
+        <v>1996</v>
       </c>
       <c r="F217" t="n">
         <v>-913.5</v>
@@ -14842,7 +14842,7 @@
         <v>-2831.142444919185</v>
       </c>
       <c r="E218" t="n">
-        <v>1861.5</v>
+        <v>2009</v>
       </c>
       <c r="F218" t="n">
         <v>-906.5</v>
@@ -14862,7 +14862,7 @@
         <v>-2847.887336055995</v>
       </c>
       <c r="E219" t="n">
-        <v>1890.5</v>
+        <v>2030</v>
       </c>
       <c r="F219" t="n">
         <v>-904</v>
@@ -14882,7 +14882,7 @@
         <v>-2859.234171186068</v>
       </c>
       <c r="E220" t="n">
-        <v>1910.2</v>
+        <v>2051</v>
       </c>
       <c r="F220" t="n">
         <v>-898.5</v>
@@ -14902,7 +14902,7 @@
         <v>-2863.906760512139</v>
       </c>
       <c r="E221" t="n">
-        <v>1929</v>
+        <v>2068</v>
       </c>
       <c r="F221" t="n">
         <v>-894.5</v>
@@ -14922,7 +14922,7 @@
         <v>-2869.481754611027</v>
       </c>
       <c r="E222" t="n">
-        <v>1946.9</v>
+        <v>2085</v>
       </c>
       <c r="F222" t="n">
         <v>-895</v>
@@ -14942,7 +14942,7 @@
         <v>-2877.04372839315</v>
       </c>
       <c r="E223" t="n">
-        <v>1959.7</v>
+        <v>2102</v>
       </c>
       <c r="F223" t="n">
         <v>-886.5</v>
@@ -14962,7 +14962,7 @@
         <v>-2882.166550135263</v>
       </c>
       <c r="E224" t="n">
-        <v>1988.7</v>
+        <v>2123</v>
       </c>
       <c r="F224" t="n">
         <v>-884</v>
@@ -14982,7 +14982,7 @@
         <v>-2890.706926782456</v>
       </c>
       <c r="E225" t="n">
-        <v>2018.6</v>
+        <v>2150</v>
       </c>
       <c r="F225" t="n">
         <v>-881.5</v>
@@ -15002,7 +15002,7 @@
         <v>-2905.091148813542</v>
       </c>
       <c r="E226" t="n">
-        <v>2040.5</v>
+        <v>2171</v>
       </c>
       <c r="F226" t="n">
         <v>-876</v>
@@ -15022,7 +15022,7 @@
         <v>-2917.413397911941</v>
       </c>
       <c r="E227" t="n">
-        <v>2065.5</v>
+        <v>2196</v>
       </c>
       <c r="F227" t="n">
         <v>-869</v>
@@ -15042,7 +15042,7 @@
         <v>-2926.037517440527</v>
       </c>
       <c r="E228" t="n">
-        <v>2088.5</v>
+        <v>2217</v>
       </c>
       <c r="F228" t="n">
         <v>-868</v>
@@ -15062,7 +15062,7 @@
         <v>-2933.680367025686</v>
       </c>
       <c r="E229" t="n">
-        <v>2103.5</v>
+        <v>2220</v>
       </c>
       <c r="F229" t="n">
         <v>-874.5</v>
@@ -15082,7 +15082,7 @@
         <v>-2952.896896023672</v>
       </c>
       <c r="E230" t="n">
-        <v>2128.300000000001</v>
+        <v>2241</v>
       </c>
       <c r="F230" t="n">
         <v>-872</v>
@@ -15102,7 +15102,7 @@
         <v>-2960.343292868128</v>
       </c>
       <c r="E231" t="n">
-        <v>2152.200000000001</v>
+        <v>2266</v>
       </c>
       <c r="F231" t="n">
         <v>-860.5</v>
@@ -15122,7 +15122,7 @@
         <v>-2967.159471200971</v>
       </c>
       <c r="E232" t="n">
-        <v>2172.100000000001</v>
+        <v>2293</v>
       </c>
       <c r="F232" t="n">
         <v>-864</v>
@@ -15142,7 +15142,7 @@
         <v>-2971.270695992574</v>
       </c>
       <c r="E233" t="n">
-        <v>2189.600000000001</v>
+        <v>2314</v>
       </c>
       <c r="F233" t="n">
         <v>-861.5</v>
@@ -15162,7 +15162,7 @@
         <v>-2978.701741837509</v>
       </c>
       <c r="E234" t="n">
-        <v>2209.500000000001</v>
+        <v>2333</v>
       </c>
       <c r="F234" t="n">
         <v>-854.5</v>
@@ -15182,7 +15182,7 @@
         <v>-2982.495663109822</v>
       </c>
       <c r="E235" t="n">
-        <v>2233.200000000001</v>
+        <v>2354</v>
       </c>
       <c r="F235" t="n">
         <v>-844.5</v>
@@ -15202,7 +15202,7 @@
         <v>-2991.886089889794</v>
       </c>
       <c r="E236" t="n">
-        <v>2247.800000000001</v>
+        <v>2365</v>
       </c>
       <c r="F236" t="n">
         <v>-839</v>
@@ -15222,7 +15222,7 @@
         <v>-2998.531449131573</v>
       </c>
       <c r="E237" t="n">
-        <v>2282.600000000001</v>
+        <v>2388</v>
       </c>
       <c r="F237" t="n">
         <v>-836.5</v>
@@ -15242,7 +15242,7 @@
         <v>-3005.190684462481</v>
       </c>
       <c r="E238" t="n">
-        <v>2299.600000000001</v>
+        <v>2409</v>
       </c>
       <c r="F238" t="n">
         <v>-826.5</v>
@@ -15262,7 +15262,7 @@
         <v>-3012.57993539378</v>
       </c>
       <c r="E239" t="n">
-        <v>2326.600000000001</v>
+        <v>2434</v>
       </c>
       <c r="F239" t="n">
         <v>-821</v>
@@ -15282,7 +15282,7 @@
         <v>-3019.181690166487</v>
       </c>
       <c r="E240" t="n">
-        <v>2348.500000000001</v>
+        <v>2461</v>
       </c>
       <c r="F240" t="n">
         <v>-811</v>
@@ -15302,7 +15302,7 @@
         <v>-3029.723510227472</v>
       </c>
       <c r="E241" t="n">
-        <v>2372.400000000001</v>
+        <v>2480</v>
       </c>
       <c r="F241" t="n">
         <v>-805.5</v>
@@ -15322,7 +15322,7 @@
         <v>-3044.768794353802</v>
       </c>
       <c r="E242" t="n">
-        <v>2396.300000000001</v>
+        <v>2505</v>
       </c>
       <c r="F242" t="n">
         <v>-795.5</v>
@@ -15342,7 +15342,7 @@
         <v>-3049.253943579788</v>
       </c>
       <c r="E243" t="n">
-        <v>2411.100000000001</v>
+        <v>2526</v>
       </c>
       <c r="F243" t="n">
         <v>-788.5</v>
@@ -15362,7 +15362,7 @@
         <v>-3062.158585186359</v>
       </c>
       <c r="E244" t="n">
-        <v>2426.800000000001</v>
+        <v>2547</v>
       </c>
       <c r="F244" t="n">
         <v>-783</v>
@@ -15382,7 +15382,7 @@
         <v>-3072.80400205281</v>
       </c>
       <c r="E245" t="n">
-        <v>2450.700000000001</v>
+        <v>2562</v>
       </c>
       <c r="F245" t="n">
         <v>-780.5</v>
@@ -15402,7 +15402,7 @@
         <v>-3083.144308452584</v>
       </c>
       <c r="E246" t="n">
-        <v>2463.500000000001</v>
+        <v>2583</v>
       </c>
       <c r="F246" t="n">
         <v>-776.5</v>
@@ -15422,7 +15422,7 @@
         <v>-3093.342854124372</v>
       </c>
       <c r="E247" t="n">
-        <v>2494.300000000002</v>
+        <v>2616</v>
       </c>
       <c r="F247" t="n">
         <v>-768</v>
@@ -15442,7 +15442,7 @@
         <v>-3099.197674529419</v>
       </c>
       <c r="E248" t="n">
-        <v>2513.100000000002</v>
+        <v>2649</v>
       </c>
       <c r="F248" t="n">
         <v>-756.5</v>
@@ -15462,7 +15462,7 @@
         <v>-3107.93783743703</v>
       </c>
       <c r="E249" t="n">
-        <v>2535.900000000002</v>
+        <v>2672</v>
       </c>
       <c r="F249" t="n">
         <v>-751</v>
@@ -15482,7 +15482,7 @@
         <v>-3116.610856321919</v>
       </c>
       <c r="E250" t="n">
-        <v>2568.900000000002</v>
+        <v>2693</v>
       </c>
       <c r="F250" t="n">
         <v>-747</v>
@@ -15502,7 +15502,7 @@
         <v>-3131.846443698836</v>
       </c>
       <c r="E251" t="n">
-        <v>2593.700000000002</v>
+        <v>2722</v>
       </c>
       <c r="F251" t="n">
         <v>-743</v>
@@ -15522,7 +15522,7 @@
         <v>-3141.188791284486</v>
       </c>
       <c r="E252" t="n">
-        <v>2619.400000000002</v>
+        <v>2747</v>
       </c>
       <c r="F252" t="n">
         <v>-736</v>
@@ -15542,7 +15542,7 @@
         <v>-3145.198429564543</v>
       </c>
       <c r="E253" t="n">
-        <v>2638.000000000002</v>
+        <v>2782</v>
       </c>
       <c r="F253" t="n">
         <v>-724.5</v>
@@ -15562,7 +15562,7 @@
         <v>-3152.205255122882</v>
       </c>
       <c r="E254" t="n">
-        <v>2659.900000000002</v>
+        <v>2811</v>
       </c>
       <c r="F254" t="n">
         <v>-720.5</v>
@@ -15582,7 +15582,7 @@
         <v>-3161.305777238423</v>
       </c>
       <c r="E255" t="n">
-        <v>2681.600000000002</v>
+        <v>2836</v>
       </c>
       <c r="F255" t="n">
         <v>-713.5</v>
@@ -15602,7 +15602,7 @@
         <v>-3167.988265724664</v>
       </c>
       <c r="E256" t="n">
-        <v>2702.400000000002</v>
+        <v>2855</v>
       </c>
       <c r="F256" t="n">
         <v>-705</v>
@@ -15622,7 +15622,7 @@
         <v>-3175.908105313038</v>
       </c>
       <c r="E257" t="n">
-        <v>2725.200000000002</v>
+        <v>2874</v>
       </c>
       <c r="F257" t="n">
         <v>-698</v>
@@ -15642,7 +15642,7 @@
         <v>-3191.034604595266</v>
       </c>
       <c r="E258" t="n">
-        <v>2754.200000000002</v>
+        <v>2903</v>
       </c>
       <c r="F258" t="n">
         <v>-685</v>
@@ -15662,7 +15662,7 @@
         <v>-3195.416245130696</v>
       </c>
       <c r="E259" t="n">
-        <v>2771.000000000002</v>
+        <v>2930</v>
       </c>
       <c r="F259" t="n">
         <v>-679.5</v>
@@ -15682,7 +15682,7 @@
         <v>-3205.295744035393</v>
       </c>
       <c r="E260" t="n">
-        <v>2776.900000000002</v>
+        <v>2963</v>
       </c>
       <c r="F260" t="n">
         <v>-672.5</v>
@@ -15702,7 +15702,7 @@
         <v>-3209.927166922218</v>
       </c>
       <c r="E261" t="n">
-        <v>2791.500000000002</v>
+        <v>2984</v>
       </c>
       <c r="F261" t="n">
         <v>-667</v>
@@ -15722,7 +15722,7 @@
         <v>-3222.22988090955</v>
       </c>
       <c r="E262" t="n">
-        <v>2813.200000000002</v>
+        <v>3009</v>
       </c>
       <c r="F262" t="n">
         <v>-655.5</v>
@@ -15742,7 +15742,7 @@
         <v>-3230.067213903062</v>
       </c>
       <c r="E263" t="n">
-        <v>2837.800000000002</v>
+        <v>3030</v>
       </c>
       <c r="F263" t="n">
         <v>-645.5</v>
@@ -15762,7 +15762,7 @@
         <v>-3241.369934797733</v>
       </c>
       <c r="E264" t="n">
-        <v>2857.700000000002</v>
+        <v>3055</v>
       </c>
       <c r="F264" t="n">
         <v>-647.5</v>
@@ -15782,7 +15782,7 @@
         <v>-3243.602222360006</v>
       </c>
       <c r="E265" t="n">
-        <v>2888.700000000002</v>
+        <v>3082</v>
       </c>
       <c r="F265" t="n">
         <v>-648</v>
@@ -15802,7 +15802,7 @@
         <v>-3252.448045174649</v>
       </c>
       <c r="E266" t="n">
-        <v>2904.600000000002</v>
+        <v>3089</v>
       </c>
       <c r="F266" t="n">
         <v>-638</v>
@@ -15822,7 +15822,7 @@
         <v>-3269.85310922629</v>
       </c>
       <c r="E267" t="n">
-        <v>2922.500000000002</v>
+        <v>3106</v>
       </c>
       <c r="F267" t="n">
         <v>-632.5</v>
@@ -15842,7 +15842,7 @@
         <v>-3277.350118948331</v>
       </c>
       <c r="E268" t="n">
-        <v>2949.300000000002</v>
+        <v>3133</v>
       </c>
       <c r="F268" t="n">
         <v>-640.5</v>
@@ -15862,7 +15862,7 @@
         <v>-3283.697208616799</v>
       </c>
       <c r="E269" t="n">
-        <v>2981.000000000002</v>
+        <v>3160</v>
       </c>
       <c r="F269" t="n">
         <v>-635</v>
@@ -15882,7 +15882,7 @@
         <v>-3290.310190425611</v>
       </c>
       <c r="E270" t="n">
-        <v>3018.000000000002</v>
+        <v>3179</v>
       </c>
       <c r="F270" t="n">
         <v>-631</v>
@@ -15902,7 +15902,7 @@
         <v>-3301.379587301623</v>
       </c>
       <c r="E271" t="n">
-        <v>3031.900000000002</v>
+        <v>3202</v>
       </c>
       <c r="F271" t="n">
         <v>-636</v>
@@ -15922,7 +15922,7 @@
         <v>-3305.138404816271</v>
       </c>
       <c r="E272" t="n">
-        <v>3060.900000000002</v>
+        <v>3225</v>
       </c>
       <c r="F272" t="n">
         <v>-630.5</v>
@@ -15942,7 +15942,7 @@
         <v>-3309.190282372647</v>
       </c>
       <c r="E273" t="n">
-        <v>3083.700000000003</v>
+        <v>3248</v>
       </c>
       <c r="F273" t="n">
         <v>-623.5</v>
@@ -15962,7 +15962,7 @@
         <v>-3319.712709081206</v>
       </c>
       <c r="E274" t="n">
-        <v>3117.400000000002</v>
+        <v>3283</v>
       </c>
       <c r="F274" t="n">
         <v>-615</v>
@@ -15982,7 +15982,7 @@
         <v>-3334.83939858744</v>
       </c>
       <c r="E275" t="n">
-        <v>3137.100000000002</v>
+        <v>3306</v>
       </c>
       <c r="F275" t="n">
         <v>-600.5</v>
@@ -16002,7 +16002,7 @@
         <v>-3344.123087593315</v>
       </c>
       <c r="E276" t="n">
-        <v>3153.700000000002</v>
+        <v>3319</v>
       </c>
       <c r="F276" t="n">
         <v>-592</v>
@@ -16022,7 +16022,7 @@
         <v>-3352.067332065455</v>
       </c>
       <c r="E277" t="n">
-        <v>3174.700000000002</v>
+        <v>3342</v>
       </c>
       <c r="F277" t="n">
         <v>-583.5</v>
@@ -16042,7 +16042,7 @@
         <v>-3358.24766929521</v>
       </c>
       <c r="E278" t="n">
-        <v>3199.700000000002</v>
+        <v>3369</v>
       </c>
       <c r="F278" t="n">
         <v>-578</v>
@@ -16062,7 +16062,7 @@
         <v>-3367.230130680086</v>
       </c>
       <c r="E279" t="n">
-        <v>3238.700000000002</v>
+        <v>3400</v>
       </c>
       <c r="F279" t="n">
         <v>-572.5</v>
@@ -16082,7 +16082,7 @@
         <v>-3378.257265225039</v>
       </c>
       <c r="E280" t="n">
-        <v>3267.700000000002</v>
+        <v>3431</v>
       </c>
       <c r="F280" t="n">
         <v>-559.5</v>
@@ -16102,7 +16102,7 @@
         <v>-3392.507620846764</v>
       </c>
       <c r="E281" t="n">
-        <v>3292.700000000002</v>
+        <v>3460</v>
       </c>
       <c r="F281" t="n">
         <v>-555.5</v>
@@ -16122,7 +16122,7 @@
         <v>-3399.889277450938</v>
       </c>
       <c r="E282" t="n">
-        <v>3317.700000000002</v>
+        <v>3485</v>
       </c>
       <c r="F282" t="n">
         <v>-557.5</v>
@@ -16142,7 +16142,7 @@
         <v>-3401.473221909397</v>
       </c>
       <c r="E283" t="n">
-        <v>3348.500000000002</v>
+        <v>3514</v>
       </c>
       <c r="F283" t="n">
         <v>-549</v>
@@ -16162,7 +16162,7 @@
         <v>-3406.456102738477</v>
       </c>
       <c r="E284" t="n">
-        <v>3375.500000000002</v>
+        <v>3541</v>
       </c>
       <c r="F284" t="n">
         <v>-542</v>
@@ -16182,7 +16182,7 @@
         <v>-3408.450047604576</v>
       </c>
       <c r="E285" t="n">
-        <v>3403.200000000002</v>
+        <v>3566</v>
       </c>
       <c r="F285" t="n">
         <v>-532</v>
@@ -16202,7 +16202,7 @@
         <v>-3416.413012847521</v>
       </c>
       <c r="E286" t="n">
-        <v>3432.000000000002</v>
+        <v>3599</v>
       </c>
       <c r="F286" t="n">
         <v>-522</v>
@@ -16222,7 +16222,7 @@
         <v>-3427.578290721012</v>
       </c>
       <c r="E287" t="n">
-        <v>3453.000000000002</v>
+        <v>3620</v>
       </c>
       <c r="F287" t="n">
         <v>-516.5</v>
@@ -16242,7 +16242,7 @@
         <v>-3435.452112918297</v>
       </c>
       <c r="E288" t="n">
-        <v>3474.700000000002</v>
+        <v>3647</v>
       </c>
       <c r="F288" t="n">
         <v>-512.5</v>
@@ -16262,7 +16262,7 @@
         <v>-3440.9671223373</v>
       </c>
       <c r="E289" t="n">
-        <v>3508.600000000002</v>
+        <v>3676</v>
       </c>
       <c r="F289" t="n">
         <v>-502.5</v>
@@ -16282,7 +16282,7 @@
         <v>-3451.59106610668</v>
       </c>
       <c r="E290" t="n">
-        <v>3539.400000000002</v>
+        <v>3709</v>
       </c>
       <c r="F290" t="n">
         <v>-495.5</v>
@@ -16302,7 +16302,7 @@
         <v>-3456.452350956562</v>
       </c>
       <c r="E291" t="n">
-        <v>3569.300000000002</v>
+        <v>3730</v>
       </c>
       <c r="F291" t="n">
         <v>-481</v>
@@ -16322,7 +16322,7 @@
         <v>-3461.58556908058</v>
       </c>
       <c r="E292" t="n">
-        <v>3610.300000000002</v>
+        <v>3753</v>
       </c>
       <c r="F292" t="n">
         <v>-474</v>
@@ -16342,7 +16342,7 @@
         <v>-3470.006607292975</v>
       </c>
       <c r="E293" t="n">
-        <v>3641.300000000002</v>
+        <v>3786</v>
       </c>
       <c r="F293" t="n">
         <v>-468.5</v>
@@ -16362,7 +16362,7 @@
         <v>-3477.964965275645</v>
       </c>
       <c r="E294" t="n">
-        <v>3673.200000000003</v>
+        <v>3817</v>
       </c>
       <c r="F294" t="n">
         <v>-457</v>
@@ -16382,7 +16382,7 @@
         <v>-3485.368911559648</v>
       </c>
       <c r="E295" t="n">
-        <v>3697.100000000003</v>
+        <v>3846</v>
       </c>
       <c r="F295" t="n">
         <v>-451.5</v>
@@ -16402,7 +16402,7 @@
         <v>-3487.293295582306</v>
       </c>
       <c r="E296" t="n">
-        <v>3713.900000000003</v>
+        <v>3867</v>
       </c>
       <c r="F296" t="n">
         <v>-446</v>
@@ -16422,7 +16422,7 @@
         <v>-3496.923949971694</v>
       </c>
       <c r="E297" t="n">
-        <v>3742.500000000003</v>
+        <v>3896</v>
       </c>
       <c r="F297" t="n">
         <v>-439</v>
@@ -16442,7 +16442,7 @@
         <v>-3500.726355768737</v>
       </c>
       <c r="E298" t="n">
-        <v>3768.400000000003</v>
+        <v>3923</v>
       </c>
       <c r="F298" t="n">
         <v>-429</v>
@@ -16462,7 +16462,7 @@
         <v>-3502.996915485427</v>
       </c>
       <c r="E299" t="n">
-        <v>3789.200000000003</v>
+        <v>3952</v>
       </c>
       <c r="F299" t="n">
         <v>-419</v>
@@ -16482,7 +16482,7 @@
         <v>-3508.064060609442</v>
       </c>
       <c r="E300" t="n">
-        <v>3821.100000000003</v>
+        <v>3981</v>
       </c>
       <c r="F300" t="n">
         <v>-406</v>
@@ -16502,7 +16502,7 @@
         <v>-3511.803703764135</v>
       </c>
       <c r="E301" t="n">
-        <v>3853.000000000003</v>
+        <v>4008</v>
       </c>
       <c r="F301" t="n">
         <v>-400.5</v>
@@ -16522,7 +16522,7 @@
         <v>-3515.22199682005</v>
       </c>
       <c r="E302" t="n">
-        <v>3883.800000000003</v>
+        <v>4041</v>
       </c>
       <c r="F302" t="n">
         <v>-387.5</v>
@@ -16542,7 +16542,7 @@
         <v>-3519.566902580317</v>
       </c>
       <c r="E303" t="n">
-        <v>3908.600000000004</v>
+        <v>4066</v>
       </c>
       <c r="F303" t="n">
         <v>-380.5</v>
@@ -16562,7 +16562,7 @@
         <v>-3534.860273789981</v>
       </c>
       <c r="E304" t="n">
-        <v>3937.600000000004</v>
+        <v>4097</v>
       </c>
       <c r="F304" t="n">
         <v>-369</v>
@@ -16582,7 +16582,7 @@
         <v>-3537.693585067788</v>
       </c>
       <c r="E305" t="n">
-        <v>3959.500000000004</v>
+        <v>4130</v>
       </c>
       <c r="F305" t="n">
         <v>-357.5</v>
@@ -16602,7 +16602,7 @@
         <v>-3544.181151334116</v>
       </c>
       <c r="E306" t="n">
-        <v>3995.000000000004</v>
+        <v>4167</v>
       </c>
       <c r="F306" t="n">
         <v>-346</v>
@@ -16622,7 +16622,7 @@
         <v>-3544.778710139911</v>
       </c>
       <c r="E307" t="n">
-        <v>4022.900000000004</v>
+        <v>4192</v>
       </c>
       <c r="F307" t="n">
         <v>-330</v>
@@ -16642,7 +16642,7 @@
         <v>-3551.786341633569</v>
       </c>
       <c r="E308" t="n">
-        <v>4053.500000000004</v>
+        <v>4221</v>
       </c>
       <c r="F308" t="n">
         <v>-326</v>
@@ -16662,7 +16662,7 @@
         <v>-3558.142351019079</v>
       </c>
       <c r="E309" t="n">
-        <v>4069.400000000004</v>
+        <v>4238</v>
       </c>
       <c r="F309" t="n">
         <v>-311.5</v>
@@ -16682,7 +16682,7 @@
         <v>-3570.750284406039</v>
       </c>
       <c r="E310" t="n">
-        <v>4102.200000000003</v>
+        <v>4271</v>
       </c>
       <c r="F310" t="n">
         <v>-300</v>
@@ -16702,7 +16702,7 @@
         <v>-3581.306482914772</v>
       </c>
       <c r="E311" t="n">
-        <v>4122.800000000004</v>
+        <v>4290</v>
       </c>
       <c r="F311" t="n">
         <v>-291.5</v>
@@ -16722,7 +16722,7 @@
         <v>-3589.342568314311</v>
       </c>
       <c r="E312" t="n">
-        <v>4155.600000000004</v>
+        <v>4325</v>
       </c>
       <c r="F312" t="n">
         <v>-280</v>
@@ -16742,7 +16742,7 @@
         <v>-3596.476379755604</v>
       </c>
       <c r="E313" t="n">
-        <v>4190.600000000004</v>
+        <v>4350</v>
       </c>
       <c r="F313" t="n">
         <v>-274.5</v>
@@ -16762,7 +16762,7 @@
         <v>-3598.013455449126</v>
       </c>
       <c r="E314" t="n">
-        <v>4219.600000000004</v>
+        <v>4381</v>
       </c>
       <c r="F314" t="n">
         <v>-263</v>
@@ -16782,7 +16782,7 @@
         <v>-3602.014148579711</v>
       </c>
       <c r="E315" t="n">
-        <v>4243.500000000004</v>
+        <v>4418</v>
       </c>
       <c r="F315" t="n">
         <v>-245.5</v>
@@ -16802,7 +16802,7 @@
         <v>-3609.456951383192</v>
       </c>
       <c r="E316" t="n">
-        <v>4274.100000000004</v>
+        <v>4449</v>
       </c>
       <c r="F316" t="n">
         <v>-247.5</v>
@@ -16822,7 +16822,7 @@
         <v>-3609.135695200776</v>
       </c>
       <c r="E317" t="n">
-        <v>4307.600000000004</v>
+        <v>4474</v>
       </c>
       <c r="F317" t="n">
         <v>-234.5</v>
@@ -16842,7 +16842,7 @@
         <v>-3615.733711251207</v>
       </c>
       <c r="E318" t="n">
-        <v>4324.400000000004</v>
+        <v>4507</v>
       </c>
       <c r="F318" t="n">
         <v>-224.5</v>
@@ -16862,7 +16862,7 @@
         <v>-3621.939494615843</v>
       </c>
       <c r="E319" t="n">
-        <v>4350.100000000004</v>
+        <v>4528</v>
       </c>
       <c r="F319" t="n">
         <v>-216</v>
@@ -16882,7 +16882,7 @@
         <v>-3626.818929038604</v>
       </c>
       <c r="E320" t="n">
-        <v>4375.800000000004</v>
+        <v>4565</v>
       </c>
       <c r="F320" t="n">
         <v>-201.5</v>
@@ -16902,7 +16902,7 @@
         <v>-3635.634589872756</v>
       </c>
       <c r="E321" t="n">
-        <v>4402.800000000004</v>
+        <v>4598</v>
       </c>
       <c r="F321" t="n">
         <v>-196</v>
@@ -16922,7 +16922,7 @@
         <v>-3640.514631715028</v>
       </c>
       <c r="E322" t="n">
-        <v>4431.800000000004</v>
+        <v>4635</v>
       </c>
       <c r="F322" t="n">
         <v>-180</v>
@@ -16942,7 +16942,7 @@
         <v>-3639.175563384712</v>
       </c>
       <c r="E323" t="n">
-        <v>4465.500000000004</v>
+        <v>4660</v>
       </c>
       <c r="F323" t="n">
         <v>-164</v>
@@ -16962,7 +16962,7 @@
         <v>-3646.710445421333</v>
       </c>
       <c r="E324" t="n">
-        <v>4495.400000000003</v>
+        <v>4697</v>
       </c>
       <c r="F324" t="n">
         <v>-151</v>
@@ -16982,7 +16982,7 @@
         <v>-3648.148383949301</v>
       </c>
       <c r="E325" t="n">
-        <v>4532.400000000003</v>
+        <v>4730</v>
       </c>
       <c r="F325" t="n">
         <v>-142.5</v>
@@ -17002,7 +17002,7 @@
         <v>-3651.232871333345</v>
       </c>
       <c r="E326" t="n">
-        <v>4564.300000000003</v>
+        <v>4755</v>
       </c>
       <c r="F326" t="n">
         <v>-131</v>
@@ -17022,7 +17022,7 @@
         <v>-3656.21744890121</v>
       </c>
       <c r="E327" t="n">
-        <v>4598.200000000003</v>
+        <v>4788</v>
       </c>
       <c r="F327" t="n">
         <v>-116.5</v>
@@ -17042,7 +17042,7 @@
         <v>-3668.696995170179</v>
       </c>
       <c r="E328" t="n">
-        <v>4629.000000000003</v>
+        <v>4819</v>
       </c>
       <c r="F328" t="n">
         <v>-102</v>
@@ -17062,7 +17062,7 @@
         <v>-3679.410104722284</v>
       </c>
       <c r="E329" t="n">
-        <v>4657.800000000003</v>
+        <v>4850</v>
       </c>
       <c r="F329" t="n">
         <v>-86</v>
@@ -17082,7 +17082,7 @@
         <v>-3683.624264164536</v>
       </c>
       <c r="E330" t="n">
-        <v>4691.700000000003</v>
+        <v>4877</v>
       </c>
       <c r="F330" t="n">
         <v>-76</v>
@@ -17102,7 +17102,7 @@
         <v>-3693.94601849079</v>
       </c>
       <c r="E331" t="n">
-        <v>4722.700000000003</v>
+        <v>4906</v>
       </c>
       <c r="F331" t="n">
         <v>-67.5</v>
@@ -17122,7 +17122,7 @@
         <v>-3697.793469698078</v>
       </c>
       <c r="E332" t="n">
-        <v>4750.600000000002</v>
+        <v>4935</v>
       </c>
       <c r="F332" t="n">
         <v>-56</v>
@@ -17142,7 +17142,7 @@
         <v>-3705.370581126249</v>
       </c>
       <c r="E333" t="n">
-        <v>4781.400000000002</v>
+        <v>4966</v>
       </c>
       <c r="F333" t="n">
         <v>-52</v>
@@ -17162,7 +17162,7 @@
         <v>-3717.767438119616</v>
       </c>
       <c r="E334" t="n">
-        <v>4812.400000000002</v>
+        <v>4993</v>
       </c>
       <c r="F334" t="n">
         <v>-37.5</v>
@@ -17182,7 +17182,7 @@
         <v>-3722.303630080644</v>
       </c>
       <c r="E335" t="n">
-        <v>4845.400000000002</v>
+        <v>5024</v>
       </c>
       <c r="F335" t="n">
         <v>-24.5</v>
@@ -17202,7 +17202,7 @@
         <v>-3726.097507056765</v>
       </c>
       <c r="E336" t="n">
-        <v>4866.200000000003</v>
+        <v>5055</v>
       </c>
       <c r="F336" t="n">
         <v>-17.5</v>
@@ -17222,7 +17222,7 @@
         <v>-3724.20547622087</v>
       </c>
       <c r="E337" t="n">
-        <v>4893.000000000003</v>
+        <v>5086</v>
       </c>
       <c r="F337" t="n">
         <v>-10.5</v>
@@ -17242,7 +17242,7 @@
         <v>-3731.082087006008</v>
       </c>
       <c r="E338" t="n">
-        <v>4928.000000000003</v>
+        <v>5121</v>
       </c>
       <c r="F338" t="n">
         <v>-0.5</v>
@@ -17262,7 +17262,7 @@
         <v>-3732.69794800739</v>
       </c>
       <c r="E339" t="n">
-        <v>4962.800000000003</v>
+        <v>5158</v>
       </c>
       <c r="F339" t="n">
         <v>11</v>
@@ -17282,7 +17282,7 @@
         <v>-3738.039888195955</v>
       </c>
       <c r="E340" t="n">
-        <v>4983.600000000003</v>
+        <v>5185</v>
       </c>
       <c r="F340" t="n">
         <v>21</v>
@@ -17302,7 +17302,7 @@
         <v>-3743.349243745337</v>
       </c>
       <c r="E341" t="n">
-        <v>5016.200000000003</v>
+        <v>5222</v>
       </c>
       <c r="F341" t="n">
         <v>37</v>
@@ -17322,7 +17322,7 @@
         <v>-3748.412217744176</v>
       </c>
       <c r="E342" t="n">
-        <v>5046.100000000003</v>
+        <v>5255</v>
       </c>
       <c r="F342" t="n">
         <v>50</v>
@@ -17342,7 +17342,7 @@
         <v>-3752.280285539522</v>
       </c>
       <c r="E343" t="n">
-        <v>5072.000000000003</v>
+        <v>5286</v>
       </c>
       <c r="F343" t="n">
         <v>63</v>
@@ -17362,7 +17362,7 @@
         <v>-3753.575492463974</v>
       </c>
       <c r="E344" t="n">
-        <v>5097.700000000003</v>
+        <v>5317</v>
       </c>
       <c r="F344" t="n">
         <v>74.5</v>
@@ -17382,7 +17382,7 @@
         <v>-3758.139001980158</v>
       </c>
       <c r="E345" t="n">
-        <v>5129.600000000002</v>
+        <v>5352</v>
       </c>
       <c r="F345" t="n">
         <v>86</v>
@@ -17402,7 +17402,7 @@
         <v>-3762.668687765124</v>
       </c>
       <c r="E346" t="n">
-        <v>5160.600000000002</v>
+        <v>5387</v>
       </c>
       <c r="F346" t="n">
         <v>100.5</v>
@@ -17422,7 +17422,7 @@
         <v>-3762.107047463621</v>
       </c>
       <c r="E347" t="n">
-        <v>5193.400000000002</v>
+        <v>5418</v>
       </c>
       <c r="F347" t="n">
         <v>109</v>
@@ -17442,7 +17442,7 @@
         <v>-3764.03952818164</v>
       </c>
       <c r="E348" t="n">
-        <v>5227.300000000002</v>
+        <v>5451</v>
       </c>
       <c r="F348" t="n">
         <v>125</v>
@@ -17462,7 +17462,7 @@
         <v>-3766.531605165148</v>
       </c>
       <c r="E349" t="n">
-        <v>5247.200000000002</v>
+        <v>5478</v>
       </c>
       <c r="F349" t="n">
         <v>138</v>
@@ -17482,7 +17482,7 @@
         <v>-3773.397983000457</v>
       </c>
       <c r="E350" t="n">
-        <v>5288.900000000001</v>
+        <v>5521</v>
       </c>
       <c r="F350" t="n">
         <v>143.5</v>
@@ -17502,7 +17502,7 @@
         <v>-3781.864000450392</v>
       </c>
       <c r="E351" t="n">
-        <v>5319.900000000001</v>
+        <v>5556</v>
       </c>
       <c r="F351" t="n">
         <v>149</v>
@@ -17522,7 +17522,7 @@
         <v>-3790.367359220432</v>
       </c>
       <c r="E352" t="n">
-        <v>5350.900000000001</v>
+        <v>5589</v>
       </c>
       <c r="F352" t="n">
         <v>157.5</v>
@@ -17542,7 +17542,7 @@
         <v>-3793.768881460168</v>
       </c>
       <c r="E353" t="n">
-        <v>5380.600000000001</v>
+        <v>5620</v>
       </c>
       <c r="F353" t="n">
         <v>163</v>
@@ -17562,7 +17562,7 @@
         <v>-3798.658183628825</v>
       </c>
       <c r="E354" t="n">
-        <v>5420.500000000001</v>
+        <v>5659</v>
       </c>
       <c r="F354" t="n">
         <v>168.5</v>
@@ -17582,7 +17582,7 @@
         <v>-3804.118116719195</v>
       </c>
       <c r="E355" t="n">
-        <v>5453.500000000001</v>
+        <v>5696</v>
       </c>
       <c r="F355" t="n">
         <v>183</v>
@@ -17602,7 +17602,7 @@
         <v>-3806.841289732352</v>
       </c>
       <c r="E356" t="n">
-        <v>5485.200000000001</v>
+        <v>5727</v>
       </c>
       <c r="F356" t="n">
         <v>197.5</v>
@@ -17622,7 +17622,7 @@
         <v>-3814.010650594949</v>
       </c>
       <c r="E357" t="n">
-        <v>5511.800000000001</v>
+        <v>5754</v>
       </c>
       <c r="F357" t="n">
         <v>210.5</v>
@@ -17642,7 +17642,7 @@
         <v>-3824.825360453081</v>
       </c>
       <c r="E358" t="n">
-        <v>5551.500000000001</v>
+        <v>5797</v>
       </c>
       <c r="F358" t="n">
         <v>225</v>
@@ -17662,7 +17662,7 @@
         <v>-3832.932524256652</v>
       </c>
       <c r="E359" t="n">
-        <v>5581.400000000001</v>
+        <v>5824</v>
       </c>
       <c r="F359" t="n">
         <v>236.5</v>
@@ -17682,7 +17682,7 @@
         <v>-3839.15298954926</v>
       </c>
       <c r="E360" t="n">
-        <v>5622.400000000001</v>
+        <v>5869</v>
       </c>
       <c r="F360" t="n">
         <v>255.5</v>
@@ -17702,7 +17702,7 @@
         <v>-3844.657133646032</v>
       </c>
       <c r="E361" t="n">
-        <v>5654.8</v>
+        <v>5908</v>
       </c>
       <c r="F361" t="n">
         <v>264</v>
@@ -17722,7 +17722,7 @@
         <v>-3847.132888769135</v>
       </c>
       <c r="E362" t="n">
-        <v>5679.6</v>
+        <v>5939</v>
       </c>
       <c r="F362" t="n">
         <v>281.5</v>
@@ -17742,7 +17742,7 @@
         <v>-3854.576958377807</v>
       </c>
       <c r="E363" t="n">
-        <v>5717.3</v>
+        <v>5980</v>
       </c>
       <c r="F363" t="n">
         <v>296</v>
@@ -17762,7 +17762,7 @@
         <v>-3856.598743150798</v>
       </c>
       <c r="E364" t="n">
-        <v>5748.3</v>
+        <v>6007</v>
       </c>
       <c r="F364" t="n">
         <v>310.5</v>
@@ -17782,7 +17782,7 @@
         <v>-3858.952848109181</v>
       </c>
       <c r="E365" t="n">
-        <v>5780.900000000001</v>
+        <v>6044</v>
       </c>
       <c r="F365" t="n">
         <v>329.5</v>
@@ -17802,7 +17802,7 @@
         <v>-3865.144888320866</v>
       </c>
       <c r="E366" t="n">
-        <v>5820.8</v>
+        <v>6075</v>
       </c>
       <c r="F366" t="n">
         <v>350</v>
@@ -17822,7 +17822,7 @@
         <v>-3870.820580326307</v>
       </c>
       <c r="E367" t="n">
-        <v>5863.6</v>
+        <v>6114</v>
       </c>
       <c r="F367" t="n">
         <v>366</v>
@@ -17842,7 +17842,7 @@
         <v>-3877.038631168531</v>
       </c>
       <c r="E368" t="n">
-        <v>5903.5</v>
+        <v>6149</v>
       </c>
       <c r="F368" t="n">
         <v>385</v>
@@ -17862,7 +17862,7 @@
         <v>-3880.117461284964</v>
       </c>
       <c r="E369" t="n">
-        <v>5928.5</v>
+        <v>6180</v>
       </c>
       <c r="F369" t="n">
         <v>401</v>
@@ -17882,7 +17882,7 @@
         <v>-3879.672025910747</v>
       </c>
       <c r="E370" t="n">
-        <v>5944.2</v>
+        <v>6215</v>
       </c>
       <c r="F370" t="n">
         <v>420</v>
@@ -17902,7 +17902,7 @@
         <v>-3884.97168802321</v>
       </c>
       <c r="E371" t="n">
-        <v>5975.9</v>
+        <v>6248</v>
       </c>
       <c r="F371" t="n">
         <v>440.5</v>
@@ -17922,7 +17922,7 @@
         <v>-3889.24703718335</v>
       </c>
       <c r="E372" t="n">
-        <v>6013.799999999999</v>
+        <v>6289</v>
       </c>
       <c r="F372" t="n">
         <v>461</v>
@@ -17942,7 +17942,7 @@
         <v>-3886.486922662467</v>
       </c>
       <c r="E373" t="n">
-        <v>6052.599999999999</v>
+        <v>6324</v>
       </c>
       <c r="F373" t="n">
         <v>472.5</v>
@@ -17962,7 +17962,7 @@
         <v>-3888.720098223402</v>
       </c>
       <c r="E374" t="n">
-        <v>6093.599999999999</v>
+        <v>6357</v>
       </c>
       <c r="F374" t="n">
         <v>484</v>
@@ -17982,7 +17982,7 @@
         <v>-3892.569361228206</v>
       </c>
       <c r="E375" t="n">
-        <v>6127.499999999999</v>
+        <v>6396</v>
       </c>
       <c r="F375" t="n">
         <v>497</v>
@@ -18002,7 +18002,7 @@
         <v>-3900.008679655078</v>
       </c>
       <c r="E376" t="n">
-        <v>6163.399999999999</v>
+        <v>6433</v>
       </c>
       <c r="F376" t="n">
         <v>513</v>
@@ -18022,7 +18022,7 @@
         <v>-3899.609866992836</v>
       </c>
       <c r="E377" t="n">
-        <v>6197.299999999998</v>
+        <v>6468</v>
       </c>
       <c r="F377" t="n">
         <v>530.5</v>
@@ -18042,7 +18042,7 @@
         <v>-3904.829472916613</v>
       </c>
       <c r="E378" t="n">
-        <v>6230.299999999998</v>
+        <v>6505</v>
       </c>
       <c r="F378" t="n">
         <v>540.5</v>
@@ -18062,7 +18062,7 @@
         <v>-3903.393357607637</v>
       </c>
       <c r="E379" t="n">
-        <v>6259.099999999999</v>
+        <v>6538</v>
       </c>
       <c r="F379" t="n">
         <v>561</v>
@@ -18082,7 +18082,7 @@
         <v>-3905.948903282528</v>
       </c>
       <c r="E380" t="n">
-        <v>6294.999999999998</v>
+        <v>6581</v>
       </c>
       <c r="F380" t="n">
         <v>577</v>
@@ -18102,7 +18102,7 @@
         <v>-3911.847488201251</v>
       </c>
       <c r="E381" t="n">
-        <v>6331.999999999998</v>
+        <v>6620</v>
       </c>
       <c r="F381" t="n">
         <v>591.5</v>
@@ -18122,7 +18122,7 @@
         <v>-3918.920698100097</v>
       </c>
       <c r="E382" t="n">
-        <v>6362.999999999998</v>
+        <v>6653</v>
       </c>
       <c r="F382" t="n">
         <v>598.5</v>
@@ -18142,7 +18142,7 @@
         <v>-3922.543675385281</v>
       </c>
       <c r="E383" t="n">
-        <v>6403.799999999998</v>
+        <v>6694</v>
       </c>
       <c r="F383" t="n">
         <v>617.5</v>
@@ -18162,7 +18162,7 @@
         <v>-3932.460962422097</v>
       </c>
       <c r="E384" t="n">
-        <v>6434.599999999999</v>
+        <v>6725</v>
       </c>
       <c r="F384" t="n">
         <v>630.5</v>
@@ -18182,7 +18182,7 @@
         <v>-3931.923653320499</v>
       </c>
       <c r="E385" t="n">
-        <v>6460.099999999999</v>
+        <v>6766</v>
       </c>
       <c r="F385" t="n">
         <v>648</v>
@@ -18202,7 +18202,7 @@
         <v>-3932.883867143456</v>
       </c>
       <c r="E386" t="n">
-        <v>6489.799999999998</v>
+        <v>6803</v>
       </c>
       <c r="F386" t="n">
         <v>662.5</v>
@@ -18222,7 +18222,7 @@
         <v>-3935.419434326667</v>
       </c>
       <c r="E387" t="n">
-        <v>6529.499999999998</v>
+        <v>6844</v>
       </c>
       <c r="F387" t="n">
         <v>672.5</v>
@@ -18242,7 +18242,7 @@
         <v>-3933.219293080204</v>
       </c>
       <c r="E388" t="n">
-        <v>6562.999999999998</v>
+        <v>6875</v>
       </c>
       <c r="F388" t="n">
         <v>684</v>
@@ -18262,7 +18262,7 @@
         <v>-3931.408189662529</v>
       </c>
       <c r="E389" t="n">
-        <v>6597.799999999998</v>
+        <v>6912</v>
       </c>
       <c r="F389" t="n">
         <v>701.5</v>
@@ -18282,7 +18282,7 @@
         <v>-3940.633893771014</v>
       </c>
       <c r="E390" t="n">
-        <v>6636.599999999999</v>
+        <v>6953</v>
       </c>
       <c r="F390" t="n">
         <v>716</v>
@@ -18302,7 +18302,7 @@
         <v>-3945.050139377885</v>
       </c>
       <c r="E391" t="n">
-        <v>6679.599999999999</v>
+        <v>6996</v>
       </c>
       <c r="F391" t="n">
         <v>730.5</v>
@@ -18322,7 +18322,7 @@
         <v>-3946.307294786794</v>
       </c>
       <c r="E392" t="n">
-        <v>6713.299999999998</v>
+        <v>7029</v>
       </c>
       <c r="F392" t="n">
         <v>746.5</v>
@@ -18342,7 +18342,7 @@
         <v>-3950.736386843588</v>
       </c>
       <c r="E393" t="n">
-        <v>6751.899999999999</v>
+        <v>7072</v>
       </c>
       <c r="F393" t="n">
         <v>761</v>
@@ -18362,7 +18362,7 @@
         <v>-3952.885214647476</v>
       </c>
       <c r="E394" t="n">
-        <v>6785.799999999998</v>
+        <v>7105</v>
       </c>
       <c r="F394" t="n">
         <v>775.5</v>
@@ -18382,7 +18382,7 @@
         <v>-3959.513644923875</v>
       </c>
       <c r="E395" t="n">
-        <v>6823.699999999998</v>
+        <v>7144</v>
       </c>
       <c r="F395" t="n">
         <v>793</v>
@@ -18402,7 +18402,7 @@
         <v>-3962.325267499992</v>
       </c>
       <c r="E396" t="n">
-        <v>6858.499999999998</v>
+        <v>7181</v>
       </c>
       <c r="F396" t="n">
         <v>804.5</v>
@@ -18422,7 +18422,7 @@
         <v>-3960.808919475468</v>
       </c>
       <c r="E397" t="n">
-        <v>6902.399999999998</v>
+        <v>7212</v>
       </c>
       <c r="F397" t="n">
         <v>823.5</v>
@@ -18442,7 +18442,7 @@
         <v>-3960.032963220749</v>
       </c>
       <c r="E398" t="n">
-        <v>6937.199999999998</v>
+        <v>7251</v>
       </c>
       <c r="F398" t="n">
         <v>844</v>
@@ -18462,7 +18462,7 @@
         <v>-3967.554477166513</v>
       </c>
       <c r="E399" t="n">
-        <v>6974.199999999998</v>
+        <v>7288</v>
       </c>
       <c r="F399" t="n">
         <v>863</v>
@@ -18482,7 +18482,7 @@
         <v>-3961.647557092731</v>
       </c>
       <c r="E400" t="n">
-        <v>7002.999999999998</v>
+        <v>7325</v>
       </c>
       <c r="F400" t="n">
         <v>877.5</v>
@@ -18502,7 +18502,7 @@
         <v>-3962.800357226531</v>
       </c>
       <c r="E401" t="n">
-        <v>7036.899999999998</v>
+        <v>7364</v>
       </c>
       <c r="F401" t="n">
         <v>895</v>
@@ -18522,7 +18522,7 @@
         <v>-3960.878002874664</v>
       </c>
       <c r="E402" t="n">
-        <v>7071.499999999998</v>
+        <v>7405</v>
       </c>
       <c r="F402" t="n">
         <v>908</v>
@@ -18542,7 +18542,7 @@
         <v>-3962.202650680811</v>
       </c>
       <c r="E403" t="n">
-        <v>7100.299999999998</v>
+        <v>7446</v>
       </c>
       <c r="F403" t="n">
         <v>921</v>
@@ -18562,7 +18562,7 @@
         <v>-3963.877870872013</v>
       </c>
       <c r="E404" t="n">
-        <v>7134.199999999998</v>
+        <v>7477</v>
       </c>
       <c r="F404" t="n">
         <v>938.5</v>
@@ -18582,7 +18582,7 @@
         <v>-3960.592347871313</v>
       </c>
       <c r="E405" t="n">
-        <v>7167.699999999998</v>
+        <v>7510</v>
       </c>
       <c r="F405" t="n">
         <v>950</v>
@@ -18602,7 +18602,7 @@
         <v>-3959.093445970433</v>
       </c>
       <c r="E406" t="n">
-        <v>7198.499999999998</v>
+        <v>7539</v>
       </c>
       <c r="F406" t="n">
         <v>966</v>
@@ -18622,7 +18622,7 @@
         <v>-3958.704304522837</v>
       </c>
       <c r="E407" t="n">
-        <v>7234.199999999998</v>
+        <v>7576</v>
       </c>
       <c r="F407" t="n">
         <v>986.5</v>
@@ -18642,7 +18642,7 @@
         <v>-3964.331323531655</v>
       </c>
       <c r="E408" t="n">
-        <v>7270.999999999998</v>
+        <v>7617</v>
       </c>
       <c r="F408" t="n">
         <v>1001</v>
@@ -18662,7 +18662,7 @@
         <v>-3971.761434516482</v>
       </c>
       <c r="E409" t="n">
-        <v>7309.999999999998</v>
+        <v>7656</v>
       </c>
       <c r="F409" t="n">
         <v>1023</v>
@@ -18682,7 +18682,7 @@
         <v>-3971.635816570012</v>
       </c>
       <c r="E410" t="n">
-        <v>7344.599999999999</v>
+        <v>7691</v>
       </c>
       <c r="F410" t="n">
         <v>1043.5</v>
@@ -18702,7 +18702,7 @@
         <v>-3976.72843105495</v>
       </c>
       <c r="E411" t="n">
-        <v>7383.399999999999</v>
+        <v>7734</v>
       </c>
       <c r="F411" t="n">
         <v>1053.5</v>
@@ -18722,7 +18722,7 @@
         <v>-3980.837124201093</v>
       </c>
       <c r="E412" t="n">
-        <v>7419.099999999999</v>
+        <v>7771</v>
       </c>
       <c r="F412" t="n">
         <v>1066.5</v>
@@ -18742,7 +18742,7 @@
         <v>-3988.300929029893</v>
       </c>
       <c r="E413" t="n">
-        <v>7450.999999999998</v>
+        <v>7806</v>
       </c>
       <c r="F413" t="n">
         <v>1084</v>
@@ -18762,7 +18762,7 @@
         <v>-3989.356051874164</v>
       </c>
       <c r="E414" t="n">
-        <v>7482.499999999998</v>
+        <v>7843</v>
       </c>
       <c r="F414" t="n">
         <v>1100</v>
@@ -18782,7 +18782,7 @@
         <v>-3990.571738583809</v>
       </c>
       <c r="E415" t="n">
-        <v>7516.399999999998</v>
+        <v>7878</v>
       </c>
       <c r="F415" t="n">
         <v>1117.5</v>
@@ -18802,7 +18802,7 @@
         <v>-3994.96853898736</v>
       </c>
       <c r="E416" t="n">
-        <v>7555.199999999998</v>
+        <v>7917</v>
       </c>
       <c r="F416" t="n">
         <v>1139.5</v>
@@ -18822,7 +18822,7 @@
         <v>-3997.259802583437</v>
       </c>
       <c r="E417" t="n">
-        <v>7592.199999999998</v>
+        <v>7960</v>
       </c>
       <c r="F417" t="n">
         <v>1161.5</v>
@@ -18842,7 +18842,7 @@
         <v>-3998.598786760912</v>
       </c>
       <c r="E418" t="n">
-        <v>7632.099999999998</v>
+        <v>7995</v>
       </c>
       <c r="F418" t="n">
         <v>1180.5</v>
@@ -18862,7 +18862,7 @@
         <v>-4000.97739558664</v>
       </c>
       <c r="E419" t="n">
-        <v>7669.999999999997</v>
+        <v>8032</v>
       </c>
       <c r="F419" t="n">
         <v>1201</v>
@@ -18882,7 +18882,7 @@
         <v>-4005.45556725096</v>
       </c>
       <c r="E420" t="n">
-        <v>7708.799999999997</v>
+        <v>8071</v>
       </c>
       <c r="F420" t="n">
         <v>1220</v>
@@ -18902,7 +18902,7 @@
         <v>-4001.961647623041</v>
       </c>
       <c r="E421" t="n">
-        <v>7743.399999999998</v>
+        <v>8104</v>
       </c>
       <c r="F421" t="n">
         <v>1240.5</v>
@@ -18922,7 +18922,7 @@
         <v>-4002.410954930469</v>
       </c>
       <c r="E422" t="n">
-        <v>7781.299999999997</v>
+        <v>8143</v>
       </c>
       <c r="F422" t="n">
         <v>1259.5</v>
@@ -18942,7 +18942,7 @@
         <v>-4005.940434212504</v>
       </c>
       <c r="E423" t="n">
-        <v>7814.099999999998</v>
+        <v>8186</v>
       </c>
       <c r="F423" t="n">
         <v>1280</v>
@@ -18962,7 +18962,7 @@
         <v>-4000.435071042857</v>
       </c>
       <c r="E424" t="n">
-        <v>7851.599999999998</v>
+        <v>8223</v>
       </c>
       <c r="F424" t="n">
         <v>1296</v>
@@ -18982,7 +18982,7 @@
         <v>-4001.724820208937</v>
       </c>
       <c r="E425" t="n">
-        <v>7887.499999999997</v>
+        <v>8260</v>
       </c>
       <c r="F425" t="n">
         <v>1313.5</v>
@@ -19002,7 +19002,7 @@
         <v>-4008.053166994851</v>
       </c>
       <c r="E426" t="n">
-        <v>7929.399999999997</v>
+        <v>8305</v>
       </c>
       <c r="F426" t="n">
         <v>1332.5</v>
@@ -19022,7 +19022,7 @@
         <v>-4010.298937885023</v>
       </c>
       <c r="E427" t="n">
-        <v>7969.099999999997</v>
+        <v>8348</v>
       </c>
       <c r="F427" t="n">
         <v>1353</v>
@@ -19042,7 +19042,7 @@
         <v>-4009.440312276627</v>
       </c>
       <c r="E428" t="n">
-        <v>8008.999999999996</v>
+        <v>8383</v>
       </c>
       <c r="F428" t="n">
         <v>1373.5</v>
@@ -19062,7 +19062,7 @@
         <v>-4010.880443182599</v>
       </c>
       <c r="E429" t="n">
-        <v>8042.899999999996</v>
+        <v>8424</v>
       </c>
       <c r="F429" t="n">
         <v>1391</v>
@@ -19082,7 +19082,7 @@
         <v>-4016.911976714099</v>
       </c>
       <c r="E430" t="n">
-        <v>8081.499999999996</v>
+        <v>8467</v>
       </c>
       <c r="F430" t="n">
         <v>1408.5</v>
@@ -19102,7 +19102,7 @@
         <v>-4023.395370750281</v>
       </c>
       <c r="E431" t="n">
-        <v>8121.199999999996</v>
+        <v>8510</v>
       </c>
       <c r="F431" t="n">
         <v>1430.5</v>
@@ -19122,7 +19122,7 @@
         <v>-4027.524552674005</v>
       </c>
       <c r="E432" t="n">
-        <v>8157.999999999996</v>
+        <v>8549</v>
       </c>
       <c r="F432" t="n">
         <v>1445</v>
@@ -19142,7 +19142,7 @@
         <v>-4028.064047873985</v>
       </c>
       <c r="E433" t="n">
-        <v>8196.799999999996</v>
+        <v>8588</v>
       </c>
       <c r="F433" t="n">
         <v>1464</v>
@@ -19162,7 +19162,7 @@
         <v>-4032.981425243987</v>
       </c>
       <c r="E434" t="n">
-        <v>8233.799999999996</v>
+        <v>8629</v>
       </c>
       <c r="F434" t="n">
         <v>1486</v>
@@ -19182,7 +19182,7 @@
         <v>-4034.610925039364</v>
       </c>
       <c r="E435" t="n">
-        <v>8267.699999999995</v>
+        <v>8670</v>
       </c>
       <c r="F435" t="n">
         <v>1505</v>
@@ -19202,7 +19202,7 @@
         <v>-4036.611776117434</v>
       </c>
       <c r="E436" t="n">
-        <v>8306.699999999995</v>
+        <v>8713</v>
       </c>
       <c r="F436" t="n">
         <v>1528.5</v>
@@ -19222,7 +19222,7 @@
         <v>-4037.251290035139</v>
       </c>
       <c r="E437" t="n">
-        <v>8340.399999999996</v>
+        <v>8758</v>
       </c>
       <c r="F437" t="n">
         <v>1544.5</v>
@@ -19242,7 +19242,7 @@
         <v>-4041.034667142736</v>
       </c>
       <c r="E438" t="n">
-        <v>8380.099999999997</v>
+        <v>8797</v>
       </c>
       <c r="F438" t="n">
         <v>1563.5</v>
@@ -19262,7 +19262,7 @@
         <v>-4041.225544879799</v>
       </c>
       <c r="E439" t="n">
-        <v>8419.999999999996</v>
+        <v>8840</v>
       </c>
       <c r="F439" t="n">
         <v>1581</v>
@@ -19282,7 +19282,7 @@
         <v>-4036.466317529388</v>
       </c>
       <c r="E440" t="n">
-        <v>8453.099999999997</v>
+        <v>8879</v>
       </c>
       <c r="F440" t="n">
         <v>1598.5</v>
@@ -19302,7 +19302,7 @@
         <v>-4035.788433461802</v>
       </c>
       <c r="E441" t="n">
-        <v>8489.899999999996</v>
+        <v>8920</v>
       </c>
       <c r="F441" t="n">
         <v>1616</v>
@@ -19322,7 +19322,7 @@
         <v>-4035.860191826792</v>
       </c>
       <c r="E442" t="n">
-        <v>8531.799999999996</v>
+        <v>8963</v>
       </c>
       <c r="F442" t="n">
         <v>1635</v>
@@ -19342,7 +19342,7 @@
         <v>-4037.402158199117</v>
       </c>
       <c r="E443" t="n">
-        <v>8572.799999999996</v>
+        <v>9008</v>
       </c>
       <c r="F443" t="n">
         <v>1654</v>
@@ -19362,7 +19362,7 @@
         <v>-4038.486902608306</v>
       </c>
       <c r="E444" t="n">
-        <v>8616.699999999995</v>
+        <v>9051</v>
       </c>
       <c r="F444" t="n">
         <v>1676</v>
@@ -19382,7 +19382,7 @@
         <v>-4036.009444405397</v>
       </c>
       <c r="E445" t="n">
-        <v>8650.399999999996</v>
+        <v>9092</v>
       </c>
       <c r="F445" t="n">
         <v>1692</v>
@@ -19402,7 +19402,7 @@
         <v>-4036.898085982486</v>
       </c>
       <c r="E446" t="n">
-        <v>8686.299999999996</v>
+        <v>9133</v>
       </c>
       <c r="F446" t="n">
         <v>1709.5</v>
@@ -19422,7 +19422,7 @@
         <v>-4041.040674242279</v>
       </c>
       <c r="E447" t="n">
-        <v>8727.099999999995</v>
+        <v>9176</v>
       </c>
       <c r="F447" t="n">
         <v>1728.5</v>
@@ -19442,7 +19442,7 @@
         <v>-4048.535087429127</v>
       </c>
       <c r="E448" t="n">
-        <v>8762.099999999995</v>
+        <v>9209</v>
       </c>
       <c r="F448" t="n">
         <v>1752</v>
@@ -19462,7 +19462,7 @@
         <v>-4049.116129675113</v>
       </c>
       <c r="E449" t="n">
-        <v>8799.999999999995</v>
+        <v>9244</v>
       </c>
       <c r="F449" t="n">
         <v>1771</v>
@@ -19482,7 +19482,7 @@
         <v>-4049.581186298098</v>
       </c>
       <c r="E450" t="n">
-        <v>8834.799999999994</v>
+        <v>9283</v>
       </c>
       <c r="F450" t="n">
         <v>1793</v>
@@ -19502,7 +19502,7 @@
         <v>-4049.685148401122</v>
       </c>
       <c r="E451" t="n">
-        <v>8878.699999999993</v>
+        <v>9318</v>
       </c>
       <c r="F451" t="n">
         <v>1812</v>
@@ -19522,7 +19522,7 @@
         <v>-4049.118373060276</v>
       </c>
       <c r="E452" t="n">
-        <v>8920.399999999994</v>
+        <v>9357</v>
       </c>
       <c r="F452" t="n">
         <v>1831</v>
@@ -19542,7 +19542,7 @@
         <v>-4048.270928309592</v>
       </c>
       <c r="E453" t="n">
-        <v>8966.299999999994</v>
+        <v>9394</v>
       </c>
       <c r="F453" t="n">
         <v>1848.5</v>
@@ -19562,7 +19562,7 @@
         <v>-4047.044872116019</v>
       </c>
       <c r="E454" t="n">
-        <v>9000.899999999994</v>
+        <v>9433</v>
       </c>
       <c r="F454" t="n">
         <v>1864.5</v>
@@ -19582,7 +19582,7 @@
         <v>-4048.494035159575</v>
       </c>
       <c r="E455" t="n">
-        <v>9037.699999999993</v>
+        <v>9472</v>
       </c>
       <c r="F455" t="n">
         <v>1883.5</v>
@@ -19602,7 +19602,7 @@
         <v>-4055.557076922366</v>
       </c>
       <c r="E456" t="n">
-        <v>9080.699999999993</v>
+        <v>9515</v>
       </c>
       <c r="F456" t="n">
         <v>1902.5</v>
@@ -19622,7 +19622,7 @@
         <v>-4058.816021607141</v>
       </c>
       <c r="E457" t="n">
-        <v>9120.599999999993</v>
+        <v>9560</v>
       </c>
       <c r="F457" t="n">
         <v>1921.5</v>
@@ -19642,7 +19642,7 @@
         <v>-4058.512206065356</v>
       </c>
       <c r="E458" t="n">
-        <v>9161.599999999993</v>
+        <v>9603</v>
       </c>
       <c r="F458" t="n">
         <v>1942</v>
@@ -19662,7 +19662,7 @@
         <v>-4055.586638682457</v>
       </c>
       <c r="E459" t="n">
-        <v>9199.299999999994</v>
+        <v>9648</v>
       </c>
       <c r="F459" t="n">
         <v>1962.5</v>
@@ -19682,7 +19682,7 @@
         <v>-4054.359303303845</v>
       </c>
       <c r="E460" t="n">
-        <v>9236.999999999995</v>
+        <v>9683</v>
       </c>
       <c r="F460" t="n">
         <v>1984.5</v>
@@ -19702,7 +19702,7 @@
         <v>-4054.002589768311</v>
       </c>
       <c r="E461" t="n">
-        <v>9274.699999999995</v>
+        <v>9730</v>
       </c>
       <c r="F461" t="n">
         <v>2005</v>
@@ -19722,7 +19722,7 @@
         <v>-4059.232979741861</v>
       </c>
       <c r="E462" t="n">
-        <v>9316.599999999995</v>
+        <v>9769</v>
       </c>
       <c r="F462" t="n">
         <v>2021</v>
@@ -19742,7 +19742,7 @@
         <v>-4063.701942261097</v>
       </c>
       <c r="E463" t="n">
-        <v>9353.199999999995</v>
+        <v>9810</v>
       </c>
       <c r="F463" t="n">
         <v>2043</v>
@@ -19762,7 +19762,7 @@
         <v>-4060.559718902382</v>
       </c>
       <c r="E464" t="n">
-        <v>9395.999999999995</v>
+        <v>9857</v>
       </c>
       <c r="F464" t="n">
         <v>2063.5</v>
@@ -19782,7 +19782,7 @@
         <v>-4059.534613558375</v>
       </c>
       <c r="E465" t="n">
-        <v>9439.899999999994</v>
+        <v>9900</v>
       </c>
       <c r="F465" t="n">
         <v>2085.5</v>
@@ -19802,7 +19802,7 @@
         <v>-4060.148781013936</v>
       </c>
       <c r="E466" t="n">
-        <v>9481.799999999994</v>
+        <v>9947</v>
       </c>
       <c r="F466" t="n">
         <v>2106</v>
@@ -19822,7 +19822,7 @@
         <v>-4060.964854401854</v>
       </c>
       <c r="E467" t="n">
-        <v>9524.599999999993</v>
+        <v>9988</v>
       </c>
       <c r="F467" t="n">
         <v>2126.5</v>
@@ -19842,7 +19842,7 @@
         <v>-4059.827515825782</v>
       </c>
       <c r="E468" t="n">
-        <v>9571.599999999993</v>
+        <v>10033</v>
       </c>
       <c r="F468" t="n">
         <v>2150</v>
@@ -19862,7 +19862,7 @@
         <v>-4059.136003735782</v>
       </c>
       <c r="E469" t="n">
-        <v>9616.399999999992</v>
+        <v>10080</v>
       </c>
       <c r="F469" t="n">
         <v>2172</v>
@@ -19882,7 +19882,7 @@
         <v>-4056.885637515954</v>
       </c>
       <c r="E470" t="n">
-        <v>9651.199999999992</v>
+        <v>10121</v>
       </c>
       <c r="F470" t="n">
         <v>2192.5</v>
@@ -19902,7 +19902,7 @@
         <v>-4056.865030009566</v>
       </c>
       <c r="E471" t="n">
-        <v>9694.199999999992</v>
+        <v>10168</v>
       </c>
       <c r="F471" t="n">
         <v>2213</v>
@@ -19922,7 +19922,7 @@
         <v>-4057.924999673819</v>
       </c>
       <c r="E472" t="n">
-        <v>9737.199999999992</v>
+        <v>10211</v>
       </c>
       <c r="F472" t="n">
         <v>2232</v>
@@ -19942,7 +19942,7 @@
         <v>-4059.632842196756</v>
       </c>
       <c r="E473" t="n">
-        <v>9778.199999999992</v>
+        <v>10256</v>
       </c>
       <c r="F473" t="n">
         <v>2255.5</v>
@@ -19962,7 +19962,7 @@
         <v>-4054.543605559077</v>
       </c>
       <c r="E474" t="n">
-        <v>9822.999999999991</v>
+        <v>10299</v>
       </c>
       <c r="F474" t="n">
         <v>2274.5</v>
@@ -19982,7 +19982,7 @@
         <v>-4053.444922666721</v>
       </c>
       <c r="E475" t="n">
-        <v>9858.899999999991</v>
+        <v>10344</v>
       </c>
       <c r="F475" t="n">
         <v>2298</v>
@@ -20002,7 +20002,7 @@
         <v>-4051.321292763216</v>
       </c>
       <c r="E476" t="n">
-        <v>9901.69999999999</v>
+        <v>10389</v>
       </c>
       <c r="F476" t="n">
         <v>2321.5</v>
@@ -20022,7 +20022,7 @@
         <v>-4048.733330681505</v>
       </c>
       <c r="E477" t="n">
-        <v>9942.29999999999</v>
+        <v>10434</v>
       </c>
       <c r="F477" t="n">
         <v>2343.5</v>
@@ -20042,7 +20042,7 @@
         <v>-4047.268118905349</v>
       </c>
       <c r="E478" t="n">
-        <v>9985.999999999991</v>
+        <v>10479</v>
       </c>
       <c r="F478" t="n">
         <v>2364</v>
@@ -20062,7 +20062,7 @@
         <v>-4045.040387993271</v>
       </c>
       <c r="E479" t="n">
-        <v>10028.79999999999</v>
+        <v>10526</v>
       </c>
       <c r="F479" t="n">
         <v>2387.5</v>
@@ -20082,7 +20082,7 @@
         <v>-4047.892899492597</v>
       </c>
       <c r="E480" t="n">
-        <v>10067.59999999999</v>
+        <v>10567</v>
       </c>
       <c r="F480" t="n">
         <v>2408</v>
@@ -20102,7 +20102,7 @@
         <v>-4046.2367983871</v>
       </c>
       <c r="E481" t="n">
-        <v>10111.49999999999</v>
+        <v>10614</v>
       </c>
       <c r="F481" t="n">
         <v>2431.5</v>
@@ -20122,7 +20122,7 @@
         <v>-4048.418393428551</v>
       </c>
       <c r="E482" t="n">
-        <v>10153.39999999999</v>
+        <v>10657</v>
       </c>
       <c r="F482" t="n">
         <v>2453.5</v>
@@ -20142,7 +20142,7 @@
         <v>-4046.108654955806</v>
       </c>
       <c r="E483" t="n">
-        <v>10190.89999999999</v>
+        <v>10700</v>
       </c>
       <c r="F483" t="n">
         <v>2475.5</v>
@@ -20162,7 +20162,7 @@
         <v>-4043.188097460521</v>
       </c>
       <c r="E484" t="n">
-        <v>10234.59999999999</v>
+        <v>10745</v>
       </c>
       <c r="F484" t="n">
         <v>2499</v>
@@ -20182,7 +20182,7 @@
         <v>-4041.925950284332</v>
       </c>
       <c r="E485" t="n">
-        <v>10281.59999999999</v>
+        <v>10792</v>
       </c>
       <c r="F485" t="n">
         <v>2522.5</v>
@@ -20202,7 +20202,7 @@
         <v>-4040.367790099444</v>
       </c>
       <c r="E486" t="n">
-        <v>10327.49999999999</v>
+        <v>10837</v>
       </c>
       <c r="F486" t="n">
         <v>2544.5</v>
@@ -20222,7 +20222,7 @@
         <v>-4047.889551106271</v>
       </c>
       <c r="E487" t="n">
-        <v>10372.49999999999</v>
+        <v>10882</v>
       </c>
       <c r="F487" t="n">
         <v>2568</v>
@@ -20242,7 +20242,7 @@
         <v>-4054.314805480587</v>
       </c>
       <c r="E488" t="n">
-        <v>10413.49999999999</v>
+        <v>10927</v>
       </c>
       <c r="F488" t="n">
         <v>2590</v>
@@ -20262,7 +20262,7 @@
         <v>-4054.61323076822</v>
       </c>
       <c r="E489" t="n">
-        <v>10459.39999999999</v>
+        <v>10974</v>
       </c>
       <c r="F489" t="n">
         <v>2612</v>
@@ -20282,7 +20282,7 @@
         <v>-4052.706525031029</v>
       </c>
       <c r="E490" t="n">
-        <v>10501.29999999999</v>
+        <v>11021</v>
       </c>
       <c r="F490" t="n">
         <v>2632.5</v>
@@ -20302,7 +20302,7 @@
         <v>-4054.532108159449</v>
       </c>
       <c r="E491" t="n">
-        <v>10544.99999999999</v>
+        <v>11068</v>
       </c>
       <c r="F491" t="n">
         <v>2654.5</v>
@@ -20322,7 +20322,7 @@
         <v>-4055.085345573185</v>
       </c>
       <c r="E492" t="n">
-        <v>10585.59999999999</v>
+        <v>11113</v>
       </c>
       <c r="F492" t="n">
         <v>2675</v>
@@ -20342,7 +20342,7 @@
         <v>-4055.677224792183</v>
       </c>
       <c r="E493" t="n">
-        <v>10630.59999999999</v>
+        <v>11158</v>
       </c>
       <c r="F493" t="n">
         <v>2698.5</v>
@@ -20362,7 +20362,7 @@
         <v>-4052.884307252981</v>
       </c>
       <c r="E494" t="n">
-        <v>10674.49999999999</v>
+        <v>11205</v>
       </c>
       <c r="F494" t="n">
         <v>2722</v>
@@ -20382,7 +20382,7 @@
         <v>-4053.024143158859</v>
       </c>
       <c r="E495" t="n">
-        <v>10721.49999999999</v>
+        <v>11252</v>
       </c>
       <c r="F495" t="n">
         <v>2744</v>
@@ -20402,7 +20402,7 @@
         <v>-4055.144808586346</v>
       </c>
       <c r="E496" t="n">
-        <v>10764.09999999999</v>
+        <v>11299</v>
       </c>
       <c r="F496" t="n">
         <v>2767.5</v>
@@ -20422,7 +20422,7 @@
         <v>-4053.920156087494</v>
       </c>
       <c r="E497" t="n">
-        <v>10806.89999999999</v>
+        <v>11346</v>
       </c>
       <c r="F497" t="n">
         <v>2791</v>
@@ -20442,7 +20442,7 @@
         <v>-4051.232614879372</v>
       </c>
       <c r="E498" t="n">
-        <v>10847.69999999999</v>
+        <v>11389</v>
       </c>
       <c r="F498" t="n">
         <v>2811.5</v>
@@ -20462,7 +20462,7 @@
         <v>-4050.40853163551</v>
       </c>
       <c r="E499" t="n">
-        <v>10891.59999999999</v>
+        <v>11432</v>
       </c>
       <c r="F499" t="n">
         <v>2835</v>
@@ -20482,7 +20482,7 @@
         <v>-4047.778277271393</v>
       </c>
       <c r="E500" t="n">
-        <v>10936.39999999999</v>
+        <v>11479</v>
       </c>
       <c r="F500" t="n">
         <v>2858.5</v>
@@ -20502,7 +20502,7 @@
         <v>-4042.788712033161</v>
       </c>
       <c r="E501" t="n">
-        <v>10981.19999999999</v>
+        <v>11526</v>
       </c>
       <c r="F501" t="n">
         <v>2882</v>
@@ -20622,19 +20622,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.962</v>
+        <v>23.052</v>
       </c>
       <c r="C5" t="n">
-        <v>14.461</v>
+        <v>15.039</v>
       </c>
       <c r="D5" t="n">
-        <v>-13.2</v>
+        <v>-13</v>
       </c>
       <c r="E5" t="n">
         <v>47</v>
       </c>
       <c r="F5" t="n">
-        <v>10981.2</v>
+        <v>11526</v>
       </c>
     </row>
     <row r="6">

--- a/results/plots/agent_rewards_cumulative.xlsx
+++ b/results/plots/agent_rewards_cumulative.xlsx
@@ -476,7 +476,7 @@
         <v>-20.88028902850273</v>
       </c>
       <c r="E2" t="n">
-        <v>-3</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
         <v>-0.5</v>
@@ -496,7 +496,7 @@
         <v>-15.08041566639237</v>
       </c>
       <c r="E3" t="n">
-        <v>-13</v>
+        <v>-29</v>
       </c>
       <c r="F3" t="n">
         <v>-18.5</v>
@@ -516,7 +516,7 @@
         <v>-16.24192719111304</v>
       </c>
       <c r="E4" t="n">
-        <v>-3</v>
+        <v>-16</v>
       </c>
       <c r="F4" t="n">
         <v>-18.5</v>
@@ -536,7 +536,7 @@
         <v>-18.76282389482354</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F5" t="n">
         <v>-3.5</v>
@@ -556,7 +556,7 @@
         <v>-9.011605956684511</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>-21</v>
       </c>
       <c r="F6" t="n">
         <v>-12.5</v>
@@ -576,7 +576,7 @@
         <v>-16.88493498782972</v>
       </c>
       <c r="E7" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="F7" t="n">
         <v>-12.5</v>
@@ -596,7 +596,7 @@
         <v>-22.1585517447926</v>
       </c>
       <c r="E8" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="F8" t="n">
         <v>-8</v>
@@ -616,7 +616,7 @@
         <v>-14.86028872807583</v>
       </c>
       <c r="E9" t="n">
-        <v>-11</v>
+        <v>-13</v>
       </c>
       <c r="F9" t="n">
         <v>-11</v>
@@ -636,7 +636,7 @@
         <v>-16.66542535497044</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
         <v>-2</v>
@@ -656,7 +656,7 @@
         <v>-16.50768248317392</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="F11" t="n">
         <v>-11</v>
@@ -676,7 +676,7 @@
         <v>-22.1585747570583</v>
       </c>
       <c r="E12" t="n">
-        <v>-11</v>
+        <v>72</v>
       </c>
       <c r="F12" t="n">
         <v>-12.5</v>
@@ -696,7 +696,7 @@
         <v>-16.07701479937518</v>
       </c>
       <c r="E13" t="n">
-        <v>-9</v>
+        <v>22</v>
       </c>
       <c r="F13" t="n">
         <v>-3.5</v>
@@ -716,7 +716,7 @@
         <v>-25.44342248327767</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F14" t="n">
         <v>-5</v>
@@ -736,7 +736,7 @@
         <v>-14.49481384471911</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F15" t="n">
         <v>-18.5</v>
@@ -756,7 +756,7 @@
         <v>-19.39923887184475</v>
       </c>
       <c r="E16" t="n">
-        <v>-13</v>
+        <v>24</v>
       </c>
       <c r="F16" t="n">
         <v>-12.5</v>
@@ -776,7 +776,7 @@
         <v>-15.21056902635355</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>-12.5</v>
@@ -796,7 +796,7 @@
         <v>-18.66489425226396</v>
       </c>
       <c r="E18" t="n">
-        <v>-11</v>
+        <v>32</v>
       </c>
       <c r="F18" t="n">
         <v>-11</v>
@@ -816,7 +816,7 @@
         <v>-9.011666353277461</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="F19" t="n">
         <v>-12.5</v>
@@ -836,7 +836,7 @@
         <v>-12.42194598309683</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="F20" t="n">
         <v>-8</v>
@@ -856,7 +856,7 @@
         <v>-8.344026407773633</v>
       </c>
       <c r="E21" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
         <v>-17</v>
@@ -876,7 +876,7 @@
         <v>-10.61191573078219</v>
       </c>
       <c r="E22" t="n">
-        <v>-11</v>
+        <v>-25</v>
       </c>
       <c r="F22" t="n">
         <v>-5</v>
@@ -896,7 +896,7 @@
         <v>-13.76809791504057</v>
       </c>
       <c r="E23" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="F23" t="n">
         <v>-21.5</v>
@@ -916,7 +916,7 @@
         <v>-13.61382958064067</v>
       </c>
       <c r="E24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F24" t="n">
         <v>-9.5</v>
@@ -936,7 +936,7 @@
         <v>-17.04709742089801</v>
       </c>
       <c r="E25" t="n">
-        <v>-5</v>
+        <v>28</v>
       </c>
       <c r="F25" t="n">
         <v>-5</v>
@@ -956,7 +956,7 @@
         <v>-11.45515617083332</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F26" t="n">
         <v>-9.5</v>
@@ -976,7 +976,7 @@
         <v>-22.65071637595969</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="F27" t="n">
         <v>-12.5</v>
@@ -996,7 +996,7 @@
         <v>-18.723853564575</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F28" t="n">
         <v>-6.5</v>
@@ -1016,7 +1016,7 @@
         <v>-19.58043031028957</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F29" t="n">
         <v>-11</v>
@@ -1036,7 +1036,7 @@
         <v>-21.81599222693938</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F30" t="n">
         <v>-5</v>
@@ -1056,7 +1056,7 @@
         <v>-12.33207495069766</v>
       </c>
       <c r="E31" t="n">
-        <v>-3</v>
+        <v>65</v>
       </c>
       <c r="F31" t="n">
         <v>-9.5</v>
@@ -1076,7 +1076,7 @@
         <v>-12.07550353950178</v>
       </c>
       <c r="E32" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
@@ -1096,7 +1096,7 @@
         <v>-13.9055061383892</v>
       </c>
       <c r="E33" t="n">
-        <v>-7</v>
+        <v>24</v>
       </c>
       <c r="F33" t="n">
         <v>-5</v>
@@ -1116,7 +1116,7 @@
         <v>-20.68298851778319</v>
       </c>
       <c r="E34" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F34" t="n">
         <v>-0.5</v>
@@ -1136,7 +1136,7 @@
         <v>-13.67390778367567</v>
       </c>
       <c r="E35" t="n">
-        <v>-1</v>
+        <v>41</v>
       </c>
       <c r="F35" t="n">
         <v>-9.5</v>
@@ -1156,7 +1156,7 @@
         <v>-9.665718240118361</v>
       </c>
       <c r="E36" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="F36" t="n">
         <v>-20</v>
@@ -1176,7 +1176,7 @@
         <v>-15.36778170122901</v>
       </c>
       <c r="E37" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="F37" t="n">
         <v>-12.5</v>
@@ -1196,7 +1196,7 @@
         <v>-12.35413898216171</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F38" t="n">
         <v>-21.5</v>
@@ -1216,7 +1216,7 @@
         <v>-16.22217341588913</v>
       </c>
       <c r="E39" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="F39" t="n">
         <v>2.5</v>
@@ -1236,7 +1236,7 @@
         <v>-10.00948967549725</v>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="F40" t="n">
         <v>-17</v>
@@ -1256,7 +1256,7 @@
         <v>-15.10350776269546</v>
       </c>
       <c r="E41" t="n">
-        <v>-3</v>
+        <v>13</v>
       </c>
       <c r="F41" t="n">
         <v>-17</v>
@@ -1276,7 +1276,7 @@
         <v>-13.62641184742081</v>
       </c>
       <c r="E42" t="n">
-        <v>-11</v>
+        <v>16</v>
       </c>
       <c r="F42" t="n">
         <v>-12.5</v>
@@ -1296,7 +1296,7 @@
         <v>-14.71610395027719</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="F43" t="n">
         <v>-11</v>
@@ -1316,7 +1316,7 @@
         <v>-17.32238709223246</v>
       </c>
       <c r="E44" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F44" t="n">
         <v>-6.5</v>
@@ -1336,7 +1336,7 @@
         <v>-18.3985178425561</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="F45" t="n">
         <v>2.5</v>
@@ -1356,7 +1356,7 @@
         <v>-13.92117656900311</v>
       </c>
       <c r="E46" t="n">
-        <v>-7</v>
+        <v>39</v>
       </c>
       <c r="F46" t="n">
         <v>-11</v>
@@ -1376,7 +1376,7 @@
         <v>-11.07952799310252</v>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="F47" t="n">
         <v>-8</v>
@@ -1396,7 +1396,7 @@
         <v>-17.00931480520146</v>
       </c>
       <c r="E48" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F48" t="n">
         <v>-18.5</v>
@@ -1416,7 +1416,7 @@
         <v>-12.51496523440635</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
@@ -1436,7 +1436,7 @@
         <v>-12.56933176486039</v>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="F50" t="n">
         <v>-2</v>
@@ -1456,7 +1456,7 @@
         <v>-18.61042700136766</v>
       </c>
       <c r="E51" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F51" t="n">
         <v>-9.5</v>
@@ -1476,7 +1476,7 @@
         <v>-19.98298420591642</v>
       </c>
       <c r="E52" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="F52" t="n">
         <v>-18.5</v>
@@ -1496,7 +1496,7 @@
         <v>-6.672983718717866</v>
       </c>
       <c r="E53" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F53" t="n">
         <v>-8</v>
@@ -1516,7 +1516,7 @@
         <v>-15.35638027898899</v>
       </c>
       <c r="E54" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F54" t="n">
         <v>-11</v>
@@ -1536,7 +1536,7 @@
         <v>-15.19729180569158</v>
       </c>
       <c r="E55" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F55" t="n">
         <v>-5</v>
@@ -1556,7 +1556,7 @@
         <v>-14.51951403443939</v>
       </c>
       <c r="E56" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>-14</v>
@@ -1576,7 +1576,7 @@
         <v>-16.3915095915476</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F57" t="n">
         <v>-9.5</v>
@@ -1596,7 +1596,7 @@
         <v>-16.72760094092684</v>
       </c>
       <c r="E58" t="n">
-        <v>-9</v>
+        <v>-13</v>
       </c>
       <c r="F58" t="n">
         <v>-9.5</v>
@@ -1616,7 +1616,7 @@
         <v>-11.78050191422369</v>
       </c>
       <c r="E59" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="F59" t="n">
         <v>-9.5</v>
@@ -1636,7 +1636,7 @@
         <v>-13.16902826441466</v>
       </c>
       <c r="E60" t="n">
-        <v>-9</v>
+        <v>82</v>
       </c>
       <c r="F60" t="n">
         <v>-0.5</v>
@@ -1656,7 +1656,7 @@
         <v>-18.54419594854977</v>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F61" t="n">
         <v>-11</v>
@@ -1676,7 +1676,7 @@
         <v>-8.807644726031004</v>
       </c>
       <c r="E62" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="F62" t="n">
         <v>-11</v>
@@ -1696,7 +1696,7 @@
         <v>-14.28909157388709</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="F63" t="n">
         <v>-8</v>
@@ -1716,7 +1716,7 @@
         <v>-15.86301331944633</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="F64" t="n">
         <v>-9.5</v>
@@ -1736,7 +1736,7 @@
         <v>-16.55071283344781</v>
       </c>
       <c r="E65" t="n">
-        <v>-3</v>
+        <v>60</v>
       </c>
       <c r="F65" t="n">
         <v>-0.5</v>
@@ -1756,7 +1756,7 @@
         <v>-17.9336097374753</v>
       </c>
       <c r="E66" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="F66" t="n">
         <v>-17</v>
@@ -1776,7 +1776,7 @@
         <v>-11.96824934592622</v>
       </c>
       <c r="E67" t="n">
-        <v>-5</v>
+        <v>63</v>
       </c>
       <c r="F67" t="n">
         <v>-3.5</v>
@@ -1796,7 +1796,7 @@
         <v>-11.58305819485098</v>
       </c>
       <c r="E68" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F68" t="n">
         <v>-6.5</v>
@@ -1816,7 +1816,7 @@
         <v>-16.96770942927208</v>
       </c>
       <c r="E69" t="n">
-        <v>-11</v>
+        <v>42</v>
       </c>
       <c r="F69" t="n">
         <v>-5</v>
@@ -1836,7 +1836,7 @@
         <v>-13.70594101887073</v>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F70" t="n">
         <v>-11</v>
@@ -1856,7 +1856,7 @@
         <v>-13.35983540697217</v>
       </c>
       <c r="E71" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F71" t="n">
         <v>-11</v>
@@ -1876,7 +1876,7 @@
         <v>-13.73945420010882</v>
       </c>
       <c r="E72" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="F72" t="n">
         <v>-9.5</v>
@@ -1896,7 +1896,7 @@
         <v>-21.43215273472283</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F73" t="n">
         <v>-14</v>
@@ -1916,7 +1916,7 @@
         <v>-19.93026650520377</v>
       </c>
       <c r="E74" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="F74" t="n">
         <v>-6.5</v>
@@ -1936,7 +1936,7 @@
         <v>-13.63373489971633</v>
       </c>
       <c r="E75" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="F75" t="n">
         <v>-9.5</v>
@@ -1956,7 +1956,7 @@
         <v>-14.70893704404678</v>
       </c>
       <c r="E76" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F76" t="n">
         <v>2.5</v>
@@ -1976,7 +1976,7 @@
         <v>-20.41126671783133</v>
       </c>
       <c r="E77" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="F77" t="n">
         <v>-2</v>
@@ -1996,7 +1996,7 @@
         <v>-8.298668334372483</v>
       </c>
       <c r="E78" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F78" t="n">
         <v>-9.5</v>
@@ -2016,7 +2016,7 @@
         <v>-11.09414578630654</v>
       </c>
       <c r="E79" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="F79" t="n">
         <v>-3.5</v>
@@ -2036,7 +2036,7 @@
         <v>-14.76956546226694</v>
       </c>
       <c r="E80" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
         <v>-5</v>
@@ -2056,7 +2056,7 @@
         <v>-14.11114333061668</v>
       </c>
       <c r="E81" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="F81" t="n">
         <v>-11</v>
@@ -2076,7 +2076,7 @@
         <v>-17.36533220259155</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="F82" t="n">
         <v>-9.5</v>
@@ -2096,7 +2096,7 @@
         <v>-14.29537266647307</v>
       </c>
       <c r="E83" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="F83" t="n">
         <v>-11</v>
@@ -2116,7 +2116,7 @@
         <v>-15.52673225528131</v>
       </c>
       <c r="E84" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="F84" t="n">
         <v>-2</v>
@@ -2136,7 +2136,7 @@
         <v>-10.61618120478381</v>
       </c>
       <c r="E85" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="F85" t="n">
         <v>-6.5</v>
@@ -2156,7 +2156,7 @@
         <v>-9.558453099269794</v>
       </c>
       <c r="E86" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F86" t="n">
         <v>-3.5</v>
@@ -2176,7 +2176,7 @@
         <v>-11.95578259847385</v>
       </c>
       <c r="E87" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F87" t="n">
         <v>-2</v>
@@ -2196,7 +2196,7 @@
         <v>-14.53892114818133</v>
       </c>
       <c r="E88" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="F88" t="n">
         <v>-0.5</v>
@@ -2216,7 +2216,7 @@
         <v>-14.98567711898332</v>
       </c>
       <c r="E89" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="F89" t="n">
         <v>-2</v>
@@ -2236,7 +2236,7 @@
         <v>-8.626986066168405</v>
       </c>
       <c r="E90" t="n">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="F90" t="n">
         <v>-9.5</v>
@@ -2256,7 +2256,7 @@
         <v>-14.42115485021459</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
         <v>-2</v>
@@ -2276,7 +2276,7 @@
         <v>-14.81963907250334</v>
       </c>
       <c r="E92" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="F92" t="n">
         <v>-8</v>
@@ -2296,7 +2296,7 @@
         <v>-18.27445887317804</v>
       </c>
       <c r="E93" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F93" t="n">
         <v>-0.5</v>
@@ -2316,7 +2316,7 @@
         <v>-14.01149006572236</v>
       </c>
       <c r="E94" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F94" t="n">
         <v>-2</v>
@@ -2336,7 +2336,7 @@
         <v>-11.76638385536769</v>
       </c>
       <c r="E95" t="n">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="F95" t="n">
         <v>-5</v>
@@ -2356,7 +2356,7 @@
         <v>-9.413356115683376</v>
       </c>
       <c r="E96" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="F96" t="n">
         <v>-5</v>
@@ -2376,7 +2376,7 @@
         <v>-14.28585576463446</v>
       </c>
       <c r="E97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F97" t="n">
         <v>2.5</v>
@@ -2396,7 +2396,7 @@
         <v>-11.85349409751063</v>
       </c>
       <c r="E98" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="F98" t="n">
         <v>-3.5</v>
@@ -2416,7 +2416,7 @@
         <v>-15.24029031651793</v>
       </c>
       <c r="E99" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="F99" t="n">
         <v>-5</v>
@@ -2436,7 +2436,7 @@
         <v>-16.01872556029471</v>
       </c>
       <c r="E100" t="n">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="F100" t="n">
         <v>-2</v>
@@ -2456,7 +2456,7 @@
         <v>-11.30979160160691</v>
       </c>
       <c r="E101" t="n">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
@@ -2476,7 +2476,7 @@
         <v>-15.21465658295874</v>
       </c>
       <c r="E102" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="F102" t="n">
         <v>-9.5</v>
@@ -2496,7 +2496,7 @@
         <v>-11.91209159844877</v>
       </c>
       <c r="E103" t="n">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -2516,7 +2516,7 @@
         <v>-18.47233524338426</v>
       </c>
       <c r="E104" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F104" t="n">
         <v>-11</v>
@@ -2536,7 +2536,7 @@
         <v>-15.99683898329127</v>
       </c>
       <c r="E105" t="n">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="F105" t="n">
         <v>4</v>
@@ -2556,7 +2556,7 @@
         <v>-11.78397827839792</v>
       </c>
       <c r="E106" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="F106" t="n">
         <v>-12.5</v>
@@ -2576,7 +2576,7 @@
         <v>-14.09994806721748</v>
       </c>
       <c r="E107" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F107" t="n">
         <v>-14</v>
@@ -2596,7 +2596,7 @@
         <v>-13.11527797743044</v>
       </c>
       <c r="E108" t="n">
-        <v>21</v>
+        <v>-14</v>
       </c>
       <c r="F108" t="n">
         <v>-9.5</v>
@@ -2616,7 +2616,7 @@
         <v>-10.20573754684604</v>
       </c>
       <c r="E109" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F109" t="n">
         <v>-11</v>
@@ -2636,7 +2636,7 @@
         <v>-12.319581041081</v>
       </c>
       <c r="E110" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F110" t="n">
         <v>-5</v>
@@ -2656,7 +2656,7 @@
         <v>-6.059953702883841</v>
       </c>
       <c r="E111" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F111" t="n">
         <v>-0.5</v>
@@ -2676,7 +2676,7 @@
         <v>-13.07604183385386</v>
       </c>
       <c r="E112" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
@@ -2696,7 +2696,7 @@
         <v>-12.00565567818595</v>
       </c>
       <c r="E113" t="n">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F113" t="n">
         <v>-6.5</v>
@@ -2716,7 +2716,7 @@
         <v>-18.23586872181258</v>
       </c>
       <c r="E114" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F114" t="n">
         <v>-2</v>
@@ -2736,7 +2736,7 @@
         <v>-16.23673636012176</v>
       </c>
       <c r="E115" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F115" t="n">
         <v>-0.5</v>
@@ -2756,7 +2756,7 @@
         <v>-9.138045441859136</v>
       </c>
       <c r="E116" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="F116" t="n">
         <v>-6.5</v>
@@ -2776,7 +2776,7 @@
         <v>-8.735620769461221</v>
       </c>
       <c r="E117" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F117" t="n">
         <v>1</v>
@@ -2796,7 +2796,7 @@
         <v>-3.275988466822424</v>
       </c>
       <c r="E118" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="F118" t="n">
         <v>-2</v>
@@ -2816,7 +2816,7 @@
         <v>-21.46730196390546</v>
       </c>
       <c r="E119" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F119" t="n">
         <v>-8</v>
@@ -2836,7 +2836,7 @@
         <v>-9.30602509382889</v>
       </c>
       <c r="E120" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F120" t="n">
         <v>-2</v>
@@ -2856,7 +2856,7 @@
         <v>-15.45651431364378</v>
       </c>
       <c r="E121" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="F121" t="n">
         <v>-2</v>
@@ -2876,7 +2876,7 @@
         <v>-6.65815148548338</v>
       </c>
       <c r="E122" t="n">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="F122" t="n">
         <v>-8</v>
@@ -2896,7 +2896,7 @@
         <v>-6.936543698335337</v>
       </c>
       <c r="E123" t="n">
-        <v>-1</v>
+        <v>82</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
@@ -2916,7 +2916,7 @@
         <v>-11.38242419822538</v>
       </c>
       <c r="E124" t="n">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="F124" t="n">
         <v>-6.5</v>
@@ -2936,7 +2936,7 @@
         <v>-15.10018684775595</v>
       </c>
       <c r="E125" t="n">
-        <v>7</v>
+        <v>94</v>
       </c>
       <c r="F125" t="n">
         <v>-3.5</v>
@@ -2956,7 +2956,7 @@
         <v>-14.27988774904433</v>
       </c>
       <c r="E126" t="n">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="F126" t="n">
         <v>-5</v>
@@ -2976,7 +2976,7 @@
         <v>-6.334648954400722</v>
       </c>
       <c r="E127" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="F127" t="n">
         <v>-12.5</v>
@@ -2996,7 +2996,7 @@
         <v>-13.5475756767352</v>
       </c>
       <c r="E128" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F128" t="n">
         <v>-6.5</v>
@@ -3016,7 +3016,7 @@
         <v>-11.66477267457763</v>
       </c>
       <c r="E129" t="n">
-        <v>-1</v>
+        <v>70</v>
       </c>
       <c r="F129" t="n">
         <v>-3.5</v>
@@ -3036,7 +3036,7 @@
         <v>-14.70454073338186</v>
       </c>
       <c r="E130" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
@@ -3056,7 +3056,7 @@
         <v>-11.29764528453063</v>
       </c>
       <c r="E131" t="n">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="F131" t="n">
         <v>-5</v>
@@ -3076,7 +3076,7 @@
         <v>-9.092734146744514</v>
       </c>
       <c r="E132" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F132" t="n">
         <v>1</v>
@@ -3096,7 +3096,7 @@
         <v>-7.953307220522068</v>
       </c>
       <c r="E133" t="n">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="F133" t="n">
         <v>-5</v>
@@ -3116,7 +3116,7 @@
         <v>-8.629619074258962</v>
       </c>
       <c r="E134" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="F134" t="n">
         <v>-6.5</v>
@@ -3136,7 +3136,7 @@
         <v>-12.45493151160171</v>
       </c>
       <c r="E135" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F135" t="n">
         <v>5.5</v>
@@ -3156,7 +3156,7 @@
         <v>-15.35178539224634</v>
       </c>
       <c r="E136" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="F136" t="n">
         <v>-3.5</v>
@@ -3176,7 +3176,7 @@
         <v>-14.42757650544786</v>
       </c>
       <c r="E137" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="F137" t="n">
         <v>-11</v>
@@ -3196,7 +3196,7 @@
         <v>-13.78355315746162</v>
       </c>
       <c r="E138" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F138" t="n">
         <v>-5</v>
@@ -3216,7 +3216,7 @@
         <v>-11.16316554267884</v>
       </c>
       <c r="E139" t="n">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="F139" t="n">
         <v>-0.5</v>
@@ -3236,7 +3236,7 @@
         <v>-15.7222577936834</v>
       </c>
       <c r="E140" t="n">
-        <v>9</v>
+        <v>103</v>
       </c>
       <c r="F140" t="n">
         <v>1</v>
@@ -3256,7 +3256,7 @@
         <v>-18.80056717765801</v>
       </c>
       <c r="E141" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F141" t="n">
         <v>5.5</v>
@@ -3276,7 +3276,7 @@
         <v>-12.75547358832381</v>
       </c>
       <c r="E142" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F142" t="n">
         <v>-2</v>
@@ -3296,7 +3296,7 @@
         <v>-13.05017477055378</v>
       </c>
       <c r="E143" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F143" t="n">
         <v>2.5</v>
@@ -3316,7 +3316,7 @@
         <v>-9.492785338822856</v>
       </c>
       <c r="E144" t="n">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="F144" t="n">
         <v>5.5</v>
@@ -3336,7 +3336,7 @@
         <v>-12.82451007415136</v>
       </c>
       <c r="E145" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="F145" t="n">
         <v>-2</v>
@@ -3356,7 +3356,7 @@
         <v>-15.2583426766281</v>
       </c>
       <c r="E146" t="n">
-        <v>-1</v>
+        <v>91</v>
       </c>
       <c r="F146" t="n">
         <v>-5</v>
@@ -3376,7 +3376,7 @@
         <v>-8.936160793676258</v>
       </c>
       <c r="E147" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="F147" t="n">
         <v>-5</v>
@@ -3396,7 +3396,7 @@
         <v>-12.01544842174979</v>
       </c>
       <c r="E148" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F148" t="n">
         <v>-3.5</v>
@@ -3416,7 +3416,7 @@
         <v>-9.976100682743448</v>
       </c>
       <c r="E149" t="n">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="F149" t="n">
         <v>2.5</v>
@@ -3436,7 +3436,7 @@
         <v>-9.072845539237004</v>
       </c>
       <c r="E150" t="n">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="F150" t="n">
         <v>-0.5</v>
@@ -3456,7 +3456,7 @@
         <v>-9.050443784764134</v>
       </c>
       <c r="E151" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="F151" t="n">
         <v>2.5</v>
@@ -3476,7 +3476,7 @@
         <v>-9.19299135802768</v>
       </c>
       <c r="E152" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="F152" t="n">
         <v>-6.5</v>
@@ -3496,7 +3496,7 @@
         <v>-11.48622657143188</v>
       </c>
       <c r="E153" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F153" t="n">
         <v>-5</v>
@@ -3516,7 +3516,7 @@
         <v>-12.33292625264692</v>
       </c>
       <c r="E154" t="n">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="F154" t="n">
         <v>-5</v>
@@ -3536,7 +3536,7 @@
         <v>-8.749082119178086</v>
       </c>
       <c r="E155" t="n">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="F155" t="n">
         <v>-6.5</v>
@@ -3556,7 +3556,7 @@
         <v>-8.914449436079753</v>
       </c>
       <c r="E156" t="n">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="F156" t="n">
         <v>-3.5</v>
@@ -3576,7 +3576,7 @@
         <v>-3.178563438316917</v>
       </c>
       <c r="E157" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="F157" t="n">
         <v>2.5</v>
@@ -3596,7 +3596,7 @@
         <v>-11.29514140666748</v>
       </c>
       <c r="E158" t="n">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="F158" t="n">
         <v>4</v>
@@ -3616,7 +3616,7 @@
         <v>-16.68234331642212</v>
       </c>
       <c r="E159" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F159" t="n">
         <v>5.5</v>
@@ -3636,7 +3636,7 @@
         <v>-17.327950736185</v>
       </c>
       <c r="E160" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="F160" t="n">
         <v>2.5</v>
@@ -3656,7 +3656,7 @@
         <v>-11.49020960393287</v>
       </c>
       <c r="E161" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F161" t="n">
         <v>4</v>
@@ -3676,7 +3676,7 @@
         <v>-1.895934786610538</v>
       </c>
       <c r="E162" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F162" t="n">
         <v>-5</v>
@@ -3696,7 +3696,7 @@
         <v>-11.60328510091501</v>
       </c>
       <c r="E163" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="F163" t="n">
         <v>-9.5</v>
@@ -3716,7 +3716,7 @@
         <v>-4.872661986196267</v>
       </c>
       <c r="E164" t="n">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="F164" t="n">
         <v>-6.5</v>
@@ -3736,7 +3736,7 @@
         <v>-16.53562999078624</v>
       </c>
       <c r="E165" t="n">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="F165" t="n">
         <v>-0.5</v>
@@ -3756,7 +3756,7 @@
         <v>-10.779735566366</v>
       </c>
       <c r="E166" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F166" t="n">
         <v>1</v>
@@ -3776,7 +3776,7 @@
         <v>-7.441839040123449</v>
       </c>
       <c r="E167" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="F167" t="n">
         <v>2.5</v>
@@ -3796,7 +3796,7 @@
         <v>-8.540216823457699</v>
       </c>
       <c r="E168" t="n">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="F168" t="n">
         <v>1</v>
@@ -3816,7 +3816,7 @@
         <v>-13.36124095935507</v>
       </c>
       <c r="E169" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="F169" t="n">
         <v>-6.5</v>
@@ -3836,7 +3836,7 @@
         <v>-7.941572000257956</v>
       </c>
       <c r="E170" t="n">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="F170" t="n">
         <v>7</v>
@@ -3856,7 +3856,7 @@
         <v>-12.24259454888164</v>
       </c>
       <c r="E171" t="n">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="F171" t="n">
         <v>2.5</v>
@@ -3876,7 +3876,7 @@
         <v>-9.577734981138333</v>
       </c>
       <c r="E172" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F172" t="n">
         <v>2.5</v>
@@ -3896,7 +3896,7 @@
         <v>-16.95493489049333</v>
       </c>
       <c r="E173" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F173" t="n">
         <v>-6.5</v>
@@ -3916,7 +3916,7 @@
         <v>-7.956608854497154</v>
       </c>
       <c r="E174" t="n">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="F174" t="n">
         <v>-3.5</v>
@@ -3936,7 +3936,7 @@
         <v>-6.940769548170551</v>
       </c>
       <c r="E175" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="F175" t="n">
         <v>4</v>
@@ -3956,7 +3956,7 @@
         <v>-8.448732765702129</v>
       </c>
       <c r="E176" t="n">
-        <v>13</v>
+        <v>105</v>
       </c>
       <c r="F176" t="n">
         <v>7</v>
@@ -3976,7 +3976,7 @@
         <v>-11.73009639391955</v>
       </c>
       <c r="E177" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="F177" t="n">
         <v>4</v>
@@ -3996,7 +3996,7 @@
         <v>-16.77275246571654</v>
       </c>
       <c r="E178" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F178" t="n">
         <v>7</v>
@@ -4016,7 +4016,7 @@
         <v>-7.272125353914878</v>
       </c>
       <c r="E179" t="n">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="F179" t="n">
         <v>-0.5</v>
@@ -4036,7 +4036,7 @@
         <v>-16.31510018076369</v>
       </c>
       <c r="E180" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F180" t="n">
         <v>-2</v>
@@ -4056,7 +4056,7 @@
         <v>-12.74747409402433</v>
       </c>
       <c r="E181" t="n">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="F181" t="n">
         <v>5.5</v>
@@ -4076,7 +4076,7 @@
         <v>-13.55980417347203</v>
       </c>
       <c r="E182" t="n">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="F182" t="n">
         <v>8.5</v>
@@ -4096,7 +4096,7 @@
         <v>-13.27490502800834</v>
       </c>
       <c r="E183" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="F183" t="n">
         <v>7</v>
@@ -4116,7 +4116,7 @@
         <v>-12.74484715468625</v>
       </c>
       <c r="E184" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F184" t="n">
         <v>7</v>
@@ -4136,7 +4136,7 @@
         <v>-12.34849872044505</v>
       </c>
       <c r="E185" t="n">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="F185" t="n">
         <v>-0.5</v>
@@ -4156,7 +4156,7 @@
         <v>-8.532723933054008</v>
       </c>
       <c r="E186" t="n">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="F186" t="n">
         <v>-0.5</v>
@@ -4176,7 +4176,7 @@
         <v>-7.575287710323443</v>
       </c>
       <c r="E187" t="n">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="F187" t="n">
         <v>-8</v>
@@ -4196,7 +4196,7 @@
         <v>-11.86378417977766</v>
       </c>
       <c r="E188" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F188" t="n">
         <v>5.5</v>
@@ -4216,7 +4216,7 @@
         <v>-12.69125732972837</v>
       </c>
       <c r="E189" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F189" t="n">
         <v>4</v>
@@ -4236,7 +4236,7 @@
         <v>-7.146291150027026</v>
       </c>
       <c r="E190" t="n">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="F190" t="n">
         <v>4</v>
@@ -4256,7 +4256,7 @@
         <v>-10.73034245970168</v>
       </c>
       <c r="E191" t="n">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F191" t="n">
         <v>-8</v>
@@ -4276,7 +4276,7 @@
         <v>-18.78829949929933</v>
       </c>
       <c r="E192" t="n">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="F192" t="n">
         <v>4</v>
@@ -4296,7 +4296,7 @@
         <v>-19.06989102055279</v>
       </c>
       <c r="E193" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F193" t="n">
         <v>8.5</v>
@@ -4316,7 +4316,7 @@
         <v>-5.042595232131265</v>
       </c>
       <c r="E194" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="F194" t="n">
         <v>-0.5</v>
@@ -4336,7 +4336,7 @@
         <v>-7.306725776447404</v>
       </c>
       <c r="E195" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="F195" t="n">
         <v>-2</v>
@@ -4356,7 +4356,7 @@
         <v>-11.2969328754405</v>
       </c>
       <c r="E196" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F196" t="n">
         <v>-0.5</v>
@@ -4376,7 +4376,7 @@
         <v>-10.80408612837662</v>
       </c>
       <c r="E197" t="n">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="F197" t="n">
         <v>-5</v>
@@ -4396,7 +4396,7 @@
         <v>-10.88759817733926</v>
       </c>
       <c r="E198" t="n">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="F198" t="n">
         <v>-0.5</v>
@@ -4416,7 +4416,7 @@
         <v>-13.59431403174799</v>
       </c>
       <c r="E199" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="F199" t="n">
         <v>8.5</v>
@@ -4436,7 +4436,7 @@
         <v>-16.73414753036879</v>
       </c>
       <c r="E200" t="n">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="F200" t="n">
         <v>2.5</v>
@@ -4456,7 +4456,7 @@
         <v>-12.17065885528252</v>
       </c>
       <c r="E201" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="F201" t="n">
         <v>-0.5</v>
@@ -4476,7 +4476,7 @@
         <v>-9.682425408507925</v>
       </c>
       <c r="E202" t="n">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="F202" t="n">
         <v>7</v>
@@ -4496,7 +4496,7 @@
         <v>-14.42541224847953</v>
       </c>
       <c r="E203" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="F203" t="n">
         <v>7</v>
@@ -4516,7 +4516,7 @@
         <v>-11.55982853942983</v>
       </c>
       <c r="E204" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F204" t="n">
         <v>2.5</v>
@@ -4536,7 +4536,7 @@
         <v>-11.76448565489094</v>
       </c>
       <c r="E205" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="F205" t="n">
         <v>4</v>
@@ -4556,7 +4556,7 @@
         <v>-8.468822193825609</v>
       </c>
       <c r="E206" t="n">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="F206" t="n">
         <v>1</v>
@@ -4576,7 +4576,7 @@
         <v>-8.670738161587693</v>
       </c>
       <c r="E207" t="n">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="F207" t="n">
         <v>1</v>
@@ -4596,7 +4596,7 @@
         <v>-7.822106310077424</v>
       </c>
       <c r="E208" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="F208" t="n">
         <v>-14</v>
@@ -4616,7 +4616,7 @@
         <v>-12.1449725681243</v>
       </c>
       <c r="E209" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F209" t="n">
         <v>-6.5</v>
@@ -4636,7 +4636,7 @@
         <v>-7.434250898971669</v>
       </c>
       <c r="E210" t="n">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="F210" t="n">
         <v>4</v>
@@ -4656,7 +4656,7 @@
         <v>-10.3552216026977</v>
       </c>
       <c r="E211" t="n">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="F211" t="n">
         <v>2.5</v>
@@ -4676,7 +4676,7 @@
         <v>-12.97258588476429</v>
       </c>
       <c r="E212" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="F212" t="n">
         <v>5.5</v>
@@ -4696,7 +4696,7 @@
         <v>-7.268733793080432</v>
       </c>
       <c r="E213" t="n">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="F213" t="n">
         <v>8.5</v>
@@ -4716,7 +4716,7 @@
         <v>-14.64730992827486</v>
       </c>
       <c r="E214" t="n">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="F214" t="n">
         <v>11.5</v>
@@ -4736,7 +4736,7 @@
         <v>-6.230069394523568</v>
       </c>
       <c r="E215" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="F215" t="n">
         <v>-6.5</v>
@@ -4756,7 +4756,7 @@
         <v>-5.029168024832028</v>
       </c>
       <c r="E216" t="n">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="F216" t="n">
         <v>4</v>
@@ -4776,7 +4776,7 @@
         <v>-17.20137440692926</v>
       </c>
       <c r="E217" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="F217" t="n">
         <v>-2</v>
@@ -4796,7 +4796,7 @@
         <v>-11.79624044528628</v>
       </c>
       <c r="E218" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F218" t="n">
         <v>7</v>
@@ -4816,7 +4816,7 @@
         <v>-16.74489113681049</v>
       </c>
       <c r="E219" t="n">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="F219" t="n">
         <v>2.5</v>
@@ -4836,7 +4836,7 @@
         <v>-11.34683513007241</v>
       </c>
       <c r="E220" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="F220" t="n">
         <v>5.5</v>
@@ -4856,7 +4856,7 @@
         <v>-4.672589326071132</v>
       </c>
       <c r="E221" t="n">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="F221" t="n">
         <v>4</v>
@@ -4876,7 +4876,7 @@
         <v>-5.574994098887871</v>
       </c>
       <c r="E222" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="F222" t="n">
         <v>-0.5</v>
@@ -4896,7 +4896,7 @@
         <v>-7.561973782123608</v>
       </c>
       <c r="E223" t="n">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="F223" t="n">
         <v>8.5</v>
@@ -4916,7 +4916,7 @@
         <v>-5.122821742112643</v>
       </c>
       <c r="E224" t="n">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="F224" t="n">
         <v>2.5</v>
@@ -4936,7 +4936,7 @@
         <v>-8.540376647193753</v>
       </c>
       <c r="E225" t="n">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="F225" t="n">
         <v>2.5</v>
@@ -4956,7 +4956,7 @@
         <v>-14.38422203108571</v>
       </c>
       <c r="E226" t="n">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="F226" t="n">
         <v>5.5</v>
@@ -4976,7 +4976,7 @@
         <v>-12.3222490983983</v>
       </c>
       <c r="E227" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F227" t="n">
         <v>7</v>
@@ -4996,7 +4996,7 @@
         <v>-8.624119528586101</v>
       </c>
       <c r="E228" t="n">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="F228" t="n">
         <v>1</v>
@@ -5016,7 +5016,7 @@
         <v>-7.642849585159722</v>
       </c>
       <c r="E229" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="F229" t="n">
         <v>-6.5</v>
@@ -5036,7 +5036,7 @@
         <v>-19.21652899798537</v>
       </c>
       <c r="E230" t="n">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="F230" t="n">
         <v>2.5</v>
@@ -5056,7 +5056,7 @@
         <v>-7.446396844456115</v>
       </c>
       <c r="E231" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F231" t="n">
         <v>11.5</v>
@@ -5076,7 +5076,7 @@
         <v>-6.816178332842622</v>
       </c>
       <c r="E232" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="F232" t="n">
         <v>-3.5</v>
@@ -5096,7 +5096,7 @@
         <v>-4.111224791603618</v>
       </c>
       <c r="E233" t="n">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="F233" t="n">
         <v>2.5</v>
@@ -5116,7 +5116,7 @@
         <v>-7.431045844935011</v>
       </c>
       <c r="E234" t="n">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="F234" t="n">
         <v>7</v>
@@ -5136,7 +5136,7 @@
         <v>-3.793921272312653</v>
       </c>
       <c r="E235" t="n">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="F235" t="n">
         <v>10</v>
@@ -5156,7 +5156,7 @@
         <v>-9.390426779972652</v>
       </c>
       <c r="E236" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F236" t="n">
         <v>5.5</v>
@@ -5176,7 +5176,7 @@
         <v>-6.645359241779041</v>
       </c>
       <c r="E237" t="n">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="F237" t="n">
         <v>2.5</v>
@@ -5196,7 +5196,7 @@
         <v>-6.659235330907647</v>
       </c>
       <c r="E238" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F238" t="n">
         <v>10</v>
@@ -5216,7 +5216,7 @@
         <v>-7.389250931299761</v>
       </c>
       <c r="E239" t="n">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="F239" t="n">
         <v>5.5</v>
@@ -5236,7 +5236,7 @@
         <v>-6.601754772706715</v>
       </c>
       <c r="E240" t="n">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="F240" t="n">
         <v>10</v>
@@ -5256,7 +5256,7 @@
         <v>-10.54182006098494</v>
       </c>
       <c r="E241" t="n">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="F241" t="n">
         <v>5.5</v>
@@ -5276,7 +5276,7 @@
         <v>-15.04528412633056</v>
       </c>
       <c r="E242" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F242" t="n">
         <v>10</v>
@@ -5296,7 +5296,7 @@
         <v>-4.485149225985528</v>
       </c>
       <c r="E243" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="F243" t="n">
         <v>7</v>
@@ -5316,7 +5316,7 @@
         <v>-12.90464160657133</v>
       </c>
       <c r="E244" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="F244" t="n">
         <v>5.5</v>
@@ -5336,7 +5336,7 @@
         <v>-10.64541686645118</v>
       </c>
       <c r="E245" t="n">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="F245" t="n">
         <v>2.5</v>
@@ -5356,7 +5356,7 @@
         <v>-10.34030639977348</v>
       </c>
       <c r="E246" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="F246" t="n">
         <v>4</v>
@@ -5376,7 +5376,7 @@
         <v>-10.19854567178833</v>
       </c>
       <c r="E247" t="n">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="F247" t="n">
         <v>8.5</v>
@@ -5396,7 +5396,7 @@
         <v>-5.854820405046824</v>
       </c>
       <c r="E248" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="F248" t="n">
         <v>11.5</v>
@@ -5416,7 +5416,7 @@
         <v>-8.740162907611163</v>
       </c>
       <c r="E249" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="F249" t="n">
         <v>5.5</v>
@@ -5436,7 +5436,7 @@
         <v>-8.67301888488873</v>
       </c>
       <c r="E250" t="n">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="F250" t="n">
         <v>4</v>
@@ -5456,7 +5456,7 @@
         <v>-15.23558737691752</v>
       </c>
       <c r="E251" t="n">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F251" t="n">
         <v>4</v>
@@ -5476,7 +5476,7 @@
         <v>-9.342347585650238</v>
       </c>
       <c r="E252" t="n">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="F252" t="n">
         <v>7</v>
@@ -5496,7 +5496,7 @@
         <v>-4.00963828005715</v>
       </c>
       <c r="E253" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="F253" t="n">
         <v>11.5</v>
@@ -5516,7 +5516,7 @@
         <v>-7.006825558338786</v>
       </c>
       <c r="E254" t="n">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="F254" t="n">
         <v>4</v>
@@ -5536,7 +5536,7 @@
         <v>-9.100522115540389</v>
       </c>
       <c r="E255" t="n">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="F255" t="n">
         <v>7</v>
@@ -5556,7 +5556,7 @@
         <v>-6.682488486241348</v>
       </c>
       <c r="E256" t="n">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="F256" t="n">
         <v>8.5</v>
@@ -5576,7 +5576,7 @@
         <v>-7.919839588373449</v>
       </c>
       <c r="E257" t="n">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="F257" t="n">
         <v>7</v>
@@ -5596,7 +5596,7 @@
         <v>-15.12649928222833</v>
       </c>
       <c r="E258" t="n">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="F258" t="n">
         <v>13</v>
@@ -5616,7 +5616,7 @@
         <v>-4.38164053542964</v>
       </c>
       <c r="E259" t="n">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="F259" t="n">
         <v>5.5</v>
@@ -5636,7 +5636,7 @@
         <v>-9.879498904697028</v>
       </c>
       <c r="E260" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F260" t="n">
         <v>7</v>
@@ -5656,7 +5656,7 @@
         <v>-4.631422886825721</v>
       </c>
       <c r="E261" t="n">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="F261" t="n">
         <v>5.5</v>
@@ -5676,7 +5676,7 @@
         <v>-12.30271398733114</v>
       </c>
       <c r="E262" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F262" t="n">
         <v>11.5</v>
@@ -5696,7 +5696,7 @@
         <v>-7.837332993512454</v>
       </c>
       <c r="E263" t="n">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="F263" t="n">
         <v>10</v>
@@ -5716,7 +5716,7 @@
         <v>-11.30272089467063</v>
       </c>
       <c r="E264" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F264" t="n">
         <v>-2</v>
@@ -5736,7 +5736,7 @@
         <v>-2.232287562273741</v>
       </c>
       <c r="E265" t="n">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="F265" t="n">
         <v>-0.5</v>
@@ -5756,7 +5756,7 @@
         <v>-8.845822814643235</v>
       </c>
       <c r="E266" t="n">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="F266" t="n">
         <v>10</v>
@@ -5776,7 +5776,7 @@
         <v>-17.40506405164033</v>
       </c>
       <c r="E267" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="F267" t="n">
         <v>5.5</v>
@@ -5796,7 +5796,7 @@
         <v>-7.497009722041158</v>
       </c>
       <c r="E268" t="n">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="F268" t="n">
         <v>-8</v>
@@ -5816,7 +5816,7 @@
         <v>-6.347089668468085</v>
       </c>
       <c r="E269" t="n">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="F269" t="n">
         <v>5.5</v>
@@ -5836,7 +5836,7 @@
         <v>-6.612981808812417</v>
       </c>
       <c r="E270" t="n">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="F270" t="n">
         <v>4</v>
@@ -5856,7 +5856,7 @@
         <v>-11.06939687601137</v>
       </c>
       <c r="E271" t="n">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="F271" t="n">
         <v>-5</v>
@@ -5876,7 +5876,7 @@
         <v>-3.758817514648497</v>
       </c>
       <c r="E272" t="n">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="F272" t="n">
         <v>5.5</v>
@@ -5896,7 +5896,7 @@
         <v>-4.051877556375617</v>
       </c>
       <c r="E273" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="F273" t="n">
         <v>7</v>
@@ -5916,7 +5916,7 @@
         <v>-10.52242670855952</v>
       </c>
       <c r="E274" t="n">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="F274" t="n">
         <v>8.5</v>
@@ -5936,7 +5936,7 @@
         <v>-15.126689506234</v>
       </c>
       <c r="E275" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="F275" t="n">
         <v>14.5</v>
@@ -5956,7 +5956,7 @@
         <v>-9.283689005874132</v>
       </c>
       <c r="E276" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="F276" t="n">
         <v>8.5</v>
@@ -5976,7 +5976,7 @@
         <v>-7.94424447213977</v>
       </c>
       <c r="E277" t="n">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="F277" t="n">
         <v>8.5</v>
@@ -5996,7 +5996,7 @@
         <v>-6.180337229755344</v>
       </c>
       <c r="E278" t="n">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="F278" t="n">
         <v>5.5</v>
@@ -6016,7 +6016,7 @@
         <v>-8.982461384875723</v>
       </c>
       <c r="E279" t="n">
-        <v>31</v>
+        <v>160</v>
       </c>
       <c r="F279" t="n">
         <v>5.5</v>
@@ -6036,7 +6036,7 @@
         <v>-11.02713454495316</v>
       </c>
       <c r="E280" t="n">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="F280" t="n">
         <v>13</v>
@@ -6056,7 +6056,7 @@
         <v>-14.250355621725</v>
       </c>
       <c r="E281" t="n">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="F281" t="n">
         <v>4</v>
@@ -6076,7 +6076,7 @@
         <v>-7.381656604173806</v>
       </c>
       <c r="E282" t="n">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="F282" t="n">
         <v>-2</v>
@@ -6096,7 +6096,7 @@
         <v>-1.583944458459632</v>
       </c>
       <c r="E283" t="n">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="F283" t="n">
         <v>8.5</v>
@@ -6116,7 +6116,7 @@
         <v>-4.982880829079921</v>
       </c>
       <c r="E284" t="n">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="F284" t="n">
         <v>7</v>
@@ -6136,7 +6136,7 @@
         <v>-1.993944866098498</v>
       </c>
       <c r="E285" t="n">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="F285" t="n">
         <v>10</v>
@@ -6156,7 +6156,7 @@
         <v>-7.962965242945846</v>
       </c>
       <c r="E286" t="n">
-        <v>33</v>
+        <v>88</v>
       </c>
       <c r="F286" t="n">
         <v>10</v>
@@ -6176,7 +6176,7 @@
         <v>-11.165277873491</v>
       </c>
       <c r="E287" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="F287" t="n">
         <v>5.5</v>
@@ -6196,7 +6196,7 @@
         <v>-7.873822197284354</v>
       </c>
       <c r="E288" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="F288" t="n">
         <v>4</v>
@@ -6216,7 +6216,7 @@
         <v>-5.515009419003278</v>
       </c>
       <c r="E289" t="n">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="F289" t="n">
         <v>10</v>
@@ -6236,7 +6236,7 @@
         <v>-10.62394376937941</v>
       </c>
       <c r="E290" t="n">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="F290" t="n">
         <v>7</v>
@@ -6256,7 +6256,7 @@
         <v>-4.861284849882093</v>
       </c>
       <c r="E291" t="n">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="F291" t="n">
         <v>14.5</v>
@@ -6276,7 +6276,7 @@
         <v>-5.133218124018798</v>
       </c>
       <c r="E292" t="n">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="F292" t="n">
         <v>7</v>
@@ -6296,7 +6296,7 @@
         <v>-8.421038212394912</v>
       </c>
       <c r="E293" t="n">
-        <v>33</v>
+        <v>129</v>
       </c>
       <c r="F293" t="n">
         <v>5.5</v>
@@ -6316,7 +6316,7 @@
         <v>-7.958357982669677</v>
       </c>
       <c r="E294" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="F294" t="n">
         <v>11.5</v>
@@ -6336,7 +6336,7 @@
         <v>-7.403946284003434</v>
       </c>
       <c r="E295" t="n">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="F295" t="n">
         <v>5.5</v>
@@ -6356,7 +6356,7 @@
         <v>-1.924384022657788</v>
       </c>
       <c r="E296" t="n">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="F296" t="n">
         <v>5.5</v>
@@ -6376,7 +6376,7 @@
         <v>-9.63065438938828</v>
       </c>
       <c r="E297" t="n">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="F297" t="n">
         <v>7</v>
@@ -6396,7 +6396,7 @@
         <v>-3.802405797042502</v>
       </c>
       <c r="E298" t="n">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="F298" t="n">
         <v>10</v>
@@ -6416,7 +6416,7 @@
         <v>-2.270559716689897</v>
       </c>
       <c r="E299" t="n">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="F299" t="n">
         <v>10</v>
@@ -6436,7 +6436,7 @@
         <v>-5.067145124015414</v>
       </c>
       <c r="E300" t="n">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="F300" t="n">
         <v>13</v>
@@ -6456,7 +6456,7 @@
         <v>-3.739643154692641</v>
       </c>
       <c r="E301" t="n">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="F301" t="n">
         <v>5.5</v>
@@ -6476,7 +6476,7 @@
         <v>-3.418293055915066</v>
       </c>
       <c r="E302" t="n">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="F302" t="n">
         <v>13</v>
@@ -6496,7 +6496,7 @@
         <v>-4.344905760267247</v>
       </c>
       <c r="E303" t="n">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="F303" t="n">
         <v>7</v>
@@ -6516,7 +6516,7 @@
         <v>-15.2933712096641</v>
       </c>
       <c r="E304" t="n">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="F304" t="n">
         <v>11.5</v>
@@ -6536,7 +6536,7 @@
         <v>-2.833311277806506</v>
       </c>
       <c r="E305" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="F305" t="n">
         <v>11.5</v>
@@ -6556,7 +6556,7 @@
         <v>-6.487566266327902</v>
       </c>
       <c r="E306" t="n">
-        <v>37</v>
+        <v>111</v>
       </c>
       <c r="F306" t="n">
         <v>11.5</v>
@@ -6576,7 +6576,7 @@
         <v>-0.597558805795496</v>
       </c>
       <c r="E307" t="n">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="F307" t="n">
         <v>16</v>
@@ -6596,7 +6596,7 @@
         <v>-7.007631493657506</v>
       </c>
       <c r="E308" t="n">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="F308" t="n">
         <v>4</v>
@@ -6616,7 +6616,7 @@
         <v>-6.356009385510418</v>
       </c>
       <c r="E309" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F309" t="n">
         <v>14.5</v>
@@ -6636,7 +6636,7 @@
         <v>-12.60793338696019</v>
       </c>
       <c r="E310" t="n">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="F310" t="n">
         <v>11.5</v>
@@ -6656,7 +6656,7 @@
         <v>-10.55619850873314</v>
       </c>
       <c r="E311" t="n">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="F311" t="n">
         <v>8.5</v>
@@ -6676,7 +6676,7 @@
         <v>-8.036085399538264</v>
       </c>
       <c r="E312" t="n">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="F312" t="n">
         <v>11.5</v>
@@ -6696,7 +6696,7 @@
         <v>-7.133811441293342</v>
       </c>
       <c r="E313" t="n">
-        <v>25</v>
+        <v>137</v>
       </c>
       <c r="F313" t="n">
         <v>5.5</v>
@@ -6716,7 +6716,7 @@
         <v>-1.537075693521595</v>
       </c>
       <c r="E314" t="n">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="F314" t="n">
         <v>11.5</v>
@@ -6736,7 +6736,7 @@
         <v>-4.000693130585137</v>
       </c>
       <c r="E315" t="n">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="F315" t="n">
         <v>17.5</v>
@@ -6756,7 +6756,7 @@
         <v>-7.442802803480682</v>
       </c>
       <c r="E316" t="n">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="F316" t="n">
         <v>-2</v>
@@ -6776,7 +6776,7 @@
         <v>0.321256182415646</v>
       </c>
       <c r="E317" t="n">
-        <v>25</v>
+        <v>147</v>
       </c>
       <c r="F317" t="n">
         <v>13</v>
@@ -6796,7 +6796,7 @@
         <v>-6.598016050430667</v>
       </c>
       <c r="E318" t="n">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="F318" t="n">
         <v>10</v>
@@ -6816,7 +6816,7 @@
         <v>-6.205783364635726</v>
       </c>
       <c r="E319" t="n">
-        <v>21</v>
+        <v>127</v>
       </c>
       <c r="F319" t="n">
         <v>8.5</v>
@@ -6836,7 +6836,7 @@
         <v>-4.879434422761875</v>
       </c>
       <c r="E320" t="n">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="F320" t="n">
         <v>14.5</v>
@@ -6856,7 +6856,7 @@
         <v>-8.815660834151867</v>
       </c>
       <c r="E321" t="n">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="F321" t="n">
         <v>5.5</v>
@@ -6876,7 +6876,7 @@
         <v>-4.880041842271443</v>
       </c>
       <c r="E322" t="n">
-        <v>37</v>
+        <v>125</v>
       </c>
       <c r="F322" t="n">
         <v>16</v>
@@ -6896,7 +6896,7 @@
         <v>1.3390683303161</v>
       </c>
       <c r="E323" t="n">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="F323" t="n">
         <v>16</v>
@@ -6916,7 +6916,7 @@
         <v>-7.534882036620827</v>
       </c>
       <c r="E324" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="F324" t="n">
         <v>13</v>
@@ -6936,7 +6936,7 @@
         <v>-1.437938527968541</v>
       </c>
       <c r="E325" t="n">
-        <v>33</v>
+        <v>123</v>
       </c>
       <c r="F325" t="n">
         <v>8.5</v>
@@ -6956,7 +6956,7 @@
         <v>-3.084487384043165</v>
       </c>
       <c r="E326" t="n">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c r="F326" t="n">
         <v>11.5</v>
@@ -6976,7 +6976,7 @@
         <v>-4.984577567865049</v>
       </c>
       <c r="E327" t="n">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="F327" t="n">
         <v>14.5</v>
@@ -6996,7 +6996,7 @@
         <v>-12.47954626896995</v>
       </c>
       <c r="E328" t="n">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="F328" t="n">
         <v>14.5</v>
@@ -7016,7 +7016,7 @@
         <v>-10.71310955210427</v>
       </c>
       <c r="E329" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="F329" t="n">
         <v>16</v>
@@ -7036,7 +7036,7 @@
         <v>-4.214159442252412</v>
       </c>
       <c r="E330" t="n">
-        <v>27</v>
+        <v>147</v>
       </c>
       <c r="F330" t="n">
         <v>10</v>
@@ -7056,7 +7056,7 @@
         <v>-10.32175432625408</v>
       </c>
       <c r="E331" t="n">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="F331" t="n">
         <v>8.5</v>
@@ -7076,7 +7076,7 @@
         <v>-3.847451207287437</v>
       </c>
       <c r="E332" t="n">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="F332" t="n">
         <v>11.5</v>
@@ -7096,7 +7096,7 @@
         <v>-7.577111428170915</v>
       </c>
       <c r="E333" t="n">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="F333" t="n">
         <v>4</v>
@@ -7116,7 +7116,7 @@
         <v>-12.39685699336666</v>
       </c>
       <c r="E334" t="n">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="F334" t="n">
         <v>14.5</v>
@@ -7136,7 +7136,7 @@
         <v>-4.536191961028859</v>
       </c>
       <c r="E335" t="n">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="F335" t="n">
         <v>13</v>
@@ -7156,7 +7156,7 @@
         <v>-3.793876976120675</v>
       </c>
       <c r="E336" t="n">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="F336" t="n">
         <v>7</v>
@@ -7176,7 +7176,7 @@
         <v>1.892030835894608</v>
       </c>
       <c r="E337" t="n">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="F337" t="n">
         <v>7</v>
@@ -7196,7 +7196,7 @@
         <v>-6.876610785137544</v>
       </c>
       <c r="E338" t="n">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="F338" t="n">
         <v>10</v>
@@ -7216,7 +7216,7 @@
         <v>-1.615861001382153</v>
       </c>
       <c r="E339" t="n">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="F339" t="n">
         <v>11.5</v>
@@ -7236,7 +7236,7 @@
         <v>-5.341940188564537</v>
       </c>
       <c r="E340" t="n">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="F340" t="n">
         <v>10</v>
@@ -7256,7 +7256,7 @@
         <v>-5.309355549382947</v>
       </c>
       <c r="E341" t="n">
-        <v>37</v>
+        <v>111</v>
       </c>
       <c r="F341" t="n">
         <v>16</v>
@@ -7276,7 +7276,7 @@
         <v>-5.062973998838486</v>
       </c>
       <c r="E342" t="n">
-        <v>33</v>
+        <v>126</v>
       </c>
       <c r="F342" t="n">
         <v>13</v>
@@ -7296,7 +7296,7 @@
         <v>-3.868067795346402</v>
       </c>
       <c r="E343" t="n">
-        <v>31</v>
+        <v>112</v>
       </c>
       <c r="F343" t="n">
         <v>13</v>
@@ -7316,7 +7316,7 @@
         <v>-1.295206924452152</v>
       </c>
       <c r="E344" t="n">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="F344" t="n">
         <v>11.5</v>
@@ -7336,7 +7336,7 @@
         <v>-4.563509516184059</v>
       </c>
       <c r="E345" t="n">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="F345" t="n">
         <v>11.5</v>
@@ -7356,7 +7356,7 @@
         <v>-4.52968578496577</v>
       </c>
       <c r="E346" t="n">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="F346" t="n">
         <v>14.5</v>
@@ -7376,7 +7376,7 @@
         <v>0.5616403015032345</v>
       </c>
       <c r="E347" t="n">
-        <v>31</v>
+        <v>137</v>
       </c>
       <c r="F347" t="n">
         <v>8.5</v>
@@ -7396,7 +7396,7 @@
         <v>-1.932480718018562</v>
       </c>
       <c r="E348" t="n">
-        <v>33</v>
+        <v>117</v>
       </c>
       <c r="F348" t="n">
         <v>16</v>
@@ -7416,7 +7416,7 @@
         <v>-2.492076983508796</v>
       </c>
       <c r="E349" t="n">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="F349" t="n">
         <v>13</v>
@@ -7436,7 +7436,7 @@
         <v>-6.866377835308298</v>
       </c>
       <c r="E350" t="n">
-        <v>43</v>
+        <v>145</v>
       </c>
       <c r="F350" t="n">
         <v>5.5</v>
@@ -7456,7 +7456,7 @@
         <v>-8.46601744993502</v>
       </c>
       <c r="E351" t="n">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="F351" t="n">
         <v>5.5</v>
@@ -7476,7 +7476,7 @@
         <v>-8.503358770040659</v>
       </c>
       <c r="E352" t="n">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="F352" t="n">
         <v>8.5</v>
@@ -7496,7 +7496,7 @@
         <v>-3.401522239735685</v>
       </c>
       <c r="E353" t="n">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="F353" t="n">
         <v>5.5</v>
@@ -7516,7 +7516,7 @@
         <v>-4.889302168656975</v>
       </c>
       <c r="E354" t="n">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="F354" t="n">
         <v>5.5</v>
@@ -7536,7 +7536,7 @@
         <v>-5.45993309037005</v>
       </c>
       <c r="E355" t="n">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="F355" t="n">
         <v>14.5</v>
@@ -7556,7 +7556,7 @@
         <v>-2.72317301315674</v>
       </c>
       <c r="E356" t="n">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="F356" t="n">
         <v>14.5</v>
@@ -7576,7 +7576,7 @@
         <v>-7.169360862597371</v>
       </c>
       <c r="E357" t="n">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="F357" t="n">
         <v>13</v>
@@ -7596,7 +7596,7 @@
         <v>-10.81470985813222</v>
       </c>
       <c r="E358" t="n">
-        <v>43</v>
+        <v>115</v>
       </c>
       <c r="F358" t="n">
         <v>14.5</v>
@@ -7616,7 +7616,7 @@
         <v>-8.107163803570021</v>
       </c>
       <c r="E359" t="n">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="F359" t="n">
         <v>11.5</v>
@@ -7636,7 +7636,7 @@
         <v>-6.220465292608457</v>
       </c>
       <c r="E360" t="n">
-        <v>45</v>
+        <v>137</v>
       </c>
       <c r="F360" t="n">
         <v>19</v>
@@ -7656,7 +7656,7 @@
         <v>-5.504144096772184</v>
       </c>
       <c r="E361" t="n">
-        <v>39</v>
+        <v>115</v>
       </c>
       <c r="F361" t="n">
         <v>8.5</v>
@@ -7676,7 +7676,7 @@
         <v>-2.475755123102916</v>
       </c>
       <c r="E362" t="n">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="F362" t="n">
         <v>17.5</v>
@@ -7696,7 +7696,7 @@
         <v>-7.444069608672705</v>
       </c>
       <c r="E363" t="n">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="F363" t="n">
         <v>14.5</v>
@@ -7716,7 +7716,7 @@
         <v>-2.021784772990322</v>
       </c>
       <c r="E364" t="n">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="F364" t="n">
         <v>14.5</v>
@@ -7736,7 +7736,7 @@
         <v>-2.354104958383093</v>
       </c>
       <c r="E365" t="n">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="F365" t="n">
         <v>19</v>
@@ -7756,7 +7756,7 @@
         <v>-6.192040211684938</v>
       </c>
       <c r="E366" t="n">
-        <v>31</v>
+        <v>161</v>
       </c>
       <c r="F366" t="n">
         <v>20.5</v>
@@ -7776,7 +7776,7 @@
         <v>-5.675692005440896</v>
       </c>
       <c r="E367" t="n">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="F367" t="n">
         <v>16</v>
@@ -7796,7 +7796,7 @@
         <v>-6.218050842224281</v>
       </c>
       <c r="E368" t="n">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="F368" t="n">
         <v>19</v>
@@ -7816,7 +7816,7 @@
         <v>-3.07883011643317</v>
       </c>
       <c r="E369" t="n">
-        <v>31</v>
+        <v>111</v>
       </c>
       <c r="F369" t="n">
         <v>16</v>
@@ -7836,7 +7836,7 @@
         <v>0.4454353742164699</v>
       </c>
       <c r="E370" t="n">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="F370" t="n">
         <v>19</v>
@@ -7856,7 +7856,7 @@
         <v>-5.299662112462816</v>
       </c>
       <c r="E371" t="n">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="F371" t="n">
         <v>20.5</v>
@@ -7876,7 +7876,7 @@
         <v>-4.275349160139813</v>
       </c>
       <c r="E372" t="n">
-        <v>41</v>
+        <v>137</v>
       </c>
       <c r="F372" t="n">
         <v>20.5</v>
@@ -7896,7 +7896,7 @@
         <v>2.760114520882845</v>
       </c>
       <c r="E373" t="n">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="F373" t="n">
         <v>11.5</v>
@@ -7916,7 +7916,7 @@
         <v>-2.233175560934974</v>
       </c>
       <c r="E374" t="n">
-        <v>33</v>
+        <v>125</v>
       </c>
       <c r="F374" t="n">
         <v>11.5</v>
@@ -7936,7 +7936,7 @@
         <v>-3.849263004804139</v>
       </c>
       <c r="E375" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="F375" t="n">
         <v>13</v>
@@ -7956,7 +7956,7 @@
         <v>-7.439318426871877</v>
       </c>
       <c r="E376" t="n">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="F376" t="n">
         <v>16</v>
@@ -7976,7 +7976,7 @@
         <v>0.3988126622416603</v>
       </c>
       <c r="E377" t="n">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="F377" t="n">
         <v>17.5</v>
@@ -7996,7 +7996,7 @@
         <v>-5.219605923776177</v>
       </c>
       <c r="E378" t="n">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="F378" t="n">
         <v>10</v>
@@ -8016,7 +8016,7 @@
         <v>1.436115308975747</v>
       </c>
       <c r="E379" t="n">
-        <v>33</v>
+        <v>117</v>
       </c>
       <c r="F379" t="n">
         <v>20.5</v>
@@ -8036,7 +8036,7 @@
         <v>-2.555545674890773</v>
       </c>
       <c r="E380" t="n">
-        <v>43</v>
+        <v>115</v>
       </c>
       <c r="F380" t="n">
         <v>16</v>
@@ -8056,7 +8056,7 @@
         <v>-5.898584918723315</v>
       </c>
       <c r="E381" t="n">
-        <v>39</v>
+        <v>154</v>
       </c>
       <c r="F381" t="n">
         <v>14.5</v>
@@ -8076,7 +8076,7 @@
         <v>-7.073209898845452</v>
       </c>
       <c r="E382" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="F382" t="n">
         <v>7</v>
@@ -8096,7 +8096,7 @@
         <v>-3.622977285184998</v>
       </c>
       <c r="E383" t="n">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="F383" t="n">
         <v>19</v>
@@ -8116,7 +8116,7 @@
         <v>-9.917287036815871</v>
       </c>
       <c r="E384" t="n">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="F384" t="n">
         <v>13</v>
@@ -8136,7 +8136,7 @@
         <v>0.5373091015979023</v>
       </c>
       <c r="E385" t="n">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="F385" t="n">
         <v>17.5</v>
@@ -8156,7 +8156,7 @@
         <v>-0.9602138229564684</v>
       </c>
       <c r="E386" t="n">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="F386" t="n">
         <v>14.5</v>
@@ -8176,7 +8176,7 @@
         <v>-2.535567183211558</v>
       </c>
       <c r="E387" t="n">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="F387" t="n">
         <v>10</v>
@@ -8196,7 +8196,7 @@
         <v>2.200141246463018</v>
       </c>
       <c r="E388" t="n">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="F388" t="n">
         <v>11.5</v>
@@ -8216,7 +8216,7 @@
         <v>1.811103417675227</v>
       </c>
       <c r="E389" t="n">
-        <v>37</v>
+        <v>145</v>
       </c>
       <c r="F389" t="n">
         <v>17.5</v>
@@ -8236,7 +8236,7 @@
         <v>-9.225704108485532</v>
       </c>
       <c r="E390" t="n">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="F390" t="n">
         <v>14.5</v>
@@ -8256,7 +8256,7 @@
         <v>-4.416245606870039</v>
       </c>
       <c r="E391" t="n">
-        <v>43</v>
+        <v>127</v>
       </c>
       <c r="F391" t="n">
         <v>14.5</v>
@@ -8276,7 +8276,7 @@
         <v>-1.257155408909161</v>
       </c>
       <c r="E392" t="n">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="F392" t="n">
         <v>16</v>
@@ -8296,7 +8296,7 @@
         <v>-4.429092056794652</v>
       </c>
       <c r="E393" t="n">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="F393" t="n">
         <v>14.5</v>
@@ -8316,7 +8316,7 @@
         <v>-2.148827803887845</v>
       </c>
       <c r="E394" t="n">
-        <v>33</v>
+        <v>140</v>
       </c>
       <c r="F394" t="n">
         <v>14.5</v>
@@ -8336,7 +8336,7 @@
         <v>-6.628430276399285</v>
       </c>
       <c r="E395" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="F395" t="n">
         <v>17.5</v>
@@ -8356,7 +8356,7 @@
         <v>-2.811622576116388</v>
       </c>
       <c r="E396" t="n">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="F396" t="n">
         <v>11.5</v>
@@ -8376,7 +8376,7 @@
         <v>1.516348024524294</v>
       </c>
       <c r="E397" t="n">
-        <v>31</v>
+        <v>178</v>
       </c>
       <c r="F397" t="n">
         <v>19</v>
@@ -8396,7 +8396,7 @@
         <v>0.7759562547179837</v>
       </c>
       <c r="E398" t="n">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="F398" t="n">
         <v>20.5</v>
@@ -8416,7 +8416,7 @@
         <v>-7.521513945763667</v>
       </c>
       <c r="E399" t="n">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="F399" t="n">
         <v>19</v>
@@ -8436,7 +8436,7 @@
         <v>5.906920073781943</v>
       </c>
       <c r="E400" t="n">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="F400" t="n">
         <v>14.5</v>
@@ -8456,7 +8456,7 @@
         <v>-1.152800133799763</v>
       </c>
       <c r="E401" t="n">
-        <v>39</v>
+        <v>143</v>
       </c>
       <c r="F401" t="n">
         <v>17.5</v>
@@ -8476,7 +8476,7 @@
         <v>1.92235435186735</v>
       </c>
       <c r="E402" t="n">
-        <v>41</v>
+        <v>157</v>
       </c>
       <c r="F402" t="n">
         <v>13</v>
@@ -8496,7 +8496,7 @@
         <v>-1.324647806147128</v>
       </c>
       <c r="E403" t="n">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="F403" t="n">
         <v>13</v>
@@ -8516,7 +8516,7 @@
         <v>-1.675220191202326</v>
       </c>
       <c r="E404" t="n">
-        <v>31</v>
+        <v>137</v>
       </c>
       <c r="F404" t="n">
         <v>17.5</v>
@@ -8536,7 +8536,7 @@
         <v>3.285523000699553</v>
       </c>
       <c r="E405" t="n">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="F405" t="n">
         <v>11.5</v>
@@ -8556,7 +8556,7 @@
         <v>1.498901900880138</v>
       </c>
       <c r="E406" t="n">
-        <v>29</v>
+        <v>122</v>
       </c>
       <c r="F406" t="n">
         <v>16</v>
@@ -8576,7 +8576,7 @@
         <v>0.3891414475957226</v>
       </c>
       <c r="E407" t="n">
-        <v>37</v>
+        <v>110</v>
       </c>
       <c r="F407" t="n">
         <v>20.5</v>
@@ -8596,7 +8596,7 @@
         <v>-5.627019008818197</v>
       </c>
       <c r="E408" t="n">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="F408" t="n">
         <v>14.5</v>
@@ -8616,7 +8616,7 @@
         <v>-7.430110984826372</v>
       </c>
       <c r="E409" t="n">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="F409" t="n">
         <v>22</v>
@@ -8636,7 +8636,7 @@
         <v>0.125617946470375</v>
       </c>
       <c r="E410" t="n">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="F410" t="n">
         <v>20.5</v>
@@ -8656,7 +8656,7 @@
         <v>-5.092614484938498</v>
       </c>
       <c r="E411" t="n">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="F411" t="n">
         <v>10</v>
@@ -8676,7 +8676,7 @@
         <v>-4.108693146142889</v>
       </c>
       <c r="E412" t="n">
-        <v>37</v>
+        <v>106</v>
       </c>
       <c r="F412" t="n">
         <v>13</v>
@@ -8696,7 +8696,7 @@
         <v>-7.463804828800212</v>
       </c>
       <c r="E413" t="n">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="F413" t="n">
         <v>17.5</v>
@@ -8716,7 +8716,7 @@
         <v>-1.055122844270363</v>
       </c>
       <c r="E414" t="n">
-        <v>37</v>
+        <v>131</v>
       </c>
       <c r="F414" t="n">
         <v>16</v>
@@ -8736,7 +8736,7 @@
         <v>-1.215686709645218</v>
       </c>
       <c r="E415" t="n">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="F415" t="n">
         <v>17.5</v>
@@ -8756,7 +8756,7 @@
         <v>-4.396800403551372</v>
       </c>
       <c r="E416" t="n">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="F416" t="n">
         <v>22</v>
@@ -8776,7 +8776,7 @@
         <v>-2.291263596076391</v>
       </c>
       <c r="E417" t="n">
-        <v>43</v>
+        <v>147</v>
       </c>
       <c r="F417" t="n">
         <v>22</v>
@@ -8796,7 +8796,7 @@
         <v>-1.338984177475091</v>
       </c>
       <c r="E418" t="n">
-        <v>35</v>
+        <v>161</v>
       </c>
       <c r="F418" t="n">
         <v>19</v>
@@ -8816,7 +8816,7 @@
         <v>-2.378608825728114</v>
       </c>
       <c r="E419" t="n">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="F419" t="n">
         <v>20.5</v>
@@ -8836,7 +8836,7 @@
         <v>-4.478171664319876</v>
       </c>
       <c r="E420" t="n">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="F420" t="n">
         <v>19</v>
@@ -8856,7 +8856,7 @@
         <v>3.493919627918584</v>
       </c>
       <c r="E421" t="n">
-        <v>33</v>
+        <v>144</v>
       </c>
       <c r="F421" t="n">
         <v>20.5</v>
@@ -8876,7 +8876,7 @@
         <v>-0.4493073074287441</v>
       </c>
       <c r="E422" t="n">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="F422" t="n">
         <v>19</v>
@@ -8896,7 +8896,7 @@
         <v>-3.529479282034087</v>
       </c>
       <c r="E423" t="n">
-        <v>43</v>
+        <v>143</v>
       </c>
       <c r="F423" t="n">
         <v>20.5</v>
@@ -8916,7 +8916,7 @@
         <v>5.505363169646428</v>
       </c>
       <c r="E424" t="n">
-        <v>37</v>
+        <v>147</v>
       </c>
       <c r="F424" t="n">
         <v>16</v>
@@ -8936,7 +8936,7 @@
         <v>-1.289749166080068</v>
       </c>
       <c r="E425" t="n">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="F425" t="n">
         <v>17.5</v>
@@ -8956,7 +8956,7 @@
         <v>-6.328346785914285</v>
       </c>
       <c r="E426" t="n">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="F426" t="n">
         <v>19</v>
@@ -8976,7 +8976,7 @@
         <v>-2.245770890171666</v>
       </c>
       <c r="E427" t="n">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="F427" t="n">
         <v>20.5</v>
@@ -8996,7 +8996,7 @@
         <v>0.8586256083960975</v>
       </c>
       <c r="E428" t="n">
-        <v>35</v>
+        <v>156</v>
       </c>
       <c r="F428" t="n">
         <v>20.5</v>
@@ -9016,7 +9016,7 @@
         <v>-1.440130905972663</v>
       </c>
       <c r="E429" t="n">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="F429" t="n">
         <v>17.5</v>
@@ -9036,7 +9036,7 @@
         <v>-6.031533531499719</v>
       </c>
       <c r="E430" t="n">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="F430" t="n">
         <v>17.5</v>
@@ -9056,7 +9056,7 @@
         <v>-6.483394036182426</v>
       </c>
       <c r="E431" t="n">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="F431" t="n">
         <v>22</v>
@@ -9076,7 +9076,7 @@
         <v>-4.129181923723293</v>
       </c>
       <c r="E432" t="n">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="F432" t="n">
         <v>14.5</v>
@@ -9096,7 +9096,7 @@
         <v>-0.5394951999804173</v>
       </c>
       <c r="E433" t="n">
-        <v>39</v>
+        <v>148</v>
       </c>
       <c r="F433" t="n">
         <v>19</v>
@@ -9116,7 +9116,7 @@
         <v>-4.91737737000209</v>
       </c>
       <c r="E434" t="n">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="F434" t="n">
         <v>22</v>
@@ -9136,7 +9136,7 @@
         <v>-1.629499795376638</v>
       </c>
       <c r="E435" t="n">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="F435" t="n">
         <v>19</v>
@@ -9156,7 +9156,7 @@
         <v>-2.000851078070042</v>
       </c>
       <c r="E436" t="n">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="F436" t="n">
         <v>23.5</v>
@@ -9176,7 +9176,7 @@
         <v>-0.6395139177057325</v>
       </c>
       <c r="E437" t="n">
-        <v>45</v>
+        <v>153</v>
       </c>
       <c r="F437" t="n">
         <v>16</v>
@@ -9196,7 +9196,7 @@
         <v>-3.783377107596139</v>
       </c>
       <c r="E438" t="n">
-        <v>39</v>
+        <v>131</v>
       </c>
       <c r="F438" t="n">
         <v>19</v>
@@ -9216,7 +9216,7 @@
         <v>-0.1908777370631427</v>
       </c>
       <c r="E439" t="n">
-        <v>43</v>
+        <v>161</v>
       </c>
       <c r="F439" t="n">
         <v>17.5</v>
@@ -9236,7 +9236,7 @@
         <v>4.759227350410999</v>
       </c>
       <c r="E440" t="n">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="F440" t="n">
         <v>17.5</v>
@@ -9256,7 +9256,7 @@
         <v>0.677884067585573</v>
       </c>
       <c r="E441" t="n">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="F441" t="n">
         <v>17.5</v>
@@ -9276,7 +9276,7 @@
         <v>-0.0717583649901857</v>
       </c>
       <c r="E442" t="n">
-        <v>43</v>
+        <v>137</v>
       </c>
       <c r="F442" t="n">
         <v>19</v>
@@ -9296,7 +9296,7 @@
         <v>-1.541966372324565</v>
       </c>
       <c r="E443" t="n">
-        <v>45</v>
+        <v>161</v>
       </c>
       <c r="F443" t="n">
         <v>19</v>
@@ -9316,7 +9316,7 @@
         <v>-1.084744409189314</v>
       </c>
       <c r="E444" t="n">
-        <v>43</v>
+        <v>169</v>
       </c>
       <c r="F444" t="n">
         <v>22</v>
@@ -9336,7 +9336,7 @@
         <v>2.477458202909179</v>
       </c>
       <c r="E445" t="n">
-        <v>41</v>
+        <v>148</v>
       </c>
       <c r="F445" t="n">
         <v>16</v>
@@ -9356,7 +9356,7 @@
         <v>-0.888641577089203</v>
       </c>
       <c r="E446" t="n">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="F446" t="n">
         <v>17.5</v>
@@ -9376,7 +9376,7 @@
         <v>-4.142588259792474</v>
       </c>
       <c r="E447" t="n">
-        <v>43</v>
+        <v>119</v>
       </c>
       <c r="F447" t="n">
         <v>19</v>
@@ -9396,7 +9396,7 @@
         <v>-7.494413186848452</v>
       </c>
       <c r="E448" t="n">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="F448" t="n">
         <v>23.5</v>
@@ -9416,7 +9416,7 @@
         <v>-0.5810422459860057</v>
       </c>
       <c r="E449" t="n">
-        <v>35</v>
+        <v>112</v>
       </c>
       <c r="F449" t="n">
         <v>19</v>
@@ -9436,7 +9436,7 @@
         <v>-0.4650566229847108</v>
       </c>
       <c r="E450" t="n">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="F450" t="n">
         <v>22</v>
@@ -9456,7 +9456,7 @@
         <v>-0.1039621030240891</v>
       </c>
       <c r="E451" t="n">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="F451" t="n">
         <v>19</v>
@@ -9476,7 +9476,7 @@
         <v>0.5667753408456071</v>
       </c>
       <c r="E452" t="n">
-        <v>39</v>
+        <v>137</v>
       </c>
       <c r="F452" t="n">
         <v>19</v>
@@ -9496,7 +9496,7 @@
         <v>0.8474447506843528</v>
       </c>
       <c r="E453" t="n">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="F453" t="n">
         <v>17.5</v>
@@ -9516,7 +9516,7 @@
         <v>1.226056193573341</v>
       </c>
       <c r="E454" t="n">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="F454" t="n">
         <v>16</v>
@@ -9536,7 +9536,7 @@
         <v>-1.449163043556349</v>
       </c>
       <c r="E455" t="n">
-        <v>39</v>
+        <v>118</v>
       </c>
       <c r="F455" t="n">
         <v>19</v>
@@ -9556,7 +9556,7 @@
         <v>-7.063041762791196</v>
       </c>
       <c r="E456" t="n">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="F456" t="n">
         <v>19</v>
@@ -9576,7 +9576,7 @@
         <v>-3.258944684774359</v>
       </c>
       <c r="E457" t="n">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="F457" t="n">
         <v>19</v>
@@ -9596,7 +9596,7 @@
         <v>0.3038155417847883</v>
       </c>
       <c r="E458" t="n">
-        <v>43</v>
+        <v>158</v>
       </c>
       <c r="F458" t="n">
         <v>20.5</v>
@@ -9616,7 +9616,7 @@
         <v>2.925567382898333</v>
       </c>
       <c r="E459" t="n">
-        <v>45</v>
+        <v>164</v>
       </c>
       <c r="F459" t="n">
         <v>20.5</v>
@@ -9636,7 +9636,7 @@
         <v>1.227335378612259</v>
       </c>
       <c r="E460" t="n">
-        <v>35</v>
+        <v>158</v>
       </c>
       <c r="F460" t="n">
         <v>22</v>
@@ -9656,7 +9656,7 @@
         <v>0.3567135355337989</v>
       </c>
       <c r="E461" t="n">
-        <v>47</v>
+        <v>167</v>
       </c>
       <c r="F461" t="n">
         <v>20.5</v>
@@ -9676,7 +9676,7 @@
         <v>-5.230389973549588</v>
       </c>
       <c r="E462" t="n">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="F462" t="n">
         <v>16</v>
@@ -9696,7 +9696,7 @@
         <v>-4.468962519235912</v>
       </c>
       <c r="E463" t="n">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="F463" t="n">
         <v>22</v>
@@ -9716,7 +9716,7 @@
         <v>3.142223358714665</v>
       </c>
       <c r="E464" t="n">
-        <v>47</v>
+        <v>166</v>
       </c>
       <c r="F464" t="n">
         <v>20.5</v>
@@ -9736,7 +9736,7 @@
         <v>1.02510534400717</v>
       </c>
       <c r="E465" t="n">
-        <v>43</v>
+        <v>175</v>
       </c>
       <c r="F465" t="n">
         <v>22</v>
@@ -9756,7 +9756,7 @@
         <v>-0.6141674555601673</v>
       </c>
       <c r="E466" t="n">
-        <v>47</v>
+        <v>168</v>
       </c>
       <c r="F466" t="n">
         <v>20.5</v>
@@ -9776,7 +9776,7 @@
         <v>-0.8160733879181367</v>
       </c>
       <c r="E467" t="n">
-        <v>41</v>
+        <v>137</v>
       </c>
       <c r="F467" t="n">
         <v>20.5</v>
@@ -9796,7 +9796,7 @@
         <v>1.137338576071934</v>
       </c>
       <c r="E468" t="n">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="F468" t="n">
         <v>23.5</v>
@@ -9816,7 +9816,7 @@
         <v>0.6915120900000564</v>
       </c>
       <c r="E469" t="n">
-        <v>47</v>
+        <v>152</v>
       </c>
       <c r="F469" t="n">
         <v>22</v>
@@ -9836,7 +9836,7 @@
         <v>2.250366219827656</v>
       </c>
       <c r="E470" t="n">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="F470" t="n">
         <v>20.5</v>
@@ -9856,7 +9856,7 @@
         <v>0.0206075063874691</v>
       </c>
       <c r="E471" t="n">
-        <v>47</v>
+        <v>165</v>
       </c>
       <c r="F471" t="n">
         <v>20.5</v>
@@ -9876,7 +9876,7 @@
         <v>-1.059969664252619</v>
       </c>
       <c r="E472" t="n">
-        <v>43</v>
+        <v>168</v>
       </c>
       <c r="F472" t="n">
         <v>19</v>
@@ -9896,7 +9896,7 @@
         <v>-1.707842522936838</v>
       </c>
       <c r="E473" t="n">
-        <v>45</v>
+        <v>161</v>
       </c>
       <c r="F473" t="n">
         <v>23.5</v>
@@ -9916,7 +9916,7 @@
         <v>5.089236637678793</v>
       </c>
       <c r="E474" t="n">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="F474" t="n">
         <v>19</v>
@@ -9936,7 +9936,7 @@
         <v>1.09868289235606</v>
       </c>
       <c r="E475" t="n">
-        <v>45</v>
+        <v>147</v>
       </c>
       <c r="F475" t="n">
         <v>23.5</v>
@@ -9956,7 +9956,7 @@
         <v>2.123629903505583</v>
       </c>
       <c r="E476" t="n">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="F476" t="n">
         <v>23.5</v>
@@ -9976,7 +9976,7 @@
         <v>2.587962081711049</v>
       </c>
       <c r="E477" t="n">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="F477" t="n">
         <v>22</v>
@@ -9996,7 +9996,7 @@
         <v>1.46521177615566</v>
       </c>
       <c r="E478" t="n">
-        <v>45</v>
+        <v>149</v>
       </c>
       <c r="F478" t="n">
         <v>20.5</v>
@@ -10016,7 +10016,7 @@
         <v>2.227730912077593</v>
       </c>
       <c r="E479" t="n">
-        <v>47</v>
+        <v>175</v>
       </c>
       <c r="F479" t="n">
         <v>23.5</v>
@@ -10036,7 +10036,7 @@
         <v>-2.852511499325471</v>
       </c>
       <c r="E480" t="n">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="F480" t="n">
         <v>20.5</v>
@@ -10056,7 +10056,7 @@
         <v>1.656101105496402</v>
       </c>
       <c r="E481" t="n">
-        <v>47</v>
+        <v>175</v>
       </c>
       <c r="F481" t="n">
         <v>23.5</v>
@@ -10076,7 +10076,7 @@
         <v>-2.181595041450903</v>
       </c>
       <c r="E482" t="n">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="F482" t="n">
         <v>22</v>
@@ -10096,7 +10096,7 @@
         <v>2.309738472745105</v>
       </c>
       <c r="E483" t="n">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="F483" t="n">
         <v>22</v>
@@ -10116,7 +10116,7 @@
         <v>2.92055749528471</v>
       </c>
       <c r="E484" t="n">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="F484" t="n">
         <v>23.5</v>
@@ -10136,7 +10136,7 @@
         <v>1.26214717618925</v>
       </c>
       <c r="E485" t="n">
-        <v>47</v>
+        <v>182</v>
       </c>
       <c r="F485" t="n">
         <v>23.5</v>
@@ -10156,7 +10156,7 @@
         <v>1.558160184887974</v>
       </c>
       <c r="E486" t="n">
-        <v>45</v>
+        <v>182</v>
       </c>
       <c r="F486" t="n">
         <v>22</v>
@@ -10176,7 +10176,7 @@
         <v>-7.521761006827451</v>
       </c>
       <c r="E487" t="n">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="F487" t="n">
         <v>23.5</v>
@@ -10196,7 +10196,7 @@
         <v>-6.425254374315139</v>
       </c>
       <c r="E488" t="n">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="F488" t="n">
         <v>22</v>
@@ -10216,7 +10216,7 @@
         <v>-0.2984252876331439</v>
       </c>
       <c r="E489" t="n">
-        <v>47</v>
+        <v>182</v>
       </c>
       <c r="F489" t="n">
         <v>22</v>
@@ -10236,7 +10236,7 @@
         <v>1.906705737190377</v>
       </c>
       <c r="E490" t="n">
-        <v>47</v>
+        <v>153</v>
       </c>
       <c r="F490" t="n">
         <v>20.5</v>
@@ -10256,7 +10256,7 @@
         <v>-1.825583128419374</v>
       </c>
       <c r="E491" t="n">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="F491" t="n">
         <v>22</v>
@@ -10276,7 +10276,7 @@
         <v>-0.5532374137363099</v>
       </c>
       <c r="E492" t="n">
-        <v>45</v>
+        <v>128</v>
       </c>
       <c r="F492" t="n">
         <v>20.5</v>
@@ -10296,7 +10296,7 @@
         <v>-0.5918792189979392</v>
       </c>
       <c r="E493" t="n">
-        <v>45</v>
+        <v>172</v>
       </c>
       <c r="F493" t="n">
         <v>23.5</v>
@@ -10316,7 +10316,7 @@
         <v>2.792917539201678</v>
       </c>
       <c r="E494" t="n">
-        <v>47</v>
+        <v>160</v>
       </c>
       <c r="F494" t="n">
         <v>23.5</v>
@@ -10336,7 +10336,7 @@
         <v>-0.1398359058776345</v>
       </c>
       <c r="E495" t="n">
-        <v>47</v>
+        <v>143</v>
       </c>
       <c r="F495" t="n">
         <v>22</v>
@@ -10356,7 +10356,7 @@
         <v>-2.12066542748762</v>
       </c>
       <c r="E496" t="n">
-        <v>47</v>
+        <v>128</v>
       </c>
       <c r="F496" t="n">
         <v>23.5</v>
@@ -10376,7 +10376,7 @@
         <v>1.224652498852347</v>
       </c>
       <c r="E497" t="n">
-        <v>47</v>
+        <v>145</v>
       </c>
       <c r="F497" t="n">
         <v>23.5</v>
@@ -10396,7 +10396,7 @@
         <v>2.687541208121736</v>
       </c>
       <c r="E498" t="n">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="F498" t="n">
         <v>20.5</v>
@@ -10416,7 +10416,7 @@
         <v>0.8240832438619535</v>
       </c>
       <c r="E499" t="n">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="F499" t="n">
         <v>23.5</v>
@@ -10436,7 +10436,7 @@
         <v>2.630254364117565</v>
       </c>
       <c r="E500" t="n">
-        <v>47</v>
+        <v>179</v>
       </c>
       <c r="F500" t="n">
         <v>23.5</v>
@@ -10456,7 +10456,7 @@
         <v>4.989565238231685</v>
       </c>
       <c r="E501" t="n">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="F501" t="n">
         <v>23.5</v>
@@ -10522,7 +10522,7 @@
         <v>-20.88028902850273</v>
       </c>
       <c r="E2" t="n">
-        <v>-3</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
         <v>-0.5</v>
@@ -10542,7 +10542,7 @@
         <v>-35.9607046948951</v>
       </c>
       <c r="E3" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="F3" t="n">
         <v>-19</v>
@@ -10562,7 +10562,7 @@
         <v>-52.20263188600813</v>
       </c>
       <c r="E4" t="n">
-        <v>-19</v>
+        <v>-25</v>
       </c>
       <c r="F4" t="n">
         <v>-37.5</v>
@@ -10582,7 +10582,7 @@
         <v>-70.96545578083168</v>
       </c>
       <c r="E5" t="n">
-        <v>-14</v>
+        <v>-2</v>
       </c>
       <c r="F5" t="n">
         <v>-41</v>
@@ -10602,7 +10602,7 @@
         <v>-79.97706173751618</v>
       </c>
       <c r="E6" t="n">
-        <v>-11</v>
+        <v>-23</v>
       </c>
       <c r="F6" t="n">
         <v>-53.5</v>
@@ -10622,7 +10622,7 @@
         <v>-96.8619967253459</v>
       </c>
       <c r="E7" t="n">
-        <v>-20</v>
+        <v>-33</v>
       </c>
       <c r="F7" t="n">
         <v>-66</v>
@@ -10642,7 +10642,7 @@
         <v>-119.0205484701385</v>
       </c>
       <c r="E8" t="n">
-        <v>-27</v>
+        <v>-35</v>
       </c>
       <c r="F8" t="n">
         <v>-74</v>
@@ -10662,7 +10662,7 @@
         <v>-133.8808371982143</v>
       </c>
       <c r="E9" t="n">
-        <v>-38</v>
+        <v>-48</v>
       </c>
       <c r="F9" t="n">
         <v>-85</v>
@@ -10682,7 +10682,7 @@
         <v>-150.5462625531848</v>
       </c>
       <c r="E10" t="n">
-        <v>-31</v>
+        <v>-25</v>
       </c>
       <c r="F10" t="n">
         <v>-87</v>
@@ -10702,7 +10702,7 @@
         <v>-167.0539450363587</v>
       </c>
       <c r="E11" t="n">
-        <v>-28</v>
+        <v>-3</v>
       </c>
       <c r="F11" t="n">
         <v>-98</v>
@@ -10722,7 +10722,7 @@
         <v>-189.212519793417</v>
       </c>
       <c r="E12" t="n">
-        <v>-39</v>
+        <v>69</v>
       </c>
       <c r="F12" t="n">
         <v>-110.5</v>
@@ -10742,7 +10742,7 @@
         <v>-205.2895345927922</v>
       </c>
       <c r="E13" t="n">
-        <v>-48</v>
+        <v>91</v>
       </c>
       <c r="F13" t="n">
         <v>-114</v>
@@ -10762,7 +10762,7 @@
         <v>-230.7329570760698</v>
       </c>
       <c r="E14" t="n">
-        <v>-43</v>
+        <v>103</v>
       </c>
       <c r="F14" t="n">
         <v>-119</v>
@@ -10782,7 +10782,7 @@
         <v>-245.2277709207889</v>
       </c>
       <c r="E15" t="n">
-        <v>-42</v>
+        <v>128</v>
       </c>
       <c r="F15" t="n">
         <v>-137.5</v>
@@ -10802,7 +10802,7 @@
         <v>-264.6270097926337</v>
       </c>
       <c r="E16" t="n">
-        <v>-55</v>
+        <v>152</v>
       </c>
       <c r="F16" t="n">
         <v>-150</v>
@@ -10822,7 +10822,7 @@
         <v>-279.8375788189873</v>
       </c>
       <c r="E17" t="n">
-        <v>-48</v>
+        <v>153</v>
       </c>
       <c r="F17" t="n">
         <v>-162.5</v>
@@ -10842,7 +10842,7 @@
         <v>-298.5024730712512</v>
       </c>
       <c r="E18" t="n">
-        <v>-59</v>
+        <v>185</v>
       </c>
       <c r="F18" t="n">
         <v>-173.5</v>
@@ -10862,7 +10862,7 @@
         <v>-307.5141394245287</v>
       </c>
       <c r="E19" t="n">
-        <v>-52</v>
+        <v>248</v>
       </c>
       <c r="F19" t="n">
         <v>-186</v>
@@ -10882,7 +10882,7 @@
         <v>-319.9360854076255</v>
       </c>
       <c r="E20" t="n">
-        <v>-49</v>
+        <v>282</v>
       </c>
       <c r="F20" t="n">
         <v>-194</v>
@@ -10902,7 +10902,7 @@
         <v>-328.2801118153991</v>
       </c>
       <c r="E21" t="n">
-        <v>-52</v>
+        <v>286</v>
       </c>
       <c r="F21" t="n">
         <v>-211</v>
@@ -10922,7 +10922,7 @@
         <v>-338.8920275461813</v>
       </c>
       <c r="E22" t="n">
-        <v>-63</v>
+        <v>261</v>
       </c>
       <c r="F22" t="n">
         <v>-216</v>
@@ -10942,7 +10942,7 @@
         <v>-352.6601254612219</v>
       </c>
       <c r="E23" t="n">
-        <v>-50</v>
+        <v>308</v>
       </c>
       <c r="F23" t="n">
         <v>-237.5</v>
@@ -10962,7 +10962,7 @@
         <v>-366.2739550418626</v>
       </c>
       <c r="E24" t="n">
-        <v>-41</v>
+        <v>319</v>
       </c>
       <c r="F24" t="n">
         <v>-247</v>
@@ -10982,7 +10982,7 @@
         <v>-383.3210524627606</v>
       </c>
       <c r="E25" t="n">
-        <v>-46</v>
+        <v>347</v>
       </c>
       <c r="F25" t="n">
         <v>-252</v>
@@ -11002,7 +11002,7 @@
         <v>-394.7762086335939</v>
       </c>
       <c r="E26" t="n">
-        <v>-43</v>
+        <v>359</v>
       </c>
       <c r="F26" t="n">
         <v>-261.5</v>
@@ -11022,7 +11022,7 @@
         <v>-417.4269250095536</v>
       </c>
       <c r="E27" t="n">
-        <v>-42</v>
+        <v>400</v>
       </c>
       <c r="F27" t="n">
         <v>-274</v>
@@ -11042,7 +11042,7 @@
         <v>-436.1507785741286</v>
       </c>
       <c r="E28" t="n">
-        <v>-37</v>
+        <v>406</v>
       </c>
       <c r="F28" t="n">
         <v>-280.5</v>
@@ -11062,7 +11062,7 @@
         <v>-455.7312088844182</v>
       </c>
       <c r="E29" t="n">
-        <v>-32</v>
+        <v>425</v>
       </c>
       <c r="F29" t="n">
         <v>-291.5</v>
@@ -11082,7 +11082,7 @@
         <v>-477.5472011113575</v>
       </c>
       <c r="E30" t="n">
-        <v>-27</v>
+        <v>457</v>
       </c>
       <c r="F30" t="n">
         <v>-296.5</v>
@@ -11102,7 +11102,7 @@
         <v>-489.8792760620552</v>
       </c>
       <c r="E31" t="n">
-        <v>-30</v>
+        <v>522</v>
       </c>
       <c r="F31" t="n">
         <v>-306</v>
@@ -11122,7 +11122,7 @@
         <v>-501.9547796015569</v>
       </c>
       <c r="E32" t="n">
-        <v>-21</v>
+        <v>560</v>
       </c>
       <c r="F32" t="n">
         <v>-305</v>
@@ -11142,7 +11142,7 @@
         <v>-515.8602857399461</v>
       </c>
       <c r="E33" t="n">
-        <v>-28</v>
+        <v>584</v>
       </c>
       <c r="F33" t="n">
         <v>-310</v>
@@ -11162,7 +11162,7 @@
         <v>-536.5432742577293</v>
       </c>
       <c r="E34" t="n">
-        <v>-23</v>
+        <v>609</v>
       </c>
       <c r="F34" t="n">
         <v>-310.5</v>
@@ -11182,7 +11182,7 @@
         <v>-550.217182041405</v>
       </c>
       <c r="E35" t="n">
-        <v>-24</v>
+        <v>650</v>
       </c>
       <c r="F35" t="n">
         <v>-320</v>
@@ -11202,7 +11202,7 @@
         <v>-559.8829002815233</v>
       </c>
       <c r="E36" t="n">
-        <v>-15</v>
+        <v>687</v>
       </c>
       <c r="F36" t="n">
         <v>-340</v>
@@ -11222,7 +11222,7 @@
         <v>-575.2506819827523</v>
       </c>
       <c r="E37" t="n">
-        <v>-2</v>
+        <v>732</v>
       </c>
       <c r="F37" t="n">
         <v>-352.5</v>
@@ -11242,7 +11242,7 @@
         <v>-587.6048209649141</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>753</v>
       </c>
       <c r="F38" t="n">
         <v>-374</v>
@@ -11262,7 +11262,7 @@
         <v>-603.8269943808032</v>
       </c>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>797</v>
       </c>
       <c r="F39" t="n">
         <v>-371.5</v>
@@ -11282,7 +11282,7 @@
         <v>-613.8364840563004</v>
       </c>
       <c r="E40" t="n">
-        <v>11</v>
+        <v>879</v>
       </c>
       <c r="F40" t="n">
         <v>-388.5</v>
@@ -11302,7 +11302,7 @@
         <v>-628.9399918189958</v>
       </c>
       <c r="E41" t="n">
-        <v>8</v>
+        <v>892</v>
       </c>
       <c r="F41" t="n">
         <v>-405.5</v>
@@ -11322,7 +11322,7 @@
         <v>-642.5664036664167</v>
       </c>
       <c r="E42" t="n">
-        <v>-3</v>
+        <v>908</v>
       </c>
       <c r="F42" t="n">
         <v>-418</v>
@@ -11342,7 +11342,7 @@
         <v>-657.2825076166939</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>930</v>
       </c>
       <c r="F43" t="n">
         <v>-429</v>
@@ -11362,7 +11362,7 @@
         <v>-674.6048947089264</v>
       </c>
       <c r="E44" t="n">
-        <v>5</v>
+        <v>949</v>
       </c>
       <c r="F44" t="n">
         <v>-435.5</v>
@@ -11382,7 +11382,7 @@
         <v>-693.0034125514825</v>
       </c>
       <c r="E45" t="n">
-        <v>6</v>
+        <v>971</v>
       </c>
       <c r="F45" t="n">
         <v>-433</v>
@@ -11402,7 +11402,7 @@
         <v>-706.9245891204856</v>
       </c>
       <c r="E46" t="n">
-        <v>-1</v>
+        <v>1010</v>
       </c>
       <c r="F46" t="n">
         <v>-444</v>
@@ -11422,7 +11422,7 @@
         <v>-718.0041171135881</v>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>1087</v>
       </c>
       <c r="F47" t="n">
         <v>-452</v>
@@ -11442,7 +11442,7 @@
         <v>-735.0134319187896</v>
       </c>
       <c r="E48" t="n">
-        <v>9</v>
+        <v>1125</v>
       </c>
       <c r="F48" t="n">
         <v>-470.5</v>
@@ -11462,7 +11462,7 @@
         <v>-747.5283971531959</v>
       </c>
       <c r="E49" t="n">
-        <v>10</v>
+        <v>1144</v>
       </c>
       <c r="F49" t="n">
         <v>-469.5</v>
@@ -11482,7 +11482,7 @@
         <v>-760.0977289180563</v>
       </c>
       <c r="E50" t="n">
-        <v>13</v>
+        <v>1199</v>
       </c>
       <c r="F50" t="n">
         <v>-471.5</v>
@@ -11502,7 +11502,7 @@
         <v>-778.7081559194239</v>
       </c>
       <c r="E51" t="n">
-        <v>20</v>
+        <v>1218</v>
       </c>
       <c r="F51" t="n">
         <v>-481</v>
@@ -11522,7 +11522,7 @@
         <v>-798.6911401253403</v>
       </c>
       <c r="E52" t="n">
-        <v>31</v>
+        <v>1263</v>
       </c>
       <c r="F52" t="n">
         <v>-499.5</v>
@@ -11542,7 +11542,7 @@
         <v>-805.3641238440582</v>
       </c>
       <c r="E53" t="n">
-        <v>42</v>
+        <v>1287</v>
       </c>
       <c r="F53" t="n">
         <v>-507.5</v>
@@ -11562,7 +11562,7 @@
         <v>-820.7205041230472</v>
       </c>
       <c r="E54" t="n">
-        <v>49</v>
+        <v>1289</v>
       </c>
       <c r="F54" t="n">
         <v>-518.5</v>
@@ -11582,7 +11582,7 @@
         <v>-835.9177959287388</v>
       </c>
       <c r="E55" t="n">
-        <v>62</v>
+        <v>1310</v>
       </c>
       <c r="F55" t="n">
         <v>-523.5</v>
@@ -11602,7 +11602,7 @@
         <v>-850.4373099631781</v>
       </c>
       <c r="E56" t="n">
-        <v>61</v>
+        <v>1327</v>
       </c>
       <c r="F56" t="n">
         <v>-537.5</v>
@@ -11622,7 +11622,7 @@
         <v>-866.8288195547257</v>
       </c>
       <c r="E57" t="n">
-        <v>66</v>
+        <v>1359</v>
       </c>
       <c r="F57" t="n">
         <v>-547</v>
@@ -11642,7 +11642,7 @@
         <v>-883.5564204956526</v>
       </c>
       <c r="E58" t="n">
-        <v>57</v>
+        <v>1346</v>
       </c>
       <c r="F58" t="n">
         <v>-556.5</v>
@@ -11662,7 +11662,7 @@
         <v>-895.3369224098763</v>
       </c>
       <c r="E59" t="n">
-        <v>60</v>
+        <v>1434</v>
       </c>
       <c r="F59" t="n">
         <v>-566</v>
@@ -11682,7 +11682,7 @@
         <v>-908.5059506742909</v>
       </c>
       <c r="E60" t="n">
-        <v>51</v>
+        <v>1516</v>
       </c>
       <c r="F60" t="n">
         <v>-566.5</v>
@@ -11702,7 +11702,7 @@
         <v>-927.0501466228407</v>
       </c>
       <c r="E61" t="n">
-        <v>54</v>
+        <v>1546</v>
       </c>
       <c r="F61" t="n">
         <v>-577.5</v>
@@ -11722,7 +11722,7 @@
         <v>-935.8577913488716</v>
       </c>
       <c r="E62" t="n">
-        <v>59</v>
+        <v>1586</v>
       </c>
       <c r="F62" t="n">
         <v>-588.5</v>
@@ -11742,7 +11742,7 @@
         <v>-950.1468829227587</v>
       </c>
       <c r="E63" t="n">
-        <v>60</v>
+        <v>1578</v>
       </c>
       <c r="F63" t="n">
         <v>-596.5</v>
@@ -11762,7 +11762,7 @@
         <v>-966.0098962422049</v>
       </c>
       <c r="E64" t="n">
-        <v>73</v>
+        <v>1622</v>
       </c>
       <c r="F64" t="n">
         <v>-606</v>
@@ -11782,7 +11782,7 @@
         <v>-982.5606090756528</v>
       </c>
       <c r="E65" t="n">
-        <v>70</v>
+        <v>1682</v>
       </c>
       <c r="F65" t="n">
         <v>-606.5</v>
@@ -11802,7 +11802,7 @@
         <v>-1000.494218813128</v>
       </c>
       <c r="E66" t="n">
-        <v>73</v>
+        <v>1731</v>
       </c>
       <c r="F66" t="n">
         <v>-623.5</v>
@@ -11822,7 +11822,7 @@
         <v>-1012.462468159054</v>
       </c>
       <c r="E67" t="n">
-        <v>68</v>
+        <v>1794</v>
       </c>
       <c r="F67" t="n">
         <v>-627</v>
@@ -11842,7 +11842,7 @@
         <v>-1024.045526353905</v>
       </c>
       <c r="E68" t="n">
-        <v>77</v>
+        <v>1821</v>
       </c>
       <c r="F68" t="n">
         <v>-633.5</v>
@@ -11862,7 +11862,7 @@
         <v>-1041.013235783177</v>
       </c>
       <c r="E69" t="n">
-        <v>66</v>
+        <v>1863</v>
       </c>
       <c r="F69" t="n">
         <v>-638.5</v>
@@ -11882,7 +11882,7 @@
         <v>-1054.719176802048</v>
       </c>
       <c r="E70" t="n">
-        <v>69</v>
+        <v>1877</v>
       </c>
       <c r="F70" t="n">
         <v>-649.5</v>
@@ -11902,7 +11902,7 @@
         <v>-1068.07901220902</v>
       </c>
       <c r="E71" t="n">
-        <v>68</v>
+        <v>1885</v>
       </c>
       <c r="F71" t="n">
         <v>-660.5</v>
@@ -11922,7 +11922,7 @@
         <v>-1081.818466409129</v>
       </c>
       <c r="E72" t="n">
-        <v>77</v>
+        <v>1939</v>
       </c>
       <c r="F72" t="n">
         <v>-670</v>
@@ -11942,7 +11942,7 @@
         <v>-1103.250619143852</v>
       </c>
       <c r="E73" t="n">
-        <v>88</v>
+        <v>1978</v>
       </c>
       <c r="F73" t="n">
         <v>-684</v>
@@ -11962,7 +11962,7 @@
         <v>-1123.180885649056</v>
       </c>
       <c r="E74" t="n">
-        <v>93</v>
+        <v>2023</v>
       </c>
       <c r="F74" t="n">
         <v>-690.5</v>
@@ -11982,7 +11982,7 @@
         <v>-1136.814620548772</v>
       </c>
       <c r="E75" t="n">
-        <v>98</v>
+        <v>2060</v>
       </c>
       <c r="F75" t="n">
         <v>-700</v>
@@ -12002,7 +12002,7 @@
         <v>-1151.523557592819</v>
       </c>
       <c r="E76" t="n">
-        <v>103</v>
+        <v>2090</v>
       </c>
       <c r="F76" t="n">
         <v>-697.5</v>
@@ -12022,7 +12022,7 @@
         <v>-1171.93482431065</v>
       </c>
       <c r="E77" t="n">
-        <v>98</v>
+        <v>2083</v>
       </c>
       <c r="F77" t="n">
         <v>-699.5</v>
@@ -12042,7 +12042,7 @@
         <v>-1180.233492645022</v>
       </c>
       <c r="E78" t="n">
-        <v>113</v>
+        <v>2108</v>
       </c>
       <c r="F78" t="n">
         <v>-709</v>
@@ -12062,7 +12062,7 @@
         <v>-1191.327638431329</v>
       </c>
       <c r="E79" t="n">
-        <v>116</v>
+        <v>2163</v>
       </c>
       <c r="F79" t="n">
         <v>-712.5</v>
@@ -12082,7 +12082,7 @@
         <v>-1206.097203893596</v>
       </c>
       <c r="E80" t="n">
-        <v>133</v>
+        <v>2164</v>
       </c>
       <c r="F80" t="n">
         <v>-717.5</v>
@@ -12102,7 +12102,7 @@
         <v>-1220.208347224213</v>
       </c>
       <c r="E81" t="n">
-        <v>148</v>
+        <v>2219</v>
       </c>
       <c r="F81" t="n">
         <v>-728.5</v>
@@ -12122,7 +12122,7 @@
         <v>-1237.573679426804</v>
       </c>
       <c r="E82" t="n">
-        <v>151</v>
+        <v>2275</v>
       </c>
       <c r="F82" t="n">
         <v>-738</v>
@@ -12142,7 +12142,7 @@
         <v>-1251.869052093277</v>
       </c>
       <c r="E83" t="n">
-        <v>158</v>
+        <v>2324</v>
       </c>
       <c r="F83" t="n">
         <v>-749</v>
@@ -12162,7 +12162,7 @@
         <v>-1267.395784348558</v>
       </c>
       <c r="E84" t="n">
-        <v>161</v>
+        <v>2363</v>
       </c>
       <c r="F84" t="n">
         <v>-751</v>
@@ -12182,7 +12182,7 @@
         <v>-1278.011965553342</v>
       </c>
       <c r="E85" t="n">
-        <v>170</v>
+        <v>2398</v>
       </c>
       <c r="F85" t="n">
         <v>-757.5</v>
@@ -12202,7 +12202,7 @@
         <v>-1287.570418652612</v>
       </c>
       <c r="E86" t="n">
-        <v>185</v>
+        <v>2443</v>
       </c>
       <c r="F86" t="n">
         <v>-761</v>
@@ -12222,7 +12222,7 @@
         <v>-1299.526201251086</v>
       </c>
       <c r="E87" t="n">
-        <v>192</v>
+        <v>2449</v>
       </c>
       <c r="F87" t="n">
         <v>-763</v>
@@ -12242,7 +12242,7 @@
         <v>-1314.065122399267</v>
       </c>
       <c r="E88" t="n">
-        <v>203</v>
+        <v>2526</v>
       </c>
       <c r="F88" t="n">
         <v>-763.5</v>
@@ -12262,7 +12262,7 @@
         <v>-1329.050799518251</v>
       </c>
       <c r="E89" t="n">
-        <v>212</v>
+        <v>2582</v>
       </c>
       <c r="F89" t="n">
         <v>-765.5</v>
@@ -12282,7 +12282,7 @@
         <v>-1337.677785584419</v>
       </c>
       <c r="E90" t="n">
-        <v>221</v>
+        <v>2658</v>
       </c>
       <c r="F90" t="n">
         <v>-775</v>
@@ -12302,7 +12302,7 @@
         <v>-1352.098940434634</v>
       </c>
       <c r="E91" t="n">
-        <v>224</v>
+        <v>2658</v>
       </c>
       <c r="F91" t="n">
         <v>-777</v>
@@ -12322,7 +12322,7 @@
         <v>-1366.918579507137</v>
       </c>
       <c r="E92" t="n">
-        <v>223</v>
+        <v>2673</v>
       </c>
       <c r="F92" t="n">
         <v>-785</v>
@@ -12342,7 +12342,7 @@
         <v>-1385.193038380315</v>
       </c>
       <c r="E93" t="n">
-        <v>234</v>
+        <v>2706</v>
       </c>
       <c r="F93" t="n">
         <v>-785.5</v>
@@ -12362,7 +12362,7 @@
         <v>-1399.204528446038</v>
       </c>
       <c r="E94" t="n">
-        <v>241</v>
+        <v>2744</v>
       </c>
       <c r="F94" t="n">
         <v>-787.5</v>
@@ -12382,7 +12382,7 @@
         <v>-1410.970912301405</v>
       </c>
       <c r="E95" t="n">
-        <v>252</v>
+        <v>2825</v>
       </c>
       <c r="F95" t="n">
         <v>-792.5</v>
@@ -12402,7 +12402,7 @@
         <v>-1420.384268417089</v>
       </c>
       <c r="E96" t="n">
-        <v>267</v>
+        <v>2884</v>
       </c>
       <c r="F96" t="n">
         <v>-797.5</v>
@@ -12422,7 +12422,7 @@
         <v>-1434.670124181723</v>
       </c>
       <c r="E97" t="n">
-        <v>270</v>
+        <v>2888</v>
       </c>
       <c r="F97" t="n">
         <v>-795</v>
@@ -12442,7 +12442,7 @@
         <v>-1446.523618279234</v>
       </c>
       <c r="E98" t="n">
-        <v>277</v>
+        <v>2925</v>
       </c>
       <c r="F98" t="n">
         <v>-798.5</v>
@@ -12462,7 +12462,7 @@
         <v>-1461.763908595752</v>
       </c>
       <c r="E99" t="n">
-        <v>292</v>
+        <v>2968</v>
       </c>
       <c r="F99" t="n">
         <v>-803.5</v>
@@ -12482,7 +12482,7 @@
         <v>-1477.782634156046</v>
       </c>
       <c r="E100" t="n">
-        <v>299</v>
+        <v>3032</v>
       </c>
       <c r="F100" t="n">
         <v>-805.5</v>
@@ -12502,7 +12502,7 @@
         <v>-1489.092425757653</v>
       </c>
       <c r="E101" t="n">
-        <v>316</v>
+        <v>3104</v>
       </c>
       <c r="F101" t="n">
         <v>-804.5</v>
@@ -12522,7 +12522,7 @@
         <v>-1504.307082340612</v>
       </c>
       <c r="E102" t="n">
-        <v>325</v>
+        <v>3147</v>
       </c>
       <c r="F102" t="n">
         <v>-814</v>
@@ -12542,7 +12542,7 @@
         <v>-1516.219173939061</v>
       </c>
       <c r="E103" t="n">
-        <v>338</v>
+        <v>3216</v>
       </c>
       <c r="F103" t="n">
         <v>-813</v>
@@ -12562,7 +12562,7 @@
         <v>-1534.691509182445</v>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>3260</v>
       </c>
       <c r="F104" t="n">
         <v>-824</v>
@@ -12582,7 +12582,7 @@
         <v>-1550.688348165737</v>
       </c>
       <c r="E105" t="n">
-        <v>374</v>
+        <v>3327</v>
       </c>
       <c r="F105" t="n">
         <v>-820</v>
@@ -12602,7 +12602,7 @@
         <v>-1562.472326444135</v>
       </c>
       <c r="E106" t="n">
-        <v>379</v>
+        <v>3390</v>
       </c>
       <c r="F106" t="n">
         <v>-832.5</v>
@@ -12622,7 +12622,7 @@
         <v>-1576.572274511352</v>
       </c>
       <c r="E107" t="n">
-        <v>382</v>
+        <v>3410</v>
       </c>
       <c r="F107" t="n">
         <v>-846.5</v>
@@ -12642,7 +12642,7 @@
         <v>-1589.687552488782</v>
       </c>
       <c r="E108" t="n">
-        <v>403</v>
+        <v>3396</v>
       </c>
       <c r="F108" t="n">
         <v>-856</v>
@@ -12662,7 +12662,7 @@
         <v>-1599.893290035628</v>
       </c>
       <c r="E109" t="n">
-        <v>416</v>
+        <v>3423</v>
       </c>
       <c r="F109" t="n">
         <v>-867</v>
@@ -12682,7 +12682,7 @@
         <v>-1612.212871076709</v>
       </c>
       <c r="E110" t="n">
-        <v>437</v>
+        <v>3459</v>
       </c>
       <c r="F110" t="n">
         <v>-872</v>
@@ -12702,7 +12702,7 @@
         <v>-1618.272824779593</v>
       </c>
       <c r="E111" t="n">
-        <v>448</v>
+        <v>3490</v>
       </c>
       <c r="F111" t="n">
         <v>-872.5</v>
@@ -12722,7 +12722,7 @@
         <v>-1631.348866613447</v>
       </c>
       <c r="E112" t="n">
-        <v>459</v>
+        <v>3516</v>
       </c>
       <c r="F112" t="n">
         <v>-871.5</v>
@@ -12742,7 +12742,7 @@
         <v>-1643.354522291633</v>
       </c>
       <c r="E113" t="n">
-        <v>472</v>
+        <v>3572</v>
       </c>
       <c r="F113" t="n">
         <v>-878</v>
@@ -12762,7 +12762,7 @@
         <v>-1661.590391013445</v>
       </c>
       <c r="E114" t="n">
-        <v>481</v>
+        <v>3592</v>
       </c>
       <c r="F114" t="n">
         <v>-880</v>
@@ -12782,7 +12782,7 @@
         <v>-1677.827127373567</v>
       </c>
       <c r="E115" t="n">
-        <v>494</v>
+        <v>3604</v>
       </c>
       <c r="F115" t="n">
         <v>-880.5</v>
@@ -12802,7 +12802,7 @@
         <v>-1686.965172815426</v>
       </c>
       <c r="E116" t="n">
-        <v>499</v>
+        <v>3648</v>
       </c>
       <c r="F116" t="n">
         <v>-887</v>
@@ -12822,7 +12822,7 @@
         <v>-1695.700793584888</v>
       </c>
       <c r="E117" t="n">
-        <v>508</v>
+        <v>3675</v>
       </c>
       <c r="F117" t="n">
         <v>-886</v>
@@ -12842,7 +12842,7 @@
         <v>-1698.97678205171</v>
       </c>
       <c r="E118" t="n">
-        <v>519</v>
+        <v>3732</v>
       </c>
       <c r="F118" t="n">
         <v>-888</v>
@@ -12862,7 +12862,7 @@
         <v>-1720.444084015615</v>
       </c>
       <c r="E119" t="n">
-        <v>526</v>
+        <v>3754</v>
       </c>
       <c r="F119" t="n">
         <v>-896</v>
@@ -12882,7 +12882,7 @@
         <v>-1729.750109109444</v>
       </c>
       <c r="E120" t="n">
-        <v>537</v>
+        <v>3787</v>
       </c>
       <c r="F120" t="n">
         <v>-898</v>
@@ -12902,7 +12902,7 @@
         <v>-1745.206623423088</v>
       </c>
       <c r="E121" t="n">
-        <v>556</v>
+        <v>3846</v>
       </c>
       <c r="F121" t="n">
         <v>-900</v>
@@ -12922,7 +12922,7 @@
         <v>-1751.864774908571</v>
       </c>
       <c r="E122" t="n">
-        <v>565</v>
+        <v>3921</v>
       </c>
       <c r="F122" t="n">
         <v>-908</v>
@@ -12942,7 +12942,7 @@
         <v>-1758.801318606907</v>
       </c>
       <c r="E123" t="n">
-        <v>564</v>
+        <v>4003</v>
       </c>
       <c r="F123" t="n">
         <v>-907</v>
@@ -12962,7 +12962,7 @@
         <v>-1770.183742805132</v>
       </c>
       <c r="E124" t="n">
-        <v>573</v>
+        <v>4098</v>
       </c>
       <c r="F124" t="n">
         <v>-913.5</v>
@@ -12982,7 +12982,7 @@
         <v>-1785.283929652888</v>
       </c>
       <c r="E125" t="n">
-        <v>580</v>
+        <v>4192</v>
       </c>
       <c r="F125" t="n">
         <v>-917</v>
@@ -13002,7 +13002,7 @@
         <v>-1799.563817401932</v>
       </c>
       <c r="E126" t="n">
-        <v>589</v>
+        <v>4291</v>
       </c>
       <c r="F126" t="n">
         <v>-922</v>
@@ -13022,7 +13022,7 @@
         <v>-1805.898466356333</v>
       </c>
       <c r="E127" t="n">
-        <v>604</v>
+        <v>4337</v>
       </c>
       <c r="F127" t="n">
         <v>-934.5</v>
@@ -13042,7 +13042,7 @@
         <v>-1819.446042033068</v>
       </c>
       <c r="E128" t="n">
-        <v>607</v>
+        <v>4354</v>
       </c>
       <c r="F128" t="n">
         <v>-941</v>
@@ -13062,7 +13062,7 @@
         <v>-1831.110814707646</v>
       </c>
       <c r="E129" t="n">
-        <v>606</v>
+        <v>4424</v>
       </c>
       <c r="F129" t="n">
         <v>-944.5</v>
@@ -13082,7 +13082,7 @@
         <v>-1845.815355441028</v>
       </c>
       <c r="E130" t="n">
-        <v>631</v>
+        <v>4489</v>
       </c>
       <c r="F130" t="n">
         <v>-943.5</v>
@@ -13102,7 +13102,7 @@
         <v>-1857.113000725558</v>
       </c>
       <c r="E131" t="n">
-        <v>656</v>
+        <v>4558</v>
       </c>
       <c r="F131" t="n">
         <v>-948.5</v>
@@ -13122,7 +13122,7 @@
         <v>-1866.205734872303</v>
       </c>
       <c r="E132" t="n">
-        <v>679</v>
+        <v>4584</v>
       </c>
       <c r="F132" t="n">
         <v>-947.5</v>
@@ -13142,7 +13142,7 @@
         <v>-1874.159042092825</v>
       </c>
       <c r="E133" t="n">
-        <v>694</v>
+        <v>4656</v>
       </c>
       <c r="F133" t="n">
         <v>-952.5</v>
@@ -13162,7 +13162,7 @@
         <v>-1882.788661167084</v>
       </c>
       <c r="E134" t="n">
-        <v>703</v>
+        <v>4681</v>
       </c>
       <c r="F134" t="n">
         <v>-959</v>
@@ -13182,7 +13182,7 @@
         <v>-1895.243592678685</v>
       </c>
       <c r="E135" t="n">
-        <v>704</v>
+        <v>4698</v>
       </c>
       <c r="F135" t="n">
         <v>-953.5</v>
@@ -13202,7 +13202,7 @@
         <v>-1910.595378070932</v>
       </c>
       <c r="E136" t="n">
-        <v>723</v>
+        <v>4749</v>
       </c>
       <c r="F136" t="n">
         <v>-957</v>
@@ -13222,7 +13222,7 @@
         <v>-1925.02295457638</v>
       </c>
       <c r="E137" t="n">
-        <v>746</v>
+        <v>4812</v>
       </c>
       <c r="F137" t="n">
         <v>-968</v>
@@ -13242,7 +13242,7 @@
         <v>-1938.806507733841</v>
       </c>
       <c r="E138" t="n">
-        <v>757</v>
+        <v>4850</v>
       </c>
       <c r="F138" t="n">
         <v>-973</v>
@@ -13262,7 +13262,7 @@
         <v>-1949.96967327652</v>
       </c>
       <c r="E139" t="n">
-        <v>762</v>
+        <v>4916</v>
       </c>
       <c r="F139" t="n">
         <v>-973.5</v>
@@ -13282,7 +13282,7 @@
         <v>-1965.691931070204</v>
       </c>
       <c r="E140" t="n">
-        <v>771</v>
+        <v>5019</v>
       </c>
       <c r="F140" t="n">
         <v>-972.5</v>
@@ -13302,7 +13302,7 @@
         <v>-1984.492498247861</v>
       </c>
       <c r="E141" t="n">
-        <v>782</v>
+        <v>5060</v>
       </c>
       <c r="F141" t="n">
         <v>-967</v>
@@ -13322,7 +13322,7 @@
         <v>-1997.247971836185</v>
       </c>
       <c r="E142" t="n">
-        <v>805</v>
+        <v>5079</v>
       </c>
       <c r="F142" t="n">
         <v>-969</v>
@@ -13342,7 +13342,7 @@
         <v>-2010.298146606739</v>
       </c>
       <c r="E143" t="n">
-        <v>810</v>
+        <v>5091</v>
       </c>
       <c r="F143" t="n">
         <v>-966.5</v>
@@ -13362,7 +13362,7 @@
         <v>-2019.790931945562</v>
       </c>
       <c r="E144" t="n">
-        <v>817</v>
+        <v>5172</v>
       </c>
       <c r="F144" t="n">
         <v>-961</v>
@@ -13382,7 +13382,7 @@
         <v>-2032.615442019713</v>
       </c>
       <c r="E145" t="n">
-        <v>824</v>
+        <v>5214</v>
       </c>
       <c r="F145" t="n">
         <v>-963</v>
@@ -13402,7 +13402,7 @@
         <v>-2047.873784696341</v>
       </c>
       <c r="E146" t="n">
-        <v>823</v>
+        <v>5305</v>
       </c>
       <c r="F146" t="n">
         <v>-968</v>
@@ -13422,7 +13422,7 @@
         <v>-2056.809945490018</v>
       </c>
       <c r="E147" t="n">
-        <v>836</v>
+        <v>5362</v>
       </c>
       <c r="F147" t="n">
         <v>-973</v>
@@ -13442,7 +13442,7 @@
         <v>-2068.825393911767</v>
       </c>
       <c r="E148" t="n">
-        <v>851</v>
+        <v>5407</v>
       </c>
       <c r="F148" t="n">
         <v>-976.5</v>
@@ -13462,7 +13462,7 @@
         <v>-2078.801494594511</v>
       </c>
       <c r="E149" t="n">
-        <v>866</v>
+        <v>5474</v>
       </c>
       <c r="F149" t="n">
         <v>-974</v>
@@ -13482,7 +13482,7 @@
         <v>-2087.874340133747</v>
       </c>
       <c r="E150" t="n">
-        <v>877</v>
+        <v>5538</v>
       </c>
       <c r="F150" t="n">
         <v>-974.5</v>
@@ -13502,7 +13502,7 @@
         <v>-2096.924783918511</v>
       </c>
       <c r="E151" t="n">
-        <v>906</v>
+        <v>5623</v>
       </c>
       <c r="F151" t="n">
         <v>-972</v>
@@ -13522,7 +13522,7 @@
         <v>-2106.117775276539</v>
       </c>
       <c r="E152" t="n">
-        <v>915</v>
+        <v>5671</v>
       </c>
       <c r="F152" t="n">
         <v>-978.5</v>
@@ -13542,7 +13542,7 @@
         <v>-2117.604001847971</v>
       </c>
       <c r="E153" t="n">
-        <v>924</v>
+        <v>5691</v>
       </c>
       <c r="F153" t="n">
         <v>-983.5</v>
@@ -13562,7 +13562,7 @@
         <v>-2129.936928100617</v>
       </c>
       <c r="E154" t="n">
-        <v>933</v>
+        <v>5759</v>
       </c>
       <c r="F154" t="n">
         <v>-988.5</v>
@@ -13582,7 +13582,7 @@
         <v>-2138.686010219796</v>
       </c>
       <c r="E155" t="n">
-        <v>948</v>
+        <v>5816</v>
       </c>
       <c r="F155" t="n">
         <v>-995</v>
@@ -13602,7 +13602,7 @@
         <v>-2147.600459655876</v>
       </c>
       <c r="E156" t="n">
-        <v>973</v>
+        <v>5892</v>
       </c>
       <c r="F156" t="n">
         <v>-998.5</v>
@@ -13622,7 +13622,7 @@
         <v>-2150.779023094192</v>
       </c>
       <c r="E157" t="n">
-        <v>1002</v>
+        <v>5946</v>
       </c>
       <c r="F157" t="n">
         <v>-996</v>
@@ -13642,7 +13642,7 @@
         <v>-2162.07416450086</v>
       </c>
       <c r="E158" t="n">
-        <v>1023</v>
+        <v>6005</v>
       </c>
       <c r="F158" t="n">
         <v>-992</v>
@@ -13662,7 +13662,7 @@
         <v>-2178.756507817282</v>
       </c>
       <c r="E159" t="n">
-        <v>1024</v>
+        <v>6014</v>
       </c>
       <c r="F159" t="n">
         <v>-986.5</v>
@@ -13682,7 +13682,7 @@
         <v>-2196.084458553467</v>
       </c>
       <c r="E160" t="n">
-        <v>1043</v>
+        <v>6070</v>
       </c>
       <c r="F160" t="n">
         <v>-984</v>
@@ -13702,7 +13702,7 @@
         <v>-2207.5746681574</v>
       </c>
       <c r="E161" t="n">
-        <v>1052</v>
+        <v>6100</v>
       </c>
       <c r="F161" t="n">
         <v>-980</v>
@@ -13722,7 +13722,7 @@
         <v>-2209.47060294401</v>
       </c>
       <c r="E162" t="n">
-        <v>1059</v>
+        <v>6138</v>
       </c>
       <c r="F162" t="n">
         <v>-985</v>
@@ -13742,7 +13742,7 @@
         <v>-2221.073888044925</v>
       </c>
       <c r="E163" t="n">
-        <v>1072</v>
+        <v>6184</v>
       </c>
       <c r="F163" t="n">
         <v>-994.5</v>
@@ -13762,7 +13762,7 @@
         <v>-2225.946550031122</v>
       </c>
       <c r="E164" t="n">
-        <v>1095</v>
+        <v>6250</v>
       </c>
       <c r="F164" t="n">
         <v>-1001</v>
@@ -13782,7 +13782,7 @@
         <v>-2242.482180021908</v>
       </c>
       <c r="E165" t="n">
-        <v>1120</v>
+        <v>6321</v>
       </c>
       <c r="F165" t="n">
         <v>-1001.5</v>
@@ -13802,7 +13802,7 @@
         <v>-2253.261915588274</v>
       </c>
       <c r="E166" t="n">
-        <v>1129</v>
+        <v>6353</v>
       </c>
       <c r="F166" t="n">
         <v>-1000.5</v>
@@ -13822,7 +13822,7 @@
         <v>-2260.703754628397</v>
       </c>
       <c r="E167" t="n">
-        <v>1156</v>
+        <v>6399</v>
       </c>
       <c r="F167" t="n">
         <v>-998</v>
@@ -13842,7 +13842,7 @@
         <v>-2269.243971451855</v>
       </c>
       <c r="E168" t="n">
-        <v>1169</v>
+        <v>6469</v>
       </c>
       <c r="F168" t="n">
         <v>-997</v>
@@ -13862,7 +13862,7 @@
         <v>-2282.60521241121</v>
       </c>
       <c r="E169" t="n">
-        <v>1180</v>
+        <v>6526</v>
       </c>
       <c r="F169" t="n">
         <v>-1003.5</v>
@@ -13882,7 +13882,7 @@
         <v>-2290.546784411468</v>
       </c>
       <c r="E170" t="n">
-        <v>1197</v>
+        <v>6599</v>
       </c>
       <c r="F170" t="n">
         <v>-996.5</v>
@@ -13902,7 +13902,7 @@
         <v>-2302.78937896035</v>
       </c>
       <c r="E171" t="n">
-        <v>1204</v>
+        <v>6697</v>
       </c>
       <c r="F171" t="n">
         <v>-994</v>
@@ -13922,7 +13922,7 @@
         <v>-2312.367113941488</v>
       </c>
       <c r="E172" t="n">
-        <v>1225</v>
+        <v>6744</v>
       </c>
       <c r="F172" t="n">
         <v>-991.5</v>
@@ -13942,7 +13942,7 @@
         <v>-2329.322048831982</v>
       </c>
       <c r="E173" t="n">
-        <v>1240</v>
+        <v>6789</v>
       </c>
       <c r="F173" t="n">
         <v>-998</v>
@@ -13962,7 +13962,7 @@
         <v>-2337.278657686479</v>
       </c>
       <c r="E174" t="n">
-        <v>1257</v>
+        <v>6872</v>
       </c>
       <c r="F174" t="n">
         <v>-1001.5</v>
@@ -13982,7 +13982,7 @@
         <v>-2344.219427234649</v>
       </c>
       <c r="E175" t="n">
-        <v>1270</v>
+        <v>6943</v>
       </c>
       <c r="F175" t="n">
         <v>-997.5</v>
@@ -14002,7 +14002,7 @@
         <v>-2352.668160000351</v>
       </c>
       <c r="E176" t="n">
-        <v>1283</v>
+        <v>7048</v>
       </c>
       <c r="F176" t="n">
         <v>-990.5</v>
@@ -14022,7 +14022,7 @@
         <v>-2364.398256394271</v>
       </c>
       <c r="E177" t="n">
-        <v>1314</v>
+        <v>7108</v>
       </c>
       <c r="F177" t="n">
         <v>-986.5</v>
@@ -14042,7 +14042,7 @@
         <v>-2381.171008859988</v>
       </c>
       <c r="E178" t="n">
-        <v>1325</v>
+        <v>7136</v>
       </c>
       <c r="F178" t="n">
         <v>-979.5</v>
@@ -14062,7 +14062,7 @@
         <v>-2388.443134213902</v>
       </c>
       <c r="E179" t="n">
-        <v>1336</v>
+        <v>7215</v>
       </c>
       <c r="F179" t="n">
         <v>-980</v>
@@ -14082,7 +14082,7 @@
         <v>-2404.758234394666</v>
       </c>
       <c r="E180" t="n">
-        <v>1349</v>
+        <v>7250</v>
       </c>
       <c r="F180" t="n">
         <v>-982</v>
@@ -14102,7 +14102,7 @@
         <v>-2417.50570848869</v>
       </c>
       <c r="E181" t="n">
-        <v>1372</v>
+        <v>7325</v>
       </c>
       <c r="F181" t="n">
         <v>-976.5</v>
@@ -14122,7 +14122,7 @@
         <v>-2431.065512662162</v>
       </c>
       <c r="E182" t="n">
-        <v>1401</v>
+        <v>7405</v>
       </c>
       <c r="F182" t="n">
         <v>-968</v>
@@ -14142,7 +14142,7 @@
         <v>-2444.340417690171</v>
       </c>
       <c r="E183" t="n">
-        <v>1424</v>
+        <v>7463</v>
       </c>
       <c r="F183" t="n">
         <v>-961</v>
@@ -14162,7 +14162,7 @@
         <v>-2457.085264844857</v>
       </c>
       <c r="E184" t="n">
-        <v>1441</v>
+        <v>7515</v>
       </c>
       <c r="F184" t="n">
         <v>-954</v>
@@ -14182,7 +14182,7 @@
         <v>-2469.433763565302</v>
       </c>
       <c r="E185" t="n">
-        <v>1458</v>
+        <v>7594</v>
       </c>
       <c r="F185" t="n">
         <v>-954.5</v>
@@ -14202,7 +14202,7 @@
         <v>-2477.966487498356</v>
       </c>
       <c r="E186" t="n">
-        <v>1475</v>
+        <v>7686</v>
       </c>
       <c r="F186" t="n">
         <v>-955</v>
@@ -14222,7 +14222,7 @@
         <v>-2485.54177520868</v>
       </c>
       <c r="E187" t="n">
-        <v>1496</v>
+        <v>7769</v>
       </c>
       <c r="F187" t="n">
         <v>-963</v>
@@ -14242,7 +14242,7 @@
         <v>-2497.405559388458</v>
       </c>
       <c r="E188" t="n">
-        <v>1511</v>
+        <v>7808</v>
       </c>
       <c r="F188" t="n">
         <v>-957.5</v>
@@ -14262,7 +14262,7 @@
         <v>-2510.096816718186</v>
       </c>
       <c r="E189" t="n">
-        <v>1534</v>
+        <v>7837</v>
       </c>
       <c r="F189" t="n">
         <v>-953.5</v>
@@ -14282,7 +14282,7 @@
         <v>-2517.243107868213</v>
       </c>
       <c r="E190" t="n">
-        <v>1551</v>
+        <v>7937</v>
       </c>
       <c r="F190" t="n">
         <v>-949.5</v>
@@ -14302,7 +14302,7 @@
         <v>-2527.973450327915</v>
       </c>
       <c r="E191" t="n">
-        <v>1564</v>
+        <v>8010</v>
       </c>
       <c r="F191" t="n">
         <v>-957.5</v>
@@ -14322,7 +14322,7 @@
         <v>-2546.761749827214</v>
       </c>
       <c r="E192" t="n">
-        <v>1583</v>
+        <v>8076</v>
       </c>
       <c r="F192" t="n">
         <v>-953.5</v>
@@ -14342,7 +14342,7 @@
         <v>-2565.831640847767</v>
       </c>
       <c r="E193" t="n">
-        <v>1602</v>
+        <v>8131</v>
       </c>
       <c r="F193" t="n">
         <v>-945</v>
@@ -14362,7 +14362,7 @@
         <v>-2570.874236079898</v>
       </c>
       <c r="E194" t="n">
-        <v>1613</v>
+        <v>8183</v>
       </c>
       <c r="F194" t="n">
         <v>-945.5</v>
@@ -14382,7 +14382,7 @@
         <v>-2578.180961856345</v>
       </c>
       <c r="E195" t="n">
-        <v>1620</v>
+        <v>8234</v>
       </c>
       <c r="F195" t="n">
         <v>-947.5</v>
@@ -14402,7 +14402,7 @@
         <v>-2589.477894731786</v>
       </c>
       <c r="E196" t="n">
-        <v>1627</v>
+        <v>8234</v>
       </c>
       <c r="F196" t="n">
         <v>-948</v>
@@ -14422,7 +14422,7 @@
         <v>-2600.281980860163</v>
       </c>
       <c r="E197" t="n">
-        <v>1642</v>
+        <v>8302</v>
       </c>
       <c r="F197" t="n">
         <v>-953</v>
@@ -14442,7 +14442,7 @@
         <v>-2611.169579037502</v>
       </c>
       <c r="E198" t="n">
-        <v>1665</v>
+        <v>8375</v>
       </c>
       <c r="F198" t="n">
         <v>-953.5</v>
@@ -14462,7 +14462,7 @@
         <v>-2624.76389306925</v>
       </c>
       <c r="E199" t="n">
-        <v>1686</v>
+        <v>8466</v>
       </c>
       <c r="F199" t="n">
         <v>-945</v>
@@ -14482,7 +14482,7 @@
         <v>-2641.498040599619</v>
       </c>
       <c r="E200" t="n">
-        <v>1701</v>
+        <v>8574</v>
       </c>
       <c r="F200" t="n">
         <v>-942.5</v>
@@ -14502,7 +14502,7 @@
         <v>-2653.668699454901</v>
       </c>
       <c r="E201" t="n">
-        <v>1708</v>
+        <v>8628</v>
       </c>
       <c r="F201" t="n">
         <v>-943</v>
@@ -14522,7 +14522,7 @@
         <v>-2663.351124863409</v>
       </c>
       <c r="E202" t="n">
-        <v>1723</v>
+        <v>8686</v>
       </c>
       <c r="F202" t="n">
         <v>-936</v>
@@ -14542,7 +14542,7 @@
         <v>-2677.776537111889</v>
       </c>
       <c r="E203" t="n">
-        <v>1732</v>
+        <v>8741</v>
       </c>
       <c r="F203" t="n">
         <v>-929</v>
@@ -14562,7 +14562,7 @@
         <v>-2689.336365651319</v>
       </c>
       <c r="E204" t="n">
-        <v>1749</v>
+        <v>8778</v>
       </c>
       <c r="F204" t="n">
         <v>-926.5</v>
@@ -14582,7 +14582,7 @@
         <v>-2701.10085130621</v>
       </c>
       <c r="E205" t="n">
-        <v>1774</v>
+        <v>8841</v>
       </c>
       <c r="F205" t="n">
         <v>-922.5</v>
@@ -14602,7 +14602,7 @@
         <v>-2709.569673500035</v>
       </c>
       <c r="E206" t="n">
-        <v>1791</v>
+        <v>8900</v>
       </c>
       <c r="F206" t="n">
         <v>-921.5</v>
@@ -14622,7 +14622,7 @@
         <v>-2718.240411661623</v>
       </c>
       <c r="E207" t="n">
-        <v>1808</v>
+        <v>8972</v>
       </c>
       <c r="F207" t="n">
         <v>-920.5</v>
@@ -14642,7 +14642,7 @@
         <v>-2726.0625179717</v>
       </c>
       <c r="E208" t="n">
-        <v>1817</v>
+        <v>9046</v>
       </c>
       <c r="F208" t="n">
         <v>-934.5</v>
@@ -14662,7 +14662,7 @@
         <v>-2738.207490539824</v>
       </c>
       <c r="E209" t="n">
-        <v>1836</v>
+        <v>9089</v>
       </c>
       <c r="F209" t="n">
         <v>-941</v>
@@ -14682,7 +14682,7 @@
         <v>-2745.641741438796</v>
       </c>
       <c r="E210" t="n">
-        <v>1857</v>
+        <v>9150</v>
       </c>
       <c r="F210" t="n">
         <v>-937</v>
@@ -14702,7 +14702,7 @@
         <v>-2755.996963041494</v>
       </c>
       <c r="E211" t="n">
-        <v>1868</v>
+        <v>9206</v>
       </c>
       <c r="F211" t="n">
         <v>-934.5</v>
@@ -14722,7 +14722,7 @@
         <v>-2768.969548926258</v>
       </c>
       <c r="E212" t="n">
-        <v>1901</v>
+        <v>9270</v>
       </c>
       <c r="F212" t="n">
         <v>-929</v>
@@ -14742,7 +14742,7 @@
         <v>-2776.238282719339</v>
       </c>
       <c r="E213" t="n">
-        <v>1918</v>
+        <v>9368</v>
       </c>
       <c r="F213" t="n">
         <v>-920.5</v>
@@ -14762,7 +14762,7 @@
         <v>-2790.885592647614</v>
       </c>
       <c r="E214" t="n">
-        <v>1939</v>
+        <v>9497</v>
       </c>
       <c r="F214" t="n">
         <v>-909</v>
@@ -14782,7 +14782,7 @@
         <v>-2797.115662042137</v>
       </c>
       <c r="E215" t="n">
-        <v>1956</v>
+        <v>9551</v>
       </c>
       <c r="F215" t="n">
         <v>-915.5</v>
@@ -14802,7 +14802,7 @@
         <v>-2802.144830066969</v>
       </c>
       <c r="E216" t="n">
-        <v>1977</v>
+        <v>9641</v>
       </c>
       <c r="F216" t="n">
         <v>-911.5</v>
@@ -14822,7 +14822,7 @@
         <v>-2819.346204473898</v>
       </c>
       <c r="E217" t="n">
-        <v>1996</v>
+        <v>9698</v>
       </c>
       <c r="F217" t="n">
         <v>-913.5</v>
@@ -14842,7 +14842,7 @@
         <v>-2831.142444919185</v>
       </c>
       <c r="E218" t="n">
-        <v>2009</v>
+        <v>9732</v>
       </c>
       <c r="F218" t="n">
         <v>-906.5</v>
@@ -14862,7 +14862,7 @@
         <v>-2847.887336055995</v>
       </c>
       <c r="E219" t="n">
-        <v>2030</v>
+        <v>9820</v>
       </c>
       <c r="F219" t="n">
         <v>-904</v>
@@ -14882,7 +14882,7 @@
         <v>-2859.234171186068</v>
       </c>
       <c r="E220" t="n">
-        <v>2051</v>
+        <v>9884</v>
       </c>
       <c r="F220" t="n">
         <v>-898.5</v>
@@ -14902,7 +14902,7 @@
         <v>-2863.906760512139</v>
       </c>
       <c r="E221" t="n">
-        <v>2068</v>
+        <v>9974</v>
       </c>
       <c r="F221" t="n">
         <v>-894.5</v>
@@ -14922,7 +14922,7 @@
         <v>-2869.481754611027</v>
       </c>
       <c r="E222" t="n">
-        <v>2085</v>
+        <v>10039</v>
       </c>
       <c r="F222" t="n">
         <v>-895</v>
@@ -14942,7 +14942,7 @@
         <v>-2877.04372839315</v>
       </c>
       <c r="E223" t="n">
-        <v>2102</v>
+        <v>10097</v>
       </c>
       <c r="F223" t="n">
         <v>-886.5</v>
@@ -14962,7 +14962,7 @@
         <v>-2882.166550135263</v>
       </c>
       <c r="E224" t="n">
-        <v>2123</v>
+        <v>10210</v>
       </c>
       <c r="F224" t="n">
         <v>-884</v>
@@ -14982,7 +14982,7 @@
         <v>-2890.706926782456</v>
       </c>
       <c r="E225" t="n">
-        <v>2150</v>
+        <v>10309</v>
       </c>
       <c r="F225" t="n">
         <v>-881.5</v>
@@ -15002,7 +15002,7 @@
         <v>-2905.091148813542</v>
       </c>
       <c r="E226" t="n">
-        <v>2171</v>
+        <v>10372</v>
       </c>
       <c r="F226" t="n">
         <v>-876</v>
@@ -15022,7 +15022,7 @@
         <v>-2917.413397911941</v>
       </c>
       <c r="E227" t="n">
-        <v>2196</v>
+        <v>10432</v>
       </c>
       <c r="F227" t="n">
         <v>-869</v>
@@ -15042,7 +15042,7 @@
         <v>-2926.037517440527</v>
       </c>
       <c r="E228" t="n">
-        <v>2217</v>
+        <v>10517</v>
       </c>
       <c r="F228" t="n">
         <v>-868</v>
@@ -15062,7 +15062,7 @@
         <v>-2933.680367025686</v>
       </c>
       <c r="E229" t="n">
-        <v>2220</v>
+        <v>10586</v>
       </c>
       <c r="F229" t="n">
         <v>-874.5</v>
@@ -15082,7 +15082,7 @@
         <v>-2952.896896023672</v>
       </c>
       <c r="E230" t="n">
-        <v>2241</v>
+        <v>10706</v>
       </c>
       <c r="F230" t="n">
         <v>-872</v>
@@ -15102,7 +15102,7 @@
         <v>-2960.343292868128</v>
       </c>
       <c r="E231" t="n">
-        <v>2266</v>
+        <v>10772</v>
       </c>
       <c r="F231" t="n">
         <v>-860.5</v>
@@ -15122,7 +15122,7 @@
         <v>-2967.159471200971</v>
       </c>
       <c r="E232" t="n">
-        <v>2293</v>
+        <v>10840</v>
       </c>
       <c r="F232" t="n">
         <v>-864</v>
@@ -15142,7 +15142,7 @@
         <v>-2971.270695992574</v>
       </c>
       <c r="E233" t="n">
-        <v>2314</v>
+        <v>10933</v>
       </c>
       <c r="F233" t="n">
         <v>-861.5</v>
@@ -15162,7 +15162,7 @@
         <v>-2978.701741837509</v>
       </c>
       <c r="E234" t="n">
-        <v>2333</v>
+        <v>11018</v>
       </c>
       <c r="F234" t="n">
         <v>-854.5</v>
@@ -15182,7 +15182,7 @@
         <v>-2982.495663109822</v>
       </c>
       <c r="E235" t="n">
-        <v>2354</v>
+        <v>11103</v>
       </c>
       <c r="F235" t="n">
         <v>-844.5</v>
@@ -15202,7 +15202,7 @@
         <v>-2991.886089889794</v>
       </c>
       <c r="E236" t="n">
-        <v>2365</v>
+        <v>11165</v>
       </c>
       <c r="F236" t="n">
         <v>-839</v>
@@ -15222,7 +15222,7 @@
         <v>-2998.531449131573</v>
       </c>
       <c r="E237" t="n">
-        <v>2388</v>
+        <v>11288</v>
       </c>
       <c r="F237" t="n">
         <v>-836.5</v>
@@ -15242,7 +15242,7 @@
         <v>-3005.190684462481</v>
       </c>
       <c r="E238" t="n">
-        <v>2409</v>
+        <v>11345</v>
       </c>
       <c r="F238" t="n">
         <v>-826.5</v>
@@ -15262,7 +15262,7 @@
         <v>-3012.57993539378</v>
       </c>
       <c r="E239" t="n">
-        <v>2434</v>
+        <v>11457</v>
       </c>
       <c r="F239" t="n">
         <v>-821</v>
@@ -15282,7 +15282,7 @@
         <v>-3019.181690166487</v>
       </c>
       <c r="E240" t="n">
-        <v>2461</v>
+        <v>11534</v>
       </c>
       <c r="F240" t="n">
         <v>-811</v>
@@ -15302,7 +15302,7 @@
         <v>-3029.723510227472</v>
       </c>
       <c r="E241" t="n">
-        <v>2480</v>
+        <v>11601</v>
       </c>
       <c r="F241" t="n">
         <v>-805.5</v>
@@ -15322,7 +15322,7 @@
         <v>-3044.768794353802</v>
       </c>
       <c r="E242" t="n">
-        <v>2505</v>
+        <v>11667</v>
       </c>
       <c r="F242" t="n">
         <v>-795.5</v>
@@ -15342,7 +15342,7 @@
         <v>-3049.253943579788</v>
       </c>
       <c r="E243" t="n">
-        <v>2526</v>
+        <v>11736</v>
       </c>
       <c r="F243" t="n">
         <v>-788.5</v>
@@ -15362,7 +15362,7 @@
         <v>-3062.158585186359</v>
       </c>
       <c r="E244" t="n">
-        <v>2547</v>
+        <v>11781</v>
       </c>
       <c r="F244" t="n">
         <v>-783</v>
@@ -15382,7 +15382,7 @@
         <v>-3072.80400205281</v>
       </c>
       <c r="E245" t="n">
-        <v>2562</v>
+        <v>11880</v>
       </c>
       <c r="F245" t="n">
         <v>-780.5</v>
@@ -15402,7 +15402,7 @@
         <v>-3083.144308452584</v>
       </c>
       <c r="E246" t="n">
-        <v>2583</v>
+        <v>11951</v>
       </c>
       <c r="F246" t="n">
         <v>-776.5</v>
@@ -15422,7 +15422,7 @@
         <v>-3093.342854124372</v>
       </c>
       <c r="E247" t="n">
-        <v>2616</v>
+        <v>12042</v>
       </c>
       <c r="F247" t="n">
         <v>-768</v>
@@ -15442,7 +15442,7 @@
         <v>-3099.197674529419</v>
       </c>
       <c r="E248" t="n">
-        <v>2649</v>
+        <v>12108</v>
       </c>
       <c r="F248" t="n">
         <v>-756.5</v>
@@ -15462,7 +15462,7 @@
         <v>-3107.93783743703</v>
       </c>
       <c r="E249" t="n">
-        <v>2672</v>
+        <v>12178</v>
       </c>
       <c r="F249" t="n">
         <v>-751</v>
@@ -15482,7 +15482,7 @@
         <v>-3116.610856321919</v>
       </c>
       <c r="E250" t="n">
-        <v>2693</v>
+        <v>12309</v>
       </c>
       <c r="F250" t="n">
         <v>-747</v>
@@ -15502,7 +15502,7 @@
         <v>-3131.846443698836</v>
       </c>
       <c r="E251" t="n">
-        <v>2722</v>
+        <v>12385</v>
       </c>
       <c r="F251" t="n">
         <v>-743</v>
@@ -15522,7 +15522,7 @@
         <v>-3141.188791284486</v>
       </c>
       <c r="E252" t="n">
-        <v>2747</v>
+        <v>12464</v>
       </c>
       <c r="F252" t="n">
         <v>-736</v>
@@ -15542,7 +15542,7 @@
         <v>-3145.198429564543</v>
       </c>
       <c r="E253" t="n">
-        <v>2782</v>
+        <v>12559</v>
       </c>
       <c r="F253" t="n">
         <v>-724.5</v>
@@ -15562,7 +15562,7 @@
         <v>-3152.205255122882</v>
       </c>
       <c r="E254" t="n">
-        <v>2811</v>
+        <v>12664</v>
       </c>
       <c r="F254" t="n">
         <v>-720.5</v>
@@ -15582,7 +15582,7 @@
         <v>-3161.305777238423</v>
       </c>
       <c r="E255" t="n">
-        <v>2836</v>
+        <v>12776</v>
       </c>
       <c r="F255" t="n">
         <v>-713.5</v>
@@ -15602,7 +15602,7 @@
         <v>-3167.988265724664</v>
       </c>
       <c r="E256" t="n">
-        <v>2855</v>
+        <v>12874</v>
       </c>
       <c r="F256" t="n">
         <v>-705</v>
@@ -15622,7 +15622,7 @@
         <v>-3175.908105313038</v>
       </c>
       <c r="E257" t="n">
-        <v>2874</v>
+        <v>12979</v>
       </c>
       <c r="F257" t="n">
         <v>-698</v>
@@ -15642,7 +15642,7 @@
         <v>-3191.034604595266</v>
       </c>
       <c r="E258" t="n">
-        <v>2903</v>
+        <v>13051</v>
       </c>
       <c r="F258" t="n">
         <v>-685</v>
@@ -15662,7 +15662,7 @@
         <v>-3195.416245130696</v>
       </c>
       <c r="E259" t="n">
-        <v>2930</v>
+        <v>13135</v>
       </c>
       <c r="F259" t="n">
         <v>-679.5</v>
@@ -15682,7 +15682,7 @@
         <v>-3205.295744035393</v>
       </c>
       <c r="E260" t="n">
-        <v>2963</v>
+        <v>13177</v>
       </c>
       <c r="F260" t="n">
         <v>-672.5</v>
@@ -15702,7 +15702,7 @@
         <v>-3209.927166922218</v>
       </c>
       <c r="E261" t="n">
-        <v>2984</v>
+        <v>13259</v>
       </c>
       <c r="F261" t="n">
         <v>-667</v>
@@ -15722,7 +15722,7 @@
         <v>-3222.22988090955</v>
       </c>
       <c r="E262" t="n">
-        <v>3009</v>
+        <v>13325</v>
       </c>
       <c r="F262" t="n">
         <v>-655.5</v>
@@ -15742,7 +15742,7 @@
         <v>-3230.067213903062</v>
       </c>
       <c r="E263" t="n">
-        <v>3030</v>
+        <v>13421</v>
       </c>
       <c r="F263" t="n">
         <v>-645.5</v>
@@ -15762,7 +15762,7 @@
         <v>-3241.369934797733</v>
       </c>
       <c r="E264" t="n">
-        <v>3055</v>
+        <v>13479</v>
       </c>
       <c r="F264" t="n">
         <v>-647.5</v>
@@ -15782,7 +15782,7 @@
         <v>-3243.602222360006</v>
       </c>
       <c r="E265" t="n">
-        <v>3082</v>
+        <v>13583</v>
       </c>
       <c r="F265" t="n">
         <v>-648</v>
@@ -15802,7 +15802,7 @@
         <v>-3252.448045174649</v>
       </c>
       <c r="E266" t="n">
-        <v>3089</v>
+        <v>13663</v>
       </c>
       <c r="F266" t="n">
         <v>-638</v>
@@ -15822,7 +15822,7 @@
         <v>-3269.85310922629</v>
       </c>
       <c r="E267" t="n">
-        <v>3106</v>
+        <v>13706</v>
       </c>
       <c r="F267" t="n">
         <v>-632.5</v>
@@ -15842,7 +15842,7 @@
         <v>-3277.350118948331</v>
       </c>
       <c r="E268" t="n">
-        <v>3133</v>
+        <v>13790</v>
       </c>
       <c r="F268" t="n">
         <v>-640.5</v>
@@ -15862,7 +15862,7 @@
         <v>-3283.697208616799</v>
       </c>
       <c r="E269" t="n">
-        <v>3160</v>
+        <v>13903</v>
       </c>
       <c r="F269" t="n">
         <v>-635</v>
@@ -15882,7 +15882,7 @@
         <v>-3290.310190425611</v>
       </c>
       <c r="E270" t="n">
-        <v>3179</v>
+        <v>14053</v>
       </c>
       <c r="F270" t="n">
         <v>-631</v>
@@ -15902,7 +15902,7 @@
         <v>-3301.379587301623</v>
       </c>
       <c r="E271" t="n">
-        <v>3202</v>
+        <v>14127</v>
       </c>
       <c r="F271" t="n">
         <v>-636</v>
@@ -15922,7 +15922,7 @@
         <v>-3305.138404816271</v>
       </c>
       <c r="E272" t="n">
-        <v>3225</v>
+        <v>14223</v>
       </c>
       <c r="F272" t="n">
         <v>-630.5</v>
@@ -15942,7 +15942,7 @@
         <v>-3309.190282372647</v>
       </c>
       <c r="E273" t="n">
-        <v>3248</v>
+        <v>14299</v>
       </c>
       <c r="F273" t="n">
         <v>-623.5</v>
@@ -15962,7 +15962,7 @@
         <v>-3319.712709081206</v>
       </c>
       <c r="E274" t="n">
-        <v>3283</v>
+        <v>14401</v>
       </c>
       <c r="F274" t="n">
         <v>-615</v>
@@ -15982,7 +15982,7 @@
         <v>-3334.83939858744</v>
       </c>
       <c r="E275" t="n">
-        <v>3306</v>
+        <v>14471</v>
       </c>
       <c r="F275" t="n">
         <v>-600.5</v>
@@ -16002,7 +16002,7 @@
         <v>-3344.123087593315</v>
       </c>
       <c r="E276" t="n">
-        <v>3319</v>
+        <v>14528</v>
       </c>
       <c r="F276" t="n">
         <v>-592</v>
@@ -16022,7 +16022,7 @@
         <v>-3352.067332065455</v>
       </c>
       <c r="E277" t="n">
-        <v>3342</v>
+        <v>14602</v>
       </c>
       <c r="F277" t="n">
         <v>-583.5</v>
@@ -16042,7 +16042,7 @@
         <v>-3358.24766929521</v>
       </c>
       <c r="E278" t="n">
-        <v>3369</v>
+        <v>14682</v>
       </c>
       <c r="F278" t="n">
         <v>-578</v>
@@ -16062,7 +16062,7 @@
         <v>-3367.230130680086</v>
       </c>
       <c r="E279" t="n">
-        <v>3400</v>
+        <v>14842</v>
       </c>
       <c r="F279" t="n">
         <v>-572.5</v>
@@ -16082,7 +16082,7 @@
         <v>-3378.257265225039</v>
       </c>
       <c r="E280" t="n">
-        <v>3431</v>
+        <v>14913</v>
       </c>
       <c r="F280" t="n">
         <v>-559.5</v>
@@ -16102,7 +16102,7 @@
         <v>-3392.507620846764</v>
       </c>
       <c r="E281" t="n">
-        <v>3460</v>
+        <v>14977</v>
       </c>
       <c r="F281" t="n">
         <v>-555.5</v>
@@ -16122,7 +16122,7 @@
         <v>-3399.889277450938</v>
       </c>
       <c r="E282" t="n">
-        <v>3485</v>
+        <v>15056</v>
       </c>
       <c r="F282" t="n">
         <v>-557.5</v>
@@ -16142,7 +16142,7 @@
         <v>-3401.473221909397</v>
       </c>
       <c r="E283" t="n">
-        <v>3514</v>
+        <v>15187</v>
       </c>
       <c r="F283" t="n">
         <v>-549</v>
@@ -16162,7 +16162,7 @@
         <v>-3406.456102738477</v>
       </c>
       <c r="E284" t="n">
-        <v>3541</v>
+        <v>15299</v>
       </c>
       <c r="F284" t="n">
         <v>-542</v>
@@ -16182,7 +16182,7 @@
         <v>-3408.450047604576</v>
       </c>
       <c r="E285" t="n">
-        <v>3566</v>
+        <v>15391</v>
       </c>
       <c r="F285" t="n">
         <v>-532</v>
@@ -16202,7 +16202,7 @@
         <v>-3416.413012847521</v>
       </c>
       <c r="E286" t="n">
-        <v>3599</v>
+        <v>15479</v>
       </c>
       <c r="F286" t="n">
         <v>-522</v>
@@ -16222,7 +16222,7 @@
         <v>-3427.578290721012</v>
       </c>
       <c r="E287" t="n">
-        <v>3620</v>
+        <v>15537</v>
       </c>
       <c r="F287" t="n">
         <v>-516.5</v>
@@ -16242,7 +16242,7 @@
         <v>-3435.452112918297</v>
       </c>
       <c r="E288" t="n">
-        <v>3647</v>
+        <v>15610</v>
       </c>
       <c r="F288" t="n">
         <v>-512.5</v>
@@ -16262,7 +16262,7 @@
         <v>-3440.9671223373</v>
       </c>
       <c r="E289" t="n">
-        <v>3676</v>
+        <v>15750</v>
       </c>
       <c r="F289" t="n">
         <v>-502.5</v>
@@ -16282,7 +16282,7 @@
         <v>-3451.59106610668</v>
       </c>
       <c r="E290" t="n">
-        <v>3709</v>
+        <v>15836</v>
       </c>
       <c r="F290" t="n">
         <v>-495.5</v>
@@ -16302,7 +16302,7 @@
         <v>-3456.452350956562</v>
       </c>
       <c r="E291" t="n">
-        <v>3730</v>
+        <v>15966</v>
       </c>
       <c r="F291" t="n">
         <v>-481</v>
@@ -16322,7 +16322,7 @@
         <v>-3461.58556908058</v>
       </c>
       <c r="E292" t="n">
-        <v>3753</v>
+        <v>16127</v>
       </c>
       <c r="F292" t="n">
         <v>-474</v>
@@ -16342,7 +16342,7 @@
         <v>-3470.006607292975</v>
       </c>
       <c r="E293" t="n">
-        <v>3786</v>
+        <v>16256</v>
       </c>
       <c r="F293" t="n">
         <v>-468.5</v>
@@ -16362,7 +16362,7 @@
         <v>-3477.964965275645</v>
       </c>
       <c r="E294" t="n">
-        <v>3817</v>
+        <v>16333</v>
       </c>
       <c r="F294" t="n">
         <v>-457</v>
@@ -16382,7 +16382,7 @@
         <v>-3485.368911559648</v>
       </c>
       <c r="E295" t="n">
-        <v>3846</v>
+        <v>16410</v>
       </c>
       <c r="F295" t="n">
         <v>-451.5</v>
@@ -16402,7 +16402,7 @@
         <v>-3487.293295582306</v>
       </c>
       <c r="E296" t="n">
-        <v>3867</v>
+        <v>16473</v>
       </c>
       <c r="F296" t="n">
         <v>-446</v>
@@ -16422,7 +16422,7 @@
         <v>-3496.923949971694</v>
       </c>
       <c r="E297" t="n">
-        <v>3896</v>
+        <v>16555</v>
       </c>
       <c r="F297" t="n">
         <v>-439</v>
@@ -16442,7 +16442,7 @@
         <v>-3500.726355768737</v>
       </c>
       <c r="E298" t="n">
-        <v>3923</v>
+        <v>16667</v>
       </c>
       <c r="F298" t="n">
         <v>-429</v>
@@ -16462,7 +16462,7 @@
         <v>-3502.996915485427</v>
       </c>
       <c r="E299" t="n">
-        <v>3952</v>
+        <v>16766</v>
       </c>
       <c r="F299" t="n">
         <v>-419</v>
@@ -16482,7 +16482,7 @@
         <v>-3508.064060609442</v>
       </c>
       <c r="E300" t="n">
-        <v>3981</v>
+        <v>16867</v>
       </c>
       <c r="F300" t="n">
         <v>-406</v>
@@ -16502,7 +16502,7 @@
         <v>-3511.803703764135</v>
       </c>
       <c r="E301" t="n">
-        <v>4008</v>
+        <v>17004</v>
       </c>
       <c r="F301" t="n">
         <v>-400.5</v>
@@ -16522,7 +16522,7 @@
         <v>-3515.22199682005</v>
       </c>
       <c r="E302" t="n">
-        <v>4041</v>
+        <v>17131</v>
       </c>
       <c r="F302" t="n">
         <v>-387.5</v>
@@ -16542,7 +16542,7 @@
         <v>-3519.566902580317</v>
       </c>
       <c r="E303" t="n">
-        <v>4066</v>
+        <v>17236</v>
       </c>
       <c r="F303" t="n">
         <v>-380.5</v>
@@ -16562,7 +16562,7 @@
         <v>-3534.860273789981</v>
       </c>
       <c r="E304" t="n">
-        <v>4097</v>
+        <v>17308</v>
       </c>
       <c r="F304" t="n">
         <v>-369</v>
@@ -16582,7 +16582,7 @@
         <v>-3537.693585067788</v>
       </c>
       <c r="E305" t="n">
-        <v>4130</v>
+        <v>17373</v>
       </c>
       <c r="F305" t="n">
         <v>-357.5</v>
@@ -16602,7 +16602,7 @@
         <v>-3544.181151334116</v>
       </c>
       <c r="E306" t="n">
-        <v>4167</v>
+        <v>17484</v>
       </c>
       <c r="F306" t="n">
         <v>-346</v>
@@ -16622,7 +16622,7 @@
         <v>-3544.778710139911</v>
       </c>
       <c r="E307" t="n">
-        <v>4192</v>
+        <v>17589</v>
       </c>
       <c r="F307" t="n">
         <v>-330</v>
@@ -16642,7 +16642,7 @@
         <v>-3551.786341633569</v>
       </c>
       <c r="E308" t="n">
-        <v>4221</v>
+        <v>17695</v>
       </c>
       <c r="F308" t="n">
         <v>-326</v>
@@ -16662,7 +16662,7 @@
         <v>-3558.142351019079</v>
       </c>
       <c r="E309" t="n">
-        <v>4238</v>
+        <v>17741</v>
       </c>
       <c r="F309" t="n">
         <v>-311.5</v>
@@ -16682,7 +16682,7 @@
         <v>-3570.750284406039</v>
       </c>
       <c r="E310" t="n">
-        <v>4271</v>
+        <v>17832</v>
       </c>
       <c r="F310" t="n">
         <v>-300</v>
@@ -16702,7 +16702,7 @@
         <v>-3581.306482914772</v>
       </c>
       <c r="E311" t="n">
-        <v>4290</v>
+        <v>17916</v>
       </c>
       <c r="F311" t="n">
         <v>-291.5</v>
@@ -16722,7 +16722,7 @@
         <v>-3589.342568314311</v>
       </c>
       <c r="E312" t="n">
-        <v>4325</v>
+        <v>18062</v>
       </c>
       <c r="F312" t="n">
         <v>-280</v>
@@ -16742,7 +16742,7 @@
         <v>-3596.476379755604</v>
       </c>
       <c r="E313" t="n">
-        <v>4350</v>
+        <v>18199</v>
       </c>
       <c r="F313" t="n">
         <v>-274.5</v>
@@ -16762,7 +16762,7 @@
         <v>-3598.013455449126</v>
       </c>
       <c r="E314" t="n">
-        <v>4381</v>
+        <v>18322</v>
       </c>
       <c r="F314" t="n">
         <v>-263</v>
@@ -16782,7 +16782,7 @@
         <v>-3602.014148579711</v>
       </c>
       <c r="E315" t="n">
-        <v>4418</v>
+        <v>18427</v>
       </c>
       <c r="F315" t="n">
         <v>-245.5</v>
@@ -16802,7 +16802,7 @@
         <v>-3609.456951383192</v>
       </c>
       <c r="E316" t="n">
-        <v>4449</v>
+        <v>18558</v>
       </c>
       <c r="F316" t="n">
         <v>-247.5</v>
@@ -16822,7 +16822,7 @@
         <v>-3609.135695200776</v>
       </c>
       <c r="E317" t="n">
-        <v>4474</v>
+        <v>18705</v>
       </c>
       <c r="F317" t="n">
         <v>-234.5</v>
@@ -16842,7 +16842,7 @@
         <v>-3615.733711251207</v>
       </c>
       <c r="E318" t="n">
-        <v>4507</v>
+        <v>18787</v>
       </c>
       <c r="F318" t="n">
         <v>-224.5</v>
@@ -16862,7 +16862,7 @@
         <v>-3621.939494615843</v>
       </c>
       <c r="E319" t="n">
-        <v>4528</v>
+        <v>18914</v>
       </c>
       <c r="F319" t="n">
         <v>-216</v>
@@ -16882,7 +16882,7 @@
         <v>-3626.818929038604</v>
       </c>
       <c r="E320" t="n">
-        <v>4565</v>
+        <v>19027</v>
       </c>
       <c r="F320" t="n">
         <v>-201.5</v>
@@ -16902,7 +16902,7 @@
         <v>-3635.634589872756</v>
       </c>
       <c r="E321" t="n">
-        <v>4598</v>
+        <v>19145</v>
       </c>
       <c r="F321" t="n">
         <v>-196</v>
@@ -16922,7 +16922,7 @@
         <v>-3640.514631715028</v>
       </c>
       <c r="E322" t="n">
-        <v>4635</v>
+        <v>19270</v>
       </c>
       <c r="F322" t="n">
         <v>-180</v>
@@ -16942,7 +16942,7 @@
         <v>-3639.175563384712</v>
       </c>
       <c r="E323" t="n">
-        <v>4660</v>
+        <v>19402</v>
       </c>
       <c r="F323" t="n">
         <v>-164</v>
@@ -16962,7 +16962,7 @@
         <v>-3646.710445421333</v>
       </c>
       <c r="E324" t="n">
-        <v>4697</v>
+        <v>19482</v>
       </c>
       <c r="F324" t="n">
         <v>-151</v>
@@ -16982,7 +16982,7 @@
         <v>-3648.148383949301</v>
       </c>
       <c r="E325" t="n">
-        <v>4730</v>
+        <v>19605</v>
       </c>
       <c r="F325" t="n">
         <v>-142.5</v>
@@ -17002,7 +17002,7 @@
         <v>-3651.232871333345</v>
       </c>
       <c r="E326" t="n">
-        <v>4755</v>
+        <v>19738</v>
       </c>
       <c r="F326" t="n">
         <v>-131</v>
@@ -17022,7 +17022,7 @@
         <v>-3656.21744890121</v>
       </c>
       <c r="E327" t="n">
-        <v>4788</v>
+        <v>19865</v>
       </c>
       <c r="F327" t="n">
         <v>-116.5</v>
@@ -17042,7 +17042,7 @@
         <v>-3668.696995170179</v>
       </c>
       <c r="E328" t="n">
-        <v>4819</v>
+        <v>19956</v>
       </c>
       <c r="F328" t="n">
         <v>-102</v>
@@ -17062,7 +17062,7 @@
         <v>-3679.410104722284</v>
       </c>
       <c r="E329" t="n">
-        <v>4850</v>
+        <v>20032</v>
       </c>
       <c r="F329" t="n">
         <v>-86</v>
@@ -17082,7 +17082,7 @@
         <v>-3683.624264164536</v>
       </c>
       <c r="E330" t="n">
-        <v>4877</v>
+        <v>20179</v>
       </c>
       <c r="F330" t="n">
         <v>-76</v>
@@ -17102,7 +17102,7 @@
         <v>-3693.94601849079</v>
       </c>
       <c r="E331" t="n">
-        <v>4906</v>
+        <v>20256</v>
       </c>
       <c r="F331" t="n">
         <v>-67.5</v>
@@ -17122,7 +17122,7 @@
         <v>-3697.793469698078</v>
       </c>
       <c r="E332" t="n">
-        <v>4935</v>
+        <v>20356</v>
       </c>
       <c r="F332" t="n">
         <v>-56</v>
@@ -17142,7 +17142,7 @@
         <v>-3705.370581126249</v>
       </c>
       <c r="E333" t="n">
-        <v>4966</v>
+        <v>20441</v>
       </c>
       <c r="F333" t="n">
         <v>-52</v>
@@ -17162,7 +17162,7 @@
         <v>-3717.767438119616</v>
       </c>
       <c r="E334" t="n">
-        <v>4993</v>
+        <v>20567</v>
       </c>
       <c r="F334" t="n">
         <v>-37.5</v>
@@ -17182,7 +17182,7 @@
         <v>-3722.303630080644</v>
       </c>
       <c r="E335" t="n">
-        <v>5024</v>
+        <v>20675</v>
       </c>
       <c r="F335" t="n">
         <v>-24.5</v>
@@ -17202,7 +17202,7 @@
         <v>-3726.097507056765</v>
       </c>
       <c r="E336" t="n">
-        <v>5055</v>
+        <v>20747</v>
       </c>
       <c r="F336" t="n">
         <v>-17.5</v>
@@ -17222,7 +17222,7 @@
         <v>-3724.20547622087</v>
       </c>
       <c r="E337" t="n">
-        <v>5086</v>
+        <v>20866</v>
       </c>
       <c r="F337" t="n">
         <v>-10.5</v>
@@ -17242,7 +17242,7 @@
         <v>-3731.082087006008</v>
       </c>
       <c r="E338" t="n">
-        <v>5121</v>
+        <v>21006</v>
       </c>
       <c r="F338" t="n">
         <v>-0.5</v>
@@ -17262,7 +17262,7 @@
         <v>-3732.69794800739</v>
       </c>
       <c r="E339" t="n">
-        <v>5158</v>
+        <v>21133</v>
       </c>
       <c r="F339" t="n">
         <v>11</v>
@@ -17282,7 +17282,7 @@
         <v>-3738.039888195955</v>
       </c>
       <c r="E340" t="n">
-        <v>5185</v>
+        <v>21219</v>
       </c>
       <c r="F340" t="n">
         <v>21</v>
@@ -17302,7 +17302,7 @@
         <v>-3743.349243745337</v>
       </c>
       <c r="E341" t="n">
-        <v>5222</v>
+        <v>21330</v>
       </c>
       <c r="F341" t="n">
         <v>37</v>
@@ -17322,7 +17322,7 @@
         <v>-3748.412217744176</v>
       </c>
       <c r="E342" t="n">
-        <v>5255</v>
+        <v>21456</v>
       </c>
       <c r="F342" t="n">
         <v>50</v>
@@ -17342,7 +17342,7 @@
         <v>-3752.280285539522</v>
       </c>
       <c r="E343" t="n">
-        <v>5286</v>
+        <v>21568</v>
       </c>
       <c r="F343" t="n">
         <v>63</v>
@@ -17362,7 +17362,7 @@
         <v>-3753.575492463974</v>
       </c>
       <c r="E344" t="n">
-        <v>5317</v>
+        <v>21661</v>
       </c>
       <c r="F344" t="n">
         <v>74.5</v>
@@ -17382,7 +17382,7 @@
         <v>-3758.139001980158</v>
       </c>
       <c r="E345" t="n">
-        <v>5352</v>
+        <v>21795</v>
       </c>
       <c r="F345" t="n">
         <v>86</v>
@@ -17402,7 +17402,7 @@
         <v>-3762.668687765124</v>
       </c>
       <c r="E346" t="n">
-        <v>5387</v>
+        <v>21881</v>
       </c>
       <c r="F346" t="n">
         <v>100.5</v>
@@ -17422,7 +17422,7 @@
         <v>-3762.107047463621</v>
       </c>
       <c r="E347" t="n">
-        <v>5418</v>
+        <v>22018</v>
       </c>
       <c r="F347" t="n">
         <v>109</v>
@@ -17442,7 +17442,7 @@
         <v>-3764.03952818164</v>
       </c>
       <c r="E348" t="n">
-        <v>5451</v>
+        <v>22135</v>
       </c>
       <c r="F348" t="n">
         <v>125</v>
@@ -17462,7 +17462,7 @@
         <v>-3766.531605165148</v>
       </c>
       <c r="E349" t="n">
-        <v>5478</v>
+        <v>22216</v>
       </c>
       <c r="F349" t="n">
         <v>138</v>
@@ -17482,7 +17482,7 @@
         <v>-3773.397983000457</v>
       </c>
       <c r="E350" t="n">
-        <v>5521</v>
+        <v>22361</v>
       </c>
       <c r="F350" t="n">
         <v>143.5</v>
@@ -17502,7 +17502,7 @@
         <v>-3781.864000450392</v>
       </c>
       <c r="E351" t="n">
-        <v>5556</v>
+        <v>22488</v>
       </c>
       <c r="F351" t="n">
         <v>149</v>
@@ -17522,7 +17522,7 @@
         <v>-3790.367359220432</v>
       </c>
       <c r="E352" t="n">
-        <v>5589</v>
+        <v>22568</v>
       </c>
       <c r="F352" t="n">
         <v>157.5</v>
@@ -17542,7 +17542,7 @@
         <v>-3793.768881460168</v>
       </c>
       <c r="E353" t="n">
-        <v>5620</v>
+        <v>22675</v>
       </c>
       <c r="F353" t="n">
         <v>163</v>
@@ -17562,7 +17562,7 @@
         <v>-3798.658183628825</v>
       </c>
       <c r="E354" t="n">
-        <v>5659</v>
+        <v>22809</v>
       </c>
       <c r="F354" t="n">
         <v>168.5</v>
@@ -17582,7 +17582,7 @@
         <v>-3804.118116719195</v>
       </c>
       <c r="E355" t="n">
-        <v>5696</v>
+        <v>22939</v>
       </c>
       <c r="F355" t="n">
         <v>183</v>
@@ -17602,7 +17602,7 @@
         <v>-3806.841289732352</v>
       </c>
       <c r="E356" t="n">
-        <v>5727</v>
+        <v>23052</v>
       </c>
       <c r="F356" t="n">
         <v>197.5</v>
@@ -17622,7 +17622,7 @@
         <v>-3814.010650594949</v>
       </c>
       <c r="E357" t="n">
-        <v>5754</v>
+        <v>23149</v>
       </c>
       <c r="F357" t="n">
         <v>210.5</v>
@@ -17642,7 +17642,7 @@
         <v>-3824.825360453081</v>
       </c>
       <c r="E358" t="n">
-        <v>5797</v>
+        <v>23264</v>
       </c>
       <c r="F358" t="n">
         <v>225</v>
@@ -17662,7 +17662,7 @@
         <v>-3832.932524256652</v>
       </c>
       <c r="E359" t="n">
-        <v>5824</v>
+        <v>23345</v>
       </c>
       <c r="F359" t="n">
         <v>236.5</v>
@@ -17682,7 +17682,7 @@
         <v>-3839.15298954926</v>
       </c>
       <c r="E360" t="n">
-        <v>5869</v>
+        <v>23482</v>
       </c>
       <c r="F360" t="n">
         <v>255.5</v>
@@ -17702,7 +17702,7 @@
         <v>-3844.657133646032</v>
       </c>
       <c r="E361" t="n">
-        <v>5908</v>
+        <v>23597</v>
       </c>
       <c r="F361" t="n">
         <v>264</v>
@@ -17722,7 +17722,7 @@
         <v>-3847.132888769135</v>
       </c>
       <c r="E362" t="n">
-        <v>5939</v>
+        <v>23698</v>
       </c>
       <c r="F362" t="n">
         <v>281.5</v>
@@ -17742,7 +17742,7 @@
         <v>-3854.576958377807</v>
       </c>
       <c r="E363" t="n">
-        <v>5980</v>
+        <v>23810</v>
       </c>
       <c r="F363" t="n">
         <v>296</v>
@@ -17762,7 +17762,7 @@
         <v>-3856.598743150798</v>
       </c>
       <c r="E364" t="n">
-        <v>6007</v>
+        <v>23904</v>
       </c>
       <c r="F364" t="n">
         <v>310.5</v>
@@ -17782,7 +17782,7 @@
         <v>-3858.952848109181</v>
       </c>
       <c r="E365" t="n">
-        <v>6044</v>
+        <v>24020</v>
       </c>
       <c r="F365" t="n">
         <v>329.5</v>
@@ -17802,7 +17802,7 @@
         <v>-3865.144888320866</v>
       </c>
       <c r="E366" t="n">
-        <v>6075</v>
+        <v>24181</v>
       </c>
       <c r="F366" t="n">
         <v>350</v>
@@ -17822,7 +17822,7 @@
         <v>-3870.820580326307</v>
       </c>
       <c r="E367" t="n">
-        <v>6114</v>
+        <v>24320</v>
       </c>
       <c r="F367" t="n">
         <v>366</v>
@@ -17842,7 +17842,7 @@
         <v>-3877.038631168531</v>
       </c>
       <c r="E368" t="n">
-        <v>6149</v>
+        <v>24456</v>
       </c>
       <c r="F368" t="n">
         <v>385</v>
@@ -17862,7 +17862,7 @@
         <v>-3880.117461284964</v>
       </c>
       <c r="E369" t="n">
-        <v>6180</v>
+        <v>24567</v>
       </c>
       <c r="F369" t="n">
         <v>401</v>
@@ -17882,7 +17882,7 @@
         <v>-3879.672025910747</v>
       </c>
       <c r="E370" t="n">
-        <v>6215</v>
+        <v>24643</v>
       </c>
       <c r="F370" t="n">
         <v>420</v>
@@ -17902,7 +17902,7 @@
         <v>-3884.97168802321</v>
       </c>
       <c r="E371" t="n">
-        <v>6248</v>
+        <v>24737</v>
       </c>
       <c r="F371" t="n">
         <v>440.5</v>
@@ -17922,7 +17922,7 @@
         <v>-3889.24703718335</v>
       </c>
       <c r="E372" t="n">
-        <v>6289</v>
+        <v>24874</v>
       </c>
       <c r="F372" t="n">
         <v>461</v>
@@ -17942,7 +17942,7 @@
         <v>-3886.486922662467</v>
       </c>
       <c r="E373" t="n">
-        <v>6324</v>
+        <v>25020</v>
       </c>
       <c r="F373" t="n">
         <v>472.5</v>
@@ -17962,7 +17962,7 @@
         <v>-3888.720098223402</v>
       </c>
       <c r="E374" t="n">
-        <v>6357</v>
+        <v>25145</v>
       </c>
       <c r="F374" t="n">
         <v>484</v>
@@ -17982,7 +17982,7 @@
         <v>-3892.569361228206</v>
       </c>
       <c r="E375" t="n">
-        <v>6396</v>
+        <v>25243</v>
       </c>
       <c r="F375" t="n">
         <v>497</v>
@@ -18002,7 +18002,7 @@
         <v>-3900.008679655078</v>
       </c>
       <c r="E376" t="n">
-        <v>6433</v>
+        <v>25339</v>
       </c>
       <c r="F376" t="n">
         <v>513</v>
@@ -18022,7 +18022,7 @@
         <v>-3899.609866992836</v>
       </c>
       <c r="E377" t="n">
-        <v>6468</v>
+        <v>25458</v>
       </c>
       <c r="F377" t="n">
         <v>530.5</v>
@@ -18042,7 +18042,7 @@
         <v>-3904.829472916613</v>
       </c>
       <c r="E378" t="n">
-        <v>6505</v>
+        <v>25555</v>
       </c>
       <c r="F378" t="n">
         <v>540.5</v>
@@ -18062,7 +18062,7 @@
         <v>-3903.393357607637</v>
       </c>
       <c r="E379" t="n">
-        <v>6538</v>
+        <v>25672</v>
       </c>
       <c r="F379" t="n">
         <v>561</v>
@@ -18082,7 +18082,7 @@
         <v>-3905.948903282528</v>
       </c>
       <c r="E380" t="n">
-        <v>6581</v>
+        <v>25787</v>
       </c>
       <c r="F380" t="n">
         <v>577</v>
@@ -18102,7 +18102,7 @@
         <v>-3911.847488201251</v>
       </c>
       <c r="E381" t="n">
-        <v>6620</v>
+        <v>25941</v>
       </c>
       <c r="F381" t="n">
         <v>591.5</v>
@@ -18122,7 +18122,7 @@
         <v>-3918.920698100097</v>
       </c>
       <c r="E382" t="n">
-        <v>6653</v>
+        <v>26019</v>
       </c>
       <c r="F382" t="n">
         <v>598.5</v>
@@ -18142,7 +18142,7 @@
         <v>-3922.543675385281</v>
       </c>
       <c r="E383" t="n">
-        <v>6694</v>
+        <v>26132</v>
       </c>
       <c r="F383" t="n">
         <v>617.5</v>
@@ -18162,7 +18162,7 @@
         <v>-3932.460962422097</v>
       </c>
       <c r="E384" t="n">
-        <v>6725</v>
+        <v>26226</v>
       </c>
       <c r="F384" t="n">
         <v>630.5</v>
@@ -18182,7 +18182,7 @@
         <v>-3931.923653320499</v>
       </c>
       <c r="E385" t="n">
-        <v>6766</v>
+        <v>26344</v>
       </c>
       <c r="F385" t="n">
         <v>648</v>
@@ -18202,7 +18202,7 @@
         <v>-3932.883867143456</v>
       </c>
       <c r="E386" t="n">
-        <v>6803</v>
+        <v>26446</v>
       </c>
       <c r="F386" t="n">
         <v>662.5</v>
@@ -18222,7 +18222,7 @@
         <v>-3935.419434326667</v>
       </c>
       <c r="E387" t="n">
-        <v>6844</v>
+        <v>26562</v>
       </c>
       <c r="F387" t="n">
         <v>672.5</v>
@@ -18242,7 +18242,7 @@
         <v>-3933.219293080204</v>
       </c>
       <c r="E388" t="n">
-        <v>6875</v>
+        <v>26694</v>
       </c>
       <c r="F388" t="n">
         <v>684</v>
@@ -18262,7 +18262,7 @@
         <v>-3931.408189662529</v>
       </c>
       <c r="E389" t="n">
-        <v>6912</v>
+        <v>26839</v>
       </c>
       <c r="F389" t="n">
         <v>701.5</v>
@@ -18282,7 +18282,7 @@
         <v>-3940.633893771014</v>
       </c>
       <c r="E390" t="n">
-        <v>6953</v>
+        <v>26945</v>
       </c>
       <c r="F390" t="n">
         <v>716</v>
@@ -18302,7 +18302,7 @@
         <v>-3945.050139377885</v>
       </c>
       <c r="E391" t="n">
-        <v>6996</v>
+        <v>27072</v>
       </c>
       <c r="F391" t="n">
         <v>730.5</v>
@@ -18322,7 +18322,7 @@
         <v>-3946.307294786794</v>
       </c>
       <c r="E392" t="n">
-        <v>7029</v>
+        <v>27163</v>
       </c>
       <c r="F392" t="n">
         <v>746.5</v>
@@ -18342,7 +18342,7 @@
         <v>-3950.736386843588</v>
       </c>
       <c r="E393" t="n">
-        <v>7072</v>
+        <v>27280</v>
       </c>
       <c r="F393" t="n">
         <v>761</v>
@@ -18362,7 +18362,7 @@
         <v>-3952.885214647476</v>
       </c>
       <c r="E394" t="n">
-        <v>7105</v>
+        <v>27420</v>
       </c>
       <c r="F394" t="n">
         <v>775.5</v>
@@ -18382,7 +18382,7 @@
         <v>-3959.513644923875</v>
       </c>
       <c r="E395" t="n">
-        <v>7144</v>
+        <v>27518</v>
       </c>
       <c r="F395" t="n">
         <v>793</v>
@@ -18402,7 +18402,7 @@
         <v>-3962.325267499992</v>
       </c>
       <c r="E396" t="n">
-        <v>7181</v>
+        <v>27621</v>
       </c>
       <c r="F396" t="n">
         <v>804.5</v>
@@ -18422,7 +18422,7 @@
         <v>-3960.808919475468</v>
       </c>
       <c r="E397" t="n">
-        <v>7212</v>
+        <v>27799</v>
       </c>
       <c r="F397" t="n">
         <v>823.5</v>
@@ -18442,7 +18442,7 @@
         <v>-3960.032963220749</v>
       </c>
       <c r="E398" t="n">
-        <v>7251</v>
+        <v>27927</v>
       </c>
       <c r="F398" t="n">
         <v>844</v>
@@ -18462,7 +18462,7 @@
         <v>-3967.554477166513</v>
       </c>
       <c r="E399" t="n">
-        <v>7288</v>
+        <v>28017</v>
       </c>
       <c r="F399" t="n">
         <v>863</v>
@@ -18482,7 +18482,7 @@
         <v>-3961.647557092731</v>
       </c>
       <c r="E400" t="n">
-        <v>7325</v>
+        <v>28132</v>
       </c>
       <c r="F400" t="n">
         <v>877.5</v>
@@ -18502,7 +18502,7 @@
         <v>-3962.800357226531</v>
       </c>
       <c r="E401" t="n">
-        <v>7364</v>
+        <v>28275</v>
       </c>
       <c r="F401" t="n">
         <v>895</v>
@@ -18522,7 +18522,7 @@
         <v>-3960.878002874664</v>
       </c>
       <c r="E402" t="n">
-        <v>7405</v>
+        <v>28432</v>
       </c>
       <c r="F402" t="n">
         <v>908</v>
@@ -18542,7 +18542,7 @@
         <v>-3962.202650680811</v>
       </c>
       <c r="E403" t="n">
-        <v>7446</v>
+        <v>28513</v>
       </c>
       <c r="F403" t="n">
         <v>921</v>
@@ -18562,7 +18562,7 @@
         <v>-3963.877870872013</v>
       </c>
       <c r="E404" t="n">
-        <v>7477</v>
+        <v>28650</v>
       </c>
       <c r="F404" t="n">
         <v>938.5</v>
@@ -18582,7 +18582,7 @@
         <v>-3960.592347871313</v>
       </c>
       <c r="E405" t="n">
-        <v>7510</v>
+        <v>28777</v>
       </c>
       <c r="F405" t="n">
         <v>950</v>
@@ -18602,7 +18602,7 @@
         <v>-3959.093445970433</v>
       </c>
       <c r="E406" t="n">
-        <v>7539</v>
+        <v>28899</v>
       </c>
       <c r="F406" t="n">
         <v>966</v>
@@ -18622,7 +18622,7 @@
         <v>-3958.704304522837</v>
       </c>
       <c r="E407" t="n">
-        <v>7576</v>
+        <v>29009</v>
       </c>
       <c r="F407" t="n">
         <v>986.5</v>
@@ -18642,7 +18642,7 @@
         <v>-3964.331323531655</v>
       </c>
       <c r="E408" t="n">
-        <v>7617</v>
+        <v>29130</v>
       </c>
       <c r="F408" t="n">
         <v>1001</v>
@@ -18662,7 +18662,7 @@
         <v>-3971.761434516482</v>
       </c>
       <c r="E409" t="n">
-        <v>7656</v>
+        <v>29231</v>
       </c>
       <c r="F409" t="n">
         <v>1023</v>
@@ -18682,7 +18682,7 @@
         <v>-3971.635816570012</v>
       </c>
       <c r="E410" t="n">
-        <v>7691</v>
+        <v>29377</v>
       </c>
       <c r="F410" t="n">
         <v>1043.5</v>
@@ -18702,7 +18702,7 @@
         <v>-3976.72843105495</v>
       </c>
       <c r="E411" t="n">
-        <v>7734</v>
+        <v>29486</v>
       </c>
       <c r="F411" t="n">
         <v>1053.5</v>
@@ -18722,7 +18722,7 @@
         <v>-3980.837124201093</v>
       </c>
       <c r="E412" t="n">
-        <v>7771</v>
+        <v>29592</v>
       </c>
       <c r="F412" t="n">
         <v>1066.5</v>
@@ -18742,7 +18742,7 @@
         <v>-3988.300929029893</v>
       </c>
       <c r="E413" t="n">
-        <v>7806</v>
+        <v>29674</v>
       </c>
       <c r="F413" t="n">
         <v>1084</v>
@@ -18762,7 +18762,7 @@
         <v>-3989.356051874164</v>
       </c>
       <c r="E414" t="n">
-        <v>7843</v>
+        <v>29805</v>
       </c>
       <c r="F414" t="n">
         <v>1100</v>
@@ -18782,7 +18782,7 @@
         <v>-3990.571738583809</v>
       </c>
       <c r="E415" t="n">
-        <v>7878</v>
+        <v>29945</v>
       </c>
       <c r="F415" t="n">
         <v>1117.5</v>
@@ -18802,7 +18802,7 @@
         <v>-3994.96853898736</v>
       </c>
       <c r="E416" t="n">
-        <v>7917</v>
+        <v>30068</v>
       </c>
       <c r="F416" t="n">
         <v>1139.5</v>
@@ -18822,7 +18822,7 @@
         <v>-3997.259802583437</v>
       </c>
       <c r="E417" t="n">
-        <v>7960</v>
+        <v>30215</v>
       </c>
       <c r="F417" t="n">
         <v>1161.5</v>
@@ -18842,7 +18842,7 @@
         <v>-3998.598786760912</v>
       </c>
       <c r="E418" t="n">
-        <v>7995</v>
+        <v>30376</v>
       </c>
       <c r="F418" t="n">
         <v>1180.5</v>
@@ -18862,7 +18862,7 @@
         <v>-4000.97739558664</v>
       </c>
       <c r="E419" t="n">
-        <v>8032</v>
+        <v>30504</v>
       </c>
       <c r="F419" t="n">
         <v>1201</v>
@@ -18882,7 +18882,7 @@
         <v>-4005.45556725096</v>
       </c>
       <c r="E420" t="n">
-        <v>8071</v>
+        <v>30617</v>
       </c>
       <c r="F420" t="n">
         <v>1220</v>
@@ -18902,7 +18902,7 @@
         <v>-4001.961647623041</v>
       </c>
       <c r="E421" t="n">
-        <v>8104</v>
+        <v>30761</v>
       </c>
       <c r="F421" t="n">
         <v>1240.5</v>
@@ -18922,7 +18922,7 @@
         <v>-4002.410954930469</v>
       </c>
       <c r="E422" t="n">
-        <v>8143</v>
+        <v>30910</v>
       </c>
       <c r="F422" t="n">
         <v>1259.5</v>
@@ -18942,7 +18942,7 @@
         <v>-4005.940434212504</v>
       </c>
       <c r="E423" t="n">
-        <v>8186</v>
+        <v>31053</v>
       </c>
       <c r="F423" t="n">
         <v>1280</v>
@@ -18962,7 +18962,7 @@
         <v>-4000.435071042857</v>
       </c>
       <c r="E424" t="n">
-        <v>8223</v>
+        <v>31200</v>
       </c>
       <c r="F424" t="n">
         <v>1296</v>
@@ -18982,7 +18982,7 @@
         <v>-4001.724820208937</v>
       </c>
       <c r="E425" t="n">
-        <v>8260</v>
+        <v>31321</v>
       </c>
       <c r="F425" t="n">
         <v>1313.5</v>
@@ -19002,7 +19002,7 @@
         <v>-4008.053166994851</v>
       </c>
       <c r="E426" t="n">
-        <v>8305</v>
+        <v>31435</v>
       </c>
       <c r="F426" t="n">
         <v>1332.5</v>
@@ -19022,7 +19022,7 @@
         <v>-4010.298937885023</v>
       </c>
       <c r="E427" t="n">
-        <v>8348</v>
+        <v>31547</v>
       </c>
       <c r="F427" t="n">
         <v>1353</v>
@@ -19042,7 +19042,7 @@
         <v>-4009.440312276627</v>
       </c>
       <c r="E428" t="n">
-        <v>8383</v>
+        <v>31703</v>
       </c>
       <c r="F428" t="n">
         <v>1373.5</v>
@@ -19062,7 +19062,7 @@
         <v>-4010.880443182599</v>
       </c>
       <c r="E429" t="n">
-        <v>8424</v>
+        <v>31850</v>
       </c>
       <c r="F429" t="n">
         <v>1391</v>
@@ -19082,7 +19082,7 @@
         <v>-4016.911976714099</v>
       </c>
       <c r="E430" t="n">
-        <v>8467</v>
+        <v>31968</v>
       </c>
       <c r="F430" t="n">
         <v>1408.5</v>
@@ -19102,7 +19102,7 @@
         <v>-4023.395370750281</v>
       </c>
       <c r="E431" t="n">
-        <v>8510</v>
+        <v>32081</v>
       </c>
       <c r="F431" t="n">
         <v>1430.5</v>
@@ -19122,7 +19122,7 @@
         <v>-4027.524552674005</v>
       </c>
       <c r="E432" t="n">
-        <v>8549</v>
+        <v>32185</v>
       </c>
       <c r="F432" t="n">
         <v>1445</v>
@@ -19142,7 +19142,7 @@
         <v>-4028.064047873985</v>
       </c>
       <c r="E433" t="n">
-        <v>8588</v>
+        <v>32333</v>
       </c>
       <c r="F433" t="n">
         <v>1464</v>
@@ -19162,7 +19162,7 @@
         <v>-4032.981425243987</v>
       </c>
       <c r="E434" t="n">
-        <v>8629</v>
+        <v>32431</v>
       </c>
       <c r="F434" t="n">
         <v>1486</v>
@@ -19182,7 +19182,7 @@
         <v>-4034.610925039364</v>
       </c>
       <c r="E435" t="n">
-        <v>8670</v>
+        <v>32566</v>
       </c>
       <c r="F435" t="n">
         <v>1505</v>
@@ -19202,7 +19202,7 @@
         <v>-4036.611776117434</v>
       </c>
       <c r="E436" t="n">
-        <v>8713</v>
+        <v>32689</v>
       </c>
       <c r="F436" t="n">
         <v>1528.5</v>
@@ -19222,7 +19222,7 @@
         <v>-4037.251290035139</v>
       </c>
       <c r="E437" t="n">
-        <v>8758</v>
+        <v>32842</v>
       </c>
       <c r="F437" t="n">
         <v>1544.5</v>
@@ -19242,7 +19242,7 @@
         <v>-4041.034667142736</v>
       </c>
       <c r="E438" t="n">
-        <v>8797</v>
+        <v>32973</v>
       </c>
       <c r="F438" t="n">
         <v>1563.5</v>
@@ -19262,7 +19262,7 @@
         <v>-4041.225544879799</v>
       </c>
       <c r="E439" t="n">
-        <v>8840</v>
+        <v>33134</v>
       </c>
       <c r="F439" t="n">
         <v>1581</v>
@@ -19282,7 +19282,7 @@
         <v>-4036.466317529388</v>
       </c>
       <c r="E440" t="n">
-        <v>8879</v>
+        <v>33267</v>
       </c>
       <c r="F440" t="n">
         <v>1598.5</v>
@@ -19302,7 +19302,7 @@
         <v>-4035.788433461802</v>
       </c>
       <c r="E441" t="n">
-        <v>8920</v>
+        <v>33421</v>
       </c>
       <c r="F441" t="n">
         <v>1616</v>
@@ -19322,7 +19322,7 @@
         <v>-4035.860191826792</v>
       </c>
       <c r="E442" t="n">
-        <v>8963</v>
+        <v>33558</v>
       </c>
       <c r="F442" t="n">
         <v>1635</v>
@@ -19342,7 +19342,7 @@
         <v>-4037.402158199117</v>
       </c>
       <c r="E443" t="n">
-        <v>9008</v>
+        <v>33719</v>
       </c>
       <c r="F443" t="n">
         <v>1654</v>
@@ -19362,7 +19362,7 @@
         <v>-4038.486902608306</v>
       </c>
       <c r="E444" t="n">
-        <v>9051</v>
+        <v>33888</v>
       </c>
       <c r="F444" t="n">
         <v>1676</v>
@@ -19382,7 +19382,7 @@
         <v>-4036.009444405397</v>
       </c>
       <c r="E445" t="n">
-        <v>9092</v>
+        <v>34036</v>
       </c>
       <c r="F445" t="n">
         <v>1692</v>
@@ -19402,7 +19402,7 @@
         <v>-4036.898085982486</v>
       </c>
       <c r="E446" t="n">
-        <v>9133</v>
+        <v>34183</v>
       </c>
       <c r="F446" t="n">
         <v>1709.5</v>
@@ -19422,7 +19422,7 @@
         <v>-4041.040674242279</v>
       </c>
       <c r="E447" t="n">
-        <v>9176</v>
+        <v>34302</v>
       </c>
       <c r="F447" t="n">
         <v>1728.5</v>
@@ -19442,7 +19442,7 @@
         <v>-4048.535087429127</v>
       </c>
       <c r="E448" t="n">
-        <v>9209</v>
+        <v>34391</v>
       </c>
       <c r="F448" t="n">
         <v>1752</v>
@@ -19462,7 +19462,7 @@
         <v>-4049.116129675113</v>
       </c>
       <c r="E449" t="n">
-        <v>9244</v>
+        <v>34503</v>
       </c>
       <c r="F449" t="n">
         <v>1771</v>
@@ -19482,7 +19482,7 @@
         <v>-4049.581186298098</v>
       </c>
       <c r="E450" t="n">
-        <v>9283</v>
+        <v>34648</v>
       </c>
       <c r="F450" t="n">
         <v>1793</v>
@@ -19502,7 +19502,7 @@
         <v>-4049.685148401122</v>
       </c>
       <c r="E451" t="n">
-        <v>9318</v>
+        <v>34823</v>
       </c>
       <c r="F451" t="n">
         <v>1812</v>
@@ -19522,7 +19522,7 @@
         <v>-4049.118373060276</v>
       </c>
       <c r="E452" t="n">
-        <v>9357</v>
+        <v>34960</v>
       </c>
       <c r="F452" t="n">
         <v>1831</v>
@@ -19542,7 +19542,7 @@
         <v>-4048.270928309592</v>
       </c>
       <c r="E453" t="n">
-        <v>9394</v>
+        <v>35142</v>
       </c>
       <c r="F453" t="n">
         <v>1848.5</v>
@@ -19562,7 +19562,7 @@
         <v>-4047.044872116019</v>
       </c>
       <c r="E454" t="n">
-        <v>9433</v>
+        <v>35256</v>
       </c>
       <c r="F454" t="n">
         <v>1864.5</v>
@@ -19582,7 +19582,7 @@
         <v>-4048.494035159575</v>
       </c>
       <c r="E455" t="n">
-        <v>9472</v>
+        <v>35374</v>
       </c>
       <c r="F455" t="n">
         <v>1883.5</v>
@@ -19602,7 +19602,7 @@
         <v>-4055.557076922366</v>
       </c>
       <c r="E456" t="n">
-        <v>9515</v>
+        <v>35479</v>
       </c>
       <c r="F456" t="n">
         <v>1902.5</v>
@@ -19622,7 +19622,7 @@
         <v>-4058.816021607141</v>
       </c>
       <c r="E457" t="n">
-        <v>9560</v>
+        <v>35587</v>
       </c>
       <c r="F457" t="n">
         <v>1921.5</v>
@@ -19642,7 +19642,7 @@
         <v>-4058.512206065356</v>
       </c>
       <c r="E458" t="n">
-        <v>9603</v>
+        <v>35745</v>
       </c>
       <c r="F458" t="n">
         <v>1942</v>
@@ -19662,7 +19662,7 @@
         <v>-4055.586638682457</v>
       </c>
       <c r="E459" t="n">
-        <v>9648</v>
+        <v>35909</v>
       </c>
       <c r="F459" t="n">
         <v>1962.5</v>
@@ -19682,7 +19682,7 @@
         <v>-4054.359303303845</v>
       </c>
       <c r="E460" t="n">
-        <v>9683</v>
+        <v>36067</v>
       </c>
       <c r="F460" t="n">
         <v>1984.5</v>
@@ -19702,7 +19702,7 @@
         <v>-4054.002589768311</v>
       </c>
       <c r="E461" t="n">
-        <v>9730</v>
+        <v>36234</v>
       </c>
       <c r="F461" t="n">
         <v>2005</v>
@@ -19722,7 +19722,7 @@
         <v>-4059.232979741861</v>
       </c>
       <c r="E462" t="n">
-        <v>9769</v>
+        <v>36345</v>
       </c>
       <c r="F462" t="n">
         <v>2021</v>
@@ -19742,7 +19742,7 @@
         <v>-4063.701942261097</v>
       </c>
       <c r="E463" t="n">
-        <v>9810</v>
+        <v>36459</v>
       </c>
       <c r="F463" t="n">
         <v>2043</v>
@@ -19762,7 +19762,7 @@
         <v>-4060.559718902382</v>
       </c>
       <c r="E464" t="n">
-        <v>9857</v>
+        <v>36625</v>
       </c>
       <c r="F464" t="n">
         <v>2063.5</v>
@@ -19782,7 +19782,7 @@
         <v>-4059.534613558375</v>
       </c>
       <c r="E465" t="n">
-        <v>9900</v>
+        <v>36800</v>
       </c>
       <c r="F465" t="n">
         <v>2085.5</v>
@@ -19802,7 +19802,7 @@
         <v>-4060.148781013936</v>
       </c>
       <c r="E466" t="n">
-        <v>9947</v>
+        <v>36968</v>
       </c>
       <c r="F466" t="n">
         <v>2106</v>
@@ -19822,7 +19822,7 @@
         <v>-4060.964854401854</v>
       </c>
       <c r="E467" t="n">
-        <v>9988</v>
+        <v>37105</v>
       </c>
       <c r="F467" t="n">
         <v>2126.5</v>
@@ -19842,7 +19842,7 @@
         <v>-4059.827515825782</v>
       </c>
       <c r="E468" t="n">
-        <v>10033</v>
+        <v>37251</v>
       </c>
       <c r="F468" t="n">
         <v>2150</v>
@@ -19862,7 +19862,7 @@
         <v>-4059.136003735782</v>
       </c>
       <c r="E469" t="n">
-        <v>10080</v>
+        <v>37403</v>
       </c>
       <c r="F469" t="n">
         <v>2172</v>
@@ -19882,7 +19882,7 @@
         <v>-4056.885637515954</v>
       </c>
       <c r="E470" t="n">
-        <v>10121</v>
+        <v>37525</v>
       </c>
       <c r="F470" t="n">
         <v>2192.5</v>
@@ -19902,7 +19902,7 @@
         <v>-4056.865030009566</v>
       </c>
       <c r="E471" t="n">
-        <v>10168</v>
+        <v>37690</v>
       </c>
       <c r="F471" t="n">
         <v>2213</v>
@@ -19922,7 +19922,7 @@
         <v>-4057.924999673819</v>
       </c>
       <c r="E472" t="n">
-        <v>10211</v>
+        <v>37858</v>
       </c>
       <c r="F472" t="n">
         <v>2232</v>
@@ -19942,7 +19942,7 @@
         <v>-4059.632842196756</v>
       </c>
       <c r="E473" t="n">
-        <v>10256</v>
+        <v>38019</v>
       </c>
       <c r="F473" t="n">
         <v>2255.5</v>
@@ -19962,7 +19962,7 @@
         <v>-4054.543605559077</v>
       </c>
       <c r="E474" t="n">
-        <v>10299</v>
+        <v>38171</v>
       </c>
       <c r="F474" t="n">
         <v>2274.5</v>
@@ -19982,7 +19982,7 @@
         <v>-4053.444922666721</v>
       </c>
       <c r="E475" t="n">
-        <v>10344</v>
+        <v>38318</v>
       </c>
       <c r="F475" t="n">
         <v>2298</v>
@@ -20002,7 +20002,7 @@
         <v>-4051.321292763216</v>
       </c>
       <c r="E476" t="n">
-        <v>10389</v>
+        <v>38478</v>
       </c>
       <c r="F476" t="n">
         <v>2321.5</v>
@@ -20022,7 +20022,7 @@
         <v>-4048.733330681505</v>
       </c>
       <c r="E477" t="n">
-        <v>10434</v>
+        <v>38612</v>
       </c>
       <c r="F477" t="n">
         <v>2343.5</v>
@@ -20042,7 +20042,7 @@
         <v>-4047.268118905349</v>
       </c>
       <c r="E478" t="n">
-        <v>10479</v>
+        <v>38761</v>
       </c>
       <c r="F478" t="n">
         <v>2364</v>
@@ -20062,7 +20062,7 @@
         <v>-4045.040387993271</v>
       </c>
       <c r="E479" t="n">
-        <v>10526</v>
+        <v>38936</v>
       </c>
       <c r="F479" t="n">
         <v>2387.5</v>
@@ -20082,7 +20082,7 @@
         <v>-4047.892899492597</v>
       </c>
       <c r="E480" t="n">
-        <v>10567</v>
+        <v>39046</v>
       </c>
       <c r="F480" t="n">
         <v>2408</v>
@@ -20102,7 +20102,7 @@
         <v>-4046.2367983871</v>
       </c>
       <c r="E481" t="n">
-        <v>10614</v>
+        <v>39221</v>
       </c>
       <c r="F481" t="n">
         <v>2431.5</v>
@@ -20122,7 +20122,7 @@
         <v>-4048.418393428551</v>
       </c>
       <c r="E482" t="n">
-        <v>10657</v>
+        <v>39365</v>
       </c>
       <c r="F482" t="n">
         <v>2453.5</v>
@@ -20142,7 +20142,7 @@
         <v>-4046.108654955806</v>
       </c>
       <c r="E483" t="n">
-        <v>10700</v>
+        <v>39488</v>
       </c>
       <c r="F483" t="n">
         <v>2475.5</v>
@@ -20162,7 +20162,7 @@
         <v>-4043.188097460521</v>
       </c>
       <c r="E484" t="n">
-        <v>10745</v>
+        <v>39640</v>
       </c>
       <c r="F484" t="n">
         <v>2499</v>
@@ -20182,7 +20182,7 @@
         <v>-4041.925950284332</v>
       </c>
       <c r="E485" t="n">
-        <v>10792</v>
+        <v>39822</v>
       </c>
       <c r="F485" t="n">
         <v>2522.5</v>
@@ -20202,7 +20202,7 @@
         <v>-4040.367790099444</v>
       </c>
       <c r="E486" t="n">
-        <v>10837</v>
+        <v>40004</v>
       </c>
       <c r="F486" t="n">
         <v>2544.5</v>
@@ -20222,7 +20222,7 @@
         <v>-4047.889551106271</v>
       </c>
       <c r="E487" t="n">
-        <v>10882</v>
+        <v>40116</v>
       </c>
       <c r="F487" t="n">
         <v>2568</v>
@@ -20242,7 +20242,7 @@
         <v>-4054.314805480587</v>
       </c>
       <c r="E488" t="n">
-        <v>10927</v>
+        <v>40214</v>
       </c>
       <c r="F488" t="n">
         <v>2590</v>
@@ -20262,7 +20262,7 @@
         <v>-4054.61323076822</v>
       </c>
       <c r="E489" t="n">
-        <v>10974</v>
+        <v>40396</v>
       </c>
       <c r="F489" t="n">
         <v>2612</v>
@@ -20282,7 +20282,7 @@
         <v>-4052.706525031029</v>
       </c>
       <c r="E490" t="n">
-        <v>11021</v>
+        <v>40549</v>
       </c>
       <c r="F490" t="n">
         <v>2632.5</v>
@@ -20302,7 +20302,7 @@
         <v>-4054.532108159449</v>
       </c>
       <c r="E491" t="n">
-        <v>11068</v>
+        <v>40671</v>
       </c>
       <c r="F491" t="n">
         <v>2654.5</v>
@@ -20322,7 +20322,7 @@
         <v>-4055.085345573185</v>
       </c>
       <c r="E492" t="n">
-        <v>11113</v>
+        <v>40799</v>
       </c>
       <c r="F492" t="n">
         <v>2675</v>
@@ -20342,7 +20342,7 @@
         <v>-4055.677224792183</v>
       </c>
       <c r="E493" t="n">
-        <v>11158</v>
+        <v>40971</v>
       </c>
       <c r="F493" t="n">
         <v>2698.5</v>
@@ -20362,7 +20362,7 @@
         <v>-4052.884307252981</v>
       </c>
       <c r="E494" t="n">
-        <v>11205</v>
+        <v>41131</v>
       </c>
       <c r="F494" t="n">
         <v>2722</v>
@@ -20382,7 +20382,7 @@
         <v>-4053.024143158859</v>
       </c>
       <c r="E495" t="n">
-        <v>11252</v>
+        <v>41274</v>
       </c>
       <c r="F495" t="n">
         <v>2744</v>
@@ -20402,7 +20402,7 @@
         <v>-4055.144808586346</v>
       </c>
       <c r="E496" t="n">
-        <v>11299</v>
+        <v>41402</v>
       </c>
       <c r="F496" t="n">
         <v>2767.5</v>
@@ -20422,7 +20422,7 @@
         <v>-4053.920156087494</v>
       </c>
       <c r="E497" t="n">
-        <v>11346</v>
+        <v>41547</v>
       </c>
       <c r="F497" t="n">
         <v>2791</v>
@@ -20442,7 +20442,7 @@
         <v>-4051.232614879372</v>
       </c>
       <c r="E498" t="n">
-        <v>11389</v>
+        <v>41680</v>
       </c>
       <c r="F498" t="n">
         <v>2811.5</v>
@@ -20462,7 +20462,7 @@
         <v>-4050.40853163551</v>
       </c>
       <c r="E499" t="n">
-        <v>11432</v>
+        <v>41847</v>
       </c>
       <c r="F499" t="n">
         <v>2835</v>
@@ -20482,7 +20482,7 @@
         <v>-4047.778277271393</v>
       </c>
       <c r="E500" t="n">
-        <v>11479</v>
+        <v>42026</v>
       </c>
       <c r="F500" t="n">
         <v>2858.5</v>
@@ -20502,7 +20502,7 @@
         <v>-4042.788712033161</v>
       </c>
       <c r="E501" t="n">
-        <v>11526</v>
+        <v>42175</v>
       </c>
       <c r="F501" t="n">
         <v>2882</v>
@@ -20622,19 +20622,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.052</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>15.039</v>
+        <v>46.175</v>
       </c>
       <c r="D5" t="n">
-        <v>-13</v>
+        <v>-29</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>182</v>
       </c>
       <c r="F5" t="n">
-        <v>11526</v>
+        <v>42175</v>
       </c>
     </row>
     <row r="6">

--- a/results/plots/agent_rewards_cumulative.xlsx
+++ b/results/plots/agent_rewards_cumulative.xlsx
@@ -9359,7 +9359,7 @@
         <v>11.5</v>
       </c>
       <c r="F446" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="447">
@@ -9839,7 +9839,7 @@
         <v>24.5</v>
       </c>
       <c r="F470" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="471">
@@ -10059,7 +10059,7 @@
         <v>32.5</v>
       </c>
       <c r="F481" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="482">
@@ -11119,7 +11119,7 @@
         <v>-12</v>
       </c>
       <c r="F534" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="535">
@@ -12399,7 +12399,7 @@
         <v>13.75</v>
       </c>
       <c r="F598" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="599">
@@ -12499,7 +12499,7 @@
         <v>26.5</v>
       </c>
       <c r="F603" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="604">
@@ -14059,7 +14059,7 @@
         <v>11</v>
       </c>
       <c r="F681" t="n">
-        <v>13</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="682">
@@ -14079,7 +14079,7 @@
         <v>22</v>
       </c>
       <c r="F682" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="683">
@@ -14099,7 +14099,7 @@
         <v>11.25</v>
       </c>
       <c r="F683" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="684">
@@ -14279,7 +14279,7 @@
         <v>37.75</v>
       </c>
       <c r="F692" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="693">
@@ -14459,7 +14459,7 @@
         <v>37</v>
       </c>
       <c r="F701" t="n">
-        <v>22</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="702">
@@ -14479,7 +14479,7 @@
         <v>13</v>
       </c>
       <c r="F702" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="703">
@@ -15039,7 +15039,7 @@
         <v>6</v>
       </c>
       <c r="F730" t="n">
-        <v>5.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="731">
@@ -15619,7 +15619,7 @@
         <v>-4</v>
       </c>
       <c r="F759" t="n">
-        <v>16</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="760">
@@ -15639,7 +15639,7 @@
         <v>-4.75</v>
       </c>
       <c r="F760" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="761">
@@ -15679,7 +15679,7 @@
         <v>33</v>
       </c>
       <c r="F762" t="n">
-        <v>17.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="763">
@@ -16299,7 +16299,7 @@
         <v>36</v>
       </c>
       <c r="F793" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="794">
@@ -16979,7 +16979,7 @@
         <v>-7.5</v>
       </c>
       <c r="F827" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="828">
@@ -16999,7 +16999,7 @@
         <v>31.25</v>
       </c>
       <c r="F828" t="n">
-        <v>14.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="829">
@@ -17359,7 +17359,7 @@
         <v>-1.25</v>
       </c>
       <c r="F846" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="847">
@@ -17399,7 +17399,7 @@
         <v>25</v>
       </c>
       <c r="F848" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="849">
@@ -17419,7 +17419,7 @@
         <v>35.75</v>
       </c>
       <c r="F849" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="850">
@@ -17459,7 +17459,7 @@
         <v>27.5</v>
       </c>
       <c r="F851" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="852">
@@ -17479,7 +17479,7 @@
         <v>33.25</v>
       </c>
       <c r="F852" t="n">
-        <v>19</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="853">
@@ -17499,7 +17499,7 @@
         <v>26.5</v>
       </c>
       <c r="F853" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="854">
@@ -17539,7 +17539,7 @@
         <v>-1.5</v>
       </c>
       <c r="F855" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="856">
@@ -18179,7 +18179,7 @@
         <v>3.25</v>
       </c>
       <c r="F887" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="888">
@@ -18259,7 +18259,7 @@
         <v>17.5</v>
       </c>
       <c r="F891" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="892">
@@ -18279,7 +18279,7 @@
         <v>20.5</v>
       </c>
       <c r="F892" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="893">
@@ -18319,7 +18319,7 @@
         <v>37.75</v>
       </c>
       <c r="F894" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="895">
@@ -18339,7 +18339,7 @@
         <v>35.75</v>
       </c>
       <c r="F895" t="n">
-        <v>22</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="896">
@@ -18379,7 +18379,7 @@
         <v>35.25</v>
       </c>
       <c r="F897" t="n">
-        <v>20.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="898">
@@ -18439,7 +18439,7 @@
         <v>35.25</v>
       </c>
       <c r="F900" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="901">
@@ -18939,7 +18939,7 @@
         <v>25.75</v>
       </c>
       <c r="F925" t="n">
-        <v>20.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="926">
@@ -19019,7 +19019,7 @@
         <v>35.75</v>
       </c>
       <c r="F929" t="n">
-        <v>22</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="930">
@@ -19599,7 +19599,7 @@
         <v>39.75</v>
       </c>
       <c r="F958" t="n">
-        <v>23.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="959">
@@ -20659,7 +20659,7 @@
         <v>11.25</v>
       </c>
       <c r="F1011" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="1012">
@@ -20679,7 +20679,7 @@
         <v>35.25</v>
       </c>
       <c r="F1012" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="1013">
@@ -20739,7 +20739,7 @@
         <v>37.25</v>
       </c>
       <c r="F1015" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1016">
@@ -21479,7 +21479,7 @@
         <v>34</v>
       </c>
       <c r="F1052" t="n">
-        <v>20.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="1053">
@@ -21519,7 +21519,7 @@
         <v>36.5</v>
       </c>
       <c r="F1054" t="n">
-        <v>23.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1055">
@@ -21539,7 +21539,7 @@
         <v>41.25</v>
       </c>
       <c r="F1055" t="n">
-        <v>22</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="1056">
@@ -26799,7 +26799,7 @@
         <v>25.25</v>
       </c>
       <c r="F1318" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1319">
@@ -26819,7 +26819,7 @@
         <v>28</v>
       </c>
       <c r="F1319" t="n">
-        <v>23.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1320">
@@ -26839,7 +26839,7 @@
         <v>31.5</v>
       </c>
       <c r="F1320" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1321">
@@ -26879,7 +26879,7 @@
         <v>3.5</v>
       </c>
       <c r="F1322" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1323">
@@ -26899,7 +26899,7 @@
         <v>24.75</v>
       </c>
       <c r="F1323" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="1324">
@@ -27299,7 +27299,7 @@
         <v>34.5</v>
       </c>
       <c r="F1343" t="n">
-        <v>22</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="1344">
@@ -27359,7 +27359,7 @@
         <v>36</v>
       </c>
       <c r="F1346" t="n">
-        <v>23.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="1347">
@@ -27479,7 +27479,7 @@
         <v>39.25</v>
       </c>
       <c r="F1352" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1353">
@@ -27819,7 +27819,7 @@
         <v>29.75</v>
       </c>
       <c r="F1369" t="n">
-        <v>20.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1370">
@@ -28899,7 +28899,7 @@
         <v>22.75</v>
       </c>
       <c r="F1423" t="n">
-        <v>20.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="1424">
@@ -28919,7 +28919,7 @@
         <v>39</v>
       </c>
       <c r="F1424" t="n">
-        <v>17.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="1425">
@@ -29079,7 +29079,7 @@
         <v>40.5</v>
       </c>
       <c r="F1432" t="n">
-        <v>22</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="1433">
@@ -29099,7 +29099,7 @@
         <v>38.5</v>
       </c>
       <c r="F1433" t="n">
-        <v>23.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1434">
@@ -29119,7 +29119,7 @@
         <v>42.5</v>
       </c>
       <c r="F1434" t="n">
-        <v>20.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1435">
@@ -30179,7 +30179,7 @@
         <v>43.25</v>
       </c>
       <c r="F1487" t="n">
-        <v>20.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="1488">
@@ -30199,7 +30199,7 @@
         <v>36.5</v>
       </c>
       <c r="F1488" t="n">
-        <v>23.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1489">
@@ -30399,7 +30399,7 @@
         <v>40.5</v>
       </c>
       <c r="F1498" t="n">
-        <v>20.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1499">
@@ -39405,7 +39405,7 @@
         <v>6476.25</v>
       </c>
       <c r="F446" t="n">
-        <v>1952.5</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="447">
@@ -39425,7 +39425,7 @@
         <v>6517.25</v>
       </c>
       <c r="F447" t="n">
-        <v>1968.5</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="448">
@@ -39445,7 +39445,7 @@
         <v>6535.25</v>
       </c>
       <c r="F448" t="n">
-        <v>1981.5</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="449">
@@ -39465,7 +39465,7 @@
         <v>6548.5</v>
       </c>
       <c r="F449" t="n">
-        <v>1984</v>
+        <v>1988.5</v>
       </c>
     </row>
     <row r="450">
@@ -39485,7 +39485,7 @@
         <v>6581.5</v>
       </c>
       <c r="F450" t="n">
-        <v>1998.5</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="451">
@@ -39505,7 +39505,7 @@
         <v>6603.5</v>
       </c>
       <c r="F451" t="n">
-        <v>2008.5</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="452">
@@ -39525,7 +39525,7 @@
         <v>6626.25</v>
       </c>
       <c r="F452" t="n">
-        <v>2026</v>
+        <v>2030.5</v>
       </c>
     </row>
     <row r="453">
@@ -39545,7 +39545,7 @@
         <v>6639.75</v>
       </c>
       <c r="F453" t="n">
-        <v>2039</v>
+        <v>2043.5</v>
       </c>
     </row>
     <row r="454">
@@ -39565,7 +39565,7 @@
         <v>6665.5</v>
       </c>
       <c r="F454" t="n">
-        <v>2050.5</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="455">
@@ -39585,7 +39585,7 @@
         <v>6696.5</v>
       </c>
       <c r="F455" t="n">
-        <v>2065</v>
+        <v>2069.5</v>
       </c>
     </row>
     <row r="456">
@@ -39605,7 +39605,7 @@
         <v>6707.75</v>
       </c>
       <c r="F456" t="n">
-        <v>2076.5</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="457">
@@ -39625,7 +39625,7 @@
         <v>6738.75</v>
       </c>
       <c r="F457" t="n">
-        <v>2091</v>
+        <v>2095.5</v>
       </c>
     </row>
     <row r="458">
@@ -39645,7 +39645,7 @@
         <v>6764.5</v>
       </c>
       <c r="F458" t="n">
-        <v>2102.5</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="459">
@@ -39665,7 +39665,7 @@
         <v>6770.5</v>
       </c>
       <c r="F459" t="n">
-        <v>2121.5</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="460">
@@ -39685,7 +39685,7 @@
         <v>6798.5</v>
       </c>
       <c r="F460" t="n">
-        <v>2139</v>
+        <v>2143.5</v>
       </c>
     </row>
     <row r="461">
@@ -39705,7 +39705,7 @@
         <v>6818.5</v>
       </c>
       <c r="F461" t="n">
-        <v>2159.5</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="462">
@@ -39725,7 +39725,7 @@
         <v>6835.75</v>
       </c>
       <c r="F462" t="n">
-        <v>2166.5</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="463">
@@ -39745,7 +39745,7 @@
         <v>6855.5</v>
       </c>
       <c r="F463" t="n">
-        <v>2178</v>
+        <v>2182.5</v>
       </c>
     </row>
     <row r="464">
@@ -39765,7 +39765,7 @@
         <v>6888.5</v>
       </c>
       <c r="F464" t="n">
-        <v>2194</v>
+        <v>2198.5</v>
       </c>
     </row>
     <row r="465">
@@ -39785,7 +39785,7 @@
         <v>6911</v>
       </c>
       <c r="F465" t="n">
-        <v>2211.5</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="466">
@@ -39805,7 +39805,7 @@
         <v>6950</v>
       </c>
       <c r="F466" t="n">
-        <v>2224.5</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="467">
@@ -39825,7 +39825,7 @@
         <v>6956</v>
       </c>
       <c r="F467" t="n">
-        <v>2234.5</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="468">
@@ -39845,7 +39845,7 @@
         <v>6977.75</v>
       </c>
       <c r="F468" t="n">
-        <v>2249</v>
+        <v>2253.5</v>
       </c>
     </row>
     <row r="469">
@@ -39865,7 +39865,7 @@
         <v>7003.5</v>
       </c>
       <c r="F469" t="n">
-        <v>2265</v>
+        <v>2269.5</v>
       </c>
     </row>
     <row r="470">
@@ -39885,7 +39885,7 @@
         <v>7028</v>
       </c>
       <c r="F470" t="n">
-        <v>2285.5</v>
+        <v>2288.5</v>
       </c>
     </row>
     <row r="471">
@@ -39905,7 +39905,7 @@
         <v>7060.5</v>
       </c>
       <c r="F471" t="n">
-        <v>2303</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="472">
@@ -39925,7 +39925,7 @@
         <v>7056.25</v>
       </c>
       <c r="F472" t="n">
-        <v>2310</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="473">
@@ -39945,7 +39945,7 @@
         <v>7084.75</v>
       </c>
       <c r="F473" t="n">
-        <v>2320</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="474">
@@ -39965,7 +39965,7 @@
         <v>7123.75</v>
       </c>
       <c r="F474" t="n">
-        <v>2333</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="475">
@@ -39985,7 +39985,7 @@
         <v>7153.5</v>
       </c>
       <c r="F475" t="n">
-        <v>2347.5</v>
+        <v>2350.5</v>
       </c>
     </row>
     <row r="476">
@@ -40005,7 +40005,7 @@
         <v>7191.25</v>
       </c>
       <c r="F476" t="n">
-        <v>2366.5</v>
+        <v>2369.5</v>
       </c>
     </row>
     <row r="477">
@@ -40025,7 +40025,7 @@
         <v>7223.75</v>
       </c>
       <c r="F477" t="n">
-        <v>2385.5</v>
+        <v>2388.5</v>
       </c>
     </row>
     <row r="478">
@@ -40045,7 +40045,7 @@
         <v>7246.75</v>
       </c>
       <c r="F478" t="n">
-        <v>2397</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="479">
@@ -40065,7 +40065,7 @@
         <v>7267.25</v>
       </c>
       <c r="F479" t="n">
-        <v>2411.5</v>
+        <v>2414.5</v>
       </c>
     </row>
     <row r="480">
@@ -40085,7 +40085,7 @@
         <v>7289</v>
       </c>
       <c r="F480" t="n">
-        <v>2424.5</v>
+        <v>2427.5</v>
       </c>
     </row>
     <row r="481">
@@ -40105,7 +40105,7 @@
         <v>7321.5</v>
       </c>
       <c r="F481" t="n">
-        <v>2439</v>
+        <v>2440.5</v>
       </c>
     </row>
     <row r="482">
@@ -40125,7 +40125,7 @@
         <v>7348.5</v>
       </c>
       <c r="F482" t="n">
-        <v>2452</v>
+        <v>2453.5</v>
       </c>
     </row>
     <row r="483">
@@ -40145,7 +40145,7 @@
         <v>7395.5</v>
       </c>
       <c r="F483" t="n">
-        <v>2468</v>
+        <v>2469.5</v>
       </c>
     </row>
     <row r="484">
@@ -40165,7 +40165,7 @@
         <v>7425.25</v>
       </c>
       <c r="F484" t="n">
-        <v>2479.5</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="485">
@@ -40185,7 +40185,7 @@
         <v>7422.75</v>
       </c>
       <c r="F485" t="n">
-        <v>2498.5</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="486">
@@ -40205,7 +40205,7 @@
         <v>7458.5</v>
       </c>
       <c r="F486" t="n">
-        <v>2513</v>
+        <v>2514.5</v>
       </c>
     </row>
     <row r="487">
@@ -40225,7 +40225,7 @@
         <v>7479</v>
       </c>
       <c r="F487" t="n">
-        <v>2527.5</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="488">
@@ -40245,7 +40245,7 @@
         <v>7493.75</v>
       </c>
       <c r="F488" t="n">
-        <v>2542</v>
+        <v>2543.5</v>
       </c>
     </row>
     <row r="489">
@@ -40265,7 +40265,7 @@
         <v>7504.25</v>
       </c>
       <c r="F489" t="n">
-        <v>2564</v>
+        <v>2565.5</v>
       </c>
     </row>
     <row r="490">
@@ -40285,7 +40285,7 @@
         <v>7528</v>
       </c>
       <c r="F490" t="n">
-        <v>2575.5</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="491">
@@ -40305,7 +40305,7 @@
         <v>7558.5</v>
       </c>
       <c r="F491" t="n">
-        <v>2599</v>
+        <v>2600.5</v>
       </c>
     </row>
     <row r="492">
@@ -40325,7 +40325,7 @@
         <v>7595.5</v>
       </c>
       <c r="F492" t="n">
-        <v>2618</v>
+        <v>2619.5</v>
       </c>
     </row>
     <row r="493">
@@ -40345,7 +40345,7 @@
         <v>7624.25</v>
       </c>
       <c r="F493" t="n">
-        <v>2628</v>
+        <v>2629.5</v>
       </c>
     </row>
     <row r="494">
@@ -40365,7 +40365,7 @@
         <v>7640</v>
       </c>
       <c r="F494" t="n">
-        <v>2645.5</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="495">
@@ -40385,7 +40385,7 @@
         <v>7640</v>
       </c>
       <c r="F495" t="n">
-        <v>2658.5</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="496">
@@ -40405,7 +40405,7 @@
         <v>7660</v>
       </c>
       <c r="F496" t="n">
-        <v>2673</v>
+        <v>2674.5</v>
       </c>
     </row>
     <row r="497">
@@ -40425,7 +40425,7 @@
         <v>7694.5</v>
       </c>
       <c r="F497" t="n">
-        <v>2687.5</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="498">
@@ -40445,7 +40445,7 @@
         <v>7728.25</v>
       </c>
       <c r="F498" t="n">
-        <v>2705</v>
+        <v>2706.5</v>
       </c>
     </row>
     <row r="499">
@@ -40465,7 +40465,7 @@
         <v>7767.25</v>
       </c>
       <c r="F499" t="n">
-        <v>2722.5</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="500">
@@ -40485,7 +40485,7 @@
         <v>7797.75</v>
       </c>
       <c r="F500" t="n">
-        <v>2737</v>
+        <v>2738.5</v>
       </c>
     </row>
     <row r="501">
@@ -40505,7 +40505,7 @@
         <v>7815.5</v>
       </c>
       <c r="F501" t="n">
-        <v>2753</v>
+        <v>2754.5</v>
       </c>
     </row>
     <row r="502">
@@ -40525,7 +40525,7 @@
         <v>7846</v>
       </c>
       <c r="F502" t="n">
-        <v>2767.5</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="503">
@@ -40545,7 +40545,7 @@
         <v>7843.25</v>
       </c>
       <c r="F503" t="n">
-        <v>2783.5</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="504">
@@ -40565,7 +40565,7 @@
         <v>7872.25</v>
       </c>
       <c r="F504" t="n">
-        <v>2796.5</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="505">
@@ -40585,7 +40585,7 @@
         <v>7910.75</v>
       </c>
       <c r="F505" t="n">
-        <v>2811</v>
+        <v>2812.5</v>
       </c>
     </row>
     <row r="506">
@@ -40605,7 +40605,7 @@
         <v>7930</v>
       </c>
       <c r="F506" t="n">
-        <v>2822.5</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="507">
@@ -40625,7 +40625,7 @@
         <v>7969.75</v>
       </c>
       <c r="F507" t="n">
-        <v>2838.5</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="508">
@@ -40645,7 +40645,7 @@
         <v>7988.5</v>
       </c>
       <c r="F508" t="n">
-        <v>2854.5</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="509">
@@ -40665,7 +40665,7 @@
         <v>8007.5</v>
       </c>
       <c r="F509" t="n">
-        <v>2864.5</v>
+        <v>2866</v>
       </c>
     </row>
     <row r="510">
@@ -40685,7 +40685,7 @@
         <v>8024.75</v>
       </c>
       <c r="F510" t="n">
-        <v>2882</v>
+        <v>2883.5</v>
       </c>
     </row>
     <row r="511">
@@ -40705,7 +40705,7 @@
         <v>8051.25</v>
       </c>
       <c r="F511" t="n">
-        <v>2901</v>
+        <v>2902.5</v>
       </c>
     </row>
     <row r="512">
@@ -40725,7 +40725,7 @@
         <v>8079</v>
       </c>
       <c r="F512" t="n">
-        <v>2914</v>
+        <v>2915.5</v>
       </c>
     </row>
     <row r="513">
@@ -40745,7 +40745,7 @@
         <v>8104</v>
       </c>
       <c r="F513" t="n">
-        <v>2936</v>
+        <v>2937.5</v>
       </c>
     </row>
     <row r="514">
@@ -40765,7 +40765,7 @@
         <v>8105.75</v>
       </c>
       <c r="F514" t="n">
-        <v>2949</v>
+        <v>2950.5</v>
       </c>
     </row>
     <row r="515">
@@ -40785,7 +40785,7 @@
         <v>8100.75</v>
       </c>
       <c r="F515" t="n">
-        <v>2966.5</v>
+        <v>2968</v>
       </c>
     </row>
     <row r="516">
@@ -40805,7 +40805,7 @@
         <v>8114.5</v>
       </c>
       <c r="F516" t="n">
-        <v>2982.5</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="517">
@@ -40825,7 +40825,7 @@
         <v>8147.5</v>
       </c>
       <c r="F517" t="n">
-        <v>2997</v>
+        <v>2998.5</v>
       </c>
     </row>
     <row r="518">
@@ -40845,7 +40845,7 @@
         <v>8154.75</v>
       </c>
       <c r="F518" t="n">
-        <v>3017.5</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="519">
@@ -40865,7 +40865,7 @@
         <v>8188.5</v>
       </c>
       <c r="F519" t="n">
-        <v>3039.5</v>
+        <v>3041</v>
       </c>
     </row>
     <row r="520">
@@ -40885,7 +40885,7 @@
         <v>8205.25</v>
       </c>
       <c r="F520" t="n">
-        <v>3063</v>
+        <v>3064.5</v>
       </c>
     </row>
     <row r="521">
@@ -40905,7 +40905,7 @@
         <v>8232.25</v>
       </c>
       <c r="F521" t="n">
-        <v>3080.5</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="522">
@@ -40925,7 +40925,7 @@
         <v>8264</v>
       </c>
       <c r="F522" t="n">
-        <v>3101</v>
+        <v>3102.5</v>
       </c>
     </row>
     <row r="523">
@@ -40945,7 +40945,7 @@
         <v>8295</v>
       </c>
       <c r="F523" t="n">
-        <v>3121.5</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="524">
@@ -40965,7 +40965,7 @@
         <v>8318.25</v>
       </c>
       <c r="F524" t="n">
-        <v>3140.5</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="525">
@@ -40985,7 +40985,7 @@
         <v>8351.5</v>
       </c>
       <c r="F525" t="n">
-        <v>3155</v>
+        <v>3156.5</v>
       </c>
     </row>
     <row r="526">
@@ -41005,7 +41005,7 @@
         <v>8369.5</v>
       </c>
       <c r="F526" t="n">
-        <v>3171</v>
+        <v>3172.5</v>
       </c>
     </row>
     <row r="527">
@@ -41025,7 +41025,7 @@
         <v>8360</v>
       </c>
       <c r="F527" t="n">
-        <v>3185.5</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="528">
@@ -41045,7 +41045,7 @@
         <v>8381.75</v>
       </c>
       <c r="F528" t="n">
-        <v>3204.5</v>
+        <v>3206</v>
       </c>
     </row>
     <row r="529">
@@ -41065,7 +41065,7 @@
         <v>8393.75</v>
       </c>
       <c r="F529" t="n">
-        <v>3217.5</v>
+        <v>3219</v>
       </c>
     </row>
     <row r="530">
@@ -41085,7 +41085,7 @@
         <v>8426.25</v>
       </c>
       <c r="F530" t="n">
-        <v>3233.5</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="531">
@@ -41105,7 +41105,7 @@
         <v>8444.25</v>
       </c>
       <c r="F531" t="n">
-        <v>3249.5</v>
+        <v>3251</v>
       </c>
     </row>
     <row r="532">
@@ -41125,7 +41125,7 @@
         <v>8473.5</v>
       </c>
       <c r="F532" t="n">
-        <v>3270</v>
+        <v>3271.5</v>
       </c>
     </row>
     <row r="533">
@@ -41145,7 +41145,7 @@
         <v>8508.25</v>
       </c>
       <c r="F533" t="n">
-        <v>3292</v>
+        <v>3293.5</v>
       </c>
     </row>
     <row r="534">
@@ -42445,7 +42445,7 @@
         <v>10144.5</v>
       </c>
       <c r="F598" t="n">
-        <v>4437</v>
+        <v>4443</v>
       </c>
     </row>
     <row r="599">
@@ -42465,7 +42465,7 @@
         <v>10172.25</v>
       </c>
       <c r="F599" t="n">
-        <v>4454.5</v>
+        <v>4460.5</v>
       </c>
     </row>
     <row r="600">
@@ -42485,7 +42485,7 @@
         <v>10159.5</v>
       </c>
       <c r="F600" t="n">
-        <v>4475</v>
+        <v>4481</v>
       </c>
     </row>
     <row r="601">
@@ -42505,7 +42505,7 @@
         <v>10194</v>
       </c>
       <c r="F601" t="n">
-        <v>4495.5</v>
+        <v>4501.5</v>
       </c>
     </row>
     <row r="602">
@@ -42525,7 +42525,7 @@
         <v>10220</v>
       </c>
       <c r="F602" t="n">
-        <v>4510</v>
+        <v>4516</v>
       </c>
     </row>
     <row r="603">
@@ -42545,7 +42545,7 @@
         <v>10246.5</v>
       </c>
       <c r="F603" t="n">
-        <v>4527.5</v>
+        <v>4532</v>
       </c>
     </row>
     <row r="604">
@@ -42565,7 +42565,7 @@
         <v>10281.75</v>
       </c>
       <c r="F604" t="n">
-        <v>4546.5</v>
+        <v>4551</v>
       </c>
     </row>
     <row r="605">
@@ -42585,7 +42585,7 @@
         <v>10309.5</v>
       </c>
       <c r="F605" t="n">
-        <v>4561</v>
+        <v>4565.5</v>
       </c>
     </row>
     <row r="606">
@@ -42605,7 +42605,7 @@
         <v>10336.75</v>
       </c>
       <c r="F606" t="n">
-        <v>4583</v>
+        <v>4587.5</v>
       </c>
     </row>
     <row r="607">
@@ -42625,7 +42625,7 @@
         <v>10364.25</v>
       </c>
       <c r="F607" t="n">
-        <v>4605</v>
+        <v>4609.5</v>
       </c>
     </row>
     <row r="608">
@@ -42645,7 +42645,7 @@
         <v>10398</v>
       </c>
       <c r="F608" t="n">
-        <v>4624</v>
+        <v>4628.5</v>
       </c>
     </row>
     <row r="609">
@@ -42665,7 +42665,7 @@
         <v>10411.75</v>
       </c>
       <c r="F609" t="n">
-        <v>4646</v>
+        <v>4650.5</v>
       </c>
     </row>
     <row r="610">
@@ -42685,7 +42685,7 @@
         <v>10444.25</v>
       </c>
       <c r="F610" t="n">
-        <v>4666.5</v>
+        <v>4671</v>
       </c>
     </row>
     <row r="611">
@@ -42705,7 +42705,7 @@
         <v>10474.75</v>
       </c>
       <c r="F611" t="n">
-        <v>4687</v>
+        <v>4691.5</v>
       </c>
     </row>
     <row r="612">
@@ -42725,7 +42725,7 @@
         <v>10497.25</v>
       </c>
       <c r="F612" t="n">
-        <v>4700</v>
+        <v>4704.5</v>
       </c>
     </row>
     <row r="613">
@@ -42745,7 +42745,7 @@
         <v>10525</v>
       </c>
       <c r="F613" t="n">
-        <v>4719</v>
+        <v>4723.5</v>
       </c>
     </row>
     <row r="614">
@@ -42765,7 +42765,7 @@
         <v>10542.75</v>
       </c>
       <c r="F614" t="n">
-        <v>4733.5</v>
+        <v>4738</v>
       </c>
     </row>
     <row r="615">
@@ -42785,7 +42785,7 @@
         <v>10573.25</v>
       </c>
       <c r="F615" t="n">
-        <v>4751</v>
+        <v>4755.5</v>
       </c>
     </row>
     <row r="616">
@@ -42805,7 +42805,7 @@
         <v>10606.5</v>
       </c>
       <c r="F616" t="n">
-        <v>4773</v>
+        <v>4777.5</v>
       </c>
     </row>
     <row r="617">
@@ -42825,7 +42825,7 @@
         <v>10621</v>
       </c>
       <c r="F617" t="n">
-        <v>4796.5</v>
+        <v>4801</v>
       </c>
     </row>
     <row r="618">
@@ -42845,7 +42845,7 @@
         <v>10662</v>
       </c>
       <c r="F618" t="n">
-        <v>4812.5</v>
+        <v>4817</v>
       </c>
     </row>
     <row r="619">
@@ -42865,7 +42865,7 @@
         <v>10683.25</v>
       </c>
       <c r="F619" t="n">
-        <v>4834.5</v>
+        <v>4839</v>
       </c>
     </row>
     <row r="620">
@@ -42885,7 +42885,7 @@
         <v>10702.25</v>
       </c>
       <c r="F620" t="n">
-        <v>4855</v>
+        <v>4859.5</v>
       </c>
     </row>
     <row r="621">
@@ -42905,7 +42905,7 @@
         <v>10726.75</v>
       </c>
       <c r="F621" t="n">
-        <v>4872.5</v>
+        <v>4877</v>
       </c>
     </row>
     <row r="622">
@@ -42925,7 +42925,7 @@
         <v>10734.5</v>
       </c>
       <c r="F622" t="n">
-        <v>4888.5</v>
+        <v>4893</v>
       </c>
     </row>
     <row r="623">
@@ -42945,7 +42945,7 @@
         <v>10757.75</v>
       </c>
       <c r="F623" t="n">
-        <v>4904.5</v>
+        <v>4909</v>
       </c>
     </row>
     <row r="624">
@@ -42965,7 +42965,7 @@
         <v>10769</v>
       </c>
       <c r="F624" t="n">
-        <v>4922</v>
+        <v>4926.5</v>
       </c>
     </row>
     <row r="625">
@@ -42985,7 +42985,7 @@
         <v>10800</v>
       </c>
       <c r="F625" t="n">
-        <v>4939.5</v>
+        <v>4944</v>
       </c>
     </row>
     <row r="626">
@@ -43005,7 +43005,7 @@
         <v>10833</v>
       </c>
       <c r="F626" t="n">
-        <v>4954</v>
+        <v>4958.5</v>
       </c>
     </row>
     <row r="627">
@@ -43025,7 +43025,7 @@
         <v>10857.5</v>
       </c>
       <c r="F627" t="n">
-        <v>4974.5</v>
+        <v>4979</v>
       </c>
     </row>
     <row r="628">
@@ -43045,7 +43045,7 @@
         <v>10893.25</v>
       </c>
       <c r="F628" t="n">
-        <v>4995</v>
+        <v>4999.5</v>
       </c>
     </row>
     <row r="629">
@@ -43065,7 +43065,7 @@
         <v>10915.75</v>
       </c>
       <c r="F629" t="n">
-        <v>5014</v>
+        <v>5018.5</v>
       </c>
     </row>
     <row r="630">
@@ -43085,7 +43085,7 @@
         <v>10933</v>
       </c>
       <c r="F630" t="n">
-        <v>5033</v>
+        <v>5037.5</v>
       </c>
     </row>
     <row r="631">
@@ -43105,7 +43105,7 @@
         <v>10967.5</v>
       </c>
       <c r="F631" t="n">
-        <v>5047.5</v>
+        <v>5052</v>
       </c>
     </row>
     <row r="632">
@@ -43125,7 +43125,7 @@
         <v>10977.25</v>
       </c>
       <c r="F632" t="n">
-        <v>5065</v>
+        <v>5069.5</v>
       </c>
     </row>
     <row r="633">
@@ -43145,7 +43145,7 @@
         <v>11004.5</v>
       </c>
       <c r="F633" t="n">
-        <v>5081</v>
+        <v>5085.5</v>
       </c>
     </row>
     <row r="634">
@@ -43165,7 +43165,7 @@
         <v>11026.5</v>
       </c>
       <c r="F634" t="n">
-        <v>5103</v>
+        <v>5107.5</v>
       </c>
     </row>
     <row r="635">
@@ -43185,7 +43185,7 @@
         <v>11045.5</v>
       </c>
       <c r="F635" t="n">
-        <v>5123.5</v>
+        <v>5128</v>
       </c>
     </row>
     <row r="636">
@@ -43205,7 +43205,7 @@
         <v>11086</v>
       </c>
       <c r="F636" t="n">
-        <v>5141</v>
+        <v>5145.5</v>
       </c>
     </row>
     <row r="637">
@@ -43225,7 +43225,7 @@
         <v>11100.5</v>
       </c>
       <c r="F637" t="n">
-        <v>5163</v>
+        <v>5167.5</v>
       </c>
     </row>
     <row r="638">
@@ -43245,7 +43245,7 @@
         <v>11133.5</v>
       </c>
       <c r="F638" t="n">
-        <v>5183.5</v>
+        <v>5188</v>
       </c>
     </row>
     <row r="639">
@@ -43265,7 +43265,7 @@
         <v>11144.5</v>
       </c>
       <c r="F639" t="n">
-        <v>5202.5</v>
+        <v>5207</v>
       </c>
     </row>
     <row r="640">
@@ -43285,7 +43285,7 @@
         <v>11179</v>
       </c>
       <c r="F640" t="n">
-        <v>5223</v>
+        <v>5227.5</v>
       </c>
     </row>
     <row r="641">
@@ -43305,7 +43305,7 @@
         <v>11189.75</v>
       </c>
       <c r="F641" t="n">
-        <v>5237.5</v>
+        <v>5242</v>
       </c>
     </row>
     <row r="642">
@@ -43325,7 +43325,7 @@
         <v>11219</v>
       </c>
       <c r="F642" t="n">
-        <v>5253.5</v>
+        <v>5258</v>
       </c>
     </row>
     <row r="643">
@@ -43345,7 +43345,7 @@
         <v>11256</v>
       </c>
       <c r="F643" t="n">
-        <v>5272.5</v>
+        <v>5277</v>
       </c>
     </row>
     <row r="644">
@@ -43365,7 +43365,7 @@
         <v>11268</v>
       </c>
       <c r="F644" t="n">
-        <v>5285.5</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="645">
@@ -43385,7 +43385,7 @@
         <v>11279.5</v>
       </c>
       <c r="F645" t="n">
-        <v>5304.5</v>
+        <v>5309</v>
       </c>
     </row>
     <row r="646">
@@ -43405,7 +43405,7 @@
         <v>11302.25</v>
       </c>
       <c r="F646" t="n">
-        <v>5328</v>
+        <v>5332.5</v>
       </c>
     </row>
     <row r="647">
@@ -43425,7 +43425,7 @@
         <v>11338</v>
       </c>
       <c r="F647" t="n">
-        <v>5345.5</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="648">
@@ -43445,7 +43445,7 @@
         <v>11374.25</v>
       </c>
       <c r="F648" t="n">
-        <v>5366</v>
+        <v>5370.5</v>
       </c>
     </row>
     <row r="649">
@@ -43465,7 +43465,7 @@
         <v>11392.75</v>
       </c>
       <c r="F649" t="n">
-        <v>5382</v>
+        <v>5386.5</v>
       </c>
     </row>
     <row r="650">
@@ -43485,7 +43485,7 @@
         <v>11422</v>
       </c>
       <c r="F650" t="n">
-        <v>5402.5</v>
+        <v>5407</v>
       </c>
     </row>
     <row r="651">
@@ -43505,7 +43505,7 @@
         <v>11428.5</v>
       </c>
       <c r="F651" t="n">
-        <v>5421.5</v>
+        <v>5426</v>
       </c>
     </row>
     <row r="652">
@@ -43525,7 +43525,7 @@
         <v>11420.25</v>
       </c>
       <c r="F652" t="n">
-        <v>5437.5</v>
+        <v>5442</v>
       </c>
     </row>
     <row r="653">
@@ -43545,7 +43545,7 @@
         <v>11432.25</v>
       </c>
       <c r="F653" t="n">
-        <v>5452</v>
+        <v>5456.5</v>
       </c>
     </row>
     <row r="654">
@@ -43565,7 +43565,7 @@
         <v>11461.5</v>
       </c>
       <c r="F654" t="n">
-        <v>5471</v>
+        <v>5475.5</v>
       </c>
     </row>
     <row r="655">
@@ -43585,7 +43585,7 @@
         <v>11487.25</v>
       </c>
       <c r="F655" t="n">
-        <v>5485.5</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="656">
@@ -43605,7 +43605,7 @@
         <v>11504</v>
       </c>
       <c r="F656" t="n">
-        <v>5509</v>
+        <v>5513.5</v>
       </c>
     </row>
     <row r="657">
@@ -43625,7 +43625,7 @@
         <v>11537.25</v>
       </c>
       <c r="F657" t="n">
-        <v>5529.5</v>
+        <v>5534</v>
       </c>
     </row>
     <row r="658">
@@ -43645,7 +43645,7 @@
         <v>11569</v>
       </c>
       <c r="F658" t="n">
-        <v>5551.5</v>
+        <v>5556</v>
       </c>
     </row>
     <row r="659">
@@ -43665,7 +43665,7 @@
         <v>11593</v>
       </c>
       <c r="F659" t="n">
-        <v>5567.5</v>
+        <v>5572</v>
       </c>
     </row>
     <row r="660">
@@ -43685,7 +43685,7 @@
         <v>11611.5</v>
       </c>
       <c r="F660" t="n">
-        <v>5585</v>
+        <v>5589.5</v>
       </c>
     </row>
     <row r="661">
@@ -43705,7 +43705,7 @@
         <v>11632</v>
       </c>
       <c r="F661" t="n">
-        <v>5605.5</v>
+        <v>5610</v>
       </c>
     </row>
     <row r="662">
@@ -43725,7 +43725,7 @@
         <v>11658.5</v>
       </c>
       <c r="F662" t="n">
-        <v>5624.5</v>
+        <v>5629</v>
       </c>
     </row>
     <row r="663">
@@ -43745,7 +43745,7 @@
         <v>11697.5</v>
       </c>
       <c r="F663" t="n">
-        <v>5646.5</v>
+        <v>5651</v>
       </c>
     </row>
     <row r="664">
@@ -43765,7 +43765,7 @@
         <v>11729.5</v>
       </c>
       <c r="F664" t="n">
-        <v>5667</v>
+        <v>5671.5</v>
       </c>
     </row>
     <row r="665">
@@ -43785,7 +43785,7 @@
         <v>11742.5</v>
       </c>
       <c r="F665" t="n">
-        <v>5681.5</v>
+        <v>5686</v>
       </c>
     </row>
     <row r="666">
@@ -43805,7 +43805,7 @@
         <v>11770.5</v>
       </c>
       <c r="F666" t="n">
-        <v>5700.5</v>
+        <v>5705</v>
       </c>
     </row>
     <row r="667">
@@ -43825,7 +43825,7 @@
         <v>11800</v>
       </c>
       <c r="F667" t="n">
-        <v>5721</v>
+        <v>5725.5</v>
       </c>
     </row>
     <row r="668">
@@ -43845,7 +43845,7 @@
         <v>11839.75</v>
       </c>
       <c r="F668" t="n">
-        <v>5741.5</v>
+        <v>5746</v>
       </c>
     </row>
     <row r="669">
@@ -43865,7 +43865,7 @@
         <v>11882.25</v>
       </c>
       <c r="F669" t="n">
-        <v>5762</v>
+        <v>5766.5</v>
       </c>
     </row>
     <row r="670">
@@ -43885,7 +43885,7 @@
         <v>11913</v>
       </c>
       <c r="F670" t="n">
-        <v>5779.5</v>
+        <v>5784</v>
       </c>
     </row>
     <row r="671">
@@ -43905,7 +43905,7 @@
         <v>11954.75</v>
       </c>
       <c r="F671" t="n">
-        <v>5800</v>
+        <v>5804.5</v>
       </c>
     </row>
     <row r="672">
@@ -43925,7 +43925,7 @@
         <v>11995.75</v>
       </c>
       <c r="F672" t="n">
-        <v>5817.5</v>
+        <v>5822</v>
       </c>
     </row>
     <row r="673">
@@ -43945,7 +43945,7 @@
         <v>12026.5</v>
       </c>
       <c r="F673" t="n">
-        <v>5833.5</v>
+        <v>5838</v>
       </c>
     </row>
     <row r="674">
@@ -43965,7 +43965,7 @@
         <v>12066.25</v>
       </c>
       <c r="F674" t="n">
-        <v>5854</v>
+        <v>5858.5</v>
       </c>
     </row>
     <row r="675">
@@ -43985,7 +43985,7 @@
         <v>12104.75</v>
       </c>
       <c r="F675" t="n">
-        <v>5874.5</v>
+        <v>5879</v>
       </c>
     </row>
     <row r="676">
@@ -44005,7 +44005,7 @@
         <v>12108.75</v>
       </c>
       <c r="F676" t="n">
-        <v>5892</v>
+        <v>5896.5</v>
       </c>
     </row>
     <row r="677">
@@ -44025,7 +44025,7 @@
         <v>12120.5</v>
       </c>
       <c r="F677" t="n">
-        <v>5912.5</v>
+        <v>5917</v>
       </c>
     </row>
     <row r="678">
@@ -44045,7 +44045,7 @@
         <v>12162.25</v>
       </c>
       <c r="F678" t="n">
-        <v>5934.5</v>
+        <v>5939</v>
       </c>
     </row>
     <row r="679">
@@ -44065,7 +44065,7 @@
         <v>12199.5</v>
       </c>
       <c r="F679" t="n">
-        <v>5955</v>
+        <v>5959.5</v>
       </c>
     </row>
     <row r="680">
@@ -44085,7 +44085,7 @@
         <v>12202</v>
       </c>
       <c r="F680" t="n">
-        <v>5972.5</v>
+        <v>5977</v>
       </c>
     </row>
     <row r="681">
@@ -44105,7 +44105,7 @@
         <v>12213</v>
       </c>
       <c r="F681" t="n">
-        <v>5985.5</v>
+        <v>5997.5</v>
       </c>
     </row>
     <row r="682">
@@ -44125,7 +44125,7 @@
         <v>12235</v>
       </c>
       <c r="F682" t="n">
-        <v>6000</v>
+        <v>6016.5</v>
       </c>
     </row>
     <row r="683">
@@ -44145,7 +44145,7 @@
         <v>12246.25</v>
       </c>
       <c r="F683" t="n">
-        <v>6016</v>
+        <v>6028</v>
       </c>
     </row>
     <row r="684">
@@ -44165,7 +44165,7 @@
         <v>12274</v>
       </c>
       <c r="F684" t="n">
-        <v>6035</v>
+        <v>6047</v>
       </c>
     </row>
     <row r="685">
@@ -44185,7 +44185,7 @@
         <v>12315</v>
       </c>
       <c r="F685" t="n">
-        <v>6057</v>
+        <v>6069</v>
       </c>
     </row>
     <row r="686">
@@ -44205,7 +44205,7 @@
         <v>12329.5</v>
       </c>
       <c r="F686" t="n">
-        <v>6076</v>
+        <v>6088</v>
       </c>
     </row>
     <row r="687">
@@ -44225,7 +44225,7 @@
         <v>12361</v>
       </c>
       <c r="F687" t="n">
-        <v>6096.5</v>
+        <v>6108.5</v>
       </c>
     </row>
     <row r="688">
@@ -44245,7 +44245,7 @@
         <v>12383.5</v>
       </c>
       <c r="F688" t="n">
-        <v>6112.5</v>
+        <v>6124.5</v>
       </c>
     </row>
     <row r="689">
@@ -44265,7 +44265,7 @@
         <v>12418.5</v>
       </c>
       <c r="F689" t="n">
-        <v>6134.5</v>
+        <v>6146.5</v>
       </c>
     </row>
     <row r="690">
@@ -44285,7 +44285,7 @@
         <v>12448.5</v>
       </c>
       <c r="F690" t="n">
-        <v>6153.5</v>
+        <v>6165.5</v>
       </c>
     </row>
     <row r="691">
@@ -44305,7 +44305,7 @@
         <v>12481.5</v>
       </c>
       <c r="F691" t="n">
-        <v>6168</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="692">
@@ -44325,7 +44325,7 @@
         <v>12519.25</v>
       </c>
       <c r="F692" t="n">
-        <v>6188.5</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="693">
@@ -44345,7 +44345,7 @@
         <v>12549.75</v>
       </c>
       <c r="F693" t="n">
-        <v>6207.5</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="694">
@@ -44365,7 +44365,7 @@
         <v>12576</v>
       </c>
       <c r="F694" t="n">
-        <v>6222</v>
+        <v>6232.5</v>
       </c>
     </row>
     <row r="695">
@@ -44385,7 +44385,7 @@
         <v>12617</v>
       </c>
       <c r="F695" t="n">
-        <v>6242.5</v>
+        <v>6253</v>
       </c>
     </row>
     <row r="696">
@@ -44405,7 +44405,7 @@
         <v>12651.5</v>
       </c>
       <c r="F696" t="n">
-        <v>6263</v>
+        <v>6273.5</v>
       </c>
     </row>
     <row r="697">
@@ -44425,7 +44425,7 @@
         <v>12672.5</v>
       </c>
       <c r="F697" t="n">
-        <v>6282</v>
+        <v>6292.5</v>
       </c>
     </row>
     <row r="698">
@@ -44445,7 +44445,7 @@
         <v>12707.75</v>
       </c>
       <c r="F698" t="n">
-        <v>6299.5</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="699">
@@ -44465,7 +44465,7 @@
         <v>12747.5</v>
       </c>
       <c r="F699" t="n">
-        <v>6320</v>
+        <v>6330.5</v>
       </c>
     </row>
     <row r="700">
@@ -44485,7 +44485,7 @@
         <v>12781.25</v>
       </c>
       <c r="F700" t="n">
-        <v>6339</v>
+        <v>6349.5</v>
       </c>
     </row>
     <row r="701">
@@ -44505,7 +44505,7 @@
         <v>12818.25</v>
       </c>
       <c r="F701" t="n">
-        <v>6361</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="702">
@@ -44525,7 +44525,7 @@
         <v>12831.25</v>
       </c>
       <c r="F702" t="n">
-        <v>6380</v>
+        <v>6387.5</v>
       </c>
     </row>
     <row r="703">
@@ -44545,7 +44545,7 @@
         <v>12872.25</v>
       </c>
       <c r="F703" t="n">
-        <v>6402</v>
+        <v>6409.5</v>
       </c>
     </row>
     <row r="704">
@@ -44565,7 +44565,7 @@
         <v>12901</v>
       </c>
       <c r="F704" t="n">
-        <v>6419.5</v>
+        <v>6427</v>
       </c>
     </row>
     <row r="705">
@@ -44585,7 +44585,7 @@
         <v>12927.5</v>
       </c>
       <c r="F705" t="n">
-        <v>6434</v>
+        <v>6441.5</v>
       </c>
     </row>
     <row r="706">
@@ -44605,7 +44605,7 @@
         <v>12966.5</v>
       </c>
       <c r="F706" t="n">
-        <v>6453</v>
+        <v>6460.5</v>
       </c>
     </row>
     <row r="707">
@@ -44625,7 +44625,7 @@
         <v>12989.75</v>
       </c>
       <c r="F707" t="n">
-        <v>6472</v>
+        <v>6479.5</v>
       </c>
     </row>
     <row r="708">
@@ -44645,7 +44645,7 @@
         <v>13029.5</v>
       </c>
       <c r="F708" t="n">
-        <v>6495.5</v>
+        <v>6503</v>
       </c>
     </row>
     <row r="709">
@@ -44665,7 +44665,7 @@
         <v>13022.5</v>
       </c>
       <c r="F709" t="n">
-        <v>6519</v>
+        <v>6526.5</v>
       </c>
     </row>
     <row r="710">
@@ -44685,7 +44685,7 @@
         <v>13068.25</v>
       </c>
       <c r="F710" t="n">
-        <v>6535</v>
+        <v>6542.5</v>
       </c>
     </row>
     <row r="711">
@@ -44705,7 +44705,7 @@
         <v>13108.75</v>
       </c>
       <c r="F711" t="n">
-        <v>6555.5</v>
+        <v>6563</v>
       </c>
     </row>
     <row r="712">
@@ -44725,7 +44725,7 @@
         <v>13143.25</v>
       </c>
       <c r="F712" t="n">
-        <v>6576</v>
+        <v>6583.5</v>
       </c>
     </row>
     <row r="713">
@@ -44745,7 +44745,7 @@
         <v>13173.75</v>
       </c>
       <c r="F713" t="n">
-        <v>6593.5</v>
+        <v>6601</v>
       </c>
     </row>
     <row r="714">
@@ -44765,7 +44765,7 @@
         <v>13212.25</v>
       </c>
       <c r="F714" t="n">
-        <v>6614</v>
+        <v>6621.5</v>
       </c>
     </row>
     <row r="715">
@@ -44785,7 +44785,7 @@
         <v>13259.25</v>
       </c>
       <c r="F715" t="n">
-        <v>6634.5</v>
+        <v>6642</v>
       </c>
     </row>
     <row r="716">
@@ -44805,7 +44805,7 @@
         <v>13299.25</v>
       </c>
       <c r="F716" t="n">
-        <v>6656.5</v>
+        <v>6664</v>
       </c>
     </row>
     <row r="717">
@@ -44825,7 +44825,7 @@
         <v>13336.5</v>
       </c>
       <c r="F717" t="n">
-        <v>6678.5</v>
+        <v>6686</v>
       </c>
     </row>
     <row r="718">
@@ -44845,7 +44845,7 @@
         <v>13369.5</v>
       </c>
       <c r="F718" t="n">
-        <v>6700.5</v>
+        <v>6708</v>
       </c>
     </row>
     <row r="719">
@@ -44865,7 +44865,7 @@
         <v>13398.75</v>
       </c>
       <c r="F719" t="n">
-        <v>6721</v>
+        <v>6728.5</v>
       </c>
     </row>
     <row r="720">
@@ -44885,7 +44885,7 @@
         <v>13434.75</v>
       </c>
       <c r="F720" t="n">
-        <v>6741.5</v>
+        <v>6749</v>
       </c>
     </row>
     <row r="721">
@@ -44905,7 +44905,7 @@
         <v>13477.75</v>
       </c>
       <c r="F721" t="n">
-        <v>6762</v>
+        <v>6769.5</v>
       </c>
     </row>
     <row r="722">
@@ -44925,7 +44925,7 @@
         <v>13512.5</v>
       </c>
       <c r="F722" t="n">
-        <v>6782.5</v>
+        <v>6790</v>
       </c>
     </row>
     <row r="723">
@@ -44945,7 +44945,7 @@
         <v>13552.5</v>
       </c>
       <c r="F723" t="n">
-        <v>6800</v>
+        <v>6807.5</v>
       </c>
     </row>
     <row r="724">
@@ -44965,7 +44965,7 @@
         <v>13595</v>
       </c>
       <c r="F724" t="n">
-        <v>6822</v>
+        <v>6829.5</v>
       </c>
     </row>
     <row r="725">
@@ -44985,7 +44985,7 @@
         <v>13626.25</v>
       </c>
       <c r="F725" t="n">
-        <v>6842.5</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="726">
@@ -45005,7 +45005,7 @@
         <v>13659</v>
       </c>
       <c r="F726" t="n">
-        <v>6864.5</v>
+        <v>6872</v>
       </c>
     </row>
     <row r="727">
@@ -45025,7 +45025,7 @@
         <v>13700</v>
       </c>
       <c r="F727" t="n">
-        <v>6886.5</v>
+        <v>6894</v>
       </c>
     </row>
     <row r="728">
@@ -45045,7 +45045,7 @@
         <v>13720.5</v>
       </c>
       <c r="F728" t="n">
-        <v>6908.5</v>
+        <v>6916</v>
       </c>
     </row>
     <row r="729">
@@ -45065,7 +45065,7 @@
         <v>13718.5</v>
       </c>
       <c r="F729" t="n">
-        <v>6929</v>
+        <v>6936.5</v>
       </c>
     </row>
     <row r="730">
@@ -45085,7 +45085,7 @@
         <v>13724.5</v>
       </c>
       <c r="F730" t="n">
-        <v>6934.5</v>
+        <v>6957</v>
       </c>
     </row>
     <row r="731">
@@ -45105,7 +45105,7 @@
         <v>13753</v>
       </c>
       <c r="F731" t="n">
-        <v>6955</v>
+        <v>6977.5</v>
       </c>
     </row>
     <row r="732">
@@ -45125,7 +45125,7 @@
         <v>13766.25</v>
       </c>
       <c r="F732" t="n">
-        <v>6974</v>
+        <v>6996.5</v>
       </c>
     </row>
     <row r="733">
@@ -45145,7 +45145,7 @@
         <v>13790.75</v>
       </c>
       <c r="F733" t="n">
-        <v>6996</v>
+        <v>7018.5</v>
       </c>
     </row>
     <row r="734">
@@ -45165,7 +45165,7 @@
         <v>13832</v>
       </c>
       <c r="F734" t="n">
-        <v>7019.5</v>
+        <v>7042</v>
       </c>
     </row>
     <row r="735">
@@ -45185,7 +45185,7 @@
         <v>13864.75</v>
       </c>
       <c r="F735" t="n">
-        <v>7040</v>
+        <v>7062.5</v>
       </c>
     </row>
     <row r="736">
@@ -45205,7 +45205,7 @@
         <v>13905.25</v>
       </c>
       <c r="F736" t="n">
-        <v>7059</v>
+        <v>7081.5</v>
       </c>
     </row>
     <row r="737">
@@ -45225,7 +45225,7 @@
         <v>13949</v>
       </c>
       <c r="F737" t="n">
-        <v>7081</v>
+        <v>7103.5</v>
       </c>
     </row>
     <row r="738">
@@ -45245,7 +45245,7 @@
         <v>13988.75</v>
       </c>
       <c r="F738" t="n">
-        <v>7103</v>
+        <v>7125.5</v>
       </c>
     </row>
     <row r="739">
@@ -45265,7 +45265,7 @@
         <v>14028.75</v>
       </c>
       <c r="F739" t="n">
-        <v>7122</v>
+        <v>7144.5</v>
       </c>
     </row>
     <row r="740">
@@ -45285,7 +45285,7 @@
         <v>14068.5</v>
       </c>
       <c r="F740" t="n">
-        <v>7142.5</v>
+        <v>7165</v>
       </c>
     </row>
     <row r="741">
@@ -45305,7 +45305,7 @@
         <v>14112.25</v>
       </c>
       <c r="F741" t="n">
-        <v>7166</v>
+        <v>7188.5</v>
       </c>
     </row>
     <row r="742">
@@ -45325,7 +45325,7 @@
         <v>14151</v>
       </c>
       <c r="F742" t="n">
-        <v>7183.5</v>
+        <v>7206</v>
       </c>
     </row>
     <row r="743">
@@ -45345,7 +45345,7 @@
         <v>14196</v>
       </c>
       <c r="F743" t="n">
-        <v>7201</v>
+        <v>7223.5</v>
       </c>
     </row>
     <row r="744">
@@ -45365,7 +45365,7 @@
         <v>14231</v>
       </c>
       <c r="F744" t="n">
-        <v>7224.5</v>
+        <v>7247</v>
       </c>
     </row>
     <row r="745">
@@ -45385,7 +45385,7 @@
         <v>14272.75</v>
       </c>
       <c r="F745" t="n">
-        <v>7239</v>
+        <v>7261.5</v>
       </c>
     </row>
     <row r="746">
@@ -45405,7 +45405,7 @@
         <v>14305.75</v>
       </c>
       <c r="F746" t="n">
-        <v>7258</v>
+        <v>7280.5</v>
       </c>
     </row>
     <row r="747">
@@ -45425,7 +45425,7 @@
         <v>14338.5</v>
       </c>
       <c r="F747" t="n">
-        <v>7280</v>
+        <v>7302.5</v>
       </c>
     </row>
     <row r="748">
@@ -45445,7 +45445,7 @@
         <v>14379.5</v>
       </c>
       <c r="F748" t="n">
-        <v>7300.5</v>
+        <v>7323</v>
       </c>
     </row>
     <row r="749">
@@ -45465,7 +45465,7 @@
         <v>14383.25</v>
       </c>
       <c r="F749" t="n">
-        <v>7322.5</v>
+        <v>7345</v>
       </c>
     </row>
     <row r="750">
@@ -45485,7 +45485,7 @@
         <v>14415.75</v>
       </c>
       <c r="F750" t="n">
-        <v>7343</v>
+        <v>7365.5</v>
       </c>
     </row>
     <row r="751">
@@ -45505,7 +45505,7 @@
         <v>14452.75</v>
       </c>
       <c r="F751" t="n">
-        <v>7363.5</v>
+        <v>7386</v>
       </c>
     </row>
     <row r="752">
@@ -45525,7 +45525,7 @@
         <v>14496.5</v>
       </c>
       <c r="F752" t="n">
-        <v>7384</v>
+        <v>7406.5</v>
       </c>
     </row>
     <row r="753">
@@ -45545,7 +45545,7 @@
         <v>14533</v>
       </c>
       <c r="F753" t="n">
-        <v>7404.5</v>
+        <v>7427</v>
       </c>
     </row>
     <row r="754">
@@ -45565,7 +45565,7 @@
         <v>14572</v>
       </c>
       <c r="F754" t="n">
-        <v>7419</v>
+        <v>7441.5</v>
       </c>
     </row>
     <row r="755">
@@ -45585,7 +45585,7 @@
         <v>14613</v>
       </c>
       <c r="F755" t="n">
-        <v>7442.5</v>
+        <v>7465</v>
       </c>
     </row>
     <row r="756">
@@ -45605,7 +45605,7 @@
         <v>14650.75</v>
       </c>
       <c r="F756" t="n">
-        <v>7460</v>
+        <v>7482.5</v>
       </c>
     </row>
     <row r="757">
@@ -45625,7 +45625,7 @@
         <v>14691.25</v>
       </c>
       <c r="F757" t="n">
-        <v>7479</v>
+        <v>7501.5</v>
       </c>
     </row>
     <row r="758">
@@ -45645,7 +45645,7 @@
         <v>14715</v>
       </c>
       <c r="F758" t="n">
-        <v>7499.5</v>
+        <v>7522</v>
       </c>
     </row>
     <row r="759">
@@ -45665,7 +45665,7 @@
         <v>14711</v>
       </c>
       <c r="F759" t="n">
-        <v>7515.5</v>
+        <v>7545.5</v>
       </c>
     </row>
     <row r="760">
@@ -45685,7 +45685,7 @@
         <v>14706.25</v>
       </c>
       <c r="F760" t="n">
-        <v>7531.5</v>
+        <v>7549.5</v>
       </c>
     </row>
     <row r="761">
@@ -45705,7 +45705,7 @@
         <v>14734</v>
       </c>
       <c r="F761" t="n">
-        <v>7546</v>
+        <v>7564</v>
       </c>
     </row>
     <row r="762">
@@ -45725,7 +45725,7 @@
         <v>14767</v>
       </c>
       <c r="F762" t="n">
-        <v>7563.5</v>
+        <v>7584.5</v>
       </c>
     </row>
     <row r="763">
@@ -45745,7 +45745,7 @@
         <v>14799.75</v>
       </c>
       <c r="F763" t="n">
-        <v>7582.5</v>
+        <v>7603.5</v>
       </c>
     </row>
     <row r="764">
@@ -45765,7 +45765,7 @@
         <v>14839.5</v>
       </c>
       <c r="F764" t="n">
-        <v>7603</v>
+        <v>7624</v>
       </c>
     </row>
     <row r="765">
@@ -45785,7 +45785,7 @@
         <v>14884</v>
       </c>
       <c r="F765" t="n">
-        <v>7625</v>
+        <v>7646</v>
       </c>
     </row>
     <row r="766">
@@ -45805,7 +45805,7 @@
         <v>14897.25</v>
       </c>
       <c r="F766" t="n">
-        <v>7647</v>
+        <v>7668</v>
       </c>
     </row>
     <row r="767">
@@ -45825,7 +45825,7 @@
         <v>14922.5</v>
       </c>
       <c r="F767" t="n">
-        <v>7664.5</v>
+        <v>7685.5</v>
       </c>
     </row>
     <row r="768">
@@ -45845,7 +45845,7 @@
         <v>14949.75</v>
       </c>
       <c r="F768" t="n">
-        <v>7685</v>
+        <v>7706</v>
       </c>
     </row>
     <row r="769">
@@ -45865,7 +45865,7 @@
         <v>14982.25</v>
       </c>
       <c r="F769" t="n">
-        <v>7701</v>
+        <v>7722</v>
       </c>
     </row>
     <row r="770">
@@ -45885,7 +45885,7 @@
         <v>15011.75</v>
       </c>
       <c r="F770" t="n">
-        <v>7718.5</v>
+        <v>7739.5</v>
       </c>
     </row>
     <row r="771">
@@ -45905,7 +45905,7 @@
         <v>15048.75</v>
       </c>
       <c r="F771" t="n">
-        <v>7739</v>
+        <v>7760</v>
       </c>
     </row>
     <row r="772">
@@ -45925,7 +45925,7 @@
         <v>15088.5</v>
       </c>
       <c r="F772" t="n">
-        <v>7758</v>
+        <v>7779</v>
       </c>
     </row>
     <row r="773">
@@ -45945,7 +45945,7 @@
         <v>15127</v>
       </c>
       <c r="F773" t="n">
-        <v>7777</v>
+        <v>7798</v>
       </c>
     </row>
     <row r="774">
@@ -45965,7 +45965,7 @@
         <v>15163.5</v>
       </c>
       <c r="F774" t="n">
-        <v>7793</v>
+        <v>7814</v>
       </c>
     </row>
     <row r="775">
@@ -45985,7 +45985,7 @@
         <v>15200</v>
       </c>
       <c r="F775" t="n">
-        <v>7815</v>
+        <v>7836</v>
       </c>
     </row>
     <row r="776">
@@ -46005,7 +46005,7 @@
         <v>15234</v>
       </c>
       <c r="F776" t="n">
-        <v>7835.5</v>
+        <v>7856.5</v>
       </c>
     </row>
     <row r="777">
@@ -46025,7 +46025,7 @@
         <v>15270.5</v>
       </c>
       <c r="F777" t="n">
-        <v>7859</v>
+        <v>7880</v>
       </c>
     </row>
     <row r="778">
@@ -46045,7 +46045,7 @@
         <v>15308.5</v>
       </c>
       <c r="F778" t="n">
-        <v>7878</v>
+        <v>7899</v>
       </c>
     </row>
     <row r="779">
@@ -46065,7 +46065,7 @@
         <v>15336.25</v>
       </c>
       <c r="F779" t="n">
-        <v>7900</v>
+        <v>7921</v>
       </c>
     </row>
     <row r="780">
@@ -46085,7 +46085,7 @@
         <v>15368</v>
       </c>
       <c r="F780" t="n">
-        <v>7920.5</v>
+        <v>7941.5</v>
       </c>
     </row>
     <row r="781">
@@ -46105,7 +46105,7 @@
         <v>15397.5</v>
       </c>
       <c r="F781" t="n">
-        <v>7942.5</v>
+        <v>7963.5</v>
       </c>
     </row>
     <row r="782">
@@ -46125,7 +46125,7 @@
         <v>15429.25</v>
       </c>
       <c r="F782" t="n">
-        <v>7966</v>
+        <v>7987</v>
       </c>
     </row>
     <row r="783">
@@ -46145,7 +46145,7 @@
         <v>15463.75</v>
       </c>
       <c r="F783" t="n">
-        <v>7983.5</v>
+        <v>8004.5</v>
       </c>
     </row>
     <row r="784">
@@ -46165,7 +46165,7 @@
         <v>15505.5</v>
       </c>
       <c r="F784" t="n">
-        <v>8007</v>
+        <v>8028</v>
       </c>
     </row>
     <row r="785">
@@ -46185,7 +46185,7 @@
         <v>15531.75</v>
       </c>
       <c r="F785" t="n">
-        <v>8026</v>
+        <v>8047</v>
       </c>
     </row>
     <row r="786">
@@ -46205,7 +46205,7 @@
         <v>15570.75</v>
       </c>
       <c r="F786" t="n">
-        <v>8048</v>
+        <v>8069</v>
       </c>
     </row>
     <row r="787">
@@ -46225,7 +46225,7 @@
         <v>15612.5</v>
       </c>
       <c r="F787" t="n">
-        <v>8067</v>
+        <v>8088</v>
       </c>
     </row>
     <row r="788">
@@ -46245,7 +46245,7 @@
         <v>15648.25</v>
       </c>
       <c r="F788" t="n">
-        <v>8087.5</v>
+        <v>8108.5</v>
       </c>
     </row>
     <row r="789">
@@ -46265,7 +46265,7 @@
         <v>15676.25</v>
       </c>
       <c r="F789" t="n">
-        <v>8108</v>
+        <v>8129</v>
       </c>
     </row>
     <row r="790">
@@ -46285,7 +46285,7 @@
         <v>15705.75</v>
       </c>
       <c r="F790" t="n">
-        <v>8127</v>
+        <v>8148</v>
       </c>
     </row>
     <row r="791">
@@ -46305,7 +46305,7 @@
         <v>15743.5</v>
       </c>
       <c r="F791" t="n">
-        <v>8146</v>
+        <v>8167</v>
       </c>
     </row>
     <row r="792">
@@ -46325,7 +46325,7 @@
         <v>15780.75</v>
       </c>
       <c r="F792" t="n">
-        <v>8168</v>
+        <v>8189</v>
       </c>
     </row>
     <row r="793">
@@ -46345,7 +46345,7 @@
         <v>15816.75</v>
       </c>
       <c r="F793" t="n">
-        <v>8185.5</v>
+        <v>8205</v>
       </c>
     </row>
     <row r="794">
@@ -46365,7 +46365,7 @@
         <v>15850</v>
       </c>
       <c r="F794" t="n">
-        <v>8201.5</v>
+        <v>8221</v>
       </c>
     </row>
     <row r="795">
@@ -46385,7 +46385,7 @@
         <v>15869</v>
       </c>
       <c r="F795" t="n">
-        <v>8222</v>
+        <v>8241.5</v>
       </c>
     </row>
     <row r="796">
@@ -46405,7 +46405,7 @@
         <v>15891</v>
       </c>
       <c r="F796" t="n">
-        <v>8244</v>
+        <v>8263.5</v>
       </c>
     </row>
     <row r="797">
@@ -46425,7 +46425,7 @@
         <v>15930</v>
       </c>
       <c r="F797" t="n">
-        <v>8267.5</v>
+        <v>8287</v>
       </c>
     </row>
     <row r="798">
@@ -46445,7 +46445,7 @@
         <v>15973.75</v>
       </c>
       <c r="F798" t="n">
-        <v>8289.5</v>
+        <v>8309</v>
       </c>
     </row>
     <row r="799">
@@ -46465,7 +46465,7 @@
         <v>16006</v>
       </c>
       <c r="F799" t="n">
-        <v>8308.5</v>
+        <v>8328</v>
       </c>
     </row>
     <row r="800">
@@ -46485,7 +46485,7 @@
         <v>16030.25</v>
       </c>
       <c r="F800" t="n">
-        <v>8330.5</v>
+        <v>8350</v>
       </c>
     </row>
     <row r="801">
@@ -46505,7 +46505,7 @@
         <v>16069.5</v>
       </c>
       <c r="F801" t="n">
-        <v>8351</v>
+        <v>8370.5</v>
       </c>
     </row>
     <row r="802">
@@ -46525,7 +46525,7 @@
         <v>16115.25</v>
       </c>
       <c r="F802" t="n">
-        <v>8371.5</v>
+        <v>8391</v>
       </c>
     </row>
     <row r="803">
@@ -46545,7 +46545,7 @@
         <v>16158.25</v>
       </c>
       <c r="F803" t="n">
-        <v>8390.5</v>
+        <v>8410</v>
       </c>
     </row>
     <row r="804">
@@ -46565,7 +46565,7 @@
         <v>16177.5</v>
       </c>
       <c r="F804" t="n">
-        <v>8414</v>
+        <v>8433.5</v>
       </c>
     </row>
     <row r="805">
@@ -46585,7 +46585,7 @@
         <v>16216.75</v>
       </c>
       <c r="F805" t="n">
-        <v>8431.5</v>
+        <v>8451</v>
       </c>
     </row>
     <row r="806">
@@ -46605,7 +46605,7 @@
         <v>16255.25</v>
       </c>
       <c r="F806" t="n">
-        <v>8449</v>
+        <v>8468.5</v>
       </c>
     </row>
     <row r="807">
@@ -46625,7 +46625,7 @@
         <v>16300.25</v>
       </c>
       <c r="F807" t="n">
-        <v>8468</v>
+        <v>8487.5</v>
       </c>
     </row>
     <row r="808">
@@ -46645,7 +46645,7 @@
         <v>16336.75</v>
       </c>
       <c r="F808" t="n">
-        <v>8487</v>
+        <v>8506.5</v>
       </c>
     </row>
     <row r="809">
@@ -46665,7 +46665,7 @@
         <v>16372.5</v>
       </c>
       <c r="F809" t="n">
-        <v>8501.5</v>
+        <v>8521</v>
       </c>
     </row>
     <row r="810">
@@ -46685,7 +46685,7 @@
         <v>16411</v>
       </c>
       <c r="F810" t="n">
-        <v>8522</v>
+        <v>8541.5</v>
       </c>
     </row>
     <row r="811">
@@ -46705,7 +46705,7 @@
         <v>16456</v>
       </c>
       <c r="F811" t="n">
-        <v>8544</v>
+        <v>8563.5</v>
       </c>
     </row>
     <row r="812">
@@ -46725,7 +46725,7 @@
         <v>16493.25</v>
       </c>
       <c r="F812" t="n">
-        <v>8561.5</v>
+        <v>8581</v>
       </c>
     </row>
     <row r="813">
@@ -46745,7 +46745,7 @@
         <v>16529.25</v>
       </c>
       <c r="F813" t="n">
-        <v>8580.5</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="814">
@@ -46765,7 +46765,7 @@
         <v>16574.25</v>
       </c>
       <c r="F814" t="n">
-        <v>8599.5</v>
+        <v>8619</v>
       </c>
     </row>
     <row r="815">
@@ -46785,7 +46785,7 @@
         <v>16616</v>
       </c>
       <c r="F815" t="n">
-        <v>8623</v>
+        <v>8642.5</v>
       </c>
     </row>
     <row r="816">
@@ -46805,7 +46805,7 @@
         <v>16632.5</v>
       </c>
       <c r="F816" t="n">
-        <v>8646.5</v>
+        <v>8666</v>
       </c>
     </row>
     <row r="817">
@@ -46825,7 +46825,7 @@
         <v>16673</v>
       </c>
       <c r="F817" t="n">
-        <v>8667</v>
+        <v>8686.5</v>
       </c>
     </row>
     <row r="818">
@@ -46845,7 +46845,7 @@
         <v>16714</v>
       </c>
       <c r="F818" t="n">
-        <v>8687.5</v>
+        <v>8707</v>
       </c>
     </row>
     <row r="819">
@@ -46865,7 +46865,7 @@
         <v>16750.75</v>
       </c>
       <c r="F819" t="n">
-        <v>8706.5</v>
+        <v>8726</v>
       </c>
     </row>
     <row r="820">
@@ -46885,7 +46885,7 @@
         <v>16793.25</v>
       </c>
       <c r="F820" t="n">
-        <v>8727</v>
+        <v>8746.5</v>
       </c>
     </row>
     <row r="821">
@@ -46905,7 +46905,7 @@
         <v>16832.5</v>
       </c>
       <c r="F821" t="n">
-        <v>8744.5</v>
+        <v>8764</v>
       </c>
     </row>
     <row r="822">
@@ -46925,7 +46925,7 @@
         <v>16873.75</v>
       </c>
       <c r="F822" t="n">
-        <v>8765</v>
+        <v>8784.5</v>
       </c>
     </row>
     <row r="823">
@@ -46945,7 +46945,7 @@
         <v>16918.25</v>
       </c>
       <c r="F823" t="n">
-        <v>8784</v>
+        <v>8803.5</v>
       </c>
     </row>
     <row r="824">
@@ -46965,7 +46965,7 @@
         <v>16956</v>
       </c>
       <c r="F824" t="n">
-        <v>8806</v>
+        <v>8825.5</v>
       </c>
     </row>
     <row r="825">
@@ -46985,7 +46985,7 @@
         <v>16997</v>
       </c>
       <c r="F825" t="n">
-        <v>8828</v>
+        <v>8847.5</v>
       </c>
     </row>
     <row r="826">
@@ -47005,7 +47005,7 @@
         <v>17021.5</v>
       </c>
       <c r="F826" t="n">
-        <v>8850</v>
+        <v>8869.5</v>
       </c>
     </row>
     <row r="827">
@@ -47025,7 +47025,7 @@
         <v>17014</v>
       </c>
       <c r="F827" t="n">
-        <v>8867.5</v>
+        <v>8891.5</v>
       </c>
     </row>
     <row r="828">
@@ -47045,7 +47045,7 @@
         <v>17045.25</v>
       </c>
       <c r="F828" t="n">
-        <v>8882</v>
+        <v>8912</v>
       </c>
     </row>
     <row r="829">
@@ -47065,7 +47065,7 @@
         <v>17084</v>
       </c>
       <c r="F829" t="n">
-        <v>8902.5</v>
+        <v>8932.5</v>
       </c>
     </row>
     <row r="830">
@@ -47085,7 +47085,7 @@
         <v>17115.25</v>
       </c>
       <c r="F830" t="n">
-        <v>8920</v>
+        <v>8950</v>
       </c>
     </row>
     <row r="831">
@@ -47105,7 +47105,7 @@
         <v>17153</v>
       </c>
       <c r="F831" t="n">
-        <v>8939</v>
+        <v>8969</v>
       </c>
     </row>
     <row r="832">
@@ -47125,7 +47125,7 @@
         <v>17192.25</v>
       </c>
       <c r="F832" t="n">
-        <v>8962.5</v>
+        <v>8992.5</v>
       </c>
     </row>
     <row r="833">
@@ -47145,7 +47145,7 @@
         <v>17221</v>
       </c>
       <c r="F833" t="n">
-        <v>8978.5</v>
+        <v>9008.5</v>
       </c>
     </row>
     <row r="834">
@@ -47165,7 +47165,7 @@
         <v>17258.25</v>
       </c>
       <c r="F834" t="n">
-        <v>9000.5</v>
+        <v>9030.5</v>
       </c>
     </row>
     <row r="835">
@@ -47185,7 +47185,7 @@
         <v>17298</v>
       </c>
       <c r="F835" t="n">
-        <v>9022.5</v>
+        <v>9052.5</v>
       </c>
     </row>
     <row r="836">
@@ -47205,7 +47205,7 @@
         <v>17337.25</v>
       </c>
       <c r="F836" t="n">
-        <v>9044.5</v>
+        <v>9074.5</v>
       </c>
     </row>
     <row r="837">
@@ -47225,7 +47225,7 @@
         <v>17381</v>
       </c>
       <c r="F837" t="n">
-        <v>9065</v>
+        <v>9095</v>
       </c>
     </row>
     <row r="838">
@@ -47245,7 +47245,7 @@
         <v>17382.25</v>
       </c>
       <c r="F838" t="n">
-        <v>9087</v>
+        <v>9117</v>
       </c>
     </row>
     <row r="839">
@@ -47265,7 +47265,7 @@
         <v>17420.75</v>
       </c>
       <c r="F839" t="n">
-        <v>9104.5</v>
+        <v>9134.5</v>
       </c>
     </row>
     <row r="840">
@@ -47285,7 +47285,7 @@
         <v>17464.5</v>
       </c>
       <c r="F840" t="n">
-        <v>9126.5</v>
+        <v>9156.5</v>
       </c>
     </row>
     <row r="841">
@@ -47305,7 +47305,7 @@
         <v>17510.25</v>
       </c>
       <c r="F841" t="n">
-        <v>9144</v>
+        <v>9174</v>
       </c>
     </row>
     <row r="842">
@@ -47325,7 +47325,7 @@
         <v>17546</v>
       </c>
       <c r="F842" t="n">
-        <v>9161.5</v>
+        <v>9191.5</v>
       </c>
     </row>
     <row r="843">
@@ -47345,7 +47345,7 @@
         <v>17593</v>
       </c>
       <c r="F843" t="n">
-        <v>9180.5</v>
+        <v>9210.5</v>
       </c>
     </row>
     <row r="844">
@@ -47365,7 +47365,7 @@
         <v>17634.25</v>
       </c>
       <c r="F844" t="n">
-        <v>9201</v>
+        <v>9231</v>
       </c>
     </row>
     <row r="845">
@@ -47385,7 +47385,7 @@
         <v>17643.5</v>
       </c>
       <c r="F845" t="n">
-        <v>9223</v>
+        <v>9253</v>
       </c>
     </row>
     <row r="846">
@@ -47405,7 +47405,7 @@
         <v>17642.25</v>
       </c>
       <c r="F846" t="n">
-        <v>9237.5</v>
+        <v>9264.5</v>
       </c>
     </row>
     <row r="847">
@@ -47425,7 +47425,7 @@
         <v>17663.25</v>
       </c>
       <c r="F847" t="n">
-        <v>9255</v>
+        <v>9282</v>
       </c>
     </row>
     <row r="848">
@@ -47445,7 +47445,7 @@
         <v>17688.25</v>
       </c>
       <c r="F848" t="n">
-        <v>9277</v>
+        <v>9299.5</v>
       </c>
     </row>
     <row r="849">
@@ -47465,7 +47465,7 @@
         <v>17724</v>
       </c>
       <c r="F849" t="n">
-        <v>9297.5</v>
+        <v>9318.5</v>
       </c>
     </row>
     <row r="850">
@@ -47485,7 +47485,7 @@
         <v>17756.5</v>
       </c>
       <c r="F850" t="n">
-        <v>9319.5</v>
+        <v>9340.5</v>
       </c>
     </row>
     <row r="851">
@@ -47505,7 +47505,7 @@
         <v>17784</v>
       </c>
       <c r="F851" t="n">
-        <v>9332.5</v>
+        <v>9355</v>
       </c>
     </row>
     <row r="852">
@@ -47525,7 +47525,7 @@
         <v>17817.25</v>
       </c>
       <c r="F852" t="n">
-        <v>9351.5</v>
+        <v>9375.5</v>
       </c>
     </row>
     <row r="853">
@@ -47545,7 +47545,7 @@
         <v>17843.75</v>
       </c>
       <c r="F853" t="n">
-        <v>9372</v>
+        <v>9394.5</v>
       </c>
     </row>
     <row r="854">
@@ -47565,7 +47565,7 @@
         <v>17850.75</v>
       </c>
       <c r="F854" t="n">
-        <v>9392.5</v>
+        <v>9415</v>
       </c>
     </row>
     <row r="855">
@@ -47585,7 +47585,7 @@
         <v>17849.25</v>
       </c>
       <c r="F855" t="n">
-        <v>9410</v>
+        <v>9434</v>
       </c>
     </row>
     <row r="856">
@@ -47605,7 +47605,7 @@
         <v>17889</v>
       </c>
       <c r="F856" t="n">
-        <v>9433.5</v>
+        <v>9457.5</v>
       </c>
     </row>
     <row r="857">
@@ -47625,7 +47625,7 @@
         <v>17933.5</v>
       </c>
       <c r="F857" t="n">
-        <v>9455.5</v>
+        <v>9479.5</v>
       </c>
     </row>
     <row r="858">
@@ -47645,7 +47645,7 @@
         <v>17973.5</v>
       </c>
       <c r="F858" t="n">
-        <v>9479</v>
+        <v>9503</v>
       </c>
     </row>
     <row r="859">
@@ -47665,7 +47665,7 @@
         <v>18014</v>
       </c>
       <c r="F859" t="n">
-        <v>9499.5</v>
+        <v>9523.5</v>
       </c>
     </row>
     <row r="860">
@@ -47685,7 +47685,7 @@
         <v>18048</v>
       </c>
       <c r="F860" t="n">
-        <v>9521.5</v>
+        <v>9545.5</v>
       </c>
     </row>
     <row r="861">
@@ -47705,7 +47705,7 @@
         <v>18091</v>
       </c>
       <c r="F861" t="n">
-        <v>9540.5</v>
+        <v>9564.5</v>
       </c>
     </row>
     <row r="862">
@@ -47725,7 +47725,7 @@
         <v>18132.75</v>
       </c>
       <c r="F862" t="n">
-        <v>9559.5</v>
+        <v>9583.5</v>
       </c>
     </row>
     <row r="863">
@@ -47745,7 +47745,7 @@
         <v>18167.75</v>
       </c>
       <c r="F863" t="n">
-        <v>9580</v>
+        <v>9604</v>
       </c>
     </row>
     <row r="864">
@@ -47765,7 +47765,7 @@
         <v>18204.5</v>
       </c>
       <c r="F864" t="n">
-        <v>9602</v>
+        <v>9626</v>
       </c>
     </row>
     <row r="865">
@@ -47785,7 +47785,7 @@
         <v>18242</v>
       </c>
       <c r="F865" t="n">
-        <v>9624</v>
+        <v>9648</v>
       </c>
     </row>
     <row r="866">
@@ -47805,7 +47805,7 @@
         <v>18284.5</v>
       </c>
       <c r="F866" t="n">
-        <v>9646</v>
+        <v>9670</v>
       </c>
     </row>
     <row r="867">
@@ -47825,7 +47825,7 @@
         <v>18323.75</v>
       </c>
       <c r="F867" t="n">
-        <v>9666.5</v>
+        <v>9690.5</v>
       </c>
     </row>
     <row r="868">
@@ -47845,7 +47845,7 @@
         <v>18360.25</v>
       </c>
       <c r="F868" t="n">
-        <v>9688.5</v>
+        <v>9712.5</v>
       </c>
     </row>
     <row r="869">
@@ -47865,7 +47865,7 @@
         <v>18391.5</v>
       </c>
       <c r="F869" t="n">
-        <v>9712</v>
+        <v>9736</v>
       </c>
     </row>
     <row r="870">
@@ -47885,7 +47885,7 @@
         <v>18429.25</v>
       </c>
       <c r="F870" t="n">
-        <v>9731</v>
+        <v>9755</v>
       </c>
     </row>
     <row r="871">
@@ -47905,7 +47905,7 @@
         <v>18476.25</v>
       </c>
       <c r="F871" t="n">
-        <v>9753</v>
+        <v>9777</v>
       </c>
     </row>
     <row r="872">
@@ -47925,7 +47925,7 @@
         <v>18505.75</v>
       </c>
       <c r="F872" t="n">
-        <v>9776.5</v>
+        <v>9800.5</v>
       </c>
     </row>
     <row r="873">
@@ -47945,7 +47945,7 @@
         <v>18550.75</v>
       </c>
       <c r="F873" t="n">
-        <v>9794</v>
+        <v>9818</v>
       </c>
     </row>
     <row r="874">
@@ -47965,7 +47965,7 @@
         <v>18591.25</v>
       </c>
       <c r="F874" t="n">
-        <v>9816</v>
+        <v>9840</v>
       </c>
     </row>
     <row r="875">
@@ -47985,7 +47985,7 @@
         <v>18629.75</v>
       </c>
       <c r="F875" t="n">
-        <v>9833.5</v>
+        <v>9857.5</v>
       </c>
     </row>
     <row r="876">
@@ -48005,7 +48005,7 @@
         <v>18663.75</v>
       </c>
       <c r="F876" t="n">
-        <v>9854</v>
+        <v>9878</v>
       </c>
     </row>
     <row r="877">
@@ -48025,7 +48025,7 @@
         <v>18703</v>
       </c>
       <c r="F877" t="n">
-        <v>9873</v>
+        <v>9897</v>
       </c>
     </row>
     <row r="878">
@@ -48045,7 +48045,7 @@
         <v>18743.5</v>
       </c>
       <c r="F878" t="n">
-        <v>9890.5</v>
+        <v>9914.5</v>
       </c>
     </row>
     <row r="879">
@@ -48065,7 +48065,7 @@
         <v>18786.75</v>
       </c>
       <c r="F879" t="n">
-        <v>9911</v>
+        <v>9935</v>
       </c>
     </row>
     <row r="880">
@@ -48085,7 +48085,7 @@
         <v>18828</v>
       </c>
       <c r="F880" t="n">
-        <v>9934.5</v>
+        <v>9958.5</v>
       </c>
     </row>
     <row r="881">
@@ -48105,7 +48105,7 @@
         <v>18865.5</v>
       </c>
       <c r="F881" t="n">
-        <v>9950.5</v>
+        <v>9974.5</v>
       </c>
     </row>
     <row r="882">
@@ -48125,7 +48125,7 @@
         <v>18906</v>
       </c>
       <c r="F882" t="n">
-        <v>9974</v>
+        <v>9998</v>
       </c>
     </row>
     <row r="883">
@@ -48145,7 +48145,7 @@
         <v>18920.5</v>
       </c>
       <c r="F883" t="n">
-        <v>9997.5</v>
+        <v>10021.5</v>
       </c>
     </row>
     <row r="884">
@@ -48165,7 +48165,7 @@
         <v>18934.25</v>
       </c>
       <c r="F884" t="n">
-        <v>10021</v>
+        <v>10045</v>
       </c>
     </row>
     <row r="885">
@@ -48185,7 +48185,7 @@
         <v>18971.5</v>
       </c>
       <c r="F885" t="n">
-        <v>10041.5</v>
+        <v>10065.5</v>
       </c>
     </row>
     <row r="886">
@@ -48205,7 +48205,7 @@
         <v>19012</v>
       </c>
       <c r="F886" t="n">
-        <v>10065</v>
+        <v>10089</v>
       </c>
     </row>
     <row r="887">
@@ -48225,7 +48225,7 @@
         <v>19015.25</v>
       </c>
       <c r="F887" t="n">
-        <v>10079.5</v>
+        <v>10108</v>
       </c>
     </row>
     <row r="888">
@@ -48245,7 +48245,7 @@
         <v>19036</v>
       </c>
       <c r="F888" t="n">
-        <v>10101.5</v>
+        <v>10130</v>
       </c>
     </row>
     <row r="889">
@@ -48265,7 +48265,7 @@
         <v>19066.5</v>
       </c>
       <c r="F889" t="n">
-        <v>10120.5</v>
+        <v>10149</v>
       </c>
     </row>
     <row r="890">
@@ -48285,7 +48285,7 @@
         <v>19108.25</v>
       </c>
       <c r="F890" t="n">
-        <v>10142.5</v>
+        <v>10171</v>
       </c>
     </row>
     <row r="891">
@@ -48305,7 +48305,7 @@
         <v>19125.75</v>
       </c>
       <c r="F891" t="n">
-        <v>10161.5</v>
+        <v>10188.5</v>
       </c>
     </row>
     <row r="892">
@@ -48325,7 +48325,7 @@
         <v>19146.25</v>
       </c>
       <c r="F892" t="n">
-        <v>10179</v>
+        <v>10204.5</v>
       </c>
     </row>
     <row r="893">
@@ -48345,7 +48345,7 @@
         <v>19176.75</v>
       </c>
       <c r="F893" t="n">
-        <v>10198</v>
+        <v>10223.5</v>
       </c>
     </row>
     <row r="894">
@@ -48365,7 +48365,7 @@
         <v>19214.5</v>
       </c>
       <c r="F894" t="n">
-        <v>10212.5</v>
+        <v>10235</v>
       </c>
     </row>
     <row r="895">
@@ -48385,7 +48385,7 @@
         <v>19250.25</v>
       </c>
       <c r="F895" t="n">
-        <v>10234.5</v>
+        <v>10255.5</v>
       </c>
     </row>
     <row r="896">
@@ -48405,7 +48405,7 @@
         <v>19290</v>
       </c>
       <c r="F896" t="n">
-        <v>10255</v>
+        <v>10276</v>
       </c>
     </row>
     <row r="897">
@@ -48425,7 +48425,7 @@
         <v>19325.25</v>
       </c>
       <c r="F897" t="n">
-        <v>10275.5</v>
+        <v>10298</v>
       </c>
     </row>
     <row r="898">
@@ -48445,7 +48445,7 @@
         <v>19357.75</v>
       </c>
       <c r="F898" t="n">
-        <v>10297.5</v>
+        <v>10320</v>
       </c>
     </row>
     <row r="899">
@@ -48465,7 +48465,7 @@
         <v>19398.25</v>
       </c>
       <c r="F899" t="n">
-        <v>10321</v>
+        <v>10343.5</v>
       </c>
     </row>
     <row r="900">
@@ -48485,7 +48485,7 @@
         <v>19433.5</v>
       </c>
       <c r="F900" t="n">
-        <v>10335.5</v>
+        <v>10362.5</v>
       </c>
     </row>
     <row r="901">
@@ -48505,7 +48505,7 @@
         <v>19458.75</v>
       </c>
       <c r="F901" t="n">
-        <v>10353</v>
+        <v>10380</v>
       </c>
     </row>
     <row r="902">
@@ -48525,7 +48525,7 @@
         <v>19486.25</v>
       </c>
       <c r="F902" t="n">
-        <v>10373.5</v>
+        <v>10400.5</v>
       </c>
     </row>
     <row r="903">
@@ -48545,7 +48545,7 @@
         <v>19502</v>
       </c>
       <c r="F903" t="n">
-        <v>10395.5</v>
+        <v>10422.5</v>
       </c>
     </row>
     <row r="904">
@@ -48565,7 +48565,7 @@
         <v>19518.5</v>
       </c>
       <c r="F904" t="n">
-        <v>10414.5</v>
+        <v>10441.5</v>
       </c>
     </row>
     <row r="905">
@@ -48585,7 +48585,7 @@
         <v>19559.5</v>
       </c>
       <c r="F905" t="n">
-        <v>10433.5</v>
+        <v>10460.5</v>
       </c>
     </row>
     <row r="906">
@@ -48605,7 +48605,7 @@
         <v>19598</v>
       </c>
       <c r="F906" t="n">
-        <v>10454</v>
+        <v>10481</v>
       </c>
     </row>
     <row r="907">
@@ -48625,7 +48625,7 @@
         <v>19634.5</v>
       </c>
       <c r="F907" t="n">
-        <v>10471.5</v>
+        <v>10498.5</v>
       </c>
     </row>
     <row r="908">
@@ -48645,7 +48645,7 @@
         <v>19670.25</v>
       </c>
       <c r="F908" t="n">
-        <v>10495</v>
+        <v>10522</v>
       </c>
     </row>
     <row r="909">
@@ -48665,7 +48665,7 @@
         <v>19666</v>
       </c>
       <c r="F909" t="n">
-        <v>10515.5</v>
+        <v>10542.5</v>
       </c>
     </row>
     <row r="910">
@@ -48685,7 +48685,7 @@
         <v>19678.5</v>
       </c>
       <c r="F910" t="n">
-        <v>10539</v>
+        <v>10566</v>
       </c>
     </row>
     <row r="911">
@@ -48705,7 +48705,7 @@
         <v>19716.5</v>
       </c>
       <c r="F911" t="n">
-        <v>10558</v>
+        <v>10585</v>
       </c>
     </row>
     <row r="912">
@@ -48725,7 +48725,7 @@
         <v>19756.25</v>
       </c>
       <c r="F912" t="n">
-        <v>10578.5</v>
+        <v>10605.5</v>
       </c>
     </row>
     <row r="913">
@@ -48745,7 +48745,7 @@
         <v>19774.75</v>
       </c>
       <c r="F913" t="n">
-        <v>10599</v>
+        <v>10626</v>
       </c>
     </row>
     <row r="914">
@@ -48765,7 +48765,7 @@
         <v>19819.25</v>
       </c>
       <c r="F914" t="n">
-        <v>10622.5</v>
+        <v>10649.5</v>
       </c>
     </row>
     <row r="915">
@@ -48785,7 +48785,7 @@
         <v>19809.75</v>
       </c>
       <c r="F915" t="n">
-        <v>10644.5</v>
+        <v>10671.5</v>
       </c>
     </row>
     <row r="916">
@@ -48805,7 +48805,7 @@
         <v>19853</v>
       </c>
       <c r="F916" t="n">
-        <v>10668</v>
+        <v>10695</v>
       </c>
     </row>
     <row r="917">
@@ -48825,7 +48825,7 @@
         <v>19862.25</v>
       </c>
       <c r="F917" t="n">
-        <v>10688.5</v>
+        <v>10715.5</v>
       </c>
     </row>
     <row r="918">
@@ -48845,7 +48845,7 @@
         <v>19880.25</v>
       </c>
       <c r="F918" t="n">
-        <v>10710.5</v>
+        <v>10737.5</v>
       </c>
     </row>
     <row r="919">
@@ -48865,7 +48865,7 @@
         <v>19912.25</v>
       </c>
       <c r="F919" t="n">
-        <v>10731</v>
+        <v>10758</v>
       </c>
     </row>
     <row r="920">
@@ -48885,7 +48885,7 @@
         <v>19952</v>
       </c>
       <c r="F920" t="n">
-        <v>10753</v>
+        <v>10780</v>
       </c>
     </row>
     <row r="921">
@@ -48905,7 +48905,7 @@
         <v>19993.75</v>
       </c>
       <c r="F921" t="n">
-        <v>10775</v>
+        <v>10802</v>
       </c>
     </row>
     <row r="922">
@@ -48925,7 +48925,7 @@
         <v>20034.75</v>
       </c>
       <c r="F922" t="n">
-        <v>10797</v>
+        <v>10824</v>
       </c>
     </row>
     <row r="923">
@@ -48945,7 +48945,7 @@
         <v>20068.5</v>
       </c>
       <c r="F923" t="n">
-        <v>10817.5</v>
+        <v>10844.5</v>
       </c>
     </row>
     <row r="924">
@@ -48965,7 +48965,7 @@
         <v>20105</v>
       </c>
       <c r="F924" t="n">
-        <v>10839.5</v>
+        <v>10866.5</v>
       </c>
     </row>
     <row r="925">
@@ -48985,7 +48985,7 @@
         <v>20130.75</v>
       </c>
       <c r="F925" t="n">
-        <v>10860</v>
+        <v>10888.5</v>
       </c>
     </row>
     <row r="926">
@@ -49005,7 +49005,7 @@
         <v>20173.25</v>
       </c>
       <c r="F926" t="n">
-        <v>10883.5</v>
+        <v>10912</v>
       </c>
     </row>
     <row r="927">
@@ -49025,7 +49025,7 @@
         <v>20204.5</v>
       </c>
       <c r="F927" t="n">
-        <v>10905.5</v>
+        <v>10934</v>
       </c>
     </row>
     <row r="928">
@@ -49045,7 +49045,7 @@
         <v>20231</v>
       </c>
       <c r="F928" t="n">
-        <v>10929</v>
+        <v>10957.5</v>
       </c>
     </row>
     <row r="929">
@@ -49065,7 +49065,7 @@
         <v>20266.75</v>
       </c>
       <c r="F929" t="n">
-        <v>10951</v>
+        <v>10981</v>
       </c>
     </row>
     <row r="930">
@@ -49085,7 +49085,7 @@
         <v>20309.75</v>
       </c>
       <c r="F930" t="n">
-        <v>10971.5</v>
+        <v>11001.5</v>
       </c>
     </row>
     <row r="931">
@@ -49105,7 +49105,7 @@
         <v>20347.5</v>
       </c>
       <c r="F931" t="n">
-        <v>10990.5</v>
+        <v>11020.5</v>
       </c>
     </row>
     <row r="932">
@@ -49125,7 +49125,7 @@
         <v>20347.5</v>
       </c>
       <c r="F932" t="n">
-        <v>11011</v>
+        <v>11041</v>
       </c>
     </row>
     <row r="933">
@@ -49145,7 +49145,7 @@
         <v>20374.75</v>
       </c>
       <c r="F933" t="n">
-        <v>11031.5</v>
+        <v>11061.5</v>
       </c>
     </row>
     <row r="934">
@@ -49165,7 +49165,7 @@
         <v>20416.5</v>
       </c>
       <c r="F934" t="n">
-        <v>11047.5</v>
+        <v>11077.5</v>
       </c>
     </row>
     <row r="935">
@@ -49185,7 +49185,7 @@
         <v>20423.25</v>
       </c>
       <c r="F935" t="n">
-        <v>11068</v>
+        <v>11098</v>
       </c>
     </row>
     <row r="936">
@@ -49205,7 +49205,7 @@
         <v>20462.25</v>
       </c>
       <c r="F936" t="n">
-        <v>11088.5</v>
+        <v>11118.5</v>
       </c>
     </row>
     <row r="937">
@@ -49225,7 +49225,7 @@
         <v>20506</v>
       </c>
       <c r="F937" t="n">
-        <v>11109</v>
+        <v>11139</v>
       </c>
     </row>
     <row r="938">
@@ -49245,7 +49245,7 @@
         <v>20515.25</v>
       </c>
       <c r="F938" t="n">
-        <v>11131</v>
+        <v>11161</v>
       </c>
     </row>
     <row r="939">
@@ -49265,7 +49265,7 @@
         <v>20511.75</v>
       </c>
       <c r="F939" t="n">
-        <v>11153</v>
+        <v>11183</v>
       </c>
     </row>
     <row r="940">
@@ -49285,7 +49285,7 @@
         <v>20520.25</v>
       </c>
       <c r="F940" t="n">
-        <v>11173.5</v>
+        <v>11203.5</v>
       </c>
     </row>
     <row r="941">
@@ -49305,7 +49305,7 @@
         <v>20552.75</v>
       </c>
       <c r="F941" t="n">
-        <v>11194</v>
+        <v>11224</v>
       </c>
     </row>
     <row r="942">
@@ -49325,7 +49325,7 @@
         <v>20558.5</v>
       </c>
       <c r="F942" t="n">
-        <v>11216</v>
+        <v>11246</v>
       </c>
     </row>
     <row r="943">
@@ -49345,7 +49345,7 @@
         <v>20603.5</v>
       </c>
       <c r="F943" t="n">
-        <v>11239.5</v>
+        <v>11269.5</v>
       </c>
     </row>
     <row r="944">
@@ -49365,7 +49365,7 @@
         <v>20629.25</v>
       </c>
       <c r="F944" t="n">
-        <v>11263</v>
+        <v>11293</v>
       </c>
     </row>
     <row r="945">
@@ -49385,7 +49385,7 @@
         <v>20634.5</v>
       </c>
       <c r="F945" t="n">
-        <v>11282</v>
+        <v>11312</v>
       </c>
     </row>
     <row r="946">
@@ -49405,7 +49405,7 @@
         <v>20667</v>
       </c>
       <c r="F946" t="n">
-        <v>11305.5</v>
+        <v>11335.5</v>
       </c>
     </row>
     <row r="947">
@@ -49425,7 +49425,7 @@
         <v>20700.75</v>
       </c>
       <c r="F947" t="n">
-        <v>11327.5</v>
+        <v>11357.5</v>
       </c>
     </row>
     <row r="948">
@@ -49445,7 +49445,7 @@
         <v>20725.25</v>
       </c>
       <c r="F948" t="n">
-        <v>11351</v>
+        <v>11381</v>
       </c>
     </row>
     <row r="949">
@@ -49465,7 +49465,7 @@
         <v>20767.75</v>
       </c>
       <c r="F949" t="n">
-        <v>11374.5</v>
+        <v>11404.5</v>
       </c>
     </row>
     <row r="950">
@@ -49485,7 +49485,7 @@
         <v>20794.75</v>
       </c>
       <c r="F950" t="n">
-        <v>11398</v>
+        <v>11428</v>
       </c>
     </row>
     <row r="951">
@@ -49505,7 +49505,7 @@
         <v>20804</v>
       </c>
       <c r="F951" t="n">
-        <v>11415.5</v>
+        <v>11445.5</v>
       </c>
     </row>
     <row r="952">
@@ -49525,7 +49525,7 @@
         <v>20843.75</v>
       </c>
       <c r="F952" t="n">
-        <v>11436</v>
+        <v>11466</v>
       </c>
     </row>
     <row r="953">
@@ -49545,7 +49545,7 @@
         <v>20880.25</v>
       </c>
       <c r="F953" t="n">
-        <v>11456.5</v>
+        <v>11486.5</v>
       </c>
     </row>
     <row r="954">
@@ -49565,7 +49565,7 @@
         <v>20912</v>
       </c>
       <c r="F954" t="n">
-        <v>11480</v>
+        <v>11510</v>
       </c>
     </row>
     <row r="955">
@@ -49585,7 +49585,7 @@
         <v>20947.25</v>
       </c>
       <c r="F955" t="n">
-        <v>11503.5</v>
+        <v>11533.5</v>
       </c>
     </row>
     <row r="956">
@@ -49605,7 +49605,7 @@
         <v>20973.75</v>
       </c>
       <c r="F956" t="n">
-        <v>11527</v>
+        <v>11557</v>
       </c>
     </row>
     <row r="957">
@@ -49625,7 +49625,7 @@
         <v>21006.75</v>
       </c>
       <c r="F957" t="n">
-        <v>11550.5</v>
+        <v>11580.5</v>
       </c>
     </row>
     <row r="958">
@@ -49645,7 +49645,7 @@
         <v>21046.5</v>
       </c>
       <c r="F958" t="n">
-        <v>11574</v>
+        <v>11602.5</v>
       </c>
     </row>
     <row r="959">
@@ -49665,7 +49665,7 @@
         <v>21086.25</v>
       </c>
       <c r="F959" t="n">
-        <v>11597.5</v>
+        <v>11626</v>
       </c>
     </row>
     <row r="960">
@@ -49685,7 +49685,7 @@
         <v>21127.5</v>
       </c>
       <c r="F960" t="n">
-        <v>11621</v>
+        <v>11649.5</v>
       </c>
     </row>
     <row r="961">
@@ -49705,7 +49705,7 @@
         <v>21154.75</v>
       </c>
       <c r="F961" t="n">
-        <v>11641.5</v>
+        <v>11670</v>
       </c>
     </row>
     <row r="962">
@@ -49725,7 +49725,7 @@
         <v>21172</v>
       </c>
       <c r="F962" t="n">
-        <v>11663.5</v>
+        <v>11692</v>
       </c>
     </row>
     <row r="963">
@@ -49745,7 +49745,7 @@
         <v>21206.5</v>
       </c>
       <c r="F963" t="n">
-        <v>11687</v>
+        <v>11715.5</v>
       </c>
     </row>
     <row r="964">
@@ -49765,7 +49765,7 @@
         <v>21239.25</v>
       </c>
       <c r="F964" t="n">
-        <v>11710.5</v>
+        <v>11739</v>
       </c>
     </row>
     <row r="965">
@@ -49785,7 +49785,7 @@
         <v>21274</v>
       </c>
       <c r="F965" t="n">
-        <v>11732.5</v>
+        <v>11761</v>
       </c>
     </row>
     <row r="966">
@@ -49805,7 +49805,7 @@
         <v>21319</v>
       </c>
       <c r="F966" t="n">
-        <v>11754.5</v>
+        <v>11783</v>
       </c>
     </row>
     <row r="967">
@@ -49825,7 +49825,7 @@
         <v>21357.5</v>
       </c>
       <c r="F967" t="n">
-        <v>11775</v>
+        <v>11803.5</v>
       </c>
     </row>
     <row r="968">
@@ -49845,7 +49845,7 @@
         <v>21386.25</v>
       </c>
       <c r="F968" t="n">
-        <v>11797</v>
+        <v>11825.5</v>
       </c>
     </row>
     <row r="969">
@@ -49865,7 +49865,7 @@
         <v>21415.5</v>
       </c>
       <c r="F969" t="n">
-        <v>11814.5</v>
+        <v>11843</v>
       </c>
     </row>
     <row r="970">
@@ -49885,7 +49885,7 @@
         <v>21438.5</v>
       </c>
       <c r="F970" t="n">
-        <v>11838</v>
+        <v>11866.5</v>
       </c>
     </row>
     <row r="971">
@@ -49905,7 +49905,7 @@
         <v>21465</v>
       </c>
       <c r="F971" t="n">
-        <v>11861.5</v>
+        <v>11890</v>
       </c>
     </row>
     <row r="972">
@@ -49925,7 +49925,7 @@
         <v>21501.5</v>
       </c>
       <c r="F972" t="n">
-        <v>11880.5</v>
+        <v>11909</v>
       </c>
     </row>
     <row r="973">
@@ -49945,7 +49945,7 @@
         <v>21536</v>
       </c>
       <c r="F973" t="n">
-        <v>11902.5</v>
+        <v>11931</v>
       </c>
     </row>
     <row r="974">
@@ -49965,7 +49965,7 @@
         <v>21534</v>
       </c>
       <c r="F974" t="n">
-        <v>11921.5</v>
+        <v>11950</v>
       </c>
     </row>
     <row r="975">
@@ -49985,7 +49985,7 @@
         <v>21577</v>
       </c>
       <c r="F975" t="n">
-        <v>11945</v>
+        <v>11973.5</v>
       </c>
     </row>
     <row r="976">
@@ -50005,7 +50005,7 @@
         <v>21610.75</v>
       </c>
       <c r="F976" t="n">
-        <v>11967</v>
+        <v>11995.5</v>
       </c>
     </row>
     <row r="977">
@@ -50025,7 +50025,7 @@
         <v>21650</v>
       </c>
       <c r="F977" t="n">
-        <v>11989</v>
+        <v>12017.5</v>
       </c>
     </row>
     <row r="978">
@@ -50045,7 +50045,7 @@
         <v>21671.25</v>
       </c>
       <c r="F978" t="n">
-        <v>12009.5</v>
+        <v>12038</v>
       </c>
     </row>
     <row r="979">
@@ -50065,7 +50065,7 @@
         <v>21711</v>
       </c>
       <c r="F979" t="n">
-        <v>12031.5</v>
+        <v>12060</v>
       </c>
     </row>
     <row r="980">
@@ -50085,7 +50085,7 @@
         <v>21756.75</v>
       </c>
       <c r="F980" t="n">
-        <v>12053.5</v>
+        <v>12082</v>
       </c>
     </row>
     <row r="981">
@@ -50105,7 +50105,7 @@
         <v>21776.5</v>
       </c>
       <c r="F981" t="n">
-        <v>12077</v>
+        <v>12105.5</v>
       </c>
     </row>
     <row r="982">
@@ -50125,7 +50125,7 @@
         <v>21820.25</v>
       </c>
       <c r="F982" t="n">
-        <v>12099</v>
+        <v>12127.5</v>
       </c>
     </row>
     <row r="983">
@@ -50145,7 +50145,7 @@
         <v>21864</v>
       </c>
       <c r="F983" t="n">
-        <v>12121</v>
+        <v>12149.5</v>
       </c>
     </row>
     <row r="984">
@@ -50165,7 +50165,7 @@
         <v>21901.75</v>
       </c>
       <c r="F984" t="n">
-        <v>12144.5</v>
+        <v>12173</v>
       </c>
     </row>
     <row r="985">
@@ -50185,7 +50185,7 @@
         <v>21946.25</v>
       </c>
       <c r="F985" t="n">
-        <v>12166.5</v>
+        <v>12195</v>
       </c>
     </row>
     <row r="986">
@@ -50205,7 +50205,7 @@
         <v>21982</v>
       </c>
       <c r="F986" t="n">
-        <v>12190</v>
+        <v>12218.5</v>
       </c>
     </row>
     <row r="987">
@@ -50225,7 +50225,7 @@
         <v>22027</v>
       </c>
       <c r="F987" t="n">
-        <v>12210.5</v>
+        <v>12239</v>
       </c>
     </row>
     <row r="988">
@@ -50245,7 +50245,7 @@
         <v>22068.75</v>
       </c>
       <c r="F988" t="n">
-        <v>12232.5</v>
+        <v>12261</v>
       </c>
     </row>
     <row r="989">
@@ -50265,7 +50265,7 @@
         <v>22105.5</v>
       </c>
       <c r="F989" t="n">
-        <v>12256</v>
+        <v>12284.5</v>
       </c>
     </row>
     <row r="990">
@@ -50285,7 +50285,7 @@
         <v>22144.25</v>
       </c>
       <c r="F990" t="n">
-        <v>12279.5</v>
+        <v>12308</v>
       </c>
     </row>
     <row r="991">
@@ -50305,7 +50305,7 @@
         <v>22184.75</v>
       </c>
       <c r="F991" t="n">
-        <v>12298.5</v>
+        <v>12327</v>
       </c>
     </row>
     <row r="992">
@@ -50325,7 +50325,7 @@
         <v>22231.75</v>
       </c>
       <c r="F992" t="n">
-        <v>12320.5</v>
+        <v>12349</v>
       </c>
     </row>
     <row r="993">
@@ -50345,7 +50345,7 @@
         <v>22274.25</v>
       </c>
       <c r="F993" t="n">
-        <v>12341</v>
+        <v>12369.5</v>
       </c>
     </row>
     <row r="994">
@@ -50365,7 +50365,7 @@
         <v>22316.75</v>
       </c>
       <c r="F994" t="n">
-        <v>12363</v>
+        <v>12391.5</v>
       </c>
     </row>
     <row r="995">
@@ -50385,7 +50385,7 @@
         <v>22359.25</v>
       </c>
       <c r="F995" t="n">
-        <v>12386.5</v>
+        <v>12415</v>
       </c>
     </row>
     <row r="996">
@@ -50405,7 +50405,7 @@
         <v>22403.75</v>
       </c>
       <c r="F996" t="n">
-        <v>12405.5</v>
+        <v>12434</v>
       </c>
     </row>
     <row r="997">
@@ -50425,7 +50425,7 @@
         <v>22449.5</v>
       </c>
       <c r="F997" t="n">
-        <v>12427.5</v>
+        <v>12456</v>
       </c>
     </row>
     <row r="998">
@@ -50445,7 +50445,7 @@
         <v>22485.5</v>
       </c>
       <c r="F998" t="n">
-        <v>12449.5</v>
+        <v>12478</v>
       </c>
     </row>
     <row r="999">
@@ -50465,7 +50465,7 @@
         <v>22522</v>
       </c>
       <c r="F999" t="n">
-        <v>12473</v>
+        <v>12501.5</v>
       </c>
     </row>
     <row r="1000">
@@ -50485,7 +50485,7 @@
         <v>22566.5</v>
       </c>
       <c r="F1000" t="n">
-        <v>12493.5</v>
+        <v>12522</v>
       </c>
     </row>
     <row r="1001">
@@ -50505,7 +50505,7 @@
         <v>22610.25</v>
       </c>
       <c r="F1001" t="n">
-        <v>12515.5</v>
+        <v>12544</v>
       </c>
     </row>
     <row r="1002">
@@ -50525,7 +50525,7 @@
         <v>22649.5</v>
       </c>
       <c r="F1002" t="n">
-        <v>12537.5</v>
+        <v>12566</v>
       </c>
     </row>
     <row r="1003">
@@ -50545,7 +50545,7 @@
         <v>22688.75</v>
       </c>
       <c r="F1003" t="n">
-        <v>12558</v>
+        <v>12586.5</v>
       </c>
     </row>
     <row r="1004">
@@ -50565,7 +50565,7 @@
         <v>22714.75</v>
       </c>
       <c r="F1004" t="n">
-        <v>12578.5</v>
+        <v>12607</v>
       </c>
     </row>
     <row r="1005">
@@ -50585,7 +50585,7 @@
         <v>22758</v>
       </c>
       <c r="F1005" t="n">
-        <v>12599</v>
+        <v>12627.5</v>
       </c>
     </row>
     <row r="1006">
@@ -50605,7 +50605,7 @@
         <v>22779.25</v>
       </c>
       <c r="F1006" t="n">
-        <v>12619.5</v>
+        <v>12648</v>
       </c>
     </row>
     <row r="1007">
@@ -50625,7 +50625,7 @@
         <v>22768.5</v>
       </c>
       <c r="F1007" t="n">
-        <v>12641.5</v>
+        <v>12670</v>
       </c>
     </row>
     <row r="1008">
@@ -50645,7 +50645,7 @@
         <v>22807</v>
       </c>
       <c r="F1008" t="n">
-        <v>12665</v>
+        <v>12693.5</v>
       </c>
     </row>
     <row r="1009">
@@ -50665,7 +50665,7 @@
         <v>22834.75</v>
       </c>
       <c r="F1009" t="n">
-        <v>12688.5</v>
+        <v>12717</v>
       </c>
     </row>
     <row r="1010">
@@ -50685,7 +50685,7 @@
         <v>22859.5</v>
       </c>
       <c r="F1010" t="n">
-        <v>12710.5</v>
+        <v>12739</v>
       </c>
     </row>
     <row r="1011">
@@ -50705,7 +50705,7 @@
         <v>22870.75</v>
       </c>
       <c r="F1011" t="n">
-        <v>12729.5</v>
+        <v>12756.5</v>
       </c>
     </row>
     <row r="1012">
@@ -50725,7 +50725,7 @@
         <v>22906</v>
       </c>
       <c r="F1012" t="n">
-        <v>12745.5</v>
+        <v>12774</v>
       </c>
     </row>
     <row r="1013">
@@ -50745,7 +50745,7 @@
         <v>22949.75</v>
       </c>
       <c r="F1013" t="n">
-        <v>12767.5</v>
+        <v>12796</v>
       </c>
     </row>
     <row r="1014">
@@ -50765,7 +50765,7 @@
         <v>22984.5</v>
       </c>
       <c r="F1014" t="n">
-        <v>12789.5</v>
+        <v>12818</v>
       </c>
     </row>
     <row r="1015">
@@ -50785,7 +50785,7 @@
         <v>23021.75</v>
       </c>
       <c r="F1015" t="n">
-        <v>12805.5</v>
+        <v>12837</v>
       </c>
     </row>
     <row r="1016">
@@ -50805,7 +50805,7 @@
         <v>23061</v>
       </c>
       <c r="F1016" t="n">
-        <v>12827.5</v>
+        <v>12859</v>
       </c>
     </row>
     <row r="1017">
@@ -50825,7 +50825,7 @@
         <v>23101.5</v>
       </c>
       <c r="F1017" t="n">
-        <v>12849.5</v>
+        <v>12881</v>
       </c>
     </row>
     <row r="1018">
@@ -50845,7 +50845,7 @@
         <v>23128.5</v>
       </c>
       <c r="F1018" t="n">
-        <v>12870</v>
+        <v>12901.5</v>
       </c>
     </row>
     <row r="1019">
@@ -50865,7 +50865,7 @@
         <v>23162.25</v>
       </c>
       <c r="F1019" t="n">
-        <v>12892</v>
+        <v>12923.5</v>
       </c>
     </row>
     <row r="1020">
@@ -50885,7 +50885,7 @@
         <v>23192</v>
       </c>
       <c r="F1020" t="n">
-        <v>12914</v>
+        <v>12945.5</v>
       </c>
     </row>
     <row r="1021">
@@ -50905,7 +50905,7 @@
         <v>23225.25</v>
       </c>
       <c r="F1021" t="n">
-        <v>12937.5</v>
+        <v>12969</v>
       </c>
     </row>
     <row r="1022">
@@ -50925,7 +50925,7 @@
         <v>23261.75</v>
       </c>
       <c r="F1022" t="n">
-        <v>12958</v>
+        <v>12989.5</v>
       </c>
     </row>
     <row r="1023">
@@ -50945,7 +50945,7 @@
         <v>23281.5</v>
       </c>
       <c r="F1023" t="n">
-        <v>12980</v>
+        <v>13011.5</v>
       </c>
     </row>
     <row r="1024">
@@ -50965,7 +50965,7 @@
         <v>23267.25</v>
       </c>
       <c r="F1024" t="n">
-        <v>13002</v>
+        <v>13033.5</v>
       </c>
     </row>
     <row r="1025">
@@ -50985,7 +50985,7 @@
         <v>23270.5</v>
       </c>
       <c r="F1025" t="n">
-        <v>13024</v>
+        <v>13055.5</v>
       </c>
     </row>
     <row r="1026">
@@ -51005,7 +51005,7 @@
         <v>23309.5</v>
       </c>
       <c r="F1026" t="n">
-        <v>13046</v>
+        <v>13077.5</v>
       </c>
     </row>
     <row r="1027">
@@ -51025,7 +51025,7 @@
         <v>23315.25</v>
       </c>
       <c r="F1027" t="n">
-        <v>13065</v>
+        <v>13096.5</v>
       </c>
     </row>
     <row r="1028">
@@ -51045,7 +51045,7 @@
         <v>23340.25</v>
       </c>
       <c r="F1028" t="n">
-        <v>13087</v>
+        <v>13118.5</v>
       </c>
     </row>
     <row r="1029">
@@ -51065,7 +51065,7 @@
         <v>23362</v>
       </c>
       <c r="F1029" t="n">
-        <v>13109</v>
+        <v>13140.5</v>
       </c>
     </row>
     <row r="1030">
@@ -51085,7 +51085,7 @@
         <v>23401</v>
       </c>
       <c r="F1030" t="n">
-        <v>13131</v>
+        <v>13162.5</v>
       </c>
     </row>
     <row r="1031">
@@ -51105,7 +51105,7 @@
         <v>23440.75</v>
       </c>
       <c r="F1031" t="n">
-        <v>13153</v>
+        <v>13184.5</v>
       </c>
     </row>
     <row r="1032">
@@ -51125,7 +51125,7 @@
         <v>23486.5</v>
       </c>
       <c r="F1032" t="n">
-        <v>13175</v>
+        <v>13206.5</v>
       </c>
     </row>
     <row r="1033">
@@ -51145,7 +51145,7 @@
         <v>23509</v>
       </c>
       <c r="F1033" t="n">
-        <v>13195.5</v>
+        <v>13227</v>
       </c>
     </row>
     <row r="1034">
@@ -51165,7 +51165,7 @@
         <v>23551.5</v>
       </c>
       <c r="F1034" t="n">
-        <v>13217.5</v>
+        <v>13249</v>
       </c>
     </row>
     <row r="1035">
@@ -51185,7 +51185,7 @@
         <v>23549.25</v>
       </c>
       <c r="F1035" t="n">
-        <v>13238</v>
+        <v>13269.5</v>
       </c>
     </row>
     <row r="1036">
@@ -51205,7 +51205,7 @@
         <v>23570.5</v>
       </c>
       <c r="F1036" t="n">
-        <v>13261.5</v>
+        <v>13293</v>
       </c>
     </row>
     <row r="1037">
@@ -51225,7 +51225,7 @@
         <v>23600.25</v>
       </c>
       <c r="F1037" t="n">
-        <v>13283.5</v>
+        <v>13315</v>
       </c>
     </row>
     <row r="1038">
@@ -51245,7 +51245,7 @@
         <v>23631.25</v>
       </c>
       <c r="F1038" t="n">
-        <v>13307</v>
+        <v>13338.5</v>
       </c>
     </row>
     <row r="1039">
@@ -51265,7 +51265,7 @@
         <v>23659.75</v>
       </c>
       <c r="F1039" t="n">
-        <v>13329</v>
+        <v>13360.5</v>
       </c>
     </row>
     <row r="1040">
@@ -51285,7 +51285,7 @@
         <v>23704.75</v>
       </c>
       <c r="F1040" t="n">
-        <v>13352.5</v>
+        <v>13384</v>
       </c>
     </row>
     <row r="1041">
@@ -51305,7 +51305,7 @@
         <v>23738</v>
       </c>
       <c r="F1041" t="n">
-        <v>13376</v>
+        <v>13407.5</v>
       </c>
     </row>
     <row r="1042">
@@ -51325,7 +51325,7 @@
         <v>23777.75</v>
       </c>
       <c r="F1042" t="n">
-        <v>13398</v>
+        <v>13429.5</v>
       </c>
     </row>
     <row r="1043">
@@ -51345,7 +51345,7 @@
         <v>23814.25</v>
       </c>
       <c r="F1043" t="n">
-        <v>13420</v>
+        <v>13451.5</v>
       </c>
     </row>
     <row r="1044">
@@ -51365,7 +51365,7 @@
         <v>23850</v>
       </c>
       <c r="F1044" t="n">
-        <v>13443.5</v>
+        <v>13475</v>
       </c>
     </row>
     <row r="1045">
@@ -51385,7 +51385,7 @@
         <v>23894.5</v>
       </c>
       <c r="F1045" t="n">
-        <v>13465.5</v>
+        <v>13497</v>
       </c>
     </row>
     <row r="1046">
@@ -51405,7 +51405,7 @@
         <v>23926.25</v>
       </c>
       <c r="F1046" t="n">
-        <v>13489</v>
+        <v>13520.5</v>
       </c>
     </row>
     <row r="1047">
@@ -51425,7 +51425,7 @@
         <v>23959.5</v>
       </c>
       <c r="F1047" t="n">
-        <v>13511</v>
+        <v>13542.5</v>
       </c>
     </row>
     <row r="1048">
@@ -51445,7 +51445,7 @@
         <v>24003.25</v>
       </c>
       <c r="F1048" t="n">
-        <v>13534.5</v>
+        <v>13566</v>
       </c>
     </row>
     <row r="1049">
@@ -51465,7 +51465,7 @@
         <v>24032.5</v>
       </c>
       <c r="F1049" t="n">
-        <v>13556.5</v>
+        <v>13588</v>
       </c>
     </row>
     <row r="1050">
@@ -51485,7 +51485,7 @@
         <v>24071.5</v>
       </c>
       <c r="F1050" t="n">
-        <v>13577</v>
+        <v>13608.5</v>
       </c>
     </row>
     <row r="1051">
@@ -51505,7 +51505,7 @@
         <v>24111.25</v>
       </c>
       <c r="F1051" t="n">
-        <v>13599</v>
+        <v>13630.5</v>
       </c>
     </row>
     <row r="1052">
@@ -51525,7 +51525,7 @@
         <v>24145.25</v>
       </c>
       <c r="F1052" t="n">
-        <v>13619.5</v>
+        <v>13654</v>
       </c>
     </row>
     <row r="1053">
@@ -51545,7 +51545,7 @@
         <v>24189</v>
       </c>
       <c r="F1053" t="n">
-        <v>13641.5</v>
+        <v>13676</v>
       </c>
     </row>
     <row r="1054">
@@ -51565,7 +51565,7 @@
         <v>24225.5</v>
       </c>
       <c r="F1054" t="n">
-        <v>13665</v>
+        <v>13698</v>
       </c>
     </row>
     <row r="1055">
@@ -51585,7 +51585,7 @@
         <v>24266.75</v>
       </c>
       <c r="F1055" t="n">
-        <v>13687</v>
+        <v>13718.5</v>
       </c>
     </row>
     <row r="1056">
@@ -51605,7 +51605,7 @@
         <v>24300.25</v>
       </c>
       <c r="F1056" t="n">
-        <v>13709</v>
+        <v>13740.5</v>
       </c>
     </row>
     <row r="1057">
@@ -51625,7 +51625,7 @@
         <v>24339</v>
       </c>
       <c r="F1057" t="n">
-        <v>13731</v>
+        <v>13762.5</v>
       </c>
     </row>
     <row r="1058">
@@ -51645,7 +51645,7 @@
         <v>24377.5</v>
       </c>
       <c r="F1058" t="n">
-        <v>13748.5</v>
+        <v>13780</v>
       </c>
     </row>
     <row r="1059">
@@ -51665,7 +51665,7 @@
         <v>24402.75</v>
       </c>
       <c r="F1059" t="n">
-        <v>13772</v>
+        <v>13803.5</v>
       </c>
     </row>
     <row r="1060">
@@ -51685,7 +51685,7 @@
         <v>24433.25</v>
       </c>
       <c r="F1060" t="n">
-        <v>13792.5</v>
+        <v>13824</v>
       </c>
     </row>
     <row r="1061">
@@ -51705,7 +51705,7 @@
         <v>24468.25</v>
       </c>
       <c r="F1061" t="n">
-        <v>13814.5</v>
+        <v>13846</v>
       </c>
     </row>
     <row r="1062">
@@ -51725,7 +51725,7 @@
         <v>24507.25</v>
       </c>
       <c r="F1062" t="n">
-        <v>13835</v>
+        <v>13866.5</v>
       </c>
     </row>
     <row r="1063">
@@ -51745,7 +51745,7 @@
         <v>24545</v>
       </c>
       <c r="F1063" t="n">
-        <v>13857</v>
+        <v>13888.5</v>
       </c>
     </row>
     <row r="1064">
@@ -51765,7 +51765,7 @@
         <v>24580.75</v>
       </c>
       <c r="F1064" t="n">
-        <v>13876</v>
+        <v>13907.5</v>
       </c>
     </row>
     <row r="1065">
@@ -51785,7 +51785,7 @@
         <v>24604.5</v>
       </c>
       <c r="F1065" t="n">
-        <v>13899.5</v>
+        <v>13931</v>
       </c>
     </row>
     <row r="1066">
@@ -51805,7 +51805,7 @@
         <v>24643</v>
       </c>
       <c r="F1066" t="n">
-        <v>13923</v>
+        <v>13954.5</v>
       </c>
     </row>
     <row r="1067">
@@ -51825,7 +51825,7 @@
         <v>24670</v>
       </c>
       <c r="F1067" t="n">
-        <v>13942</v>
+        <v>13973.5</v>
       </c>
     </row>
     <row r="1068">
@@ -51845,7 +51845,7 @@
         <v>24705.75</v>
       </c>
       <c r="F1068" t="n">
-        <v>13965.5</v>
+        <v>13997</v>
       </c>
     </row>
     <row r="1069">
@@ -51865,7 +51865,7 @@
         <v>24741.25</v>
       </c>
       <c r="F1069" t="n">
-        <v>13986</v>
+        <v>14017.5</v>
       </c>
     </row>
     <row r="1070">
@@ -51885,7 +51885,7 @@
         <v>24771</v>
       </c>
       <c r="F1070" t="n">
-        <v>14006.5</v>
+        <v>14038</v>
       </c>
     </row>
     <row r="1071">
@@ -51905,7 +51905,7 @@
         <v>24805.75</v>
       </c>
       <c r="F1071" t="n">
-        <v>14030</v>
+        <v>14061.5</v>
       </c>
     </row>
     <row r="1072">
@@ -51925,7 +51925,7 @@
         <v>24837.75</v>
       </c>
       <c r="F1072" t="n">
-        <v>14053.5</v>
+        <v>14085</v>
       </c>
     </row>
     <row r="1073">
@@ -51945,7 +51945,7 @@
         <v>24873.5</v>
       </c>
       <c r="F1073" t="n">
-        <v>14077</v>
+        <v>14108.5</v>
       </c>
     </row>
     <row r="1074">
@@ -51965,7 +51965,7 @@
         <v>24910.5</v>
       </c>
       <c r="F1074" t="n">
-        <v>14099</v>
+        <v>14130.5</v>
       </c>
     </row>
     <row r="1075">
@@ -51985,7 +51985,7 @@
         <v>24945.75</v>
       </c>
       <c r="F1075" t="n">
-        <v>14121</v>
+        <v>14152.5</v>
       </c>
     </row>
     <row r="1076">
@@ -52005,7 +52005,7 @@
         <v>24973.75</v>
       </c>
       <c r="F1076" t="n">
-        <v>14144.5</v>
+        <v>14176</v>
       </c>
     </row>
     <row r="1077">
@@ -52025,7 +52025,7 @@
         <v>25014.75</v>
       </c>
       <c r="F1077" t="n">
-        <v>14163.5</v>
+        <v>14195</v>
       </c>
     </row>
     <row r="1078">
@@ -52045,7 +52045,7 @@
         <v>25040</v>
       </c>
       <c r="F1078" t="n">
-        <v>14185.5</v>
+        <v>14217</v>
       </c>
     </row>
     <row r="1079">
@@ -52065,7 +52065,7 @@
         <v>25082</v>
       </c>
       <c r="F1079" t="n">
-        <v>14209</v>
+        <v>14240.5</v>
       </c>
     </row>
     <row r="1080">
@@ -52085,7 +52085,7 @@
         <v>25119.25</v>
       </c>
       <c r="F1080" t="n">
-        <v>14231</v>
+        <v>14262.5</v>
       </c>
     </row>
     <row r="1081">
@@ -52105,7 +52105,7 @@
         <v>25146</v>
       </c>
       <c r="F1081" t="n">
-        <v>14253</v>
+        <v>14284.5</v>
       </c>
     </row>
     <row r="1082">
@@ -52125,7 +52125,7 @@
         <v>25185.75</v>
       </c>
       <c r="F1082" t="n">
-        <v>14276.5</v>
+        <v>14308</v>
       </c>
     </row>
     <row r="1083">
@@ -52145,7 +52145,7 @@
         <v>25215.75</v>
       </c>
       <c r="F1083" t="n">
-        <v>14298.5</v>
+        <v>14330</v>
       </c>
     </row>
     <row r="1084">
@@ -52165,7 +52165,7 @@
         <v>25256.25</v>
       </c>
       <c r="F1084" t="n">
-        <v>14320.5</v>
+        <v>14352</v>
       </c>
     </row>
     <row r="1085">
@@ -52185,7 +52185,7 @@
         <v>25300</v>
       </c>
       <c r="F1085" t="n">
-        <v>14344</v>
+        <v>14375.5</v>
       </c>
     </row>
     <row r="1086">
@@ -52205,7 +52205,7 @@
         <v>25339.75</v>
       </c>
       <c r="F1086" t="n">
-        <v>14366</v>
+        <v>14397.5</v>
       </c>
     </row>
     <row r="1087">
@@ -52225,7 +52225,7 @@
         <v>25369.75</v>
       </c>
       <c r="F1087" t="n">
-        <v>14389.5</v>
+        <v>14421</v>
       </c>
     </row>
     <row r="1088">
@@ -52245,7 +52245,7 @@
         <v>25409.5</v>
       </c>
       <c r="F1088" t="n">
-        <v>14408.5</v>
+        <v>14440</v>
       </c>
     </row>
     <row r="1089">
@@ -52265,7 +52265,7 @@
         <v>25452</v>
       </c>
       <c r="F1089" t="n">
-        <v>14430.5</v>
+        <v>14462</v>
       </c>
     </row>
     <row r="1090">
@@ -52285,7 +52285,7 @@
         <v>25446.5</v>
       </c>
       <c r="F1090" t="n">
-        <v>14452.5</v>
+        <v>14484</v>
       </c>
     </row>
     <row r="1091">
@@ -52305,7 +52305,7 @@
         <v>25486.25</v>
       </c>
       <c r="F1091" t="n">
-        <v>14474.5</v>
+        <v>14506</v>
       </c>
     </row>
     <row r="1092">
@@ -52325,7 +52325,7 @@
         <v>25520.75</v>
       </c>
       <c r="F1092" t="n">
-        <v>14495</v>
+        <v>14526.5</v>
       </c>
     </row>
     <row r="1093">
@@ -52345,7 +52345,7 @@
         <v>25561.25</v>
       </c>
       <c r="F1093" t="n">
-        <v>14515.5</v>
+        <v>14547</v>
       </c>
     </row>
     <row r="1094">
@@ -52365,7 +52365,7 @@
         <v>25577.25</v>
       </c>
       <c r="F1094" t="n">
-        <v>14536</v>
+        <v>14567.5</v>
       </c>
     </row>
     <row r="1095">
@@ -52385,7 +52385,7 @@
         <v>25615</v>
       </c>
       <c r="F1095" t="n">
-        <v>14558</v>
+        <v>14589.5</v>
       </c>
     </row>
     <row r="1096">
@@ -52405,7 +52405,7 @@
         <v>25648</v>
       </c>
       <c r="F1096" t="n">
-        <v>14580</v>
+        <v>14611.5</v>
       </c>
     </row>
     <row r="1097">
@@ -52425,7 +52425,7 @@
         <v>25691</v>
       </c>
       <c r="F1097" t="n">
-        <v>14603.5</v>
+        <v>14635</v>
       </c>
     </row>
     <row r="1098">
@@ -52445,7 +52445,7 @@
         <v>25725</v>
       </c>
       <c r="F1098" t="n">
-        <v>14627</v>
+        <v>14658.5</v>
       </c>
     </row>
     <row r="1099">
@@ -52465,7 +52465,7 @@
         <v>25749.75</v>
       </c>
       <c r="F1099" t="n">
-        <v>14649</v>
+        <v>14680.5</v>
       </c>
     </row>
     <row r="1100">
@@ -52485,7 +52485,7 @@
         <v>25786.75</v>
       </c>
       <c r="F1100" t="n">
-        <v>14672.5</v>
+        <v>14704</v>
       </c>
     </row>
     <row r="1101">
@@ -52505,7 +52505,7 @@
         <v>25824.5</v>
       </c>
       <c r="F1101" t="n">
-        <v>14694.5</v>
+        <v>14726</v>
       </c>
     </row>
     <row r="1102">
@@ -52525,7 +52525,7 @@
         <v>25851.25</v>
       </c>
       <c r="F1102" t="n">
-        <v>14718</v>
+        <v>14749.5</v>
       </c>
     </row>
     <row r="1103">
@@ -52545,7 +52545,7 @@
         <v>25846.5</v>
       </c>
       <c r="F1103" t="n">
-        <v>14740</v>
+        <v>14771.5</v>
       </c>
     </row>
     <row r="1104">
@@ -52565,7 +52565,7 @@
         <v>25892.25</v>
       </c>
       <c r="F1104" t="n">
-        <v>14760.5</v>
+        <v>14792</v>
       </c>
     </row>
     <row r="1105">
@@ -52585,7 +52585,7 @@
         <v>25906.75</v>
       </c>
       <c r="F1105" t="n">
-        <v>14784</v>
+        <v>14815.5</v>
       </c>
     </row>
     <row r="1106">
@@ -52605,7 +52605,7 @@
         <v>25920.75</v>
       </c>
       <c r="F1106" t="n">
-        <v>14804.5</v>
+        <v>14836</v>
       </c>
     </row>
     <row r="1107">
@@ -52625,7 +52625,7 @@
         <v>25930</v>
       </c>
       <c r="F1107" t="n">
-        <v>14826.5</v>
+        <v>14858</v>
       </c>
     </row>
     <row r="1108">
@@ -52645,7 +52645,7 @@
         <v>25967</v>
       </c>
       <c r="F1108" t="n">
-        <v>14848.5</v>
+        <v>14880</v>
       </c>
     </row>
     <row r="1109">
@@ -52665,7 +52665,7 @@
         <v>26006.75</v>
       </c>
       <c r="F1109" t="n">
-        <v>14872</v>
+        <v>14903.5</v>
       </c>
     </row>
     <row r="1110">
@@ -52685,7 +52685,7 @@
         <v>26033.5</v>
       </c>
       <c r="F1110" t="n">
-        <v>14892.5</v>
+        <v>14924</v>
       </c>
     </row>
     <row r="1111">
@@ -52705,7 +52705,7 @@
         <v>26063</v>
       </c>
       <c r="F1111" t="n">
-        <v>14914.5</v>
+        <v>14946</v>
       </c>
     </row>
     <row r="1112">
@@ -52725,7 +52725,7 @@
         <v>26094.25</v>
       </c>
       <c r="F1112" t="n">
-        <v>14936.5</v>
+        <v>14968</v>
       </c>
     </row>
     <row r="1113">
@@ -52745,7 +52745,7 @@
         <v>26129.5</v>
       </c>
       <c r="F1113" t="n">
-        <v>14960</v>
+        <v>14991.5</v>
       </c>
     </row>
     <row r="1114">
@@ -52765,7 +52765,7 @@
         <v>26169.5</v>
       </c>
       <c r="F1114" t="n">
-        <v>14983.5</v>
+        <v>15015</v>
       </c>
     </row>
     <row r="1115">
@@ -52785,7 +52785,7 @@
         <v>26206.5</v>
       </c>
       <c r="F1115" t="n">
-        <v>15007</v>
+        <v>15038.5</v>
       </c>
     </row>
     <row r="1116">
@@ -52805,7 +52805,7 @@
         <v>26245</v>
       </c>
       <c r="F1116" t="n">
-        <v>15027.5</v>
+        <v>15059</v>
       </c>
     </row>
     <row r="1117">
@@ -52825,7 +52825,7 @@
         <v>26276.75</v>
       </c>
       <c r="F1117" t="n">
-        <v>15051</v>
+        <v>15082.5</v>
       </c>
     </row>
     <row r="1118">
@@ -52845,7 +52845,7 @@
         <v>26302</v>
       </c>
       <c r="F1118" t="n">
-        <v>15074.5</v>
+        <v>15106</v>
       </c>
     </row>
     <row r="1119">
@@ -52865,7 +52865,7 @@
         <v>26328.75</v>
       </c>
       <c r="F1119" t="n">
-        <v>15098</v>
+        <v>15129.5</v>
       </c>
     </row>
     <row r="1120">
@@ -52885,7 +52885,7 @@
         <v>26366.5</v>
       </c>
       <c r="F1120" t="n">
-        <v>15121.5</v>
+        <v>15153</v>
       </c>
     </row>
     <row r="1121">
@@ -52905,7 +52905,7 @@
         <v>26399</v>
       </c>
       <c r="F1121" t="n">
-        <v>15145</v>
+        <v>15176.5</v>
       </c>
     </row>
     <row r="1122">
@@ -52925,7 +52925,7 @@
         <v>26442.75</v>
       </c>
       <c r="F1122" t="n">
-        <v>15168.5</v>
+        <v>15200</v>
       </c>
     </row>
     <row r="1123">
@@ -52945,7 +52945,7 @@
         <v>26483.75</v>
       </c>
       <c r="F1123" t="n">
-        <v>15186</v>
+        <v>15217.5</v>
       </c>
     </row>
     <row r="1124">
@@ -52965,7 +52965,7 @@
         <v>26517.75</v>
       </c>
       <c r="F1124" t="n">
-        <v>15209.5</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="1125">
@@ -52985,7 +52985,7 @@
         <v>26554.5</v>
       </c>
       <c r="F1125" t="n">
-        <v>15231.5</v>
+        <v>15263</v>
       </c>
     </row>
     <row r="1126">
@@ -53005,7 +53005,7 @@
         <v>26593.5</v>
       </c>
       <c r="F1126" t="n">
-        <v>15255</v>
+        <v>15286.5</v>
       </c>
     </row>
     <row r="1127">
@@ -53025,7 +53025,7 @@
         <v>26635.25</v>
       </c>
       <c r="F1127" t="n">
-        <v>15278.5</v>
+        <v>15310</v>
       </c>
     </row>
     <row r="1128">
@@ -53045,7 +53045,7 @@
         <v>26660.5</v>
       </c>
       <c r="F1128" t="n">
-        <v>15302</v>
+        <v>15333.5</v>
       </c>
     </row>
     <row r="1129">
@@ -53065,7 +53065,7 @@
         <v>26703</v>
       </c>
       <c r="F1129" t="n">
-        <v>15322.5</v>
+        <v>15354</v>
       </c>
     </row>
     <row r="1130">
@@ -53085,7 +53085,7 @@
         <v>26735.5</v>
       </c>
       <c r="F1130" t="n">
-        <v>15344.5</v>
+        <v>15376</v>
       </c>
     </row>
     <row r="1131">
@@ -53105,7 +53105,7 @@
         <v>26772.75</v>
       </c>
       <c r="F1131" t="n">
-        <v>15365</v>
+        <v>15396.5</v>
       </c>
     </row>
     <row r="1132">
@@ -53125,7 +53125,7 @@
         <v>26814.5</v>
       </c>
       <c r="F1132" t="n">
-        <v>15388.5</v>
+        <v>15420</v>
       </c>
     </row>
     <row r="1133">
@@ -53145,7 +53145,7 @@
         <v>26838</v>
       </c>
       <c r="F1133" t="n">
-        <v>15410.5</v>
+        <v>15442</v>
       </c>
     </row>
     <row r="1134">
@@ -53165,7 +53165,7 @@
         <v>26869.5</v>
       </c>
       <c r="F1134" t="n">
-        <v>15434</v>
+        <v>15465.5</v>
       </c>
     </row>
     <row r="1135">
@@ -53185,7 +53185,7 @@
         <v>26912.5</v>
       </c>
       <c r="F1135" t="n">
-        <v>15457.5</v>
+        <v>15489</v>
       </c>
     </row>
     <row r="1136">
@@ -53205,7 +53205,7 @@
         <v>26949</v>
       </c>
       <c r="F1136" t="n">
-        <v>15479.5</v>
+        <v>15511</v>
       </c>
     </row>
     <row r="1137">
@@ -53225,7 +53225,7 @@
         <v>26980</v>
       </c>
       <c r="F1137" t="n">
-        <v>15498.5</v>
+        <v>15530</v>
       </c>
     </row>
     <row r="1138">
@@ -53245,7 +53245,7 @@
         <v>27017</v>
       </c>
       <c r="F1138" t="n">
-        <v>15520.5</v>
+        <v>15552</v>
       </c>
     </row>
     <row r="1139">
@@ -53265,7 +53265,7 @@
         <v>27054.25</v>
       </c>
       <c r="F1139" t="n">
-        <v>15542.5</v>
+        <v>15574</v>
       </c>
     </row>
     <row r="1140">
@@ -53285,7 +53285,7 @@
         <v>27092.75</v>
       </c>
       <c r="F1140" t="n">
-        <v>15563</v>
+        <v>15594.5</v>
       </c>
     </row>
     <row r="1141">
@@ -53305,7 +53305,7 @@
         <v>27136</v>
       </c>
       <c r="F1141" t="n">
-        <v>15585</v>
+        <v>15616.5</v>
       </c>
     </row>
     <row r="1142">
@@ -53325,7 +53325,7 @@
         <v>27168</v>
       </c>
       <c r="F1142" t="n">
-        <v>15607</v>
+        <v>15638.5</v>
       </c>
     </row>
     <row r="1143">
@@ -53345,7 +53345,7 @@
         <v>27193</v>
       </c>
       <c r="F1143" t="n">
-        <v>15629</v>
+        <v>15660.5</v>
       </c>
     </row>
     <row r="1144">
@@ -53365,7 +53365,7 @@
         <v>27230.25</v>
       </c>
       <c r="F1144" t="n">
-        <v>15652.5</v>
+        <v>15684</v>
       </c>
     </row>
     <row r="1145">
@@ -53385,7 +53385,7 @@
         <v>27270</v>
       </c>
       <c r="F1145" t="n">
-        <v>15674.5</v>
+        <v>15706</v>
       </c>
     </row>
     <row r="1146">
@@ -53405,7 +53405,7 @@
         <v>27307.25</v>
       </c>
       <c r="F1146" t="n">
-        <v>15698</v>
+        <v>15729.5</v>
       </c>
     </row>
     <row r="1147">
@@ -53425,7 +53425,7 @@
         <v>27347</v>
       </c>
       <c r="F1147" t="n">
-        <v>15720</v>
+        <v>15751.5</v>
       </c>
     </row>
     <row r="1148">
@@ -53445,7 +53445,7 @@
         <v>27358.75</v>
       </c>
       <c r="F1148" t="n">
-        <v>15740.5</v>
+        <v>15772</v>
       </c>
     </row>
     <row r="1149">
@@ -53465,7 +53465,7 @@
         <v>27380.5</v>
       </c>
       <c r="F1149" t="n">
-        <v>15764</v>
+        <v>15795.5</v>
       </c>
     </row>
     <row r="1150">
@@ -53485,7 +53485,7 @@
         <v>27398.5</v>
       </c>
       <c r="F1150" t="n">
-        <v>15786</v>
+        <v>15817.5</v>
       </c>
     </row>
     <row r="1151">
@@ -53505,7 +53505,7 @@
         <v>27433.75</v>
       </c>
       <c r="F1151" t="n">
-        <v>15809.5</v>
+        <v>15841</v>
       </c>
     </row>
     <row r="1152">
@@ -53525,7 +53525,7 @@
         <v>27471.75</v>
       </c>
       <c r="F1152" t="n">
-        <v>15831.5</v>
+        <v>15863</v>
       </c>
     </row>
     <row r="1153">
@@ -53545,7 +53545,7 @@
         <v>27495</v>
       </c>
       <c r="F1153" t="n">
-        <v>15853.5</v>
+        <v>15885</v>
       </c>
     </row>
     <row r="1154">
@@ -53565,7 +53565,7 @@
         <v>27518.5</v>
       </c>
       <c r="F1154" t="n">
-        <v>15877</v>
+        <v>15908.5</v>
       </c>
     </row>
     <row r="1155">
@@ -53585,7 +53585,7 @@
         <v>27560.25</v>
       </c>
       <c r="F1155" t="n">
-        <v>15894.5</v>
+        <v>15926</v>
       </c>
     </row>
     <row r="1156">
@@ -53605,7 +53605,7 @@
         <v>27595.75</v>
       </c>
       <c r="F1156" t="n">
-        <v>15916.5</v>
+        <v>15948</v>
       </c>
     </row>
     <row r="1157">
@@ -53625,7 +53625,7 @@
         <v>27635</v>
       </c>
       <c r="F1157" t="n">
-        <v>15940</v>
+        <v>15971.5</v>
       </c>
     </row>
     <row r="1158">
@@ -53645,7 +53645,7 @@
         <v>27674.75</v>
       </c>
       <c r="F1158" t="n">
-        <v>15963.5</v>
+        <v>15995</v>
       </c>
     </row>
     <row r="1159">
@@ -53665,7 +53665,7 @@
         <v>27699.25</v>
       </c>
       <c r="F1159" t="n">
-        <v>15987</v>
+        <v>16018.5</v>
       </c>
     </row>
     <row r="1160">
@@ -53685,7 +53685,7 @@
         <v>27742.25</v>
       </c>
       <c r="F1160" t="n">
-        <v>16010.5</v>
+        <v>16042</v>
       </c>
     </row>
     <row r="1161">
@@ -53705,7 +53705,7 @@
         <v>27780.75</v>
       </c>
       <c r="F1161" t="n">
-        <v>16032.5</v>
+        <v>16064</v>
       </c>
     </row>
     <row r="1162">
@@ -53725,7 +53725,7 @@
         <v>27818.75</v>
       </c>
       <c r="F1162" t="n">
-        <v>16054.5</v>
+        <v>16086</v>
       </c>
     </row>
     <row r="1163">
@@ -53745,7 +53745,7 @@
         <v>27858.5</v>
       </c>
       <c r="F1163" t="n">
-        <v>16078</v>
+        <v>16109.5</v>
       </c>
     </row>
     <row r="1164">
@@ -53765,7 +53765,7 @@
         <v>27886</v>
       </c>
       <c r="F1164" t="n">
-        <v>16098.5</v>
+        <v>16130</v>
       </c>
     </row>
     <row r="1165">
@@ -53785,7 +53785,7 @@
         <v>27923.25</v>
       </c>
       <c r="F1165" t="n">
-        <v>16120.5</v>
+        <v>16152</v>
       </c>
     </row>
     <row r="1166">
@@ -53805,7 +53805,7 @@
         <v>27963</v>
       </c>
       <c r="F1166" t="n">
-        <v>16144</v>
+        <v>16175.5</v>
       </c>
     </row>
     <row r="1167">
@@ -53825,7 +53825,7 @@
         <v>27998.75</v>
       </c>
       <c r="F1167" t="n">
-        <v>16163</v>
+        <v>16194.5</v>
       </c>
     </row>
     <row r="1168">
@@ -53845,7 +53845,7 @@
         <v>28038.5</v>
       </c>
       <c r="F1168" t="n">
-        <v>16183.5</v>
+        <v>16215</v>
       </c>
     </row>
     <row r="1169">
@@ -53865,7 +53865,7 @@
         <v>28067.75</v>
       </c>
       <c r="F1169" t="n">
-        <v>16207</v>
+        <v>16238.5</v>
       </c>
     </row>
     <row r="1170">
@@ -53885,7 +53885,7 @@
         <v>28098.25</v>
       </c>
       <c r="F1170" t="n">
-        <v>16229</v>
+        <v>16260.5</v>
       </c>
     </row>
     <row r="1171">
@@ -53905,7 +53905,7 @@
         <v>28135</v>
       </c>
       <c r="F1171" t="n">
-        <v>16249.5</v>
+        <v>16281</v>
       </c>
     </row>
     <row r="1172">
@@ -53925,7 +53925,7 @@
         <v>28176</v>
       </c>
       <c r="F1172" t="n">
-        <v>16273</v>
+        <v>16304.5</v>
       </c>
     </row>
     <row r="1173">
@@ -53945,7 +53945,7 @@
         <v>28214.5</v>
       </c>
       <c r="F1173" t="n">
-        <v>16295</v>
+        <v>16326.5</v>
       </c>
     </row>
     <row r="1174">
@@ -53965,7 +53965,7 @@
         <v>28249.75</v>
       </c>
       <c r="F1174" t="n">
-        <v>16317</v>
+        <v>16348.5</v>
       </c>
     </row>
     <row r="1175">
@@ -53985,7 +53985,7 @@
         <v>28291.5</v>
       </c>
       <c r="F1175" t="n">
-        <v>16340.5</v>
+        <v>16372</v>
       </c>
     </row>
     <row r="1176">
@@ -54005,7 +54005,7 @@
         <v>28324.25</v>
       </c>
       <c r="F1176" t="n">
-        <v>16364</v>
+        <v>16395.5</v>
       </c>
     </row>
     <row r="1177">
@@ -54025,7 +54025,7 @@
         <v>28362</v>
       </c>
       <c r="F1177" t="n">
-        <v>16387.5</v>
+        <v>16419</v>
       </c>
     </row>
     <row r="1178">
@@ -54045,7 +54045,7 @@
         <v>28406.5</v>
       </c>
       <c r="F1178" t="n">
-        <v>16411</v>
+        <v>16442.5</v>
       </c>
     </row>
     <row r="1179">
@@ -54065,7 +54065,7 @@
         <v>28438.25</v>
       </c>
       <c r="F1179" t="n">
-        <v>16434.5</v>
+        <v>16466</v>
       </c>
     </row>
     <row r="1180">
@@ -54085,7 +54085,7 @@
         <v>28469.5</v>
       </c>
       <c r="F1180" t="n">
-        <v>16458</v>
+        <v>16489.5</v>
       </c>
     </row>
     <row r="1181">
@@ -54105,7 +54105,7 @@
         <v>28512.5</v>
       </c>
       <c r="F1181" t="n">
-        <v>16481.5</v>
+        <v>16513</v>
       </c>
     </row>
     <row r="1182">
@@ -54125,7 +54125,7 @@
         <v>28550.5</v>
       </c>
       <c r="F1182" t="n">
-        <v>16502</v>
+        <v>16533.5</v>
       </c>
     </row>
     <row r="1183">
@@ -54145,7 +54145,7 @@
         <v>28585</v>
       </c>
       <c r="F1183" t="n">
-        <v>16524</v>
+        <v>16555.5</v>
       </c>
     </row>
     <row r="1184">
@@ -54165,7 +54165,7 @@
         <v>28618.5</v>
       </c>
       <c r="F1184" t="n">
-        <v>16546</v>
+        <v>16577.5</v>
       </c>
     </row>
     <row r="1185">
@@ -54185,7 +54185,7 @@
         <v>28661.5</v>
       </c>
       <c r="F1185" t="n">
-        <v>16568</v>
+        <v>16599.5</v>
       </c>
     </row>
     <row r="1186">
@@ -54205,7 +54205,7 @@
         <v>28694</v>
       </c>
       <c r="F1186" t="n">
-        <v>16590</v>
+        <v>16621.5</v>
       </c>
     </row>
     <row r="1187">
@@ -54225,7 +54225,7 @@
         <v>28735.25</v>
       </c>
       <c r="F1187" t="n">
-        <v>16613.5</v>
+        <v>16645</v>
       </c>
     </row>
     <row r="1188">
@@ -54245,7 +54245,7 @@
         <v>28767.75</v>
       </c>
       <c r="F1188" t="n">
-        <v>16635.5</v>
+        <v>16667</v>
       </c>
     </row>
     <row r="1189">
@@ -54265,7 +54265,7 @@
         <v>28792</v>
       </c>
       <c r="F1189" t="n">
-        <v>16657.5</v>
+        <v>16689</v>
       </c>
     </row>
     <row r="1190">
@@ -54285,7 +54285,7 @@
         <v>28835.25</v>
       </c>
       <c r="F1190" t="n">
-        <v>16681</v>
+        <v>16712.5</v>
       </c>
     </row>
     <row r="1191">
@@ -54305,7 +54305,7 @@
         <v>28876</v>
       </c>
       <c r="F1191" t="n">
-        <v>16704.5</v>
+        <v>16736</v>
       </c>
     </row>
     <row r="1192">
@@ -54325,7 +54325,7 @@
         <v>28911.25</v>
       </c>
       <c r="F1192" t="n">
-        <v>16728</v>
+        <v>16759.5</v>
       </c>
     </row>
     <row r="1193">
@@ -54345,7 +54345,7 @@
         <v>28941</v>
       </c>
       <c r="F1193" t="n">
-        <v>16751.5</v>
+        <v>16783</v>
       </c>
     </row>
     <row r="1194">
@@ -54365,7 +54365,7 @@
         <v>28984.75</v>
       </c>
       <c r="F1194" t="n">
-        <v>16775</v>
+        <v>16806.5</v>
       </c>
     </row>
     <row r="1195">
@@ -54385,7 +54385,7 @@
         <v>29018.5</v>
       </c>
       <c r="F1195" t="n">
-        <v>16797</v>
+        <v>16828.5</v>
       </c>
     </row>
     <row r="1196">
@@ -54405,7 +54405,7 @@
         <v>29037.25</v>
       </c>
       <c r="F1196" t="n">
-        <v>16819</v>
+        <v>16850.5</v>
       </c>
     </row>
     <row r="1197">
@@ -54425,7 +54425,7 @@
         <v>29078.5</v>
       </c>
       <c r="F1197" t="n">
-        <v>16841</v>
+        <v>16872.5</v>
       </c>
     </row>
     <row r="1198">
@@ -54445,7 +54445,7 @@
         <v>29119</v>
       </c>
       <c r="F1198" t="n">
-        <v>16864.5</v>
+        <v>16896</v>
       </c>
     </row>
     <row r="1199">
@@ -54465,7 +54465,7 @@
         <v>29155.75</v>
       </c>
       <c r="F1199" t="n">
-        <v>16886.5</v>
+        <v>16918</v>
       </c>
     </row>
     <row r="1200">
@@ -54485,7 +54485,7 @@
         <v>29195.5</v>
       </c>
       <c r="F1200" t="n">
-        <v>16910</v>
+        <v>16941.5</v>
       </c>
     </row>
     <row r="1201">
@@ -54505,7 +54505,7 @@
         <v>29235.5</v>
       </c>
       <c r="F1201" t="n">
-        <v>16933.5</v>
+        <v>16965</v>
       </c>
     </row>
     <row r="1202">
@@ -54525,7 +54525,7 @@
         <v>29265.25</v>
       </c>
       <c r="F1202" t="n">
-        <v>16957</v>
+        <v>16988.5</v>
       </c>
     </row>
     <row r="1203">
@@ -54545,7 +54545,7 @@
         <v>29262.5</v>
       </c>
       <c r="F1203" t="n">
-        <v>16980.5</v>
+        <v>17012</v>
       </c>
     </row>
     <row r="1204">
@@ -54565,7 +54565,7 @@
         <v>29307</v>
       </c>
       <c r="F1204" t="n">
-        <v>17004</v>
+        <v>17035.5</v>
       </c>
     </row>
     <row r="1205">
@@ -54585,7 +54585,7 @@
         <v>29348</v>
       </c>
       <c r="F1205" t="n">
-        <v>17024.5</v>
+        <v>17056</v>
       </c>
     </row>
     <row r="1206">
@@ -54605,7 +54605,7 @@
         <v>29387.75</v>
       </c>
       <c r="F1206" t="n">
-        <v>17046.5</v>
+        <v>17078</v>
       </c>
     </row>
     <row r="1207">
@@ -54625,7 +54625,7 @@
         <v>29428.5</v>
       </c>
       <c r="F1207" t="n">
-        <v>17070</v>
+        <v>17101.5</v>
       </c>
     </row>
     <row r="1208">
@@ -54645,7 +54645,7 @@
         <v>29471.75</v>
       </c>
       <c r="F1208" t="n">
-        <v>17093.5</v>
+        <v>17125</v>
       </c>
     </row>
     <row r="1209">
@@ -54665,7 +54665,7 @@
         <v>29508.25</v>
       </c>
       <c r="F1209" t="n">
-        <v>17117</v>
+        <v>17148.5</v>
       </c>
     </row>
     <row r="1210">
@@ -54685,7 +54685,7 @@
         <v>29553.25</v>
       </c>
       <c r="F1210" t="n">
-        <v>17140.5</v>
+        <v>17172</v>
       </c>
     </row>
     <row r="1211">
@@ -54705,7 +54705,7 @@
         <v>29584.5</v>
       </c>
       <c r="F1211" t="n">
-        <v>17161</v>
+        <v>17192.5</v>
       </c>
     </row>
     <row r="1212">
@@ -54725,7 +54725,7 @@
         <v>29629</v>
       </c>
       <c r="F1212" t="n">
-        <v>17181.5</v>
+        <v>17213</v>
       </c>
     </row>
     <row r="1213">
@@ -54745,7 +54745,7 @@
         <v>29673.5</v>
       </c>
       <c r="F1213" t="n">
-        <v>17205</v>
+        <v>17236.5</v>
       </c>
     </row>
     <row r="1214">
@@ -54765,7 +54765,7 @@
         <v>29718.5</v>
       </c>
       <c r="F1214" t="n">
-        <v>17228.5</v>
+        <v>17260</v>
       </c>
     </row>
     <row r="1215">
@@ -54785,7 +54785,7 @@
         <v>29753.75</v>
       </c>
       <c r="F1215" t="n">
-        <v>17250.5</v>
+        <v>17282</v>
       </c>
     </row>
     <row r="1216">
@@ -54805,7 +54805,7 @@
         <v>29797.5</v>
       </c>
       <c r="F1216" t="n">
-        <v>17272.5</v>
+        <v>17304</v>
       </c>
     </row>
     <row r="1217">
@@ -54825,7 +54825,7 @@
         <v>29842</v>
       </c>
       <c r="F1217" t="n">
-        <v>17294.5</v>
+        <v>17326</v>
       </c>
     </row>
     <row r="1218">
@@ -54845,7 +54845,7 @@
         <v>29881.5</v>
       </c>
       <c r="F1218" t="n">
-        <v>17318</v>
+        <v>17349.5</v>
       </c>
     </row>
     <row r="1219">
@@ -54865,7 +54865,7 @@
         <v>29924.75</v>
       </c>
       <c r="F1219" t="n">
-        <v>17340</v>
+        <v>17371.5</v>
       </c>
     </row>
     <row r="1220">
@@ -54885,7 +54885,7 @@
         <v>29968</v>
       </c>
       <c r="F1220" t="n">
-        <v>17363.5</v>
+        <v>17395</v>
       </c>
     </row>
     <row r="1221">
@@ -54905,7 +54905,7 @@
         <v>30011.25</v>
       </c>
       <c r="F1221" t="n">
-        <v>17385.5</v>
+        <v>17417</v>
       </c>
     </row>
     <row r="1222">
@@ -54925,7 +54925,7 @@
         <v>30055.75</v>
       </c>
       <c r="F1222" t="n">
-        <v>17407.5</v>
+        <v>17439</v>
       </c>
     </row>
     <row r="1223">
@@ -54945,7 +54945,7 @@
         <v>30099</v>
       </c>
       <c r="F1223" t="n">
-        <v>17429.5</v>
+        <v>17461</v>
       </c>
     </row>
     <row r="1224">
@@ -54965,7 +54965,7 @@
         <v>30141</v>
       </c>
       <c r="F1224" t="n">
-        <v>17451.5</v>
+        <v>17483</v>
       </c>
     </row>
     <row r="1225">
@@ -54985,7 +54985,7 @@
         <v>30183.5</v>
       </c>
       <c r="F1225" t="n">
-        <v>17475</v>
+        <v>17506.5</v>
       </c>
     </row>
     <row r="1226">
@@ -55005,7 +55005,7 @@
         <v>30226.75</v>
       </c>
       <c r="F1226" t="n">
-        <v>17497</v>
+        <v>17528.5</v>
       </c>
     </row>
     <row r="1227">
@@ -55025,7 +55025,7 @@
         <v>30273.75</v>
       </c>
       <c r="F1227" t="n">
-        <v>17519</v>
+        <v>17550.5</v>
       </c>
     </row>
     <row r="1228">
@@ -55045,7 +55045,7 @@
         <v>30320.75</v>
       </c>
       <c r="F1228" t="n">
-        <v>17542.5</v>
+        <v>17574</v>
       </c>
     </row>
     <row r="1229">
@@ -55065,7 +55065,7 @@
         <v>30362</v>
       </c>
       <c r="F1229" t="n">
-        <v>17566</v>
+        <v>17597.5</v>
       </c>
     </row>
     <row r="1230">
@@ -55085,7 +55085,7 @@
         <v>30406.5</v>
       </c>
       <c r="F1230" t="n">
-        <v>17589.5</v>
+        <v>17621</v>
       </c>
     </row>
     <row r="1231">
@@ -55105,7 +55105,7 @@
         <v>30447.25</v>
       </c>
       <c r="F1231" t="n">
-        <v>17613</v>
+        <v>17644.5</v>
       </c>
     </row>
     <row r="1232">
@@ -55125,7 +55125,7 @@
         <v>30491</v>
       </c>
       <c r="F1232" t="n">
-        <v>17636.5</v>
+        <v>17668</v>
       </c>
     </row>
     <row r="1233">
@@ -55145,7 +55145,7 @@
         <v>30536.75</v>
       </c>
       <c r="F1233" t="n">
-        <v>17660</v>
+        <v>17691.5</v>
       </c>
     </row>
     <row r="1234">
@@ -55165,7 +55165,7 @@
         <v>30580</v>
       </c>
       <c r="F1234" t="n">
-        <v>17683.5</v>
+        <v>17715</v>
       </c>
     </row>
     <row r="1235">
@@ -55185,7 +55185,7 @@
         <v>30625.75</v>
       </c>
       <c r="F1235" t="n">
-        <v>17705.5</v>
+        <v>17737</v>
       </c>
     </row>
     <row r="1236">
@@ -55205,7 +55205,7 @@
         <v>30667.75</v>
       </c>
       <c r="F1236" t="n">
-        <v>17729</v>
+        <v>17760.5</v>
       </c>
     </row>
     <row r="1237">
@@ -55225,7 +55225,7 @@
         <v>30712.25</v>
       </c>
       <c r="F1237" t="n">
-        <v>17752.5</v>
+        <v>17784</v>
       </c>
     </row>
     <row r="1238">
@@ -55245,7 +55245,7 @@
         <v>30751.5</v>
       </c>
       <c r="F1238" t="n">
-        <v>17774.5</v>
+        <v>17806</v>
       </c>
     </row>
     <row r="1239">
@@ -55265,7 +55265,7 @@
         <v>30792.75</v>
       </c>
       <c r="F1239" t="n">
-        <v>17796.5</v>
+        <v>17828</v>
       </c>
     </row>
     <row r="1240">
@@ -55285,7 +55285,7 @@
         <v>30839.75</v>
       </c>
       <c r="F1240" t="n">
-        <v>17817</v>
+        <v>17848.5</v>
       </c>
     </row>
     <row r="1241">
@@ -55305,7 +55305,7 @@
         <v>30882.25</v>
       </c>
       <c r="F1241" t="n">
-        <v>17840.5</v>
+        <v>17872</v>
       </c>
     </row>
     <row r="1242">
@@ -55325,7 +55325,7 @@
         <v>30921.75</v>
       </c>
       <c r="F1242" t="n">
-        <v>17862.5</v>
+        <v>17894</v>
       </c>
     </row>
     <row r="1243">
@@ -55345,7 +55345,7 @@
         <v>30961.5</v>
       </c>
       <c r="F1243" t="n">
-        <v>17886</v>
+        <v>17917.5</v>
       </c>
     </row>
     <row r="1244">
@@ -55365,7 +55365,7 @@
         <v>30995</v>
       </c>
       <c r="F1244" t="n">
-        <v>17909.5</v>
+        <v>17941</v>
       </c>
     </row>
     <row r="1245">
@@ -55385,7 +55385,7 @@
         <v>31038.75</v>
       </c>
       <c r="F1245" t="n">
-        <v>17933</v>
+        <v>17964.5</v>
       </c>
     </row>
     <row r="1246">
@@ -55405,7 +55405,7 @@
         <v>31084.5</v>
       </c>
       <c r="F1246" t="n">
-        <v>17956.5</v>
+        <v>17988</v>
       </c>
     </row>
     <row r="1247">
@@ -55425,7 +55425,7 @@
         <v>31129</v>
       </c>
       <c r="F1247" t="n">
-        <v>17978.5</v>
+        <v>18010</v>
       </c>
     </row>
     <row r="1248">
@@ -55445,7 +55445,7 @@
         <v>31174.75</v>
       </c>
       <c r="F1248" t="n">
-        <v>18000.5</v>
+        <v>18032</v>
       </c>
     </row>
     <row r="1249">
@@ -55465,7 +55465,7 @@
         <v>31220.5</v>
       </c>
       <c r="F1249" t="n">
-        <v>18024</v>
+        <v>18055.5</v>
       </c>
     </row>
     <row r="1250">
@@ -55485,7 +55485,7 @@
         <v>31242.25</v>
       </c>
       <c r="F1250" t="n">
-        <v>18047.5</v>
+        <v>18079</v>
       </c>
     </row>
     <row r="1251">
@@ -55505,7 +55505,7 @@
         <v>31289.25</v>
       </c>
       <c r="F1251" t="n">
-        <v>18069.5</v>
+        <v>18101</v>
       </c>
     </row>
     <row r="1252">
@@ -55525,7 +55525,7 @@
         <v>31335</v>
       </c>
       <c r="F1252" t="n">
-        <v>18093</v>
+        <v>18124.5</v>
       </c>
     </row>
     <row r="1253">
@@ -55545,7 +55545,7 @@
         <v>31380</v>
       </c>
       <c r="F1253" t="n">
-        <v>18115</v>
+        <v>18146.5</v>
       </c>
     </row>
     <row r="1254">
@@ -55565,7 +55565,7 @@
         <v>31425.75</v>
       </c>
       <c r="F1254" t="n">
-        <v>18137</v>
+        <v>18168.5</v>
       </c>
     </row>
     <row r="1255">
@@ -55585,7 +55585,7 @@
         <v>31466.25</v>
       </c>
       <c r="F1255" t="n">
-        <v>18157.5</v>
+        <v>18189</v>
       </c>
     </row>
     <row r="1256">
@@ -55605,7 +55605,7 @@
         <v>31512</v>
       </c>
       <c r="F1256" t="n">
-        <v>18181</v>
+        <v>18212.5</v>
       </c>
     </row>
     <row r="1257">
@@ -55625,7 +55625,7 @@
         <v>31559</v>
       </c>
       <c r="F1257" t="n">
-        <v>18204.5</v>
+        <v>18236</v>
       </c>
     </row>
     <row r="1258">
@@ -55645,7 +55645,7 @@
         <v>31602.25</v>
       </c>
       <c r="F1258" t="n">
-        <v>18228</v>
+        <v>18259.5</v>
       </c>
     </row>
     <row r="1259">
@@ -55665,7 +55665,7 @@
         <v>31646</v>
       </c>
       <c r="F1259" t="n">
-        <v>18250</v>
+        <v>18281.5</v>
       </c>
     </row>
     <row r="1260">
@@ -55685,7 +55685,7 @@
         <v>31693</v>
       </c>
       <c r="F1260" t="n">
-        <v>18273.5</v>
+        <v>18305</v>
       </c>
     </row>
     <row r="1261">
@@ -55705,7 +55705,7 @@
         <v>31736.75</v>
       </c>
       <c r="F1261" t="n">
-        <v>18295.5</v>
+        <v>18327</v>
       </c>
     </row>
     <row r="1262">
@@ -55725,7 +55725,7 @@
         <v>31772.5</v>
       </c>
       <c r="F1262" t="n">
-        <v>18317.5</v>
+        <v>18349</v>
       </c>
     </row>
     <row r="1263">
@@ -55745,7 +55745,7 @@
         <v>31818.25</v>
       </c>
       <c r="F1263" t="n">
-        <v>18341</v>
+        <v>18372.5</v>
       </c>
     </row>
     <row r="1264">
@@ -55765,7 +55765,7 @@
         <v>31862.75</v>
       </c>
       <c r="F1264" t="n">
-        <v>18364.5</v>
+        <v>18396</v>
       </c>
     </row>
     <row r="1265">
@@ -55785,7 +55785,7 @@
         <v>31907.25</v>
       </c>
       <c r="F1265" t="n">
-        <v>18388</v>
+        <v>18419.5</v>
       </c>
     </row>
     <row r="1266">
@@ -55805,7 +55805,7 @@
         <v>31953</v>
       </c>
       <c r="F1266" t="n">
-        <v>18411.5</v>
+        <v>18443</v>
       </c>
     </row>
     <row r="1267">
@@ -55825,7 +55825,7 @@
         <v>31998.75</v>
       </c>
       <c r="F1267" t="n">
-        <v>18435</v>
+        <v>18466.5</v>
       </c>
     </row>
     <row r="1268">
@@ -55845,7 +55845,7 @@
         <v>32043.25</v>
       </c>
       <c r="F1268" t="n">
-        <v>18458.5</v>
+        <v>18490</v>
       </c>
     </row>
     <row r="1269">
@@ -55865,7 +55865,7 @@
         <v>32089</v>
       </c>
       <c r="F1269" t="n">
-        <v>18480.5</v>
+        <v>18512</v>
       </c>
     </row>
     <row r="1270">
@@ -55885,7 +55885,7 @@
         <v>32132.25</v>
       </c>
       <c r="F1270" t="n">
-        <v>18502.5</v>
+        <v>18534</v>
       </c>
     </row>
     <row r="1271">
@@ -55905,7 +55905,7 @@
         <v>32173</v>
       </c>
       <c r="F1271" t="n">
-        <v>18526</v>
+        <v>18557.5</v>
       </c>
     </row>
     <row r="1272">
@@ -55925,7 +55925,7 @@
         <v>32214.75</v>
       </c>
       <c r="F1272" t="n">
-        <v>18548</v>
+        <v>18579.5</v>
       </c>
     </row>
     <row r="1273">
@@ -55945,7 +55945,7 @@
         <v>32257.25</v>
       </c>
       <c r="F1273" t="n">
-        <v>18571.5</v>
+        <v>18603</v>
       </c>
     </row>
     <row r="1274">
@@ -55965,7 +55965,7 @@
         <v>32294.5</v>
       </c>
       <c r="F1274" t="n">
-        <v>18595</v>
+        <v>18626.5</v>
       </c>
     </row>
     <row r="1275">
@@ -55985,7 +55985,7 @@
         <v>32341.5</v>
       </c>
       <c r="F1275" t="n">
-        <v>18615.5</v>
+        <v>18647</v>
       </c>
     </row>
     <row r="1276">
@@ -56005,7 +56005,7 @@
         <v>32382</v>
       </c>
       <c r="F1276" t="n">
-        <v>18639</v>
+        <v>18670.5</v>
       </c>
     </row>
     <row r="1277">
@@ -56025,7 +56025,7 @@
         <v>32429</v>
       </c>
       <c r="F1277" t="n">
-        <v>18661</v>
+        <v>18692.5</v>
       </c>
     </row>
     <row r="1278">
@@ -56045,7 +56045,7 @@
         <v>32474.75</v>
       </c>
       <c r="F1278" t="n">
-        <v>18684.5</v>
+        <v>18716</v>
       </c>
     </row>
     <row r="1279">
@@ -56065,7 +56065,7 @@
         <v>32521.75</v>
       </c>
       <c r="F1279" t="n">
-        <v>18708</v>
+        <v>18739.5</v>
       </c>
     </row>
     <row r="1280">
@@ -56085,7 +56085,7 @@
         <v>32565</v>
       </c>
       <c r="F1280" t="n">
-        <v>18731.5</v>
+        <v>18763</v>
       </c>
     </row>
     <row r="1281">
@@ -56105,7 +56105,7 @@
         <v>32607</v>
       </c>
       <c r="F1281" t="n">
-        <v>18755</v>
+        <v>18786.5</v>
       </c>
     </row>
     <row r="1282">
@@ -56125,7 +56125,7 @@
         <v>32652</v>
       </c>
       <c r="F1282" t="n">
-        <v>18777</v>
+        <v>18808.5</v>
       </c>
     </row>
     <row r="1283">
@@ -56145,7 +56145,7 @@
         <v>32697.75</v>
       </c>
       <c r="F1283" t="n">
-        <v>18800.5</v>
+        <v>18832</v>
       </c>
     </row>
     <row r="1284">
@@ -56165,7 +56165,7 @@
         <v>32743.5</v>
       </c>
       <c r="F1284" t="n">
-        <v>18822.5</v>
+        <v>18854</v>
       </c>
     </row>
     <row r="1285">
@@ -56185,7 +56185,7 @@
         <v>32786.75</v>
       </c>
       <c r="F1285" t="n">
-        <v>18846</v>
+        <v>18877.5</v>
       </c>
     </row>
     <row r="1286">
@@ -56205,7 +56205,7 @@
         <v>32829.25</v>
       </c>
       <c r="F1286" t="n">
-        <v>18869.5</v>
+        <v>18901</v>
       </c>
     </row>
     <row r="1287">
@@ -56225,7 +56225,7 @@
         <v>32875</v>
       </c>
       <c r="F1287" t="n">
-        <v>18891.5</v>
+        <v>18923</v>
       </c>
     </row>
     <row r="1288">
@@ -56245,7 +56245,7 @@
         <v>32918.75</v>
       </c>
       <c r="F1288" t="n">
-        <v>18913.5</v>
+        <v>18945</v>
       </c>
     </row>
     <row r="1289">
@@ -56265,7 +56265,7 @@
         <v>32961.75</v>
       </c>
       <c r="F1289" t="n">
-        <v>18937</v>
+        <v>18968.5</v>
       </c>
     </row>
     <row r="1290">
@@ -56285,7 +56285,7 @@
         <v>33006.75</v>
       </c>
       <c r="F1290" t="n">
-        <v>18959</v>
+        <v>18990.5</v>
       </c>
     </row>
     <row r="1291">
@@ -56305,7 +56305,7 @@
         <v>33051.75</v>
       </c>
       <c r="F1291" t="n">
-        <v>18982.5</v>
+        <v>19014</v>
       </c>
     </row>
     <row r="1292">
@@ -56325,7 +56325,7 @@
         <v>33097.5</v>
       </c>
       <c r="F1292" t="n">
-        <v>19004.5</v>
+        <v>19036</v>
       </c>
     </row>
     <row r="1293">
@@ -56345,7 +56345,7 @@
         <v>33138.75</v>
       </c>
       <c r="F1293" t="n">
-        <v>19028</v>
+        <v>19059.5</v>
       </c>
     </row>
     <row r="1294">
@@ -56365,7 +56365,7 @@
         <v>33184.5</v>
       </c>
       <c r="F1294" t="n">
-        <v>19051.5</v>
+        <v>19083</v>
       </c>
     </row>
     <row r="1295">
@@ -56385,7 +56385,7 @@
         <v>33229.5</v>
       </c>
       <c r="F1295" t="n">
-        <v>19075</v>
+        <v>19106.5</v>
       </c>
     </row>
     <row r="1296">
@@ -56405,7 +56405,7 @@
         <v>33276.5</v>
       </c>
       <c r="F1296" t="n">
-        <v>19097</v>
+        <v>19128.5</v>
       </c>
     </row>
     <row r="1297">
@@ -56425,7 +56425,7 @@
         <v>33321</v>
       </c>
       <c r="F1297" t="n">
-        <v>19119</v>
+        <v>19150.5</v>
       </c>
     </row>
     <row r="1298">
@@ -56445,7 +56445,7 @@
         <v>33366.75</v>
       </c>
       <c r="F1298" t="n">
-        <v>19142.5</v>
+        <v>19174</v>
       </c>
     </row>
     <row r="1299">
@@ -56465,7 +56465,7 @@
         <v>33411.25</v>
       </c>
       <c r="F1299" t="n">
-        <v>19163</v>
+        <v>19194.5</v>
       </c>
     </row>
     <row r="1300">
@@ -56485,7 +56485,7 @@
         <v>33453</v>
       </c>
       <c r="F1300" t="n">
-        <v>19186.5</v>
+        <v>19218</v>
       </c>
     </row>
     <row r="1301">
@@ -56505,7 +56505,7 @@
         <v>33496</v>
       </c>
       <c r="F1301" t="n">
-        <v>19208.5</v>
+        <v>19240</v>
       </c>
     </row>
     <row r="1302">
@@ -56525,7 +56525,7 @@
         <v>33537.25</v>
       </c>
       <c r="F1302" t="n">
-        <v>19232</v>
+        <v>19263.5</v>
       </c>
     </row>
     <row r="1303">
@@ -56545,7 +56545,7 @@
         <v>33573.25</v>
       </c>
       <c r="F1303" t="n">
-        <v>19255.5</v>
+        <v>19287</v>
       </c>
     </row>
     <row r="1304">
@@ -56565,7 +56565,7 @@
         <v>33605</v>
       </c>
       <c r="F1304" t="n">
-        <v>19279</v>
+        <v>19310.5</v>
       </c>
     </row>
     <row r="1305">
@@ -56585,7 +56585,7 @@
         <v>33649.5</v>
       </c>
       <c r="F1305" t="n">
-        <v>19302.5</v>
+        <v>19334</v>
       </c>
     </row>
     <row r="1306">
@@ -56605,7 +56605,7 @@
         <v>33692</v>
       </c>
       <c r="F1306" t="n">
-        <v>19324.5</v>
+        <v>19356</v>
       </c>
     </row>
     <row r="1307">
@@ -56625,7 +56625,7 @@
         <v>33733.25</v>
       </c>
       <c r="F1307" t="n">
-        <v>19348</v>
+        <v>19379.5</v>
       </c>
     </row>
     <row r="1308">
@@ -56645,7 +56645,7 @@
         <v>33775.75</v>
       </c>
       <c r="F1308" t="n">
-        <v>19370</v>
+        <v>19401.5</v>
       </c>
     </row>
     <row r="1309">
@@ -56665,7 +56665,7 @@
         <v>33816.75</v>
       </c>
       <c r="F1309" t="n">
-        <v>19392</v>
+        <v>19423.5</v>
       </c>
     </row>
     <row r="1310">
@@ -56685,7 +56685,7 @@
         <v>33858.5</v>
       </c>
       <c r="F1310" t="n">
-        <v>19415.5</v>
+        <v>19447</v>
       </c>
     </row>
     <row r="1311">
@@ -56705,7 +56705,7 @@
         <v>33902.25</v>
       </c>
       <c r="F1311" t="n">
-        <v>19439</v>
+        <v>19470.5</v>
       </c>
     </row>
     <row r="1312">
@@ -56725,7 +56725,7 @@
         <v>33949.25</v>
       </c>
       <c r="F1312" t="n">
-        <v>19461</v>
+        <v>19492.5</v>
       </c>
     </row>
     <row r="1313">
@@ -56745,7 +56745,7 @@
         <v>33992.5</v>
       </c>
       <c r="F1313" t="n">
-        <v>19484.5</v>
+        <v>19516</v>
       </c>
     </row>
     <row r="1314">
@@ -56765,7 +56765,7 @@
         <v>34026.5</v>
       </c>
       <c r="F1314" t="n">
-        <v>19508</v>
+        <v>19539.5</v>
       </c>
     </row>
     <row r="1315">
@@ -56785,7 +56785,7 @@
         <v>34069</v>
       </c>
       <c r="F1315" t="n">
-        <v>19530</v>
+        <v>19561.5</v>
       </c>
     </row>
     <row r="1316">
@@ -56805,7 +56805,7 @@
         <v>34082</v>
       </c>
       <c r="F1316" t="n">
-        <v>19553.5</v>
+        <v>19585</v>
       </c>
     </row>
     <row r="1317">
@@ -56825,7 +56825,7 @@
         <v>34129</v>
       </c>
       <c r="F1317" t="n">
-        <v>19577</v>
+        <v>19608.5</v>
       </c>
     </row>
     <row r="1318">
@@ -56845,7 +56845,7 @@
         <v>34154.25</v>
       </c>
       <c r="F1318" t="n">
-        <v>19593</v>
+        <v>19630.5</v>
       </c>
     </row>
     <row r="1319">
@@ -56865,7 +56865,7 @@
         <v>34182.25</v>
       </c>
       <c r="F1319" t="n">
-        <v>19616.5</v>
+        <v>19649.5</v>
       </c>
     </row>
     <row r="1320">
@@ -56885,7 +56885,7 @@
         <v>34213.75</v>
       </c>
       <c r="F1320" t="n">
-        <v>19637</v>
+        <v>19668.5</v>
       </c>
     </row>
     <row r="1321">
@@ -56905,7 +56905,7 @@
         <v>34246.75</v>
       </c>
       <c r="F1321" t="n">
-        <v>19659</v>
+        <v>19690.5</v>
       </c>
     </row>
     <row r="1322">
@@ -56925,7 +56925,7 @@
         <v>34250.25</v>
       </c>
       <c r="F1322" t="n">
-        <v>19678</v>
+        <v>19703.5</v>
       </c>
     </row>
     <row r="1323">
@@ -56945,7 +56945,7 @@
         <v>34275</v>
       </c>
       <c r="F1323" t="n">
-        <v>19695.5</v>
+        <v>19718</v>
       </c>
     </row>
     <row r="1324">
@@ -56965,7 +56965,7 @@
         <v>34315</v>
       </c>
       <c r="F1324" t="n">
-        <v>19714.5</v>
+        <v>19737</v>
       </c>
     </row>
     <row r="1325">
@@ -56985,7 +56985,7 @@
         <v>34356.75</v>
       </c>
       <c r="F1325" t="n">
-        <v>19736.5</v>
+        <v>19759</v>
       </c>
     </row>
     <row r="1326">
@@ -57005,7 +57005,7 @@
         <v>34397.75</v>
       </c>
       <c r="F1326" t="n">
-        <v>19760</v>
+        <v>19782.5</v>
       </c>
     </row>
     <row r="1327">
@@ -57025,7 +57025,7 @@
         <v>34441.5</v>
       </c>
       <c r="F1327" t="n">
-        <v>19782</v>
+        <v>19804.5</v>
       </c>
     </row>
     <row r="1328">
@@ -57045,7 +57045,7 @@
         <v>34482.5</v>
       </c>
       <c r="F1328" t="n">
-        <v>19805.5</v>
+        <v>19828</v>
       </c>
     </row>
     <row r="1329">
@@ -57065,7 +57065,7 @@
         <v>34522.25</v>
       </c>
       <c r="F1329" t="n">
-        <v>19829</v>
+        <v>19851.5</v>
       </c>
     </row>
     <row r="1330">
@@ -57085,7 +57085,7 @@
         <v>34560.75</v>
       </c>
       <c r="F1330" t="n">
-        <v>19852.5</v>
+        <v>19875</v>
       </c>
     </row>
     <row r="1331">
@@ -57105,7 +57105,7 @@
         <v>34590.5</v>
       </c>
       <c r="F1331" t="n">
-        <v>19876</v>
+        <v>19898.5</v>
       </c>
     </row>
     <row r="1332">
@@ -57125,7 +57125,7 @@
         <v>34631</v>
       </c>
       <c r="F1332" t="n">
-        <v>19899.5</v>
+        <v>19922</v>
       </c>
     </row>
     <row r="1333">
@@ -57145,7 +57145,7 @@
         <v>34674.75</v>
       </c>
       <c r="F1333" t="n">
-        <v>19921.5</v>
+        <v>19944</v>
       </c>
     </row>
     <row r="1334">
@@ -57165,7 +57165,7 @@
         <v>34715.75</v>
       </c>
       <c r="F1334" t="n">
-        <v>19942</v>
+        <v>19964.5</v>
       </c>
     </row>
     <row r="1335">
@@ -57185,7 +57185,7 @@
         <v>34757.5</v>
       </c>
       <c r="F1335" t="n">
-        <v>19964</v>
+        <v>19986.5</v>
       </c>
     </row>
     <row r="1336">
@@ -57205,7 +57205,7 @@
         <v>34784</v>
       </c>
       <c r="F1336" t="n">
-        <v>19986</v>
+        <v>20008.5</v>
       </c>
     </row>
     <row r="1337">
@@ -57225,7 +57225,7 @@
         <v>34820.5</v>
       </c>
       <c r="F1337" t="n">
-        <v>20009.5</v>
+        <v>20032</v>
       </c>
     </row>
     <row r="1338">
@@ -57245,7 +57245,7 @@
         <v>34862.25</v>
       </c>
       <c r="F1338" t="n">
-        <v>20031.5</v>
+        <v>20054</v>
       </c>
     </row>
     <row r="1339">
@@ -57265,7 +57265,7 @@
         <v>34898</v>
       </c>
       <c r="F1339" t="n">
-        <v>20053.5</v>
+        <v>20076</v>
       </c>
     </row>
     <row r="1340">
@@ -57285,7 +57285,7 @@
         <v>34933.75</v>
       </c>
       <c r="F1340" t="n">
-        <v>20075.5</v>
+        <v>20098</v>
       </c>
     </row>
     <row r="1341">
@@ -57305,7 +57305,7 @@
         <v>34974.25</v>
       </c>
       <c r="F1341" t="n">
-        <v>20097.5</v>
+        <v>20120</v>
       </c>
     </row>
     <row r="1342">
@@ -57325,7 +57325,7 @@
         <v>35014.75</v>
       </c>
       <c r="F1342" t="n">
-        <v>20121</v>
+        <v>20143.5</v>
       </c>
     </row>
     <row r="1343">
@@ -57345,7 +57345,7 @@
         <v>35049.25</v>
       </c>
       <c r="F1343" t="n">
-        <v>20143</v>
+        <v>20167</v>
       </c>
     </row>
     <row r="1344">
@@ -57365,7 +57365,7 @@
         <v>35094.25</v>
       </c>
       <c r="F1344" t="n">
-        <v>20166.5</v>
+        <v>20190.5</v>
       </c>
     </row>
     <row r="1345">
@@ -57385,7 +57385,7 @@
         <v>35129.25</v>
       </c>
       <c r="F1345" t="n">
-        <v>20188.5</v>
+        <v>20212.5</v>
       </c>
     </row>
     <row r="1346">
@@ -57405,7 +57405,7 @@
         <v>35165.25</v>
       </c>
       <c r="F1346" t="n">
-        <v>20212</v>
+        <v>20233</v>
       </c>
     </row>
     <row r="1347">
@@ -57425,7 +57425,7 @@
         <v>35203.75</v>
       </c>
       <c r="F1347" t="n">
-        <v>20235.5</v>
+        <v>20256.5</v>
       </c>
     </row>
     <row r="1348">
@@ -57445,7 +57445,7 @@
         <v>35243.5</v>
       </c>
       <c r="F1348" t="n">
-        <v>20259</v>
+        <v>20280</v>
       </c>
     </row>
     <row r="1349">
@@ -57465,7 +57465,7 @@
         <v>35276.75</v>
       </c>
       <c r="F1349" t="n">
-        <v>20282.5</v>
+        <v>20303.5</v>
       </c>
     </row>
     <row r="1350">
@@ -57485,7 +57485,7 @@
         <v>35315.75</v>
       </c>
       <c r="F1350" t="n">
-        <v>20306</v>
+        <v>20327</v>
       </c>
     </row>
     <row r="1351">
@@ -57505,7 +57505,7 @@
         <v>35357</v>
       </c>
       <c r="F1351" t="n">
-        <v>20326.5</v>
+        <v>20347.5</v>
       </c>
     </row>
     <row r="1352">
@@ -57525,7 +57525,7 @@
         <v>35396.25</v>
       </c>
       <c r="F1352" t="n">
-        <v>20344</v>
+        <v>20369.5</v>
       </c>
     </row>
     <row r="1353">
@@ -57545,7 +57545,7 @@
         <v>35436.25</v>
       </c>
       <c r="F1353" t="n">
-        <v>20367.5</v>
+        <v>20393</v>
       </c>
     </row>
     <row r="1354">
@@ -57565,7 +57565,7 @@
         <v>35476</v>
       </c>
       <c r="F1354" t="n">
-        <v>20391</v>
+        <v>20416.5</v>
       </c>
     </row>
     <row r="1355">
@@ -57585,7 +57585,7 @@
         <v>35518</v>
       </c>
       <c r="F1355" t="n">
-        <v>20414.5</v>
+        <v>20440</v>
       </c>
     </row>
     <row r="1356">
@@ -57605,7 +57605,7 @@
         <v>35560.5</v>
       </c>
       <c r="F1356" t="n">
-        <v>20436.5</v>
+        <v>20462</v>
       </c>
     </row>
     <row r="1357">
@@ -57625,7 +57625,7 @@
         <v>35605</v>
       </c>
       <c r="F1357" t="n">
-        <v>20457</v>
+        <v>20482.5</v>
       </c>
     </row>
     <row r="1358">
@@ -57645,7 +57645,7 @@
         <v>35633.75</v>
       </c>
       <c r="F1358" t="n">
-        <v>20479</v>
+        <v>20504.5</v>
       </c>
     </row>
     <row r="1359">
@@ -57665,7 +57665,7 @@
         <v>35678.75</v>
       </c>
       <c r="F1359" t="n">
-        <v>20502.5</v>
+        <v>20528</v>
       </c>
     </row>
     <row r="1360">
@@ -57685,7 +57685,7 @@
         <v>35716.5</v>
       </c>
       <c r="F1360" t="n">
-        <v>20526</v>
+        <v>20551.5</v>
       </c>
     </row>
     <row r="1361">
@@ -57705,7 +57705,7 @@
         <v>35756.25</v>
       </c>
       <c r="F1361" t="n">
-        <v>20546.5</v>
+        <v>20572</v>
       </c>
     </row>
     <row r="1362">
@@ -57725,7 +57725,7 @@
         <v>35798.75</v>
       </c>
       <c r="F1362" t="n">
-        <v>20568.5</v>
+        <v>20594</v>
       </c>
     </row>
     <row r="1363">
@@ -57745,7 +57745,7 @@
         <v>35836</v>
       </c>
       <c r="F1363" t="n">
-        <v>20590.5</v>
+        <v>20616</v>
       </c>
     </row>
     <row r="1364">
@@ -57765,7 +57765,7 @@
         <v>35867.75</v>
       </c>
       <c r="F1364" t="n">
-        <v>20614</v>
+        <v>20639.5</v>
       </c>
     </row>
     <row r="1365">
@@ -57785,7 +57785,7 @@
         <v>35905.25</v>
       </c>
       <c r="F1365" t="n">
-        <v>20637.5</v>
+        <v>20663</v>
       </c>
     </row>
     <row r="1366">
@@ -57805,7 +57805,7 @@
         <v>35937.75</v>
       </c>
       <c r="F1366" t="n">
-        <v>20661</v>
+        <v>20686.5</v>
       </c>
     </row>
     <row r="1367">
@@ -57825,7 +57825,7 @@
         <v>35975</v>
       </c>
       <c r="F1367" t="n">
-        <v>20681.5</v>
+        <v>20707</v>
       </c>
     </row>
     <row r="1368">
@@ -57845,7 +57845,7 @@
         <v>36019.5</v>
       </c>
       <c r="F1368" t="n">
-        <v>20705</v>
+        <v>20730.5</v>
       </c>
     </row>
     <row r="1369">
@@ -57865,7 +57865,7 @@
         <v>36049.25</v>
       </c>
       <c r="F1369" t="n">
-        <v>20725.5</v>
+        <v>20752.5</v>
       </c>
     </row>
     <row r="1370">
@@ -57885,7 +57885,7 @@
         <v>36080.75</v>
       </c>
       <c r="F1370" t="n">
-        <v>20749</v>
+        <v>20776</v>
       </c>
     </row>
     <row r="1371">
@@ -57905,7 +57905,7 @@
         <v>36114.5</v>
       </c>
       <c r="F1371" t="n">
-        <v>20772.5</v>
+        <v>20799.5</v>
       </c>
     </row>
     <row r="1372">
@@ -57925,7 +57925,7 @@
         <v>36127.75</v>
       </c>
       <c r="F1372" t="n">
-        <v>20796</v>
+        <v>20823</v>
       </c>
     </row>
     <row r="1373">
@@ -57945,7 +57945,7 @@
         <v>36171</v>
       </c>
       <c r="F1373" t="n">
-        <v>20819.5</v>
+        <v>20846.5</v>
       </c>
     </row>
     <row r="1374">
@@ -57965,7 +57965,7 @@
         <v>36200.25</v>
       </c>
       <c r="F1374" t="n">
-        <v>20843</v>
+        <v>20870</v>
       </c>
     </row>
     <row r="1375">
@@ -57985,7 +57985,7 @@
         <v>36208.75</v>
       </c>
       <c r="F1375" t="n">
-        <v>20866.5</v>
+        <v>20893.5</v>
       </c>
     </row>
     <row r="1376">
@@ -58005,7 +58005,7 @@
         <v>36245.25</v>
       </c>
       <c r="F1376" t="n">
-        <v>20890</v>
+        <v>20917</v>
       </c>
     </row>
     <row r="1377">
@@ -58025,7 +58025,7 @@
         <v>36288.5</v>
       </c>
       <c r="F1377" t="n">
-        <v>20913.5</v>
+        <v>20940.5</v>
       </c>
     </row>
     <row r="1378">
@@ -58045,7 +58045,7 @@
         <v>36308.5</v>
       </c>
       <c r="F1378" t="n">
-        <v>20937</v>
+        <v>20964</v>
       </c>
     </row>
     <row r="1379">
@@ -58065,7 +58065,7 @@
         <v>36349</v>
       </c>
       <c r="F1379" t="n">
-        <v>20960.5</v>
+        <v>20987.5</v>
       </c>
     </row>
     <row r="1380">
@@ -58085,7 +58085,7 @@
         <v>36389.5</v>
       </c>
       <c r="F1380" t="n">
-        <v>20984</v>
+        <v>21011</v>
       </c>
     </row>
     <row r="1381">
@@ -58105,7 +58105,7 @@
         <v>36427.25</v>
       </c>
       <c r="F1381" t="n">
-        <v>21007.5</v>
+        <v>21034.5</v>
       </c>
     </row>
     <row r="1382">
@@ -58125,7 +58125,7 @@
         <v>36458.25</v>
       </c>
       <c r="F1382" t="n">
-        <v>21031</v>
+        <v>21058</v>
       </c>
     </row>
     <row r="1383">
@@ -58145,7 +58145,7 @@
         <v>36496</v>
       </c>
       <c r="F1383" t="n">
-        <v>21054.5</v>
+        <v>21081.5</v>
       </c>
     </row>
     <row r="1384">
@@ -58165,7 +58165,7 @@
         <v>36543</v>
       </c>
       <c r="F1384" t="n">
-        <v>21078</v>
+        <v>21105</v>
       </c>
     </row>
     <row r="1385">
@@ -58185,7 +58185,7 @@
         <v>36585</v>
       </c>
       <c r="F1385" t="n">
-        <v>21101.5</v>
+        <v>21128.5</v>
       </c>
     </row>
     <row r="1386">
@@ -58205,7 +58205,7 @@
         <v>36623.25</v>
       </c>
       <c r="F1386" t="n">
-        <v>21125</v>
+        <v>21152</v>
       </c>
     </row>
     <row r="1387">
@@ -58225,7 +58225,7 @@
         <v>36661.75</v>
       </c>
       <c r="F1387" t="n">
-        <v>21147</v>
+        <v>21174</v>
       </c>
     </row>
     <row r="1388">
@@ -58245,7 +58245,7 @@
         <v>36703.75</v>
       </c>
       <c r="F1388" t="n">
-        <v>21170.5</v>
+        <v>21197.5</v>
       </c>
     </row>
     <row r="1389">
@@ -58265,7 +58265,7 @@
         <v>36748.25</v>
       </c>
       <c r="F1389" t="n">
-        <v>21194</v>
+        <v>21221</v>
       </c>
     </row>
     <row r="1390">
@@ -58285,7 +58285,7 @@
         <v>36795.25</v>
       </c>
       <c r="F1390" t="n">
-        <v>21217.5</v>
+        <v>21244.5</v>
       </c>
     </row>
     <row r="1391">
@@ -58305,7 +58305,7 @@
         <v>36839.75</v>
       </c>
       <c r="F1391" t="n">
-        <v>21241</v>
+        <v>21268</v>
       </c>
     </row>
     <row r="1392">
@@ -58325,7 +58325,7 @@
         <v>36884.25</v>
       </c>
       <c r="F1392" t="n">
-        <v>21264.5</v>
+        <v>21291.5</v>
       </c>
     </row>
     <row r="1393">
@@ -58345,7 +58345,7 @@
         <v>36898.75</v>
       </c>
       <c r="F1393" t="n">
-        <v>21288</v>
+        <v>21315</v>
       </c>
     </row>
     <row r="1394">
@@ -58365,7 +58365,7 @@
         <v>36943.25</v>
       </c>
       <c r="F1394" t="n">
-        <v>21311.5</v>
+        <v>21338.5</v>
       </c>
     </row>
     <row r="1395">
@@ -58385,7 +58385,7 @@
         <v>36989</v>
       </c>
       <c r="F1395" t="n">
-        <v>21335</v>
+        <v>21362</v>
       </c>
     </row>
     <row r="1396">
@@ -58405,7 +58405,7 @@
         <v>37029</v>
       </c>
       <c r="F1396" t="n">
-        <v>21358.5</v>
+        <v>21385.5</v>
       </c>
     </row>
     <row r="1397">
@@ -58425,7 +58425,7 @@
         <v>37072.25</v>
       </c>
       <c r="F1397" t="n">
-        <v>21382</v>
+        <v>21409</v>
       </c>
     </row>
     <row r="1398">
@@ -58445,7 +58445,7 @@
         <v>37115.5</v>
       </c>
       <c r="F1398" t="n">
-        <v>21405.5</v>
+        <v>21432.5</v>
       </c>
     </row>
     <row r="1399">
@@ -58465,7 +58465,7 @@
         <v>37158</v>
       </c>
       <c r="F1399" t="n">
-        <v>21427.5</v>
+        <v>21454.5</v>
       </c>
     </row>
     <row r="1400">
@@ -58485,7 +58485,7 @@
         <v>37203.75</v>
       </c>
       <c r="F1400" t="n">
-        <v>21451</v>
+        <v>21478</v>
       </c>
     </row>
     <row r="1401">
@@ -58505,7 +58505,7 @@
         <v>37247</v>
       </c>
       <c r="F1401" t="n">
-        <v>21474.5</v>
+        <v>21501.5</v>
       </c>
     </row>
     <row r="1402">
@@ -58525,7 +58525,7 @@
         <v>37289</v>
       </c>
       <c r="F1402" t="n">
-        <v>21498</v>
+        <v>21525</v>
       </c>
     </row>
     <row r="1403">
@@ -58545,7 +58545,7 @@
         <v>37333.5</v>
       </c>
       <c r="F1403" t="n">
-        <v>21520</v>
+        <v>21547</v>
       </c>
     </row>
     <row r="1404">
@@ -58565,7 +58565,7 @@
         <v>37379.25</v>
       </c>
       <c r="F1404" t="n">
-        <v>21543.5</v>
+        <v>21570.5</v>
       </c>
     </row>
     <row r="1405">
@@ -58585,7 +58585,7 @@
         <v>37423.75</v>
       </c>
       <c r="F1405" t="n">
-        <v>21567</v>
+        <v>21594</v>
       </c>
     </row>
     <row r="1406">
@@ -58605,7 +58605,7 @@
         <v>37463.5</v>
       </c>
       <c r="F1406" t="n">
-        <v>21589</v>
+        <v>21616</v>
       </c>
     </row>
     <row r="1407">
@@ -58625,7 +58625,7 @@
         <v>37500</v>
       </c>
       <c r="F1407" t="n">
-        <v>21612.5</v>
+        <v>21639.5</v>
       </c>
     </row>
     <row r="1408">
@@ -58645,7 +58645,7 @@
         <v>37543.25</v>
       </c>
       <c r="F1408" t="n">
-        <v>21636</v>
+        <v>21663</v>
       </c>
     </row>
     <row r="1409">
@@ -58665,7 +58665,7 @@
         <v>37582</v>
       </c>
       <c r="F1409" t="n">
-        <v>21659.5</v>
+        <v>21686.5</v>
       </c>
     </row>
     <row r="1410">
@@ -58685,7 +58685,7 @@
         <v>37626.5</v>
       </c>
       <c r="F1410" t="n">
-        <v>21683</v>
+        <v>21710</v>
       </c>
     </row>
     <row r="1411">
@@ -58705,7 +58705,7 @@
         <v>37673.5</v>
       </c>
       <c r="F1411" t="n">
-        <v>21705</v>
+        <v>21732</v>
       </c>
     </row>
     <row r="1412">
@@ -58725,7 +58725,7 @@
         <v>37719.25</v>
       </c>
       <c r="F1412" t="n">
-        <v>21728.5</v>
+        <v>21755.5</v>
       </c>
     </row>
     <row r="1413">
@@ -58745,7 +58745,7 @@
         <v>37758</v>
       </c>
       <c r="F1413" t="n">
-        <v>21752</v>
+        <v>21779</v>
       </c>
     </row>
     <row r="1414">
@@ -58765,7 +58765,7 @@
         <v>37802.5</v>
       </c>
       <c r="F1414" t="n">
-        <v>21775.5</v>
+        <v>21802.5</v>
       </c>
     </row>
     <row r="1415">
@@ -58785,7 +58785,7 @@
         <v>37849.5</v>
       </c>
       <c r="F1415" t="n">
-        <v>21799</v>
+        <v>21826</v>
       </c>
     </row>
     <row r="1416">
@@ -58805,7 +58805,7 @@
         <v>37892.75</v>
       </c>
       <c r="F1416" t="n">
-        <v>21822.5</v>
+        <v>21849.5</v>
       </c>
     </row>
     <row r="1417">
@@ -58825,7 +58825,7 @@
         <v>37933.5</v>
       </c>
       <c r="F1417" t="n">
-        <v>21846</v>
+        <v>21873</v>
       </c>
     </row>
     <row r="1418">
@@ -58845,7 +58845,7 @@
         <v>37976.75</v>
       </c>
       <c r="F1418" t="n">
-        <v>21869.5</v>
+        <v>21896.5</v>
       </c>
     </row>
     <row r="1419">
@@ -58865,7 +58865,7 @@
         <v>38021.25</v>
       </c>
       <c r="F1419" t="n">
-        <v>21893</v>
+        <v>21920</v>
       </c>
     </row>
     <row r="1420">
@@ -58885,7 +58885,7 @@
         <v>38064.25</v>
       </c>
       <c r="F1420" t="n">
-        <v>21915</v>
+        <v>21942</v>
       </c>
     </row>
     <row r="1421">
@@ -58905,7 +58905,7 @@
         <v>38056.25</v>
       </c>
       <c r="F1421" t="n">
-        <v>21937</v>
+        <v>21964</v>
       </c>
     </row>
     <row r="1422">
@@ -58925,7 +58925,7 @@
         <v>38094</v>
       </c>
       <c r="F1422" t="n">
-        <v>21959</v>
+        <v>21986</v>
       </c>
     </row>
     <row r="1423">
@@ -58945,7 +58945,7 @@
         <v>38116.75</v>
       </c>
       <c r="F1423" t="n">
-        <v>21979.5</v>
+        <v>22009.5</v>
       </c>
     </row>
     <row r="1424">
@@ -58965,7 +58965,7 @@
         <v>38155.75</v>
       </c>
       <c r="F1424" t="n">
-        <v>21997</v>
+        <v>22030</v>
       </c>
     </row>
     <row r="1425">
@@ -58985,7 +58985,7 @@
         <v>38200.75</v>
       </c>
       <c r="F1425" t="n">
-        <v>22020.5</v>
+        <v>22053.5</v>
       </c>
     </row>
     <row r="1426">
@@ -59005,7 +59005,7 @@
         <v>38243.75</v>
       </c>
       <c r="F1426" t="n">
-        <v>22044</v>
+        <v>22077</v>
       </c>
     </row>
     <row r="1427">
@@ -59025,7 +59025,7 @@
         <v>38287</v>
       </c>
       <c r="F1427" t="n">
-        <v>22066</v>
+        <v>22099</v>
       </c>
     </row>
     <row r="1428">
@@ -59045,7 +59045,7 @@
         <v>38323.5</v>
       </c>
       <c r="F1428" t="n">
-        <v>22089.5</v>
+        <v>22122.5</v>
       </c>
     </row>
     <row r="1429">
@@ -59065,7 +59065,7 @@
         <v>38360.5</v>
       </c>
       <c r="F1429" t="n">
-        <v>22113</v>
+        <v>22146</v>
       </c>
     </row>
     <row r="1430">
@@ -59085,7 +59085,7 @@
         <v>38405.5</v>
       </c>
       <c r="F1430" t="n">
-        <v>22136.5</v>
+        <v>22169.5</v>
       </c>
     </row>
     <row r="1431">
@@ -59105,7 +59105,7 @@
         <v>38451.25</v>
       </c>
       <c r="F1431" t="n">
-        <v>22160</v>
+        <v>22193</v>
       </c>
     </row>
     <row r="1432">
@@ -59125,7 +59125,7 @@
         <v>38491.75</v>
       </c>
       <c r="F1432" t="n">
-        <v>22182</v>
+        <v>22213.5</v>
       </c>
     </row>
     <row r="1433">
@@ -59145,7 +59145,7 @@
         <v>38530.25</v>
       </c>
       <c r="F1433" t="n">
-        <v>22205.5</v>
+        <v>22235.5</v>
       </c>
     </row>
     <row r="1434">
@@ -59165,7 +59165,7 @@
         <v>38572.75</v>
       </c>
       <c r="F1434" t="n">
-        <v>22226</v>
+        <v>22257.5</v>
       </c>
     </row>
     <row r="1435">
@@ -59185,7 +59185,7 @@
         <v>38603</v>
       </c>
       <c r="F1435" t="n">
-        <v>22246.5</v>
+        <v>22278</v>
       </c>
     </row>
     <row r="1436">
@@ -59205,7 +59205,7 @@
         <v>38637</v>
       </c>
       <c r="F1436" t="n">
-        <v>22270</v>
+        <v>22301.5</v>
       </c>
     </row>
     <row r="1437">
@@ -59225,7 +59225,7 @@
         <v>38684</v>
       </c>
       <c r="F1437" t="n">
-        <v>22293.5</v>
+        <v>22325</v>
       </c>
     </row>
     <row r="1438">
@@ -59245,7 +59245,7 @@
         <v>38721.25</v>
       </c>
       <c r="F1438" t="n">
-        <v>22317</v>
+        <v>22348.5</v>
       </c>
     </row>
     <row r="1439">
@@ -59265,7 +59265,7 @@
         <v>38748.25</v>
       </c>
       <c r="F1439" t="n">
-        <v>22340.5</v>
+        <v>22372</v>
       </c>
     </row>
     <row r="1440">
@@ -59285,7 +59285,7 @@
         <v>38785.5</v>
       </c>
       <c r="F1440" t="n">
-        <v>22364</v>
+        <v>22395.5</v>
       </c>
     </row>
     <row r="1441">
@@ -59305,7 +59305,7 @@
         <v>38820</v>
       </c>
       <c r="F1441" t="n">
-        <v>22387.5</v>
+        <v>22419</v>
       </c>
     </row>
     <row r="1442">
@@ -59325,7 +59325,7 @@
         <v>38860.5</v>
       </c>
       <c r="F1442" t="n">
-        <v>22409.5</v>
+        <v>22441</v>
       </c>
     </row>
     <row r="1443">
@@ -59345,7 +59345,7 @@
         <v>38890.5</v>
       </c>
       <c r="F1443" t="n">
-        <v>22433</v>
+        <v>22464.5</v>
       </c>
     </row>
     <row r="1444">
@@ -59365,7 +59365,7 @@
         <v>38923</v>
       </c>
       <c r="F1444" t="n">
-        <v>22456.5</v>
+        <v>22488</v>
       </c>
     </row>
     <row r="1445">
@@ -59385,7 +59385,7 @@
         <v>38958.75</v>
       </c>
       <c r="F1445" t="n">
-        <v>22480</v>
+        <v>22511.5</v>
       </c>
     </row>
     <row r="1446">
@@ -59405,7 +59405,7 @@
         <v>39000.5</v>
       </c>
       <c r="F1446" t="n">
-        <v>22502</v>
+        <v>22533.5</v>
       </c>
     </row>
     <row r="1447">
@@ -59425,7 +59425,7 @@
         <v>39047.5</v>
       </c>
       <c r="F1447" t="n">
-        <v>22525.5</v>
+        <v>22557</v>
       </c>
     </row>
     <row r="1448">
@@ -59445,7 +59445,7 @@
         <v>39089.25</v>
       </c>
       <c r="F1448" t="n">
-        <v>22549</v>
+        <v>22580.5</v>
       </c>
     </row>
     <row r="1449">
@@ -59465,7 +59465,7 @@
         <v>39124</v>
       </c>
       <c r="F1449" t="n">
-        <v>22572.5</v>
+        <v>22604</v>
       </c>
     </row>
     <row r="1450">
@@ -59485,7 +59485,7 @@
         <v>39157</v>
       </c>
       <c r="F1450" t="n">
-        <v>22596</v>
+        <v>22627.5</v>
       </c>
     </row>
     <row r="1451">
@@ -59505,7 +59505,7 @@
         <v>39189</v>
       </c>
       <c r="F1451" t="n">
-        <v>22619.5</v>
+        <v>22651</v>
       </c>
     </row>
     <row r="1452">
@@ -59525,7 +59525,7 @@
         <v>39232.25</v>
       </c>
       <c r="F1452" t="n">
-        <v>22643</v>
+        <v>22674.5</v>
       </c>
     </row>
     <row r="1453">
@@ -59545,7 +59545,7 @@
         <v>39275.25</v>
       </c>
       <c r="F1453" t="n">
-        <v>22666.5</v>
+        <v>22698</v>
       </c>
     </row>
     <row r="1454">
@@ -59565,7 +59565,7 @@
         <v>39317</v>
       </c>
       <c r="F1454" t="n">
-        <v>22690</v>
+        <v>22721.5</v>
       </c>
     </row>
     <row r="1455">
@@ -59585,7 +59585,7 @@
         <v>39350.25</v>
       </c>
       <c r="F1455" t="n">
-        <v>22712</v>
+        <v>22743.5</v>
       </c>
     </row>
     <row r="1456">
@@ -59605,7 +59605,7 @@
         <v>39389.25</v>
       </c>
       <c r="F1456" t="n">
-        <v>22734</v>
+        <v>22765.5</v>
       </c>
     </row>
     <row r="1457">
@@ -59625,7 +59625,7 @@
         <v>39427</v>
       </c>
       <c r="F1457" t="n">
-        <v>22757.5</v>
+        <v>22789</v>
       </c>
     </row>
     <row r="1458">
@@ -59645,7 +59645,7 @@
         <v>39467</v>
       </c>
       <c r="F1458" t="n">
-        <v>22781</v>
+        <v>22812.5</v>
       </c>
     </row>
     <row r="1459">
@@ -59665,7 +59665,7 @@
         <v>39506</v>
       </c>
       <c r="F1459" t="n">
-        <v>22804.5</v>
+        <v>22836</v>
       </c>
     </row>
     <row r="1460">
@@ -59685,7 +59685,7 @@
         <v>39542.5</v>
       </c>
       <c r="F1460" t="n">
-        <v>22828</v>
+        <v>22859.5</v>
       </c>
     </row>
     <row r="1461">
@@ -59705,7 +59705,7 @@
         <v>39584.5</v>
       </c>
       <c r="F1461" t="n">
-        <v>22851.5</v>
+        <v>22883</v>
       </c>
     </row>
     <row r="1462">
@@ -59725,7 +59725,7 @@
         <v>39613.5</v>
       </c>
       <c r="F1462" t="n">
-        <v>22875</v>
+        <v>22906.5</v>
       </c>
     </row>
     <row r="1463">
@@ -59745,7 +59745,7 @@
         <v>39643.75</v>
       </c>
       <c r="F1463" t="n">
-        <v>22898.5</v>
+        <v>22930</v>
       </c>
     </row>
     <row r="1464">
@@ -59765,7 +59765,7 @@
         <v>39688.25</v>
       </c>
       <c r="F1464" t="n">
-        <v>22922</v>
+        <v>22953.5</v>
       </c>
     </row>
     <row r="1465">
@@ -59785,7 +59785,7 @@
         <v>39726.25</v>
       </c>
       <c r="F1465" t="n">
-        <v>22945.5</v>
+        <v>22977</v>
       </c>
     </row>
     <row r="1466">
@@ -59805,7 +59805,7 @@
         <v>39767.25</v>
       </c>
       <c r="F1466" t="n">
-        <v>22967.5</v>
+        <v>22999</v>
       </c>
     </row>
     <row r="1467">
@@ -59825,7 +59825,7 @@
         <v>39811.75</v>
       </c>
       <c r="F1467" t="n">
-        <v>22991</v>
+        <v>23022.5</v>
       </c>
     </row>
     <row r="1468">
@@ -59845,7 +59845,7 @@
         <v>39847.5</v>
       </c>
       <c r="F1468" t="n">
-        <v>23014.5</v>
+        <v>23046</v>
       </c>
     </row>
     <row r="1469">
@@ -59865,7 +59865,7 @@
         <v>39830</v>
       </c>
       <c r="F1469" t="n">
-        <v>23038</v>
+        <v>23069.5</v>
       </c>
     </row>
     <row r="1470">
@@ -59885,7 +59885,7 @@
         <v>39867.75</v>
       </c>
       <c r="F1470" t="n">
-        <v>23058.5</v>
+        <v>23090</v>
       </c>
     </row>
     <row r="1471">
@@ -59905,7 +59905,7 @@
         <v>39888.25</v>
       </c>
       <c r="F1471" t="n">
-        <v>23082</v>
+        <v>23113.5</v>
       </c>
     </row>
     <row r="1472">
@@ -59925,7 +59925,7 @@
         <v>39929.5</v>
       </c>
       <c r="F1472" t="n">
-        <v>23105.5</v>
+        <v>23137</v>
       </c>
     </row>
     <row r="1473">
@@ -59945,7 +59945,7 @@
         <v>39971.5</v>
       </c>
       <c r="F1473" t="n">
-        <v>23129</v>
+        <v>23160.5</v>
       </c>
     </row>
     <row r="1474">
@@ -59965,7 +59965,7 @@
         <v>40000</v>
       </c>
       <c r="F1474" t="n">
-        <v>23152.5</v>
+        <v>23184</v>
       </c>
     </row>
     <row r="1475">
@@ -59985,7 +59985,7 @@
         <v>40037.75</v>
       </c>
       <c r="F1475" t="n">
-        <v>23174.5</v>
+        <v>23206</v>
       </c>
     </row>
     <row r="1476">
@@ -60005,7 +60005,7 @@
         <v>40081.5</v>
       </c>
       <c r="F1476" t="n">
-        <v>23198</v>
+        <v>23229.5</v>
       </c>
     </row>
     <row r="1477">
@@ -60025,7 +60025,7 @@
         <v>40120.75</v>
       </c>
       <c r="F1477" t="n">
-        <v>23218.5</v>
+        <v>23250</v>
       </c>
     </row>
     <row r="1478">
@@ -60045,7 +60045,7 @@
         <v>40146.75</v>
       </c>
       <c r="F1478" t="n">
-        <v>23242</v>
+        <v>23273.5</v>
       </c>
     </row>
     <row r="1479">
@@ -60065,7 +60065,7 @@
         <v>40193.75</v>
       </c>
       <c r="F1479" t="n">
-        <v>23264</v>
+        <v>23295.5</v>
       </c>
     </row>
     <row r="1480">
@@ -60085,7 +60085,7 @@
         <v>40240.75</v>
       </c>
       <c r="F1480" t="n">
-        <v>23287.5</v>
+        <v>23319</v>
       </c>
     </row>
     <row r="1481">
@@ -60105,7 +60105,7 @@
         <v>40287.75</v>
       </c>
       <c r="F1481" t="n">
-        <v>23311</v>
+        <v>23342.5</v>
       </c>
     </row>
     <row r="1482">
@@ -60125,7 +60125,7 @@
         <v>40329</v>
       </c>
       <c r="F1482" t="n">
-        <v>23334.5</v>
+        <v>23366</v>
       </c>
     </row>
     <row r="1483">
@@ -60145,7 +60145,7 @@
         <v>40356.75</v>
       </c>
       <c r="F1483" t="n">
-        <v>23358</v>
+        <v>23389.5</v>
       </c>
     </row>
     <row r="1484">
@@ -60165,7 +60165,7 @@
         <v>40400</v>
       </c>
       <c r="F1484" t="n">
-        <v>23381.5</v>
+        <v>23413</v>
       </c>
     </row>
     <row r="1485">
@@ -60185,7 +60185,7 @@
         <v>40392.75</v>
       </c>
       <c r="F1485" t="n">
-        <v>23403.5</v>
+        <v>23435</v>
       </c>
     </row>
     <row r="1486">
@@ -60205,7 +60205,7 @@
         <v>40429.75</v>
       </c>
       <c r="F1486" t="n">
-        <v>23427</v>
+        <v>23458.5</v>
       </c>
     </row>
     <row r="1487">
@@ -60225,7 +60225,7 @@
         <v>40473</v>
       </c>
       <c r="F1487" t="n">
-        <v>23447.5</v>
+        <v>23482</v>
       </c>
     </row>
     <row r="1488">
@@ -60245,7 +60245,7 @@
         <v>40509.5</v>
       </c>
       <c r="F1488" t="n">
-        <v>23471</v>
+        <v>23504</v>
       </c>
     </row>
     <row r="1489">
@@ -60265,7 +60265,7 @@
         <v>40544</v>
       </c>
       <c r="F1489" t="n">
-        <v>23494.5</v>
+        <v>23527.5</v>
       </c>
     </row>
     <row r="1490">
@@ -60285,7 +60285,7 @@
         <v>40563</v>
       </c>
       <c r="F1490" t="n">
-        <v>23518</v>
+        <v>23551</v>
       </c>
     </row>
     <row r="1491">
@@ -60305,7 +60305,7 @@
         <v>40588.75</v>
       </c>
       <c r="F1491" t="n">
-        <v>23538.5</v>
+        <v>23571.5</v>
       </c>
     </row>
     <row r="1492">
@@ -60325,7 +60325,7 @@
         <v>40633.75</v>
       </c>
       <c r="F1492" t="n">
-        <v>23559</v>
+        <v>23592</v>
       </c>
     </row>
     <row r="1493">
@@ -60345,7 +60345,7 @@
         <v>40642.5</v>
       </c>
       <c r="F1493" t="n">
-        <v>23582.5</v>
+        <v>23615.5</v>
       </c>
     </row>
     <row r="1494">
@@ -60365,7 +60365,7 @@
         <v>40657.5</v>
       </c>
       <c r="F1494" t="n">
-        <v>23606</v>
+        <v>23639</v>
       </c>
     </row>
     <row r="1495">
@@ -60385,7 +60385,7 @@
         <v>40690</v>
       </c>
       <c r="F1495" t="n">
-        <v>23629.5</v>
+        <v>23662.5</v>
       </c>
     </row>
     <row r="1496">
@@ -60405,7 +60405,7 @@
         <v>40729.25</v>
       </c>
       <c r="F1496" t="n">
-        <v>23651.5</v>
+        <v>23684.5</v>
       </c>
     </row>
     <row r="1497">
@@ -60425,7 +60425,7 @@
         <v>40752.25</v>
       </c>
       <c r="F1497" t="n">
-        <v>23675</v>
+        <v>23708</v>
       </c>
     </row>
     <row r="1498">
@@ -60445,7 +60445,7 @@
         <v>40792.75</v>
       </c>
       <c r="F1498" t="n">
-        <v>23695.5</v>
+        <v>23730</v>
       </c>
     </row>
     <row r="1499">
@@ -60465,7 +60465,7 @@
         <v>40828</v>
       </c>
       <c r="F1499" t="n">
-        <v>23719</v>
+        <v>23753.5</v>
       </c>
     </row>
     <row r="1500">
@@ -60485,7 +60485,7 @@
         <v>40850.75</v>
       </c>
       <c r="F1500" t="n">
-        <v>23741</v>
+        <v>23775.5</v>
       </c>
     </row>
     <row r="1501">
@@ -60505,7 +60505,7 @@
         <v>40890</v>
       </c>
       <c r="F1501" t="n">
-        <v>23764.5</v>
+        <v>23799</v>
       </c>
     </row>
   </sheetData>
@@ -60644,10 +60644,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.843</v>
+        <v>15.866</v>
       </c>
       <c r="C6" t="n">
-        <v>9.101000000000001</v>
+        <v>9.111000000000001</v>
       </c>
       <c r="D6" t="n">
         <v>-18.5</v>
@@ -60656,7 +60656,7 @@
         <v>23.5</v>
       </c>
       <c r="F6" t="n">
-        <v>23764.5</v>
+        <v>23799</v>
       </c>
     </row>
   </sheetData>

--- a/results/plots/agent_rewards_cumulative.xlsx
+++ b/results/plots/agent_rewards_cumulative.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:D251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,43 +443,3513 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>wind#0</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
           <t>battery#0</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>grid#0</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>load#0</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37447.52125924824</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>32084.48411535301</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>48</v>
+      </c>
+      <c r="C4" t="n">
+        <v>32707.14900149575</v>
+      </c>
+      <c r="D4" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C5" t="n">
+        <v>28552.39108416848</v>
+      </c>
+      <c r="D5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C6" t="n">
+        <v>31564.34744516323</v>
+      </c>
+      <c r="D6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>28</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30905.05364627173</v>
+      </c>
+      <c r="D7" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>26</v>
+      </c>
+      <c r="C8" t="n">
+        <v>40823.72346568709</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>36</v>
+      </c>
+      <c r="C9" t="n">
+        <v>40907.03704060733</v>
+      </c>
+      <c r="D9" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>30</v>
+      </c>
+      <c r="C10" t="n">
+        <v>42856.29459852685</v>
+      </c>
+      <c r="D10" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C11" t="n">
+        <v>38829.54115177665</v>
+      </c>
+      <c r="D11" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>40</v>
+      </c>
+      <c r="C12" t="n">
+        <v>42839.97407460878</v>
+      </c>
+      <c r="D12" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>50</v>
+      </c>
+      <c r="C13" t="n">
+        <v>44305.69811949111</v>
+      </c>
+      <c r="D13" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56</v>
+      </c>
+      <c r="C14" t="n">
+        <v>39893.26655567193</v>
+      </c>
+      <c r="D14" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>76</v>
+      </c>
+      <c r="C15" t="n">
+        <v>43187.33548977972</v>
+      </c>
+      <c r="D15" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>84</v>
+      </c>
+      <c r="C16" t="n">
+        <v>49074.53013829903</v>
+      </c>
+      <c r="D16" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>70</v>
+      </c>
+      <c r="C17" t="n">
+        <v>46769.43092141971</v>
+      </c>
+      <c r="D17" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>60</v>
+      </c>
+      <c r="C18" t="n">
+        <v>47651.33068181456</v>
+      </c>
+      <c r="D18" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>66</v>
+      </c>
+      <c r="C19" t="n">
+        <v>42834.83442807123</v>
+      </c>
+      <c r="D19" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56</v>
+      </c>
+      <c r="C20" t="n">
+        <v>43935.57829346989</v>
+      </c>
+      <c r="D20" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>88</v>
+      </c>
+      <c r="C21" t="n">
+        <v>48535.06328972657</v>
+      </c>
+      <c r="D21" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80</v>
+      </c>
+      <c r="C22" t="n">
+        <v>45527.71669088824</v>
+      </c>
+      <c r="D22" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>88</v>
+      </c>
+      <c r="C23" t="n">
+        <v>49792.19853549719</v>
+      </c>
+      <c r="D23" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106</v>
+      </c>
+      <c r="C24" t="n">
+        <v>44482.55221744867</v>
+      </c>
+      <c r="D24" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>70</v>
+      </c>
+      <c r="C25" t="n">
+        <v>51730.59996321929</v>
+      </c>
+      <c r="D25" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>104</v>
+      </c>
+      <c r="C26" t="n">
+        <v>43873.01270062249</v>
+      </c>
+      <c r="D26" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
         <v>25</v>
       </c>
-      <c r="C2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-15.09408024056189</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="B27" t="n">
+        <v>92</v>
+      </c>
+      <c r="C27" t="n">
+        <v>51900.77145106289</v>
+      </c>
+      <c r="D27" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>96</v>
+      </c>
+      <c r="C28" t="n">
+        <v>43576.43781712215</v>
+      </c>
+      <c r="D28" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>82</v>
+      </c>
+      <c r="C29" t="n">
+        <v>48738.19866300663</v>
+      </c>
+      <c r="D29" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>110</v>
+      </c>
+      <c r="C30" t="n">
+        <v>49432.99437543642</v>
+      </c>
+      <c r="D30" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>84</v>
+      </c>
+      <c r="C31" t="n">
+        <v>40292.64740287764</v>
+      </c>
+      <c r="D31" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98</v>
+      </c>
+      <c r="C32" t="n">
+        <v>54377.51103769917</v>
+      </c>
+      <c r="D32" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>122</v>
+      </c>
+      <c r="C33" t="n">
+        <v>51177.41800211072</v>
+      </c>
+      <c r="D33" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>120</v>
+      </c>
+      <c r="C34" t="n">
+        <v>49470.53995044796</v>
+      </c>
+      <c r="D34" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>130</v>
+      </c>
+      <c r="C35" t="n">
+        <v>50087.92735596791</v>
+      </c>
+      <c r="D35" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>116</v>
+      </c>
+      <c r="C36" t="n">
+        <v>47368.12376849648</v>
+      </c>
+      <c r="D36" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>102</v>
+      </c>
+      <c r="C37" t="n">
+        <v>51806.81923691716</v>
+      </c>
+      <c r="D37" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>112</v>
+      </c>
+      <c r="C38" t="n">
+        <v>48069.94627466197</v>
+      </c>
+      <c r="D38" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>128</v>
+      </c>
+      <c r="C39" t="n">
+        <v>55975.59650215632</v>
+      </c>
+      <c r="D39" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>116</v>
+      </c>
+      <c r="C40" t="n">
+        <v>46803.00287526185</v>
+      </c>
+      <c r="D40" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>136</v>
+      </c>
+      <c r="C41" t="n">
+        <v>46743.05531580098</v>
+      </c>
+      <c r="D41" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>146</v>
+      </c>
+      <c r="C42" t="n">
+        <v>50934.35990287764</v>
+      </c>
+      <c r="D42" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>150</v>
+      </c>
+      <c r="C43" t="n">
+        <v>61926.48354056172</v>
+      </c>
+      <c r="D43" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>130</v>
+      </c>
+      <c r="C44" t="n">
+        <v>47544.34871079715</v>
+      </c>
+      <c r="D44" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>114</v>
+      </c>
+      <c r="C45" t="n">
+        <v>47868.46515437337</v>
+      </c>
+      <c r="D45" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>128</v>
+      </c>
+      <c r="C46" t="n">
+        <v>59436.94876849648</v>
+      </c>
+      <c r="D46" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>130</v>
+      </c>
+      <c r="C47" t="n">
+        <v>56751.82430650708</v>
+      </c>
+      <c r="D47" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>146</v>
+      </c>
+      <c r="C48" t="n">
+        <v>63747.84251519355</v>
+      </c>
+      <c r="D48" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>132</v>
+      </c>
+      <c r="C49" t="n">
+        <v>47195.63311794976</v>
+      </c>
+      <c r="D49" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>168</v>
+      </c>
+      <c r="C50" t="n">
+        <v>50734.17705315853</v>
+      </c>
+      <c r="D50" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>126</v>
+      </c>
+      <c r="C51" t="n">
+        <v>46854.18812213348</v>
+      </c>
+      <c r="D51" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>146</v>
+      </c>
+      <c r="C52" t="n">
+        <v>52952.29597515551</v>
+      </c>
+      <c r="D52" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>130</v>
+      </c>
+      <c r="C53" t="n">
+        <v>44645.23221943042</v>
+      </c>
+      <c r="D53" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>144</v>
+      </c>
+      <c r="C54" t="n">
+        <v>47966.9082333484</v>
+      </c>
+      <c r="D54" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>166</v>
+      </c>
+      <c r="C55" t="n">
+        <v>57294.57550563385</v>
+      </c>
+      <c r="D55" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>148</v>
+      </c>
+      <c r="C56" t="n">
+        <v>56958.87561662858</v>
+      </c>
+      <c r="D56" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>148</v>
+      </c>
+      <c r="C57" t="n">
+        <v>48616.37067785105</v>
+      </c>
+      <c r="D57" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>148</v>
+      </c>
+      <c r="C58" t="n">
+        <v>46393.92924418365</v>
+      </c>
+      <c r="D58" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>150</v>
+      </c>
+      <c r="C59" t="n">
+        <v>57102.78378126786</v>
+      </c>
+      <c r="D59" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>160</v>
+      </c>
+      <c r="C60" t="n">
+        <v>50050.66281602116</v>
+      </c>
+      <c r="D60" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>152</v>
+      </c>
+      <c r="C61" t="n">
+        <v>45106.57734385713</v>
+      </c>
+      <c r="D61" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>154</v>
+      </c>
+      <c r="C62" t="n">
+        <v>50585.64907020488</v>
+      </c>
+      <c r="D62" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>152</v>
+      </c>
+      <c r="C63" t="n">
+        <v>59432.71609738024</v>
+      </c>
+      <c r="D63" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
         <v>62</v>
       </c>
-      <c r="F2" t="n">
-        <v>20.5</v>
+      <c r="B64" t="n">
+        <v>150</v>
+      </c>
+      <c r="C64" t="n">
+        <v>70207.53895304464</v>
+      </c>
+      <c r="D64" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>170</v>
+      </c>
+      <c r="C65" t="n">
+        <v>47596.01121079715</v>
+      </c>
+      <c r="D65" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>154</v>
+      </c>
+      <c r="C66" t="n">
+        <v>55632.38758962776</v>
+      </c>
+      <c r="D66" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>170</v>
+      </c>
+      <c r="C67" t="n">
+        <v>47326.26096348513</v>
+      </c>
+      <c r="D67" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>168</v>
+      </c>
+      <c r="C68" t="n">
+        <v>50934.66858350792</v>
+      </c>
+      <c r="D68" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>150</v>
+      </c>
+      <c r="C69" t="n">
+        <v>45514.98323555037</v>
+      </c>
+      <c r="D69" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>166</v>
+      </c>
+      <c r="C70" t="n">
+        <v>42399.19430452533</v>
+      </c>
+      <c r="D70" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>162</v>
+      </c>
+      <c r="C71" t="n">
+        <v>43715.38430826867</v>
+      </c>
+      <c r="D71" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>182</v>
+      </c>
+      <c r="C72" t="n">
+        <v>50876.56805870904</v>
+      </c>
+      <c r="D72" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>162</v>
+      </c>
+      <c r="C73" t="n">
+        <v>51017.60686883055</v>
+      </c>
+      <c r="D73" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>184</v>
+      </c>
+      <c r="C74" t="n">
+        <v>68690.60437609701</v>
+      </c>
+      <c r="D74" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>160</v>
+      </c>
+      <c r="C75" t="n">
+        <v>67254.38628280922</v>
+      </c>
+      <c r="D75" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>186</v>
+      </c>
+      <c r="C76" t="n">
+        <v>46885.21198400899</v>
+      </c>
+      <c r="D76" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>184</v>
+      </c>
+      <c r="C77" t="n">
+        <v>54490.70155633253</v>
+      </c>
+      <c r="D77" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>174</v>
+      </c>
+      <c r="C78" t="n">
+        <v>52370.9340686635</v>
+      </c>
+      <c r="D78" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>196</v>
+      </c>
+      <c r="C79" t="n">
+        <v>54303.78204633245</v>
+      </c>
+      <c r="D79" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>184</v>
+      </c>
+      <c r="C80" t="n">
+        <v>58159.61788230813</v>
+      </c>
+      <c r="D80" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>160</v>
+      </c>
+      <c r="C81" t="n">
+        <v>42295.94538384951</v>
+      </c>
+      <c r="D81" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>176</v>
+      </c>
+      <c r="C82" t="n">
+        <v>49706.13299594521</v>
+      </c>
+      <c r="D82" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>190</v>
+      </c>
+      <c r="C83" t="n">
+        <v>62504.64295211825</v>
+      </c>
+      <c r="D83" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>190</v>
+      </c>
+      <c r="C84" t="n">
+        <v>73080.10990618057</v>
+      </c>
+      <c r="D84" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>198</v>
+      </c>
+      <c r="C85" t="n">
+        <v>76921.19217670443</v>
+      </c>
+      <c r="D85" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>186</v>
+      </c>
+      <c r="C86" t="n">
+        <v>79523.23736103241</v>
+      </c>
+      <c r="D86" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
+        <v>166</v>
+      </c>
+      <c r="C87" t="n">
+        <v>74520.89384513265</v>
+      </c>
+      <c r="D87" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>186</v>
+      </c>
+      <c r="C88" t="n">
+        <v>56543.11597097181</v>
+      </c>
+      <c r="D88" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>170</v>
+      </c>
+      <c r="C89" t="n">
+        <v>60264.55895876974</v>
+      </c>
+      <c r="D89" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>174</v>
+      </c>
+      <c r="C90" t="n">
+        <v>55937.07972779789</v>
+      </c>
+      <c r="D90" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>192</v>
+      </c>
+      <c r="C91" t="n">
+        <v>51290.31002488216</v>
+      </c>
+      <c r="D91" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>202</v>
+      </c>
+      <c r="C92" t="n">
+        <v>50205.15567190575</v>
+      </c>
+      <c r="D92" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>190</v>
+      </c>
+      <c r="C93" t="n">
+        <v>77995.10747555031</v>
+      </c>
+      <c r="D93" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>196</v>
+      </c>
+      <c r="C94" t="n">
+        <v>73512.69270700816</v>
+      </c>
+      <c r="D94" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>210</v>
+      </c>
+      <c r="C95" t="n">
+        <v>79586.98116212587</v>
+      </c>
+      <c r="D95" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
+        <v>204</v>
+      </c>
+      <c r="C96" t="n">
+        <v>66719.35068203477</v>
+      </c>
+      <c r="D96" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>198</v>
+      </c>
+      <c r="C97" t="n">
+        <v>64925.74044287002</v>
+      </c>
+      <c r="D97" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>204</v>
+      </c>
+      <c r="C98" t="n">
+        <v>52962.33294264981</v>
+      </c>
+      <c r="D98" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>198</v>
+      </c>
+      <c r="C99" t="n">
+        <v>65064.42377950628</v>
+      </c>
+      <c r="D99" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
+        <v>194</v>
+      </c>
+      <c r="C100" t="n">
+        <v>57846.25782064528</v>
+      </c>
+      <c r="D100" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>196</v>
+      </c>
+      <c r="C101" t="n">
+        <v>60049.58597889886</v>
+      </c>
+      <c r="D101" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
+        <v>198</v>
+      </c>
+      <c r="C102" t="n">
+        <v>47541.74365111606</v>
+      </c>
+      <c r="D102" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>192</v>
+      </c>
+      <c r="C103" t="n">
+        <v>46853.91121740303</v>
+      </c>
+      <c r="D103" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
+        <v>184</v>
+      </c>
+      <c r="C104" t="n">
+        <v>46835.55264556551</v>
+      </c>
+      <c r="D104" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
+        <v>194</v>
+      </c>
+      <c r="C105" t="n">
+        <v>47842.19252290039</v>
+      </c>
+      <c r="D105" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
+        <v>194</v>
+      </c>
+      <c r="C106" t="n">
+        <v>73428.95366388741</v>
+      </c>
+      <c r="D106" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
+        <v>192</v>
+      </c>
+      <c r="C107" t="n">
+        <v>79532.40062873937</v>
+      </c>
+      <c r="D107" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
+        <v>180</v>
+      </c>
+      <c r="C108" t="n">
+        <v>62865.55919066804</v>
+      </c>
+      <c r="D108" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>182</v>
+      </c>
+      <c r="C109" t="n">
+        <v>58326.0302603036</v>
+      </c>
+      <c r="D109" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
+        <v>212</v>
+      </c>
+      <c r="C110" t="n">
+        <v>45179.6439506225</v>
+      </c>
+      <c r="D110" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
+        <v>208</v>
+      </c>
+      <c r="C111" t="n">
+        <v>71260.023127198</v>
+      </c>
+      <c r="D111" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>210</v>
+      </c>
+      <c r="C112" t="n">
+        <v>82851.64598726628</v>
+      </c>
+      <c r="D112" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="n">
+        <v>212</v>
+      </c>
+      <c r="C113" t="n">
+        <v>72669.23205624124</v>
+      </c>
+      <c r="D113" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="n">
+        <v>218</v>
+      </c>
+      <c r="C114" t="n">
+        <v>78855.59700448724</v>
+      </c>
+      <c r="D114" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="n">
+        <v>212</v>
+      </c>
+      <c r="C115" t="n">
+        <v>82279.66104760799</v>
+      </c>
+      <c r="D115" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="n">
+        <v>214</v>
+      </c>
+      <c r="C116" t="n">
+        <v>84660.64974233083</v>
+      </c>
+      <c r="D116" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="n">
+        <v>222</v>
+      </c>
+      <c r="C117" t="n">
+        <v>79259.74312962014</v>
+      </c>
+      <c r="D117" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="n">
+        <v>196</v>
+      </c>
+      <c r="C118" t="n">
+        <v>74349.29313072115</v>
+      </c>
+      <c r="D118" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="n">
+        <v>218</v>
+      </c>
+      <c r="C119" t="n">
+        <v>72773.75759755482</v>
+      </c>
+      <c r="D119" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="n">
+        <v>216</v>
+      </c>
+      <c r="C120" t="n">
+        <v>57998.76168890648</v>
+      </c>
+      <c r="D120" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="n">
+        <v>212</v>
+      </c>
+      <c r="C121" t="n">
+        <v>51015.63746211833</v>
+      </c>
+      <c r="D121" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="n">
+        <v>214</v>
+      </c>
+      <c r="C122" t="n">
+        <v>56590.02257707659</v>
+      </c>
+      <c r="D122" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="n">
+        <v>210</v>
+      </c>
+      <c r="C123" t="n">
+        <v>53766.66270172349</v>
+      </c>
+      <c r="D123" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="n">
+        <v>202</v>
+      </c>
+      <c r="C124" t="n">
+        <v>56399.03466547443</v>
+      </c>
+      <c r="D124" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="n">
+        <v>210</v>
+      </c>
+      <c r="C125" t="n">
+        <v>86899.51842582363</v>
+      </c>
+      <c r="D125" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="n">
+        <v>216</v>
+      </c>
+      <c r="C126" t="n">
+        <v>67324.8603298935</v>
+      </c>
+      <c r="D126" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="n">
+        <v>216</v>
+      </c>
+      <c r="C127" t="n">
+        <v>44136.04864979489</v>
+      </c>
+      <c r="D127" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="n">
+        <v>226</v>
+      </c>
+      <c r="C128" t="n">
+        <v>64812.26520106288</v>
+      </c>
+      <c r="D128" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="n">
+        <v>208</v>
+      </c>
+      <c r="C129" t="n">
+        <v>79266.60854496562</v>
+      </c>
+      <c r="D129" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="n">
+        <v>212</v>
+      </c>
+      <c r="C130" t="n">
+        <v>87830.4596819891</v>
+      </c>
+      <c r="D130" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="n">
+        <v>212</v>
+      </c>
+      <c r="C131" t="n">
+        <v>84009.31408715993</v>
+      </c>
+      <c r="D131" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="n">
+        <v>214</v>
+      </c>
+      <c r="C132" t="n">
+        <v>83301.1801570157</v>
+      </c>
+      <c r="D132" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="n">
+        <v>218</v>
+      </c>
+      <c r="C133" t="n">
+        <v>85884.15045233841</v>
+      </c>
+      <c r="D133" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="n">
+        <v>214</v>
+      </c>
+      <c r="C134" t="n">
+        <v>83917.847535892</v>
+      </c>
+      <c r="D134" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="n">
+        <v>216</v>
+      </c>
+      <c r="C135" t="n">
+        <v>74791.813665649</v>
+      </c>
+      <c r="D135" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="n">
+        <v>214</v>
+      </c>
+      <c r="C136" t="n">
+        <v>72099.80181025041</v>
+      </c>
+      <c r="D136" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="n">
+        <v>220</v>
+      </c>
+      <c r="C137" t="n">
+        <v>65919.55633852679</v>
+      </c>
+      <c r="D137" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="n">
+        <v>212</v>
+      </c>
+      <c r="C138" t="n">
+        <v>56458.13329655265</v>
+      </c>
+      <c r="D138" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="n">
+        <v>224</v>
+      </c>
+      <c r="C139" t="n">
+        <v>63425.58288605147</v>
+      </c>
+      <c r="D139" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="n">
+        <v>218</v>
+      </c>
+      <c r="C140" t="n">
+        <v>67076.6662204858</v>
+      </c>
+      <c r="D140" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" t="n">
+        <v>224</v>
+      </c>
+      <c r="C141" t="n">
+        <v>48299.53776052378</v>
+      </c>
+      <c r="D141" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="n">
+        <v>220</v>
+      </c>
+      <c r="C142" t="n">
+        <v>71070.48747092615</v>
+      </c>
+      <c r="D142" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="n">
+        <v>230</v>
+      </c>
+      <c r="C143" t="n">
+        <v>57600.43472977965</v>
+      </c>
+      <c r="D143" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="n">
+        <v>212</v>
+      </c>
+      <c r="C144" t="n">
+        <v>48444.30829324971</v>
+      </c>
+      <c r="D144" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="n">
+        <v>220</v>
+      </c>
+      <c r="C145" t="n">
+        <v>70850.16068599829</v>
+      </c>
+      <c r="D145" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="n">
+        <v>230</v>
+      </c>
+      <c r="C146" t="n">
+        <v>57953.00436728916</v>
+      </c>
+      <c r="D146" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="n">
+        <v>232</v>
+      </c>
+      <c r="C147" t="n">
+        <v>69792.77109605908</v>
+      </c>
+      <c r="D147" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="n">
+        <v>228</v>
+      </c>
+      <c r="C148" t="n">
+        <v>48504.37055804848</v>
+      </c>
+      <c r="D148" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" t="n">
+        <v>226</v>
+      </c>
+      <c r="C149" t="n">
+        <v>64195.65247136655</v>
+      </c>
+      <c r="D149" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" t="n">
+        <v>228</v>
+      </c>
+      <c r="C150" t="n">
+        <v>45223.57865287762</v>
+      </c>
+      <c r="D150" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="n">
+        <v>222</v>
+      </c>
+      <c r="C151" t="n">
+        <v>73033.67413671204</v>
+      </c>
+      <c r="D151" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="n">
+        <v>224</v>
+      </c>
+      <c r="C152" t="n">
+        <v>80014.68782592997</v>
+      </c>
+      <c r="D152" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="n">
+        <v>222</v>
+      </c>
+      <c r="C153" t="n">
+        <v>87537.36795652217</v>
+      </c>
+      <c r="D153" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="n">
+        <v>220</v>
+      </c>
+      <c r="C154" t="n">
+        <v>87166.56480157151</v>
+      </c>
+      <c r="D154" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="n">
+        <v>228</v>
+      </c>
+      <c r="C155" t="n">
+        <v>86965.4524801744</v>
+      </c>
+      <c r="D155" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="n">
+        <v>226</v>
+      </c>
+      <c r="C156" t="n">
+        <v>86750.9694996429</v>
+      </c>
+      <c r="D156" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" t="n">
+        <v>226</v>
+      </c>
+      <c r="C157" t="n">
+        <v>84569.21914463911</v>
+      </c>
+      <c r="D157" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" t="n">
+        <v>220</v>
+      </c>
+      <c r="C158" t="n">
+        <v>69860.88872224733</v>
+      </c>
+      <c r="D158" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" t="n">
+        <v>226</v>
+      </c>
+      <c r="C159" t="n">
+        <v>58539.5012788457</v>
+      </c>
+      <c r="D159" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" t="n">
+        <v>220</v>
+      </c>
+      <c r="C160" t="n">
+        <v>63682.99157438862</v>
+      </c>
+      <c r="D160" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" t="n">
+        <v>232</v>
+      </c>
+      <c r="C161" t="n">
+        <v>50918.26692829143</v>
+      </c>
+      <c r="D161" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" t="n">
+        <v>230</v>
+      </c>
+      <c r="C162" t="n">
+        <v>63206.78776492771</v>
+      </c>
+      <c r="D162" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" t="n">
+        <v>224</v>
+      </c>
+      <c r="C163" t="n">
+        <v>49190.77353549721</v>
+      </c>
+      <c r="D163" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" t="n">
+        <v>232</v>
+      </c>
+      <c r="C164" t="n">
+        <v>62734.18234804084</v>
+      </c>
+      <c r="D164" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" t="n">
+        <v>226</v>
+      </c>
+      <c r="C165" t="n">
+        <v>73943.55366278643</v>
+      </c>
+      <c r="D165" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" t="n">
+        <v>226</v>
+      </c>
+      <c r="C166" t="n">
+        <v>57919.79020546682</v>
+      </c>
+      <c r="D166" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" t="n">
+        <v>224</v>
+      </c>
+      <c r="C167" t="n">
+        <v>60391.59472823827</v>
+      </c>
+      <c r="D167" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" t="n">
+        <v>234</v>
+      </c>
+      <c r="C168" t="n">
+        <v>48283.56376783589</v>
+      </c>
+      <c r="D168" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>167</v>
+      </c>
+      <c r="B169" t="n">
+        <v>226</v>
+      </c>
+      <c r="C169" t="n">
+        <v>53900.7628193241</v>
+      </c>
+      <c r="D169" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>168</v>
+      </c>
+      <c r="B170" t="n">
+        <v>230</v>
+      </c>
+      <c r="C170" t="n">
+        <v>49553.16573246764</v>
+      </c>
+      <c r="D170" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>169</v>
+      </c>
+      <c r="B171" t="n">
+        <v>228</v>
+      </c>
+      <c r="C171" t="n">
+        <v>61116.35353087309</v>
+      </c>
+      <c r="D171" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>170</v>
+      </c>
+      <c r="B172" t="n">
+        <v>226</v>
+      </c>
+      <c r="C172" t="n">
+        <v>46920.3740103036</v>
+      </c>
+      <c r="D172" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>171</v>
+      </c>
+      <c r="B173" t="n">
+        <v>226</v>
+      </c>
+      <c r="C173" t="n">
+        <v>52310.07758126032</v>
+      </c>
+      <c r="D173" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>172</v>
+      </c>
+      <c r="B174" t="n">
+        <v>232</v>
+      </c>
+      <c r="C174" t="n">
+        <v>51698.40359407732</v>
+      </c>
+      <c r="D174" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>173</v>
+      </c>
+      <c r="B175" t="n">
+        <v>234</v>
+      </c>
+      <c r="C175" t="n">
+        <v>83427.53979606659</v>
+      </c>
+      <c r="D175" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>174</v>
+      </c>
+      <c r="B176" t="n">
+        <v>230</v>
+      </c>
+      <c r="C176" t="n">
+        <v>86788.09426554265</v>
+      </c>
+      <c r="D176" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>175</v>
+      </c>
+      <c r="B177" t="n">
+        <v>226</v>
+      </c>
+      <c r="C177" t="n">
+        <v>86874.88009821542</v>
+      </c>
+      <c r="D177" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>176</v>
+      </c>
+      <c r="B178" t="n">
+        <v>230</v>
+      </c>
+      <c r="C178" t="n">
+        <v>88358.77658715997</v>
+      </c>
+      <c r="D178" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>177</v>
+      </c>
+      <c r="B179" t="n">
+        <v>226</v>
+      </c>
+      <c r="C179" t="n">
+        <v>85658.52283760039</v>
+      </c>
+      <c r="D179" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>178</v>
+      </c>
+      <c r="B180" t="n">
+        <v>236</v>
+      </c>
+      <c r="C180" t="n">
+        <v>89582.57456372793</v>
+      </c>
+      <c r="D180" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>179</v>
+      </c>
+      <c r="B181" t="n">
+        <v>230</v>
+      </c>
+      <c r="C181" t="n">
+        <v>87365.8115867196</v>
+      </c>
+      <c r="D181" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>180</v>
+      </c>
+      <c r="B182" t="n">
+        <v>230</v>
+      </c>
+      <c r="C182" t="n">
+        <v>87205.20069414556</v>
+      </c>
+      <c r="D182" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>181</v>
+      </c>
+      <c r="B183" t="n">
+        <v>232</v>
+      </c>
+      <c r="C183" t="n">
+        <v>86502.64581306734</v>
+      </c>
+      <c r="D183" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>182</v>
+      </c>
+      <c r="B184" t="n">
+        <v>228</v>
+      </c>
+      <c r="C184" t="n">
+        <v>87750.76140481375</v>
+      </c>
+      <c r="D184" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>183</v>
+      </c>
+      <c r="B185" t="n">
+        <v>232</v>
+      </c>
+      <c r="C185" t="n">
+        <v>89597.76230113112</v>
+      </c>
+      <c r="D185" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>184</v>
+      </c>
+      <c r="B186" t="n">
+        <v>230</v>
+      </c>
+      <c r="C186" t="n">
+        <v>88976.26444436572</v>
+      </c>
+      <c r="D186" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>185</v>
+      </c>
+      <c r="B187" t="n">
+        <v>226</v>
+      </c>
+      <c r="C187" t="n">
+        <v>87969.95480091093</v>
+      </c>
+      <c r="D187" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>186</v>
+      </c>
+      <c r="B188" t="n">
+        <v>236</v>
+      </c>
+      <c r="C188" t="n">
+        <v>89129.34831460874</v>
+      </c>
+      <c r="D188" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>187</v>
+      </c>
+      <c r="B189" t="n">
+        <v>234</v>
+      </c>
+      <c r="C189" t="n">
+        <v>88975.12069436572</v>
+      </c>
+      <c r="D189" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>188</v>
+      </c>
+      <c r="B190" t="n">
+        <v>232</v>
+      </c>
+      <c r="C190" t="n">
+        <v>88298.43116322687</v>
+      </c>
+      <c r="D190" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>189</v>
+      </c>
+      <c r="B191" t="n">
+        <v>230</v>
+      </c>
+      <c r="C191" t="n">
+        <v>89104.38783693977</v>
+      </c>
+      <c r="D191" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>190</v>
+      </c>
+      <c r="B192" t="n">
+        <v>228</v>
+      </c>
+      <c r="C192" t="n">
+        <v>88341.2339087773</v>
+      </c>
+      <c r="D192" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>191</v>
+      </c>
+      <c r="B193" t="n">
+        <v>232</v>
+      </c>
+      <c r="C193" t="n">
+        <v>88435.09265811669</v>
+      </c>
+      <c r="D193" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>192</v>
+      </c>
+      <c r="B194" t="n">
+        <v>224</v>
+      </c>
+      <c r="C194" t="n">
+        <v>87259.14396823818</v>
+      </c>
+      <c r="D194" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>193</v>
+      </c>
+      <c r="B195" t="n">
+        <v>236</v>
+      </c>
+      <c r="C195" t="n">
+        <v>82576.62009535285</v>
+      </c>
+      <c r="D195" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>194</v>
+      </c>
+      <c r="B196" t="n">
+        <v>230</v>
+      </c>
+      <c r="C196" t="n">
+        <v>61521.53341415325</v>
+      </c>
+      <c r="D196" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>195</v>
+      </c>
+      <c r="B197" t="n">
+        <v>232</v>
+      </c>
+      <c r="C197" t="n">
+        <v>83225.20194106277</v>
+      </c>
+      <c r="D197" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>196</v>
+      </c>
+      <c r="B198" t="n">
+        <v>236</v>
+      </c>
+      <c r="C198" t="n">
+        <v>89283.64849211059</v>
+      </c>
+      <c r="D198" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>197</v>
+      </c>
+      <c r="B199" t="n">
+        <v>232</v>
+      </c>
+      <c r="C199" t="n">
+        <v>79243.63479738777</v>
+      </c>
+      <c r="D199" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>198</v>
+      </c>
+      <c r="B200" t="n">
+        <v>230</v>
+      </c>
+      <c r="C200" t="n">
+        <v>61036.66020458602</v>
+      </c>
+      <c r="D200" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>199</v>
+      </c>
+      <c r="B201" t="n">
+        <v>234</v>
+      </c>
+      <c r="C201" t="n">
+        <v>65074.29193159439</v>
+      </c>
+      <c r="D201" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>200</v>
+      </c>
+      <c r="B202" t="n">
+        <v>230</v>
+      </c>
+      <c r="C202" t="n">
+        <v>60050.68966635523</v>
+      </c>
+      <c r="D202" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>201</v>
+      </c>
+      <c r="B203" t="n">
+        <v>226</v>
+      </c>
+      <c r="C203" t="n">
+        <v>60770.43330095656</v>
+      </c>
+      <c r="D203" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>202</v>
+      </c>
+      <c r="B204" t="n">
+        <v>230</v>
+      </c>
+      <c r="C204" t="n">
+        <v>75522.2843170765</v>
+      </c>
+      <c r="D204" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>203</v>
+      </c>
+      <c r="B205" t="n">
+        <v>236</v>
+      </c>
+      <c r="C205" t="n">
+        <v>82119.64771449484</v>
+      </c>
+      <c r="D205" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>204</v>
+      </c>
+      <c r="B206" t="n">
+        <v>236</v>
+      </c>
+      <c r="C206" t="n">
+        <v>47742.97656954431</v>
+      </c>
+      <c r="D206" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>205</v>
+      </c>
+      <c r="B207" t="n">
+        <v>234</v>
+      </c>
+      <c r="C207" t="n">
+        <v>64974.54103857998</v>
+      </c>
+      <c r="D207" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>206</v>
+      </c>
+      <c r="B208" t="n">
+        <v>228</v>
+      </c>
+      <c r="C208" t="n">
+        <v>73340.64824259664</v>
+      </c>
+      <c r="D208" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>207</v>
+      </c>
+      <c r="B209" t="n">
+        <v>238</v>
+      </c>
+      <c r="C209" t="n">
+        <v>57739.71812191328</v>
+      </c>
+      <c r="D209" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>208</v>
+      </c>
+      <c r="B210" t="n">
+        <v>234</v>
+      </c>
+      <c r="C210" t="n">
+        <v>74361.2920591038</v>
+      </c>
+      <c r="D210" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>209</v>
+      </c>
+      <c r="B211" t="n">
+        <v>232</v>
+      </c>
+      <c r="C211" t="n">
+        <v>88743.01176532246</v>
+      </c>
+      <c r="D211" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>210</v>
+      </c>
+      <c r="B212" t="n">
+        <v>236</v>
+      </c>
+      <c r="C212" t="n">
+        <v>88333.07313490481</v>
+      </c>
+      <c r="D212" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>211</v>
+      </c>
+      <c r="B213" t="n">
+        <v>230</v>
+      </c>
+      <c r="C213" t="n">
+        <v>88894.04134909617</v>
+      </c>
+      <c r="D213" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>212</v>
+      </c>
+      <c r="B214" t="n">
+        <v>234</v>
+      </c>
+      <c r="C214" t="n">
+        <v>88561.03998017438</v>
+      </c>
+      <c r="D214" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>213</v>
+      </c>
+      <c r="B215" t="n">
+        <v>230</v>
+      </c>
+      <c r="C215" t="n">
+        <v>88917.21801532248</v>
+      </c>
+      <c r="D215" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>214</v>
+      </c>
+      <c r="B216" t="n">
+        <v>234</v>
+      </c>
+      <c r="C216" t="n">
+        <v>89954.9408132875</v>
+      </c>
+      <c r="D216" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>215</v>
+      </c>
+      <c r="B217" t="n">
+        <v>234</v>
+      </c>
+      <c r="C217" t="n">
+        <v>87815.52456262698</v>
+      </c>
+      <c r="D217" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>216</v>
+      </c>
+      <c r="B218" t="n">
+        <v>236</v>
+      </c>
+      <c r="C218" t="n">
+        <v>89953.59224211064</v>
+      </c>
+      <c r="D218" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>217</v>
+      </c>
+      <c r="B219" t="n">
+        <v>238</v>
+      </c>
+      <c r="C219" t="n">
+        <v>87521.4766470613</v>
+      </c>
+      <c r="D219" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>218</v>
+      </c>
+      <c r="B220" t="n">
+        <v>230</v>
+      </c>
+      <c r="C220" t="n">
+        <v>88450.98253985551</v>
+      </c>
+      <c r="D220" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>219</v>
+      </c>
+      <c r="B221" t="n">
+        <v>232</v>
+      </c>
+      <c r="C221" t="n">
+        <v>65176.36258742582</v>
+      </c>
+      <c r="D221" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>220</v>
+      </c>
+      <c r="B222" t="n">
+        <v>236</v>
+      </c>
+      <c r="C222" t="n">
+        <v>63741.95812125271</v>
+      </c>
+      <c r="D222" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>221</v>
+      </c>
+      <c r="B223" t="n">
+        <v>230</v>
+      </c>
+      <c r="C223" t="n">
+        <v>64992.96479386467</v>
+      </c>
+      <c r="D223" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>222</v>
+      </c>
+      <c r="B224" t="n">
+        <v>238</v>
+      </c>
+      <c r="C224" t="n">
+        <v>79336.48991036431</v>
+      </c>
+      <c r="D224" t="n">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>223</v>
+      </c>
+      <c r="B225" t="n">
+        <v>238</v>
+      </c>
+      <c r="C225" t="n">
+        <v>88986.78361037181</v>
+      </c>
+      <c r="D225" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>224</v>
+      </c>
+      <c r="B226" t="n">
+        <v>230</v>
+      </c>
+      <c r="C226" t="n">
+        <v>89788.4646229686</v>
+      </c>
+      <c r="D226" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>225</v>
+      </c>
+      <c r="B227" t="n">
+        <v>232</v>
+      </c>
+      <c r="C227" t="n">
+        <v>88759.84426554266</v>
+      </c>
+      <c r="D227" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>226</v>
+      </c>
+      <c r="B228" t="n">
+        <v>234</v>
+      </c>
+      <c r="C228" t="n">
+        <v>89172.4174795138</v>
+      </c>
+      <c r="D228" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>227</v>
+      </c>
+      <c r="B229" t="n">
+        <v>234</v>
+      </c>
+      <c r="C229" t="n">
+        <v>88627.95104804836</v>
+      </c>
+      <c r="D229" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>228</v>
+      </c>
+      <c r="B230" t="n">
+        <v>234</v>
+      </c>
+      <c r="C230" t="n">
+        <v>90139.91753501116</v>
+      </c>
+      <c r="D230" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>229</v>
+      </c>
+      <c r="B231" t="n">
+        <v>238</v>
+      </c>
+      <c r="C231" t="n">
+        <v>89437.94509865581</v>
+      </c>
+      <c r="D231" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>230</v>
+      </c>
+      <c r="B232" t="n">
+        <v>228</v>
+      </c>
+      <c r="C232" t="n">
+        <v>88848.66581328752</v>
+      </c>
+      <c r="D232" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>231</v>
+      </c>
+      <c r="B233" t="n">
+        <v>234</v>
+      </c>
+      <c r="C233" t="n">
+        <v>89058.55670564137</v>
+      </c>
+      <c r="D233" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>232</v>
+      </c>
+      <c r="B234" t="n">
+        <v>234</v>
+      </c>
+      <c r="C234" t="n">
+        <v>89559.09081328753</v>
+      </c>
+      <c r="D234" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>233</v>
+      </c>
+      <c r="B235" t="n">
+        <v>234</v>
+      </c>
+      <c r="C235" t="n">
+        <v>89266.74253941511</v>
+      </c>
+      <c r="D235" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>234</v>
+      </c>
+      <c r="B236" t="n">
+        <v>238</v>
+      </c>
+      <c r="C236" t="n">
+        <v>89959.72968220933</v>
+      </c>
+      <c r="D236" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>235</v>
+      </c>
+      <c r="B237" t="n">
+        <v>238</v>
+      </c>
+      <c r="C237" t="n">
+        <v>89120.03158693979</v>
+      </c>
+      <c r="D237" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>236</v>
+      </c>
+      <c r="B238" t="n">
+        <v>232</v>
+      </c>
+      <c r="C238" t="n">
+        <v>88580.97849189043</v>
+      </c>
+      <c r="D238" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>237</v>
+      </c>
+      <c r="B239" t="n">
+        <v>230</v>
+      </c>
+      <c r="C239" t="n">
+        <v>88126.68253435059</v>
+      </c>
+      <c r="D239" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>238</v>
+      </c>
+      <c r="B240" t="n">
+        <v>236</v>
+      </c>
+      <c r="C240" t="n">
+        <v>89236.02730157152</v>
+      </c>
+      <c r="D240" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>239</v>
+      </c>
+      <c r="B241" t="n">
+        <v>238</v>
+      </c>
+      <c r="C241" t="n">
+        <v>88708.3030747834</v>
+      </c>
+      <c r="D241" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>240</v>
+      </c>
+      <c r="B242" t="n">
+        <v>234</v>
+      </c>
+      <c r="C242" t="n">
+        <v>89959.72968220933</v>
+      </c>
+      <c r="D242" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>241</v>
+      </c>
+      <c r="B243" t="n">
+        <v>238</v>
+      </c>
+      <c r="C243" t="n">
+        <v>89629.77224189037</v>
+      </c>
+      <c r="D243" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>242</v>
+      </c>
+      <c r="B244" t="n">
+        <v>234</v>
+      </c>
+      <c r="C244" t="n">
+        <v>89669.18908715995</v>
+      </c>
+      <c r="D244" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>243</v>
+      </c>
+      <c r="B245" t="n">
+        <v>238</v>
+      </c>
+      <c r="C245" t="n">
+        <v>89511.52170608174</v>
+      </c>
+      <c r="D245" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>244</v>
+      </c>
+      <c r="B246" t="n">
+        <v>238</v>
+      </c>
+      <c r="C246" t="n">
+        <v>89720.46247973402</v>
+      </c>
+      <c r="D246" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>245</v>
+      </c>
+      <c r="B247" t="n">
+        <v>232</v>
+      </c>
+      <c r="C247" t="n">
+        <v>89319.88194414556</v>
+      </c>
+      <c r="D247" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>246</v>
+      </c>
+      <c r="B248" t="n">
+        <v>234</v>
+      </c>
+      <c r="C248" t="n">
+        <v>89528.44742049331</v>
+      </c>
+      <c r="D248" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>247</v>
+      </c>
+      <c r="B249" t="n">
+        <v>232</v>
+      </c>
+      <c r="C249" t="n">
+        <v>89643.15992049329</v>
+      </c>
+      <c r="D249" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>248</v>
+      </c>
+      <c r="B250" t="n">
+        <v>238</v>
+      </c>
+      <c r="C250" t="n">
+        <v>88335.82676576286</v>
+      </c>
+      <c r="D250" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>249</v>
+      </c>
+      <c r="B251" t="n">
+        <v>234</v>
+      </c>
+      <c r="C251" t="n">
+        <v>89512.47527373556</v>
+      </c>
+      <c r="D251" t="n">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -493,7 +3963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:D251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,43 +3979,3513 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>wind#0</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
           <t>battery#0</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>grid#0</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>load#0</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37447.52125924824</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>69532.00537460126</v>
+      </c>
+      <c r="D3" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>52</v>
+      </c>
+      <c r="C4" t="n">
+        <v>102239.154376097</v>
+      </c>
+      <c r="D4" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>82</v>
+      </c>
+      <c r="C5" t="n">
+        <v>130791.5454602655</v>
+      </c>
+      <c r="D5" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>162355.8929054287</v>
+      </c>
+      <c r="D6" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>128</v>
+      </c>
+      <c r="C7" t="n">
+        <v>193260.9465517004</v>
+      </c>
+      <c r="D7" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>154</v>
+      </c>
+      <c r="C8" t="n">
+        <v>234084.6700173875</v>
+      </c>
+      <c r="D8" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>190</v>
+      </c>
+      <c r="C9" t="n">
+        <v>274991.7070579948</v>
+      </c>
+      <c r="D9" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>220</v>
+      </c>
+      <c r="C10" t="n">
+        <v>317848.0016565217</v>
+      </c>
+      <c r="D10" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>242</v>
+      </c>
+      <c r="C11" t="n">
+        <v>356677.5428082984</v>
+      </c>
+      <c r="D11" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>282</v>
+      </c>
+      <c r="C12" t="n">
+        <v>399517.5168829071</v>
+      </c>
+      <c r="D12" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>332</v>
+      </c>
+      <c r="C13" t="n">
+        <v>443823.2150023982</v>
+      </c>
+      <c r="D13" t="n">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>388</v>
+      </c>
+      <c r="C14" t="n">
+        <v>483716.4815580702</v>
+      </c>
+      <c r="D14" t="n">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>464</v>
+      </c>
+      <c r="C15" t="n">
+        <v>526903.8170478499</v>
+      </c>
+      <c r="D15" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>548</v>
+      </c>
+      <c r="C16" t="n">
+        <v>575978.3471861489</v>
+      </c>
+      <c r="D16" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>618</v>
+      </c>
+      <c r="C17" t="n">
+        <v>622747.7781075686</v>
+      </c>
+      <c r="D17" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>678</v>
+      </c>
+      <c r="C18" t="n">
+        <v>670399.1087893832</v>
+      </c>
+      <c r="D18" t="n">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>744</v>
+      </c>
+      <c r="C19" t="n">
+        <v>713233.9432174545</v>
+      </c>
+      <c r="D19" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>800</v>
+      </c>
+      <c r="C20" t="n">
+        <v>757169.5215109243</v>
+      </c>
+      <c r="D20" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>888</v>
+      </c>
+      <c r="C21" t="n">
+        <v>805704.5848006509</v>
+      </c>
+      <c r="D21" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>968</v>
+      </c>
+      <c r="C22" t="n">
+        <v>851232.3014915392</v>
+      </c>
+      <c r="D22" t="n">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1056</v>
+      </c>
+      <c r="C23" t="n">
+        <v>901024.5000270364</v>
+      </c>
+      <c r="D23" t="n">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1162</v>
+      </c>
+      <c r="C24" t="n">
+        <v>945507.0522444851</v>
+      </c>
+      <c r="D24" t="n">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1232</v>
+      </c>
+      <c r="C25" t="n">
+        <v>997237.6522077044</v>
+      </c>
+      <c r="D25" t="n">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1336</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1041110.664908327</v>
+      </c>
+      <c r="D26" t="n">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
         <v>25</v>
       </c>
-      <c r="C2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-15.09408024056189</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="B27" t="n">
+        <v>1428</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1093011.43635939</v>
+      </c>
+      <c r="D27" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1524</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1136587.874176512</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1606</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1185326.072839519</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1716</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1234759.067214955</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1275051.714617833</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1898</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1329429.225655532</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1380606.643657642</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>2140</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1430077.18360809</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>2270</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1480165.110964058</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>2386</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1527533.234732555</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>2488</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1579340.053969472</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1627410.000244134</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2728</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1683385.59674629</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2844</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1730188.599621552</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2980</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1776931.654937353</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>3126</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1827866.014840231</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>3276</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1889792.498380792</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>3406</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1937336.84709159</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>3520</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1985205.312245963</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>3648</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2044642.261014459</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2616</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>3778</v>
+      </c>
+      <c r="C47" t="n">
+        <v>2101394.085320966</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2744</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>3924</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2165141.92783616</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2866</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>4056</v>
+      </c>
+      <c r="C49" t="n">
+        <v>2212337.560954109</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3002</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>4224</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2263071.738007268</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3102</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>4350</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2309925.926129401</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3234</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>4496</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2362878.222104557</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3370</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>4626</v>
+      </c>
+      <c r="C53" t="n">
+        <v>2407523.454323987</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3494</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>4770</v>
+      </c>
+      <c r="C54" t="n">
+        <v>2455490.362557336</v>
+      </c>
+      <c r="D54" t="n">
+        <v>3608</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>4936</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2512784.93806297</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>5084</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2569743.813679598</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3844</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>5232</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2618360.184357449</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3988</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>5380</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2664754.113601633</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4102</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>5530</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2721856.897382901</v>
+      </c>
+      <c r="D59" t="n">
+        <v>4226</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>5690</v>
+      </c>
+      <c r="C60" t="n">
+        <v>2771907.560198922</v>
+      </c>
+      <c r="D60" t="n">
+        <v>4342</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>5842</v>
+      </c>
+      <c r="C61" t="n">
+        <v>2817014.137542779</v>
+      </c>
+      <c r="D61" t="n">
+        <v>4476</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>5996</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2867599.786612983</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4618</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>6148</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2927032.502710363</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4752</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
         <v>62</v>
       </c>
-      <c r="F2" t="n">
-        <v>20.5</v>
+      <c r="B64" t="n">
+        <v>6298</v>
+      </c>
+      <c r="C64" t="n">
+        <v>2997240.041663408</v>
+      </c>
+      <c r="D64" t="n">
+        <v>4888</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>6468</v>
+      </c>
+      <c r="C65" t="n">
+        <v>3044836.052874205</v>
+      </c>
+      <c r="D65" t="n">
+        <v>5010</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>6622</v>
+      </c>
+      <c r="C66" t="n">
+        <v>3100468.440463833</v>
+      </c>
+      <c r="D66" t="n">
+        <v>5146</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>6792</v>
+      </c>
+      <c r="C67" t="n">
+        <v>3147794.701427318</v>
+      </c>
+      <c r="D67" t="n">
+        <v>5286</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>6960</v>
+      </c>
+      <c r="C68" t="n">
+        <v>3198729.370010826</v>
+      </c>
+      <c r="D68" t="n">
+        <v>5426</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>7110</v>
+      </c>
+      <c r="C69" t="n">
+        <v>3244244.353246377</v>
+      </c>
+      <c r="D69" t="n">
+        <v>5548</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>7276</v>
+      </c>
+      <c r="C70" t="n">
+        <v>3286643.547550902</v>
+      </c>
+      <c r="D70" t="n">
+        <v>5686</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>7438</v>
+      </c>
+      <c r="C71" t="n">
+        <v>3330358.931859171</v>
+      </c>
+      <c r="D71" t="n">
+        <v>5832</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>7620</v>
+      </c>
+      <c r="C72" t="n">
+        <v>3381235.49991788</v>
+      </c>
+      <c r="D72" t="n">
+        <v>5998</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>7782</v>
+      </c>
+      <c r="C73" t="n">
+        <v>3432253.106786711</v>
+      </c>
+      <c r="D73" t="n">
+        <v>6092</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>7966</v>
+      </c>
+      <c r="C74" t="n">
+        <v>3500943.711162808</v>
+      </c>
+      <c r="D74" t="n">
+        <v>6224</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>8126</v>
+      </c>
+      <c r="C75" t="n">
+        <v>3568198.097445617</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6368</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>8312</v>
+      </c>
+      <c r="C76" t="n">
+        <v>3615083.309429626</v>
+      </c>
+      <c r="D76" t="n">
+        <v>6502</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>8496</v>
+      </c>
+      <c r="C77" t="n">
+        <v>3669574.010985958</v>
+      </c>
+      <c r="D77" t="n">
+        <v>6642</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>8670</v>
+      </c>
+      <c r="C78" t="n">
+        <v>3721944.945054622</v>
+      </c>
+      <c r="D78" t="n">
+        <v>6798</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>8866</v>
+      </c>
+      <c r="C79" t="n">
+        <v>3776248.727100954</v>
+      </c>
+      <c r="D79" t="n">
+        <v>6948</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>9050</v>
+      </c>
+      <c r="C80" t="n">
+        <v>3834408.344983262</v>
+      </c>
+      <c r="D80" t="n">
+        <v>7114</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>9210</v>
+      </c>
+      <c r="C81" t="n">
+        <v>3876704.290367112</v>
+      </c>
+      <c r="D81" t="n">
+        <v>7226</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>9386</v>
+      </c>
+      <c r="C82" t="n">
+        <v>3926410.423363057</v>
+      </c>
+      <c r="D82" t="n">
+        <v>7346</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>9576</v>
+      </c>
+      <c r="C83" t="n">
+        <v>3988915.066315175</v>
+      </c>
+      <c r="D83" t="n">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>9766</v>
+      </c>
+      <c r="C84" t="n">
+        <v>4061995.176221356</v>
+      </c>
+      <c r="D84" t="n">
+        <v>7698</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>9964</v>
+      </c>
+      <c r="C85" t="n">
+        <v>4138916.368398061</v>
+      </c>
+      <c r="D85" t="n">
+        <v>7874</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>10150</v>
+      </c>
+      <c r="C86" t="n">
+        <v>4218439.605759093</v>
+      </c>
+      <c r="D86" t="n">
+        <v>8042</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
+        <v>10316</v>
+      </c>
+      <c r="C87" t="n">
+        <v>4292960.499604225</v>
+      </c>
+      <c r="D87" t="n">
+        <v>8212</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>10502</v>
+      </c>
+      <c r="C88" t="n">
+        <v>4349503.615575197</v>
+      </c>
+      <c r="D88" t="n">
+        <v>8344</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>10672</v>
+      </c>
+      <c r="C89" t="n">
+        <v>4409768.174533967</v>
+      </c>
+      <c r="D89" t="n">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>10846</v>
+      </c>
+      <c r="C90" t="n">
+        <v>4465705.254261765</v>
+      </c>
+      <c r="D90" t="n">
+        <v>8656</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>11038</v>
+      </c>
+      <c r="C91" t="n">
+        <v>4516995.564286646</v>
+      </c>
+      <c r="D91" t="n">
+        <v>8784</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>11240</v>
+      </c>
+      <c r="C92" t="n">
+        <v>4567200.719958552</v>
+      </c>
+      <c r="D92" t="n">
+        <v>8900</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>11430</v>
+      </c>
+      <c r="C93" t="n">
+        <v>4645195.827434102</v>
+      </c>
+      <c r="D93" t="n">
+        <v>9068</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>11626</v>
+      </c>
+      <c r="C94" t="n">
+        <v>4718708.52014111</v>
+      </c>
+      <c r="D94" t="n">
+        <v>9238</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>11836</v>
+      </c>
+      <c r="C95" t="n">
+        <v>4798295.501303236</v>
+      </c>
+      <c r="D95" t="n">
+        <v>9412</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
+        <v>12040</v>
+      </c>
+      <c r="C96" t="n">
+        <v>4865014.851985271</v>
+      </c>
+      <c r="D96" t="n">
+        <v>9554</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>12238</v>
+      </c>
+      <c r="C97" t="n">
+        <v>4929940.592428141</v>
+      </c>
+      <c r="D97" t="n">
+        <v>9706</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>12442</v>
+      </c>
+      <c r="C98" t="n">
+        <v>4982902.925370791</v>
+      </c>
+      <c r="D98" t="n">
+        <v>9846</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>12640</v>
+      </c>
+      <c r="C99" t="n">
+        <v>5047967.349150297</v>
+      </c>
+      <c r="D99" t="n">
+        <v>9992</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
+        <v>12834</v>
+      </c>
+      <c r="C100" t="n">
+        <v>5105813.606970943</v>
+      </c>
+      <c r="D100" t="n">
+        <v>10126</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>13030</v>
+      </c>
+      <c r="C101" t="n">
+        <v>5165863.192949842</v>
+      </c>
+      <c r="D101" t="n">
+        <v>10262</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
+        <v>13228</v>
+      </c>
+      <c r="C102" t="n">
+        <v>5213404.936600958</v>
+      </c>
+      <c r="D102" t="n">
+        <v>10404</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>13420</v>
+      </c>
+      <c r="C103" t="n">
+        <v>5260258.847818361</v>
+      </c>
+      <c r="D103" t="n">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
+        <v>13604</v>
+      </c>
+      <c r="C104" t="n">
+        <v>5307094.400463927</v>
+      </c>
+      <c r="D104" t="n">
+        <v>10660</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
+        <v>13798</v>
+      </c>
+      <c r="C105" t="n">
+        <v>5354936.592986827</v>
+      </c>
+      <c r="D105" t="n">
+        <v>10778</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
+        <v>13992</v>
+      </c>
+      <c r="C106" t="n">
+        <v>5428365.546650714</v>
+      </c>
+      <c r="D106" t="n">
+        <v>10950</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
+        <v>14184</v>
+      </c>
+      <c r="C107" t="n">
+        <v>5507897.947279453</v>
+      </c>
+      <c r="D107" t="n">
+        <v>11146</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
+        <v>14364</v>
+      </c>
+      <c r="C108" t="n">
+        <v>5570763.506470121</v>
+      </c>
+      <c r="D108" t="n">
+        <v>11316</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>14546</v>
+      </c>
+      <c r="C109" t="n">
+        <v>5629089.536730425</v>
+      </c>
+      <c r="D109" t="n">
+        <v>11464</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
+        <v>14758</v>
+      </c>
+      <c r="C110" t="n">
+        <v>5674269.180681048</v>
+      </c>
+      <c r="D110" t="n">
+        <v>11582</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
+        <v>14966</v>
+      </c>
+      <c r="C111" t="n">
+        <v>5745529.203808246</v>
+      </c>
+      <c r="D111" t="n">
+        <v>11778</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>15176</v>
+      </c>
+      <c r="C112" t="n">
+        <v>5828380.849795513</v>
+      </c>
+      <c r="D112" t="n">
+        <v>11968</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="n">
+        <v>15388</v>
+      </c>
+      <c r="C113" t="n">
+        <v>5901050.081851754</v>
+      </c>
+      <c r="D113" t="n">
+        <v>12154</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="n">
+        <v>15606</v>
+      </c>
+      <c r="C114" t="n">
+        <v>5979905.678856242</v>
+      </c>
+      <c r="D114" t="n">
+        <v>12350</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="n">
+        <v>15818</v>
+      </c>
+      <c r="C115" t="n">
+        <v>6062185.339903849</v>
+      </c>
+      <c r="D115" t="n">
+        <v>12538</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="n">
+        <v>16032</v>
+      </c>
+      <c r="C116" t="n">
+        <v>6146845.98964618</v>
+      </c>
+      <c r="D116" t="n">
+        <v>12738</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="n">
+        <v>16254</v>
+      </c>
+      <c r="C117" t="n">
+        <v>6226105.7327758</v>
+      </c>
+      <c r="D117" t="n">
+        <v>12942</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="n">
+        <v>16450</v>
+      </c>
+      <c r="C118" t="n">
+        <v>6300455.025906521</v>
+      </c>
+      <c r="D118" t="n">
+        <v>13122</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="n">
+        <v>16668</v>
+      </c>
+      <c r="C119" t="n">
+        <v>6373228.783504075</v>
+      </c>
+      <c r="D119" t="n">
+        <v>13320</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="n">
+        <v>16884</v>
+      </c>
+      <c r="C120" t="n">
+        <v>6431227.545192982</v>
+      </c>
+      <c r="D120" t="n">
+        <v>13488</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="n">
+        <v>17096</v>
+      </c>
+      <c r="C121" t="n">
+        <v>6482243.182655101</v>
+      </c>
+      <c r="D121" t="n">
+        <v>13636</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="n">
+        <v>17310</v>
+      </c>
+      <c r="C122" t="n">
+        <v>6538833.205232177</v>
+      </c>
+      <c r="D122" t="n">
+        <v>13790</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="n">
+        <v>17520</v>
+      </c>
+      <c r="C123" t="n">
+        <v>6592599.8679339</v>
+      </c>
+      <c r="D123" t="n">
+        <v>13942</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="n">
+        <v>17722</v>
+      </c>
+      <c r="C124" t="n">
+        <v>6648998.902599375</v>
+      </c>
+      <c r="D124" t="n">
+        <v>14072</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="n">
+        <v>17932</v>
+      </c>
+      <c r="C125" t="n">
+        <v>6735898.421025198</v>
+      </c>
+      <c r="D125" t="n">
+        <v>14260</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="n">
+        <v>18148</v>
+      </c>
+      <c r="C126" t="n">
+        <v>6803223.281355091</v>
+      </c>
+      <c r="D126" t="n">
+        <v>14424</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="n">
+        <v>18364</v>
+      </c>
+      <c r="C127" t="n">
+        <v>6847359.330004886</v>
+      </c>
+      <c r="D127" t="n">
+        <v>14558</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="n">
+        <v>18590</v>
+      </c>
+      <c r="C128" t="n">
+        <v>6912171.595205949</v>
+      </c>
+      <c r="D128" t="n">
+        <v>14726</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="n">
+        <v>18798</v>
+      </c>
+      <c r="C129" t="n">
+        <v>6991438.203750914</v>
+      </c>
+      <c r="D129" t="n">
+        <v>14934</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="n">
+        <v>19010</v>
+      </c>
+      <c r="C130" t="n">
+        <v>7079268.663432903</v>
+      </c>
+      <c r="D130" t="n">
+        <v>15148</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="n">
+        <v>19222</v>
+      </c>
+      <c r="C131" t="n">
+        <v>7163277.977520063</v>
+      </c>
+      <c r="D131" t="n">
+        <v>15370</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="n">
+        <v>19436</v>
+      </c>
+      <c r="C132" t="n">
+        <v>7246579.157677079</v>
+      </c>
+      <c r="D132" t="n">
+        <v>15580</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="n">
+        <v>19654</v>
+      </c>
+      <c r="C133" t="n">
+        <v>7332463.308129417</v>
+      </c>
+      <c r="D133" t="n">
+        <v>15794</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="n">
+        <v>19868</v>
+      </c>
+      <c r="C134" t="n">
+        <v>7416381.155665309</v>
+      </c>
+      <c r="D134" t="n">
+        <v>15994</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="n">
+        <v>20084</v>
+      </c>
+      <c r="C135" t="n">
+        <v>7491172.969330958</v>
+      </c>
+      <c r="D135" t="n">
+        <v>16194</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="n">
+        <v>20298</v>
+      </c>
+      <c r="C136" t="n">
+        <v>7563272.771141209</v>
+      </c>
+      <c r="D136" t="n">
+        <v>16384</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="n">
+        <v>20518</v>
+      </c>
+      <c r="C137" t="n">
+        <v>7629192.327479736</v>
+      </c>
+      <c r="D137" t="n">
+        <v>16584</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="n">
+        <v>20730</v>
+      </c>
+      <c r="C138" t="n">
+        <v>7685650.460776289</v>
+      </c>
+      <c r="D138" t="n">
+        <v>16776</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="n">
+        <v>20954</v>
+      </c>
+      <c r="C139" t="n">
+        <v>7749076.04366234</v>
+      </c>
+      <c r="D139" t="n">
+        <v>16936</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="n">
+        <v>21172</v>
+      </c>
+      <c r="C140" t="n">
+        <v>7816152.709882827</v>
+      </c>
+      <c r="D140" t="n">
+        <v>17134</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" t="n">
+        <v>21396</v>
+      </c>
+      <c r="C141" t="n">
+        <v>7864452.247643351</v>
+      </c>
+      <c r="D141" t="n">
+        <v>17304</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="n">
+        <v>21616</v>
+      </c>
+      <c r="C142" t="n">
+        <v>7935522.735114276</v>
+      </c>
+      <c r="D142" t="n">
+        <v>17488</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="n">
+        <v>21846</v>
+      </c>
+      <c r="C143" t="n">
+        <v>7993123.169844056</v>
+      </c>
+      <c r="D143" t="n">
+        <v>17658</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="n">
+        <v>22058</v>
+      </c>
+      <c r="C144" t="n">
+        <v>8041567.478137306</v>
+      </c>
+      <c r="D144" t="n">
+        <v>17806</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="n">
+        <v>22278</v>
+      </c>
+      <c r="C145" t="n">
+        <v>8112417.638823304</v>
+      </c>
+      <c r="D145" t="n">
+        <v>18022</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="n">
+        <v>22508</v>
+      </c>
+      <c r="C146" t="n">
+        <v>8170370.643190593</v>
+      </c>
+      <c r="D146" t="n">
+        <v>18186</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="n">
+        <v>22740</v>
+      </c>
+      <c r="C147" t="n">
+        <v>8240163.414286653</v>
+      </c>
+      <c r="D147" t="n">
+        <v>18384</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="n">
+        <v>22968</v>
+      </c>
+      <c r="C148" t="n">
+        <v>8288667.784844701</v>
+      </c>
+      <c r="D148" t="n">
+        <v>18524</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" t="n">
+        <v>23194</v>
+      </c>
+      <c r="C149" t="n">
+        <v>8352863.437316068</v>
+      </c>
+      <c r="D149" t="n">
+        <v>18694</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" t="n">
+        <v>23422</v>
+      </c>
+      <c r="C150" t="n">
+        <v>8398087.015968945</v>
+      </c>
+      <c r="D150" t="n">
+        <v>18856</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="n">
+        <v>23644</v>
+      </c>
+      <c r="C151" t="n">
+        <v>8471120.690105656</v>
+      </c>
+      <c r="D151" t="n">
+        <v>19062</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="n">
+        <v>23868</v>
+      </c>
+      <c r="C152" t="n">
+        <v>8551135.377931586</v>
+      </c>
+      <c r="D152" t="n">
+        <v>19276</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="n">
+        <v>24090</v>
+      </c>
+      <c r="C153" t="n">
+        <v>8638672.745888108</v>
+      </c>
+      <c r="D153" t="n">
+        <v>19488</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="n">
+        <v>24310</v>
+      </c>
+      <c r="C154" t="n">
+        <v>8725839.31068968</v>
+      </c>
+      <c r="D154" t="n">
+        <v>19700</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="n">
+        <v>24538</v>
+      </c>
+      <c r="C155" t="n">
+        <v>8812804.763169855</v>
+      </c>
+      <c r="D155" t="n">
+        <v>19922</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="n">
+        <v>24764</v>
+      </c>
+      <c r="C156" t="n">
+        <v>8899555.732669497</v>
+      </c>
+      <c r="D156" t="n">
+        <v>20148</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" t="n">
+        <v>24990</v>
+      </c>
+      <c r="C157" t="n">
+        <v>8984124.951814136</v>
+      </c>
+      <c r="D157" t="n">
+        <v>20364</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" t="n">
+        <v>25210</v>
+      </c>
+      <c r="C158" t="n">
+        <v>9053985.840536382</v>
+      </c>
+      <c r="D158" t="n">
+        <v>20538</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" t="n">
+        <v>25436</v>
+      </c>
+      <c r="C159" t="n">
+        <v>9112525.341815228</v>
+      </c>
+      <c r="D159" t="n">
+        <v>20734</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" t="n">
+        <v>25656</v>
+      </c>
+      <c r="C160" t="n">
+        <v>9176208.333389616</v>
+      </c>
+      <c r="D160" t="n">
+        <v>20944</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" t="n">
+        <v>25888</v>
+      </c>
+      <c r="C161" t="n">
+        <v>9227126.600317907</v>
+      </c>
+      <c r="D161" t="n">
+        <v>21156</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" t="n">
+        <v>26118</v>
+      </c>
+      <c r="C162" t="n">
+        <v>9290333.388082834</v>
+      </c>
+      <c r="D162" t="n">
+        <v>21350</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" t="n">
+        <v>26342</v>
+      </c>
+      <c r="C163" t="n">
+        <v>9339524.161618331</v>
+      </c>
+      <c r="D163" t="n">
+        <v>21522</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" t="n">
+        <v>26574</v>
+      </c>
+      <c r="C164" t="n">
+        <v>9402258.343966372</v>
+      </c>
+      <c r="D164" t="n">
+        <v>21698</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" t="n">
+        <v>26800</v>
+      </c>
+      <c r="C165" t="n">
+        <v>9476201.897629159</v>
+      </c>
+      <c r="D165" t="n">
+        <v>21904</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" t="n">
+        <v>27026</v>
+      </c>
+      <c r="C166" t="n">
+        <v>9534121.687834626</v>
+      </c>
+      <c r="D166" t="n">
+        <v>22048</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" t="n">
+        <v>27250</v>
+      </c>
+      <c r="C167" t="n">
+        <v>9594513.282562865</v>
+      </c>
+      <c r="D167" t="n">
+        <v>22214</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" t="n">
+        <v>27484</v>
+      </c>
+      <c r="C168" t="n">
+        <v>9642796.8463307</v>
+      </c>
+      <c r="D168" t="n">
+        <v>22376</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>167</v>
+      </c>
+      <c r="B169" t="n">
+        <v>27710</v>
+      </c>
+      <c r="C169" t="n">
+        <v>9696697.609150024</v>
+      </c>
+      <c r="D169" t="n">
+        <v>22528</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>168</v>
+      </c>
+      <c r="B170" t="n">
+        <v>27940</v>
+      </c>
+      <c r="C170" t="n">
+        <v>9746250.774882492</v>
+      </c>
+      <c r="D170" t="n">
+        <v>22684</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>169</v>
+      </c>
+      <c r="B171" t="n">
+        <v>28168</v>
+      </c>
+      <c r="C171" t="n">
+        <v>9807367.128413364</v>
+      </c>
+      <c r="D171" t="n">
+        <v>22834</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>170</v>
+      </c>
+      <c r="B172" t="n">
+        <v>28394</v>
+      </c>
+      <c r="C172" t="n">
+        <v>9854287.502423668</v>
+      </c>
+      <c r="D172" t="n">
+        <v>22994</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>171</v>
+      </c>
+      <c r="B173" t="n">
+        <v>28620</v>
+      </c>
+      <c r="C173" t="n">
+        <v>9906597.580004929</v>
+      </c>
+      <c r="D173" t="n">
+        <v>23130</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>172</v>
+      </c>
+      <c r="B174" t="n">
+        <v>28852</v>
+      </c>
+      <c r="C174" t="n">
+        <v>9958295.983599005</v>
+      </c>
+      <c r="D174" t="n">
+        <v>23264</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>173</v>
+      </c>
+      <c r="B175" t="n">
+        <v>29086</v>
+      </c>
+      <c r="C175" t="n">
+        <v>10041723.52339507</v>
+      </c>
+      <c r="D175" t="n">
+        <v>23452</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>174</v>
+      </c>
+      <c r="B176" t="n">
+        <v>29316</v>
+      </c>
+      <c r="C176" t="n">
+        <v>10128511.61766062</v>
+      </c>
+      <c r="D176" t="n">
+        <v>23674</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>175</v>
+      </c>
+      <c r="B177" t="n">
+        <v>29542</v>
+      </c>
+      <c r="C177" t="n">
+        <v>10215386.49775883</v>
+      </c>
+      <c r="D177" t="n">
+        <v>23904</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>176</v>
+      </c>
+      <c r="B178" t="n">
+        <v>29772</v>
+      </c>
+      <c r="C178" t="n">
+        <v>10303745.27434599</v>
+      </c>
+      <c r="D178" t="n">
+        <v>24132</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>177</v>
+      </c>
+      <c r="B179" t="n">
+        <v>29998</v>
+      </c>
+      <c r="C179" t="n">
+        <v>10389403.79718359</v>
+      </c>
+      <c r="D179" t="n">
+        <v>24364</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>178</v>
+      </c>
+      <c r="B180" t="n">
+        <v>30234</v>
+      </c>
+      <c r="C180" t="n">
+        <v>10478986.37174732</v>
+      </c>
+      <c r="D180" t="n">
+        <v>24594</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>179</v>
+      </c>
+      <c r="B181" t="n">
+        <v>30464</v>
+      </c>
+      <c r="C181" t="n">
+        <v>10566352.18333404</v>
+      </c>
+      <c r="D181" t="n">
+        <v>24816</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>180</v>
+      </c>
+      <c r="B182" t="n">
+        <v>30694</v>
+      </c>
+      <c r="C182" t="n">
+        <v>10653557.38402819</v>
+      </c>
+      <c r="D182" t="n">
+        <v>25048</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>181</v>
+      </c>
+      <c r="B183" t="n">
+        <v>30926</v>
+      </c>
+      <c r="C183" t="n">
+        <v>10740060.02984125</v>
+      </c>
+      <c r="D183" t="n">
+        <v>25276</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>182</v>
+      </c>
+      <c r="B184" t="n">
+        <v>31154</v>
+      </c>
+      <c r="C184" t="n">
+        <v>10827810.79124607</v>
+      </c>
+      <c r="D184" t="n">
+        <v>25500</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>183</v>
+      </c>
+      <c r="B185" t="n">
+        <v>31386</v>
+      </c>
+      <c r="C185" t="n">
+        <v>10917408.5535472</v>
+      </c>
+      <c r="D185" t="n">
+        <v>25728</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>184</v>
+      </c>
+      <c r="B186" t="n">
+        <v>31616</v>
+      </c>
+      <c r="C186" t="n">
+        <v>11006384.81799156</v>
+      </c>
+      <c r="D186" t="n">
+        <v>25956</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>185</v>
+      </c>
+      <c r="B187" t="n">
+        <v>31842</v>
+      </c>
+      <c r="C187" t="n">
+        <v>11094354.77279247</v>
+      </c>
+      <c r="D187" t="n">
+        <v>26188</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>186</v>
+      </c>
+      <c r="B188" t="n">
+        <v>32078</v>
+      </c>
+      <c r="C188" t="n">
+        <v>11183484.12110708</v>
+      </c>
+      <c r="D188" t="n">
+        <v>26410</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>187</v>
+      </c>
+      <c r="B189" t="n">
+        <v>32312</v>
+      </c>
+      <c r="C189" t="n">
+        <v>11272459.24180145</v>
+      </c>
+      <c r="D189" t="n">
+        <v>26634</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>188</v>
+      </c>
+      <c r="B190" t="n">
+        <v>32544</v>
+      </c>
+      <c r="C190" t="n">
+        <v>11360757.67296468</v>
+      </c>
+      <c r="D190" t="n">
+        <v>26858</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>189</v>
+      </c>
+      <c r="B191" t="n">
+        <v>32774</v>
+      </c>
+      <c r="C191" t="n">
+        <v>11449862.06080162</v>
+      </c>
+      <c r="D191" t="n">
+        <v>27096</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>190</v>
+      </c>
+      <c r="B192" t="n">
+        <v>33002</v>
+      </c>
+      <c r="C192" t="n">
+        <v>11538203.29471039</v>
+      </c>
+      <c r="D192" t="n">
+        <v>27316</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>191</v>
+      </c>
+      <c r="B193" t="n">
+        <v>33234</v>
+      </c>
+      <c r="C193" t="n">
+        <v>11626638.38736851</v>
+      </c>
+      <c r="D193" t="n">
+        <v>27540</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>192</v>
+      </c>
+      <c r="B194" t="n">
+        <v>33458</v>
+      </c>
+      <c r="C194" t="n">
+        <v>11713897.53133675</v>
+      </c>
+      <c r="D194" t="n">
+        <v>27770</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>193</v>
+      </c>
+      <c r="B195" t="n">
+        <v>33694</v>
+      </c>
+      <c r="C195" t="n">
+        <v>11796474.1514321</v>
+      </c>
+      <c r="D195" t="n">
+        <v>27996</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>194</v>
+      </c>
+      <c r="B196" t="n">
+        <v>33924</v>
+      </c>
+      <c r="C196" t="n">
+        <v>11857995.68484626</v>
+      </c>
+      <c r="D196" t="n">
+        <v>28180</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>195</v>
+      </c>
+      <c r="B197" t="n">
+        <v>34156</v>
+      </c>
+      <c r="C197" t="n">
+        <v>11941220.88678732</v>
+      </c>
+      <c r="D197" t="n">
+        <v>28384</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>196</v>
+      </c>
+      <c r="B198" t="n">
+        <v>34392</v>
+      </c>
+      <c r="C198" t="n">
+        <v>12030504.53527943</v>
+      </c>
+      <c r="D198" t="n">
+        <v>28614</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>197</v>
+      </c>
+      <c r="B199" t="n">
+        <v>34624</v>
+      </c>
+      <c r="C199" t="n">
+        <v>12109748.17007682</v>
+      </c>
+      <c r="D199" t="n">
+        <v>28820</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>198</v>
+      </c>
+      <c r="B200" t="n">
+        <v>34854</v>
+      </c>
+      <c r="C200" t="n">
+        <v>12170784.8302814</v>
+      </c>
+      <c r="D200" t="n">
+        <v>28998</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>199</v>
+      </c>
+      <c r="B201" t="n">
+        <v>35088</v>
+      </c>
+      <c r="C201" t="n">
+        <v>12235859.122213</v>
+      </c>
+      <c r="D201" t="n">
+        <v>29172</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>200</v>
+      </c>
+      <c r="B202" t="n">
+        <v>35318</v>
+      </c>
+      <c r="C202" t="n">
+        <v>12295909.81187935</v>
+      </c>
+      <c r="D202" t="n">
+        <v>29334</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>201</v>
+      </c>
+      <c r="B203" t="n">
+        <v>35544</v>
+      </c>
+      <c r="C203" t="n">
+        <v>12356680.24518031</v>
+      </c>
+      <c r="D203" t="n">
+        <v>29504</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>202</v>
+      </c>
+      <c r="B204" t="n">
+        <v>35774</v>
+      </c>
+      <c r="C204" t="n">
+        <v>12432202.52949739</v>
+      </c>
+      <c r="D204" t="n">
+        <v>29726</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>203</v>
+      </c>
+      <c r="B205" t="n">
+        <v>36010</v>
+      </c>
+      <c r="C205" t="n">
+        <v>12514322.17721188</v>
+      </c>
+      <c r="D205" t="n">
+        <v>29942</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>204</v>
+      </c>
+      <c r="B206" t="n">
+        <v>36246</v>
+      </c>
+      <c r="C206" t="n">
+        <v>12562065.15378143</v>
+      </c>
+      <c r="D206" t="n">
+        <v>30082</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>205</v>
+      </c>
+      <c r="B207" t="n">
+        <v>36480</v>
+      </c>
+      <c r="C207" t="n">
+        <v>12627039.69482001</v>
+      </c>
+      <c r="D207" t="n">
+        <v>30240</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>206</v>
+      </c>
+      <c r="B208" t="n">
+        <v>36708</v>
+      </c>
+      <c r="C208" t="n">
+        <v>12700380.3430626</v>
+      </c>
+      <c r="D208" t="n">
+        <v>30446</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>207</v>
+      </c>
+      <c r="B209" t="n">
+        <v>36946</v>
+      </c>
+      <c r="C209" t="n">
+        <v>12758120.06118452</v>
+      </c>
+      <c r="D209" t="n">
+        <v>30602</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>208</v>
+      </c>
+      <c r="B210" t="n">
+        <v>37180</v>
+      </c>
+      <c r="C210" t="n">
+        <v>12832481.35324362</v>
+      </c>
+      <c r="D210" t="n">
+        <v>30814</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>209</v>
+      </c>
+      <c r="B211" t="n">
+        <v>37412</v>
+      </c>
+      <c r="C211" t="n">
+        <v>12921224.36500894</v>
+      </c>
+      <c r="D211" t="n">
+        <v>31050</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>210</v>
+      </c>
+      <c r="B212" t="n">
+        <v>37648</v>
+      </c>
+      <c r="C212" t="n">
+        <v>13009557.43814385</v>
+      </c>
+      <c r="D212" t="n">
+        <v>31282</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>211</v>
+      </c>
+      <c r="B213" t="n">
+        <v>37878</v>
+      </c>
+      <c r="C213" t="n">
+        <v>13098451.47949294</v>
+      </c>
+      <c r="D213" t="n">
+        <v>31510</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>212</v>
+      </c>
+      <c r="B214" t="n">
+        <v>38112</v>
+      </c>
+      <c r="C214" t="n">
+        <v>13187012.51947312</v>
+      </c>
+      <c r="D214" t="n">
+        <v>31742</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>213</v>
+      </c>
+      <c r="B215" t="n">
+        <v>38342</v>
+      </c>
+      <c r="C215" t="n">
+        <v>13275929.73748844</v>
+      </c>
+      <c r="D215" t="n">
+        <v>31974</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>214</v>
+      </c>
+      <c r="B216" t="n">
+        <v>38576</v>
+      </c>
+      <c r="C216" t="n">
+        <v>13365884.67830173</v>
+      </c>
+      <c r="D216" t="n">
+        <v>32204</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>215</v>
+      </c>
+      <c r="B217" t="n">
+        <v>38810</v>
+      </c>
+      <c r="C217" t="n">
+        <v>13453700.20286436</v>
+      </c>
+      <c r="D217" t="n">
+        <v>32436</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>216</v>
+      </c>
+      <c r="B218" t="n">
+        <v>39046</v>
+      </c>
+      <c r="C218" t="n">
+        <v>13543653.79510647</v>
+      </c>
+      <c r="D218" t="n">
+        <v>32664</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>217</v>
+      </c>
+      <c r="B219" t="n">
+        <v>39284</v>
+      </c>
+      <c r="C219" t="n">
+        <v>13631175.27175353</v>
+      </c>
+      <c r="D219" t="n">
+        <v>32890</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>218</v>
+      </c>
+      <c r="B220" t="n">
+        <v>39514</v>
+      </c>
+      <c r="C220" t="n">
+        <v>13719626.25429338</v>
+      </c>
+      <c r="D220" t="n">
+        <v>33122</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>219</v>
+      </c>
+      <c r="B221" t="n">
+        <v>39746</v>
+      </c>
+      <c r="C221" t="n">
+        <v>13784802.61688081</v>
+      </c>
+      <c r="D221" t="n">
+        <v>33296</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>220</v>
+      </c>
+      <c r="B222" t="n">
+        <v>39982</v>
+      </c>
+      <c r="C222" t="n">
+        <v>13848544.57500206</v>
+      </c>
+      <c r="D222" t="n">
+        <v>33458</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>221</v>
+      </c>
+      <c r="B223" t="n">
+        <v>40212</v>
+      </c>
+      <c r="C223" t="n">
+        <v>13913537.53979593</v>
+      </c>
+      <c r="D223" t="n">
+        <v>33634</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>222</v>
+      </c>
+      <c r="B224" t="n">
+        <v>40450</v>
+      </c>
+      <c r="C224" t="n">
+        <v>13992874.02970629</v>
+      </c>
+      <c r="D224" t="n">
+        <v>33852</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>223</v>
+      </c>
+      <c r="B225" t="n">
+        <v>40688</v>
+      </c>
+      <c r="C225" t="n">
+        <v>14081860.81331666</v>
+      </c>
+      <c r="D225" t="n">
+        <v>34086</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>224</v>
+      </c>
+      <c r="B226" t="n">
+        <v>40918</v>
+      </c>
+      <c r="C226" t="n">
+        <v>14171649.27793963</v>
+      </c>
+      <c r="D226" t="n">
+        <v>34320</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>225</v>
+      </c>
+      <c r="B227" t="n">
+        <v>41150</v>
+      </c>
+      <c r="C227" t="n">
+        <v>14260409.12220517</v>
+      </c>
+      <c r="D227" t="n">
+        <v>34554</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>226</v>
+      </c>
+      <c r="B228" t="n">
+        <v>41384</v>
+      </c>
+      <c r="C228" t="n">
+        <v>14349581.53968469</v>
+      </c>
+      <c r="D228" t="n">
+        <v>34786</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>227</v>
+      </c>
+      <c r="B229" t="n">
+        <v>41618</v>
+      </c>
+      <c r="C229" t="n">
+        <v>14438209.49073274</v>
+      </c>
+      <c r="D229" t="n">
+        <v>35018</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>228</v>
+      </c>
+      <c r="B230" t="n">
+        <v>41852</v>
+      </c>
+      <c r="C230" t="n">
+        <v>14528349.40826775</v>
+      </c>
+      <c r="D230" t="n">
+        <v>35248</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>229</v>
+      </c>
+      <c r="B231" t="n">
+        <v>42090</v>
+      </c>
+      <c r="C231" t="n">
+        <v>14617787.3533664</v>
+      </c>
+      <c r="D231" t="n">
+        <v>35480</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>230</v>
+      </c>
+      <c r="B232" t="n">
+        <v>42318</v>
+      </c>
+      <c r="C232" t="n">
+        <v>14706636.01917969</v>
+      </c>
+      <c r="D232" t="n">
+        <v>35708</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>231</v>
+      </c>
+      <c r="B233" t="n">
+        <v>42552</v>
+      </c>
+      <c r="C233" t="n">
+        <v>14795694.57588533</v>
+      </c>
+      <c r="D233" t="n">
+        <v>35944</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>232</v>
+      </c>
+      <c r="B234" t="n">
+        <v>42786</v>
+      </c>
+      <c r="C234" t="n">
+        <v>14885253.66669862</v>
+      </c>
+      <c r="D234" t="n">
+        <v>36172</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>233</v>
+      </c>
+      <c r="B235" t="n">
+        <v>43020</v>
+      </c>
+      <c r="C235" t="n">
+        <v>14974520.40923803</v>
+      </c>
+      <c r="D235" t="n">
+        <v>36406</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>234</v>
+      </c>
+      <c r="B236" t="n">
+        <v>43258</v>
+      </c>
+      <c r="C236" t="n">
+        <v>15064480.13892024</v>
+      </c>
+      <c r="D236" t="n">
+        <v>36644</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>235</v>
+      </c>
+      <c r="B237" t="n">
+        <v>43496</v>
+      </c>
+      <c r="C237" t="n">
+        <v>15153600.17050718</v>
+      </c>
+      <c r="D237" t="n">
+        <v>36882</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>236</v>
+      </c>
+      <c r="B238" t="n">
+        <v>43728</v>
+      </c>
+      <c r="C238" t="n">
+        <v>15242181.14899907</v>
+      </c>
+      <c r="D238" t="n">
+        <v>37120</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>237</v>
+      </c>
+      <c r="B239" t="n">
+        <v>43958</v>
+      </c>
+      <c r="C239" t="n">
+        <v>15330307.83153342</v>
+      </c>
+      <c r="D239" t="n">
+        <v>37358</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>238</v>
+      </c>
+      <c r="B240" t="n">
+        <v>44194</v>
+      </c>
+      <c r="C240" t="n">
+        <v>15419543.85883499</v>
+      </c>
+      <c r="D240" t="n">
+        <v>37592</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>239</v>
+      </c>
+      <c r="B241" t="n">
+        <v>44432</v>
+      </c>
+      <c r="C241" t="n">
+        <v>15508252.16190978</v>
+      </c>
+      <c r="D241" t="n">
+        <v>37822</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>240</v>
+      </c>
+      <c r="B242" t="n">
+        <v>44666</v>
+      </c>
+      <c r="C242" t="n">
+        <v>15598211.89159198</v>
+      </c>
+      <c r="D242" t="n">
+        <v>38060</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>241</v>
+      </c>
+      <c r="B243" t="n">
+        <v>44904</v>
+      </c>
+      <c r="C243" t="n">
+        <v>15687841.66383388</v>
+      </c>
+      <c r="D243" t="n">
+        <v>38296</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>242</v>
+      </c>
+      <c r="B244" t="n">
+        <v>45138</v>
+      </c>
+      <c r="C244" t="n">
+        <v>15777510.85292104</v>
+      </c>
+      <c r="D244" t="n">
+        <v>38534</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>243</v>
+      </c>
+      <c r="B245" t="n">
+        <v>45376</v>
+      </c>
+      <c r="C245" t="n">
+        <v>15867022.37462712</v>
+      </c>
+      <c r="D245" t="n">
+        <v>38770</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>244</v>
+      </c>
+      <c r="B246" t="n">
+        <v>45614</v>
+      </c>
+      <c r="C246" t="n">
+        <v>15956742.83710685</v>
+      </c>
+      <c r="D246" t="n">
+        <v>39008</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>245</v>
+      </c>
+      <c r="B247" t="n">
+        <v>45846</v>
+      </c>
+      <c r="C247" t="n">
+        <v>16046062.719051</v>
+      </c>
+      <c r="D247" t="n">
+        <v>39244</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>246</v>
+      </c>
+      <c r="B248" t="n">
+        <v>46080</v>
+      </c>
+      <c r="C248" t="n">
+        <v>16135591.16647149</v>
+      </c>
+      <c r="D248" t="n">
+        <v>39478</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>247</v>
+      </c>
+      <c r="B249" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C249" t="n">
+        <v>16225234.32639198</v>
+      </c>
+      <c r="D249" t="n">
+        <v>39714</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>248</v>
+      </c>
+      <c r="B250" t="n">
+        <v>46550</v>
+      </c>
+      <c r="C250" t="n">
+        <v>16313570.15315775</v>
+      </c>
+      <c r="D250" t="n">
+        <v>39948</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>249</v>
+      </c>
+      <c r="B251" t="n">
+        <v>46784</v>
+      </c>
+      <c r="C251" t="n">
+        <v>16403082.62843148</v>
+      </c>
+      <c r="D251" t="n">
+        <v>40180</v>
       </c>
     </row>
   </sheetData>
@@ -559,7 +7499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,97 +7536,63 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>187.136</v>
+      </c>
+      <c r="C2" t="n">
+        <v>58.612</v>
+      </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>-2</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>238</v>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>46784</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>wind#0</t>
+          <t>battery#0</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>65612.33100000001</v>
+      </c>
+      <c r="C3" t="n">
+        <v>17574.146</v>
+      </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>28552.391</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>90139.91800000001</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>16403082.628</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>battery#0</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>-15.094</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="n">
-        <v>-15.094</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-15.094</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-15.094</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
           <t>grid#0</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>62</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="n">
-        <v>62</v>
-      </c>
-      <c r="E5" t="n">
-        <v>62</v>
-      </c>
-      <c r="F5" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>load#0</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>20.5</v>
+      <c r="B4" t="n">
+        <v>160.72</v>
+      </c>
+      <c r="C4" t="n">
+        <v>62.132</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>238</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40180</v>
       </c>
     </row>
   </sheetData>

--- a/results/plots/agent_rewards_cumulative.xlsx
+++ b/results/plots/agent_rewards_cumulative.xlsx
@@ -460,10 +460,10 @@
         <v>148</v>
       </c>
       <c r="C2" t="n">
-        <v>-115.25556</v>
+        <v>-131.533954</v>
       </c>
       <c r="D2" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -510,10 +510,10 @@
         <v>148</v>
       </c>
       <c r="C2" t="n">
-        <v>-115.25556</v>
+        <v>-131.533954</v>
       </c>
       <c r="D2" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -584,17 +584,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-115.256</v>
+        <v>-131.534</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>-115.256</v>
+        <v>-131.534</v>
       </c>
       <c r="E3" t="n">
-        <v>-115.256</v>
+        <v>-131.534</v>
       </c>
       <c r="F3" t="n">
-        <v>-115.256</v>
+        <v>-131.534</v>
       </c>
     </row>
     <row r="4">
@@ -604,17 +604,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
